--- a/api/1/clv1/codelist/HumanitarianPlan.xlsx
+++ b/api/1/clv1/codelist/HumanitarianPlan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2719" uniqueCount="1813">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2722" uniqueCount="1815">
   <si>
     <t>code</t>
   </si>
@@ -230,6 +230,12 @@
   </si>
   <si>
     <t>Sudan Humanitarian Needs and Response Plan 2025</t>
+  </si>
+  <si>
+    <t>FSYR25a</t>
+  </si>
+  <si>
+    <t>Syrian Arab Republic Humanitarian Response Priorities As-Sweida Crisis Addendum 2025</t>
   </si>
   <si>
     <t>FSYR25</t>
@@ -5784,7 +5790,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G905"/>
+  <dimension ref="A1:G906"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -7157,7 +7163,7 @@
         <v>252</v>
       </c>
       <c r="B124" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D124" t="s">
         <v>9</v>
@@ -7165,10 +7171,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" t="s">
+        <v>254</v>
+      </c>
+      <c r="B125" t="s">
         <v>253</v>
-      </c>
-      <c r="B125" t="s">
-        <v>254</v>
       </c>
       <c r="D125" t="s">
         <v>9</v>
@@ -7696,7 +7702,7 @@
         <v>349</v>
       </c>
       <c r="B173" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D173" t="s">
         <v>9</v>
@@ -7704,10 +7710,10 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" t="s">
+        <v>351</v>
+      </c>
+      <c r="B174" t="s">
         <v>350</v>
-      </c>
-      <c r="B174" t="s">
-        <v>351</v>
       </c>
       <c r="D174" t="s">
         <v>9</v>
@@ -8312,7 +8318,7 @@
         <v>460</v>
       </c>
       <c r="B229" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D229" t="s">
         <v>9</v>
@@ -8320,10 +8326,10 @@
     </row>
     <row r="230" spans="1:4">
       <c r="A230" t="s">
+        <v>462</v>
+      </c>
+      <c r="B230" t="s">
         <v>461</v>
-      </c>
-      <c r="B230" t="s">
-        <v>462</v>
       </c>
       <c r="D230" t="s">
         <v>9</v>
@@ -15751,6 +15757,17 @@
         <v>1812</v>
       </c>
       <c r="D905" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="906" spans="1:4">
+      <c r="A906" t="s">
+        <v>1813</v>
+      </c>
+      <c r="B906" t="s">
+        <v>1814</v>
+      </c>
+      <c r="D906" t="s">
         <v>9</v>
       </c>
     </row>

--- a/api/1/clv1/codelist/HumanitarianPlan.xlsx
+++ b/api/1/clv1/codelist/HumanitarianPlan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2722" uniqueCount="1815">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2725" uniqueCount="1815">
   <si>
     <t>code</t>
   </si>
@@ -2290,49 +2290,49 @@
     <t>OEUR17</t>
   </si>
   <si>
-    <t>2017 Europe Situation - Regional Refugee and Migrant Response</t>
+    <t>Regional Refugee and Migrant Response Plan for Europe 2017</t>
   </si>
   <si>
     <t>HAFG17</t>
   </si>
   <si>
-    <t>Afghanistan 2017</t>
+    <t>Afghanistan Humanitarian Response Plan 2017</t>
   </si>
   <si>
     <t>OBGD17</t>
   </si>
   <si>
-    <t>Bangladesh: Rohingya Refugee Crisis 2017</t>
+    <t>Rohingya Humanitarian Crisis Joint Response Plan 2017</t>
   </si>
   <si>
     <t>HBFA17</t>
   </si>
   <si>
-    <t>Burkina Faso 2017</t>
+    <t>Burkina Faso Plan de Réponse Humanitaire 2017</t>
   </si>
   <si>
     <t>HBDI17</t>
   </si>
   <si>
-    <t>Burundi 2017</t>
+    <t>Burundi Plan de Réponse Humanitaire 2017</t>
   </si>
   <si>
     <t>HCMR17</t>
   </si>
   <si>
-    <t>Cameroon 2017</t>
+    <t>Cameroun Plan de Réponse Humanitaire 2017</t>
   </si>
   <si>
     <t>HCAF17</t>
   </si>
   <si>
-    <t>Central African Republic 2017</t>
+    <t>République Centrafricaine Plan de Réponse Humanitaire 2017</t>
   </si>
   <si>
     <t>HTCD17</t>
   </si>
   <si>
-    <t>Chad 2017</t>
+    <t>Tchad Plan de Réponse Humanitaire 2017</t>
   </si>
   <si>
     <t>OCUB17</t>
@@ -2344,19 +2344,19 @@
     <t>HCOD17</t>
   </si>
   <si>
-    <t>Democratic Republic of the Congo 2017</t>
+    <t>République Démocratique du Congo Plan de Réponse Humanitaire 2017</t>
   </si>
   <si>
     <t>HDJI17</t>
   </si>
   <si>
-    <t>Djibouti 2017</t>
+    <t>Djibouti Humanitarian Response Plan 2017</t>
   </si>
   <si>
     <t>FDMA17</t>
   </si>
   <si>
-    <t>Dominica Flash Appeal 2017</t>
+    <t>Dominica Hurricane Maria Flash Appeal 2017</t>
   </si>
   <si>
     <t>OPRK17</t>
@@ -2368,25 +2368,25 @@
     <t>HETH17</t>
   </si>
   <si>
-    <t>Ethiopia 2017</t>
+    <t>Ethiopia Humanitarian Response Plan 2017</t>
   </si>
   <si>
     <t>HHTI17</t>
   </si>
   <si>
-    <t>Haiti 2017</t>
+    <t>Haiti Humanitarian Response Plan 2017</t>
   </si>
   <si>
     <t>O17</t>
   </si>
   <si>
-    <t>Hurricane Irma: Regional Response Plan for the Caribbean Region (Sep to Dec 2017)</t>
+    <t>Hurricane Irma Regional Response Plan for the Caribbean Region 2017</t>
   </si>
   <si>
     <t>HIRQ17</t>
   </si>
   <si>
-    <t>Iraq 2017</t>
+    <t>Iraq Humanitarian Response Plan 2017</t>
   </si>
   <si>
     <t>FKEN17</t>
@@ -2398,25 +2398,25 @@
     <t>HLBY17</t>
   </si>
   <si>
-    <t>Libya 2017</t>
+    <t>Libya Humanitarian Response Plan 2017</t>
   </si>
   <si>
     <t>FMDG17</t>
   </si>
   <si>
-    <t>Madagascar Flash Appeal 2017</t>
+    <t>Madagascar Tropical Cyclone Enawo Flash Appeal 2017</t>
   </si>
   <si>
     <t>HMLI17</t>
   </si>
   <si>
-    <t>Mali 2017</t>
+    <t>Mali Plan de Réponse Humanitaire 2017</t>
   </si>
   <si>
     <t>HMRT17</t>
   </si>
   <si>
-    <t>Mauritania 2017</t>
+    <t>Mauritanie Plan de Réponse Humanitaire 2017</t>
   </si>
   <si>
     <t>FMOZ17</t>
@@ -2428,25 +2428,25 @@
     <t>HMMR17</t>
   </si>
   <si>
-    <t>Myanmar 2017</t>
+    <t>Myanmar Humanitarian Response Plan 2017</t>
   </si>
   <si>
     <t>HNER17</t>
   </si>
   <si>
-    <t>Niger 2017</t>
+    <t>Niger Plan de Réponse Humanitaire 2017</t>
   </si>
   <si>
     <t>HNGA17</t>
   </si>
   <si>
-    <t>Nigeria 2017</t>
+    <t>Nigeria Humanitarian Response Plan 2017</t>
   </si>
   <si>
     <t>HPSE17</t>
   </si>
   <si>
-    <t>occupied Palestinian territory 2017</t>
+    <t>Occupied Palestinian Territory Humanitarian Response Plan 2017</t>
   </si>
   <si>
     <t>HPAK17</t>
@@ -2458,57 +2458,54 @@
     <t>FPER17</t>
   </si>
   <si>
-    <t>Peru Flash Appeal 2017</t>
+    <t>Perú Costa Norte Flash Appeal 2017</t>
   </si>
   <si>
     <t>HCOG17</t>
   </si>
   <si>
-    <t>Republic of Congo 2017</t>
+    <t>Congo Plan de Réponse Humanitaire 2017</t>
   </si>
   <si>
     <t>HSSD17</t>
   </si>
   <si>
-    <t>Republic of South Sudan 2017</t>
+    <t>South Sudan Humanitarian Response Plan 2017</t>
   </si>
   <si>
     <t>HSEN17</t>
   </si>
   <si>
-    <t>Senegal 2017</t>
+    <t>Sénégal Plan de Réponse Humanitaire 2017</t>
   </si>
   <si>
     <t>HSOM17</t>
   </si>
   <si>
-    <t>Somalia 2017</t>
+    <t>Somalia Humanitarian Response Plan 2017</t>
   </si>
   <si>
     <t>HSDN17</t>
   </si>
   <si>
-    <t>Sudan 2017</t>
+    <t>Sudan Humanitarian Response Plan 2017</t>
   </si>
   <si>
     <t>HSYR17</t>
   </si>
   <si>
-    <t>Syria Humanitarian Response Plan 2017</t>
+    <t>Syrian Arab Republic Humanitarian Response Plan 2017</t>
   </si>
   <si>
     <t>RSYR17</t>
   </si>
   <si>
-    <t>Syria regional refugee and resilience plan (3RP) 2017</t>
+    <t>Syrian Arab Republic Regional Refugee and Resilience Plan (3RP) 2017</t>
   </si>
   <si>
     <t>HSYR17b</t>
   </si>
   <si>
-    <t>Syrian Arab Republic Humanitarian Response Plan 2017</t>
-  </si>
-  <si>
     <t>HUKR17</t>
   </si>
   <si>
@@ -2524,61 +2521,61 @@
     <t>OEUR16</t>
   </si>
   <si>
-    <t>2016 Europe Situation -Regional Refugee and Migrant Response</t>
+    <t>Regional Refugee and Migrant Response Plan for Europe 2016</t>
   </si>
   <si>
     <t>HAFG16</t>
   </si>
   <si>
-    <t>Afghanistan 2016</t>
+    <t>Afghanistan Humanitarian Response Plan 2016</t>
   </si>
   <si>
     <t>FAFG16</t>
   </si>
   <si>
-    <t>Afghanistan Flash Appeal: One million people on the move (September - December 2016)</t>
+    <t>Afghanistan Flash Appeal 2016</t>
   </si>
   <si>
     <t>HBFA16</t>
   </si>
   <si>
-    <t>Burkina Faso 2016</t>
+    <t>Burkina Faso Plan de Réponse Humanitaire 2016</t>
   </si>
   <si>
     <t>HBDI16</t>
   </si>
   <si>
-    <t>Burundi 2016</t>
+    <t>Burundi Plan de Réponse Humanitaire 2016</t>
   </si>
   <si>
     <t>HCMR16</t>
   </si>
   <si>
-    <t>Cameroon 2016</t>
+    <t>Cameroun Plan de Réponse Humanitaire 2016</t>
   </si>
   <si>
     <t>HCAF16</t>
   </si>
   <si>
-    <t>Central African Republic 2016</t>
+    <t>République Centrafricaine Plan de Réponse Humanitaire 2016</t>
   </si>
   <si>
     <t>HTCD16</t>
   </si>
   <si>
-    <t>Chad 2016</t>
+    <t>Tchad Plan de Réponse Humanitaire 2016</t>
   </si>
   <si>
     <t>HCOD16</t>
   </si>
   <si>
-    <t>Democratic Republic of the Congo 2016</t>
+    <t>République Démocratique du Congo Plan de Réponse Humanitaire 2016</t>
   </si>
   <si>
     <t>HDJI16</t>
   </si>
   <si>
-    <t>Djibouti 2016</t>
+    <t>Djibouti Humanitarian Response Plan 2016</t>
   </si>
   <si>
     <t>OPRK16</t>
@@ -2590,151 +2587,151 @@
     <t>FECU16</t>
   </si>
   <si>
-    <t>Ecuador Earthquake Flash Appeal 2016</t>
+    <t>Ecuador Terremoto Flash Appeal 2016</t>
   </si>
   <si>
     <t>FFJI16</t>
   </si>
   <si>
-    <t>Fiji Tropical Cyclone Flash Appeal 2016</t>
+    <t>Fiji Tropical Cyclone Winston Flash Appeal 2016</t>
   </si>
   <si>
     <t>HGMB16</t>
   </si>
   <si>
-    <t>Gambia 2016</t>
+    <t>Gambia Humanitarian Response Plan 2016</t>
   </si>
   <si>
     <t>HGTM16</t>
   </si>
   <si>
-    <t>Guatemala 2016</t>
+    <t>Guatemala Plan de Repuesta Humanitaria 2016</t>
   </si>
   <si>
     <t>HHTI16</t>
   </si>
   <si>
-    <t>Haiti 2016</t>
+    <t>Haiti Humanitarian Response Plan 2016</t>
   </si>
   <si>
     <t>FHTI16</t>
   </si>
   <si>
-    <t>Haiti Flash Appeal: Hurricane Matthew 2016</t>
+    <t>Haiti Hurricane Matthew Flash Appeal 2016</t>
   </si>
   <si>
     <t>HHND16</t>
   </si>
   <si>
-    <t>Honduras 2016</t>
+    <t>Honduras Plan de Repuesta Humanitaria 2016</t>
   </si>
   <si>
     <t>HIRQ16</t>
   </si>
   <si>
-    <t>Iraq 2016</t>
+    <t>Iraq Humanitarian Response Plan 2016</t>
   </si>
   <si>
     <t>FLBY16</t>
   </si>
   <si>
-    <t>Libya - Sirte Flash Appeal 2016</t>
+    <t>Libya Sirt Flash Appeal 2016</t>
   </si>
   <si>
     <t>HLBY1516</t>
   </si>
   <si>
-    <t>Libya 2015-2016</t>
+    <t>Libya Humanitarian Response Plan 2015-2016</t>
   </si>
   <si>
     <t>HMLI16</t>
   </si>
   <si>
-    <t>Mali 2016</t>
+    <t>Mali Plan de Réponse Humanitaire 2016</t>
   </si>
   <si>
     <t>HMRT16</t>
   </si>
   <si>
-    <t>Mauritania 2016</t>
+    <t>Mauritanie Plan de Réponse Humanitaire 2016</t>
   </si>
   <si>
     <t>FIRQ16</t>
   </si>
   <si>
-    <t>Mosul Flash Appeal 2016</t>
+    <t>Iraq Mosul Flash Appeal 2016</t>
   </si>
   <si>
     <t>HMMR16</t>
   </si>
   <si>
-    <t>Myanmar 2016</t>
+    <t>Myanmar Humanitarian Response Plan 2016</t>
   </si>
   <si>
     <t>HNER16</t>
   </si>
   <si>
-    <t>Niger 2016</t>
+    <t>Niger Plan de Réponse Humanitaire 2016</t>
   </si>
   <si>
     <t>HNGA16</t>
   </si>
   <si>
-    <t>Nigeria 2016</t>
+    <t>Nigeria Humanitarian Response Plan 2016</t>
   </si>
   <si>
     <t>HPSE16</t>
   </si>
   <si>
-    <t>occupied Palestinian territory 2016</t>
+    <t>Occupied Palestinian Territory Humanitarian Response Plan 2016</t>
   </si>
   <si>
     <t>HSSD16</t>
   </si>
   <si>
-    <t>Republic of South Sudan 2016</t>
+    <t>South Sudan Humanitarian Response Plan 2016</t>
   </si>
   <si>
     <t>HXSHL16</t>
   </si>
   <si>
-    <t>Sahel 2016</t>
+    <t>Sahel Region Call for Humanitarian Aid 2016</t>
   </si>
   <si>
     <t>HSEN16</t>
   </si>
   <si>
-    <t>Senegal 2016</t>
+    <t>Sénégal Plan de Réponse Humanitaire 2016</t>
   </si>
   <si>
     <t>HSOM16</t>
   </si>
   <si>
-    <t>Somalia 2016</t>
+    <t>Somalia Humanitarian Response Plan 2016</t>
   </si>
   <si>
     <t>HSDN16</t>
   </si>
   <si>
-    <t>Sudan 2016</t>
+    <t>Sudan Humanitarian Response Plan 2016</t>
   </si>
   <si>
     <t>HSYR16</t>
   </si>
   <si>
-    <t>Syria Humanitarian Response Plan 2016</t>
+    <t>Syrian Arab Republic Humanitarian Response Plan 2016</t>
   </si>
   <si>
     <t>RXSYRREG16</t>
   </si>
   <si>
-    <t>Syria regional refugee and resilience plan (3RP) 2016</t>
+    <t>Syrian Arab Republic Regional Refugee and Resilience Plan (3RP) 2016</t>
   </si>
   <si>
     <t>HUKR1615</t>
   </si>
   <si>
-    <t>Ukraine 2016</t>
+    <t>Ukraine Humanitarian Response Plan 2016</t>
   </si>
   <si>
     <t>HYEM16</t>
@@ -5389,12 +5386,15 @@
     <t>Great Lakes Region and Central Africa 2000</t>
   </si>
   <si>
+    <t>CIDN00</t>
+  </si>
+  <si>
+    <t>Maluku Crisis 2000</t>
+  </si>
+  <si>
     <t>CIDN0099</t>
   </si>
   <si>
-    <t>Maluku Crisis 2000</t>
-  </si>
-  <si>
     <t>CCOG00</t>
   </si>
   <si>
@@ -5446,19 +5446,19 @@
     <t>CTLS9900</t>
   </si>
   <si>
-    <t>East Timor 1999</t>
+    <t>East Timor Consolidated Inter Agency Appeal 2000</t>
   </si>
   <si>
     <t>CRUS9900</t>
   </si>
   <si>
-    <t>Northern Caucasus (Russian Federation) 1999</t>
+    <t>Northern Caucasus (Russian Federation) Consolidated Inter Agency Appeal 2000</t>
   </si>
   <si>
     <t>CIDN9900</t>
   </si>
   <si>
-    <t>West Timor 1999</t>
+    <t>West Timor (Indonesia) Consolidated Inter Agency Appeal 2000</t>
   </si>
 </sst>
 </file>
@@ -5790,7 +5790,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G906"/>
+  <dimension ref="A1:G907"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -10353,7 +10353,7 @@
         <v>829</v>
       </c>
       <c r="B414" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="D414" t="s">
         <v>9</v>
@@ -10361,10 +10361,10 @@
     </row>
     <row r="415" spans="1:4">
       <c r="A415" t="s">
+        <v>830</v>
+      </c>
+      <c r="B415" t="s">
         <v>831</v>
-      </c>
-      <c r="B415" t="s">
-        <v>832</v>
       </c>
       <c r="D415" t="s">
         <v>9</v>
@@ -10372,10 +10372,10 @@
     </row>
     <row r="416" spans="1:4">
       <c r="A416" t="s">
+        <v>832</v>
+      </c>
+      <c r="B416" t="s">
         <v>833</v>
-      </c>
-      <c r="B416" t="s">
-        <v>834</v>
       </c>
       <c r="D416" t="s">
         <v>9</v>
@@ -10383,10 +10383,10 @@
     </row>
     <row r="417" spans="1:4">
       <c r="A417" t="s">
+        <v>834</v>
+      </c>
+      <c r="B417" t="s">
         <v>835</v>
-      </c>
-      <c r="B417" t="s">
-        <v>836</v>
       </c>
       <c r="D417" t="s">
         <v>9</v>
@@ -10394,10 +10394,10 @@
     </row>
     <row r="418" spans="1:4">
       <c r="A418" t="s">
+        <v>836</v>
+      </c>
+      <c r="B418" t="s">
         <v>837</v>
-      </c>
-      <c r="B418" t="s">
-        <v>838</v>
       </c>
       <c r="D418" t="s">
         <v>9</v>
@@ -10405,10 +10405,10 @@
     </row>
     <row r="419" spans="1:4">
       <c r="A419" t="s">
+        <v>838</v>
+      </c>
+      <c r="B419" t="s">
         <v>839</v>
-      </c>
-      <c r="B419" t="s">
-        <v>840</v>
       </c>
       <c r="D419" t="s">
         <v>9</v>
@@ -10416,10 +10416,10 @@
     </row>
     <row r="420" spans="1:4">
       <c r="A420" t="s">
+        <v>840</v>
+      </c>
+      <c r="B420" t="s">
         <v>841</v>
-      </c>
-      <c r="B420" t="s">
-        <v>842</v>
       </c>
       <c r="D420" t="s">
         <v>9</v>
@@ -10427,10 +10427,10 @@
     </row>
     <row r="421" spans="1:4">
       <c r="A421" t="s">
+        <v>842</v>
+      </c>
+      <c r="B421" t="s">
         <v>843</v>
-      </c>
-      <c r="B421" t="s">
-        <v>844</v>
       </c>
       <c r="D421" t="s">
         <v>9</v>
@@ -10438,10 +10438,10 @@
     </row>
     <row r="422" spans="1:4">
       <c r="A422" t="s">
+        <v>844</v>
+      </c>
+      <c r="B422" t="s">
         <v>845</v>
-      </c>
-      <c r="B422" t="s">
-        <v>846</v>
       </c>
       <c r="D422" t="s">
         <v>9</v>
@@ -10449,10 +10449,10 @@
     </row>
     <row r="423" spans="1:4">
       <c r="A423" t="s">
+        <v>846</v>
+      </c>
+      <c r="B423" t="s">
         <v>847</v>
-      </c>
-      <c r="B423" t="s">
-        <v>848</v>
       </c>
       <c r="D423" t="s">
         <v>9</v>
@@ -10460,10 +10460,10 @@
     </row>
     <row r="424" spans="1:4">
       <c r="A424" t="s">
+        <v>848</v>
+      </c>
+      <c r="B424" t="s">
         <v>849</v>
-      </c>
-      <c r="B424" t="s">
-        <v>850</v>
       </c>
       <c r="D424" t="s">
         <v>9</v>
@@ -10471,10 +10471,10 @@
     </row>
     <row r="425" spans="1:4">
       <c r="A425" t="s">
+        <v>850</v>
+      </c>
+      <c r="B425" t="s">
         <v>851</v>
-      </c>
-      <c r="B425" t="s">
-        <v>852</v>
       </c>
       <c r="D425" t="s">
         <v>9</v>
@@ -10482,10 +10482,10 @@
     </row>
     <row r="426" spans="1:4">
       <c r="A426" t="s">
+        <v>852</v>
+      </c>
+      <c r="B426" t="s">
         <v>853</v>
-      </c>
-      <c r="B426" t="s">
-        <v>854</v>
       </c>
       <c r="D426" t="s">
         <v>9</v>
@@ -10493,10 +10493,10 @@
     </row>
     <row r="427" spans="1:4">
       <c r="A427" t="s">
+        <v>854</v>
+      </c>
+      <c r="B427" t="s">
         <v>855</v>
-      </c>
-      <c r="B427" t="s">
-        <v>856</v>
       </c>
       <c r="D427" t="s">
         <v>9</v>
@@ -10504,10 +10504,10 @@
     </row>
     <row r="428" spans="1:4">
       <c r="A428" t="s">
+        <v>856</v>
+      </c>
+      <c r="B428" t="s">
         <v>857</v>
-      </c>
-      <c r="B428" t="s">
-        <v>858</v>
       </c>
       <c r="D428" t="s">
         <v>9</v>
@@ -10515,10 +10515,10 @@
     </row>
     <row r="429" spans="1:4">
       <c r="A429" t="s">
+        <v>858</v>
+      </c>
+      <c r="B429" t="s">
         <v>859</v>
-      </c>
-      <c r="B429" t="s">
-        <v>860</v>
       </c>
       <c r="D429" t="s">
         <v>9</v>
@@ -10526,10 +10526,10 @@
     </row>
     <row r="430" spans="1:4">
       <c r="A430" t="s">
+        <v>860</v>
+      </c>
+      <c r="B430" t="s">
         <v>861</v>
-      </c>
-      <c r="B430" t="s">
-        <v>862</v>
       </c>
       <c r="D430" t="s">
         <v>9</v>
@@ -10537,10 +10537,10 @@
     </row>
     <row r="431" spans="1:4">
       <c r="A431" t="s">
+        <v>862</v>
+      </c>
+      <c r="B431" t="s">
         <v>863</v>
-      </c>
-      <c r="B431" t="s">
-        <v>864</v>
       </c>
       <c r="D431" t="s">
         <v>9</v>
@@ -10548,10 +10548,10 @@
     </row>
     <row r="432" spans="1:4">
       <c r="A432" t="s">
+        <v>864</v>
+      </c>
+      <c r="B432" t="s">
         <v>865</v>
-      </c>
-      <c r="B432" t="s">
-        <v>866</v>
       </c>
       <c r="D432" t="s">
         <v>9</v>
@@ -10559,10 +10559,10 @@
     </row>
     <row r="433" spans="1:4">
       <c r="A433" t="s">
+        <v>866</v>
+      </c>
+      <c r="B433" t="s">
         <v>867</v>
-      </c>
-      <c r="B433" t="s">
-        <v>868</v>
       </c>
       <c r="D433" t="s">
         <v>9</v>
@@ -10570,10 +10570,10 @@
     </row>
     <row r="434" spans="1:4">
       <c r="A434" t="s">
+        <v>868</v>
+      </c>
+      <c r="B434" t="s">
         <v>869</v>
-      </c>
-      <c r="B434" t="s">
-        <v>870</v>
       </c>
       <c r="D434" t="s">
         <v>9</v>
@@ -10581,10 +10581,10 @@
     </row>
     <row r="435" spans="1:4">
       <c r="A435" t="s">
+        <v>870</v>
+      </c>
+      <c r="B435" t="s">
         <v>871</v>
-      </c>
-      <c r="B435" t="s">
-        <v>872</v>
       </c>
       <c r="D435" t="s">
         <v>9</v>
@@ -10592,10 +10592,10 @@
     </row>
     <row r="436" spans="1:4">
       <c r="A436" t="s">
+        <v>872</v>
+      </c>
+      <c r="B436" t="s">
         <v>873</v>
-      </c>
-      <c r="B436" t="s">
-        <v>874</v>
       </c>
       <c r="D436" t="s">
         <v>9</v>
@@ -10603,10 +10603,10 @@
     </row>
     <row r="437" spans="1:4">
       <c r="A437" t="s">
+        <v>874</v>
+      </c>
+      <c r="B437" t="s">
         <v>875</v>
-      </c>
-      <c r="B437" t="s">
-        <v>876</v>
       </c>
       <c r="D437" t="s">
         <v>9</v>
@@ -10614,10 +10614,10 @@
     </row>
     <row r="438" spans="1:4">
       <c r="A438" t="s">
+        <v>876</v>
+      </c>
+      <c r="B438" t="s">
         <v>877</v>
-      </c>
-      <c r="B438" t="s">
-        <v>878</v>
       </c>
       <c r="D438" t="s">
         <v>9</v>
@@ -10625,10 +10625,10 @@
     </row>
     <row r="439" spans="1:4">
       <c r="A439" t="s">
+        <v>878</v>
+      </c>
+      <c r="B439" t="s">
         <v>879</v>
-      </c>
-      <c r="B439" t="s">
-        <v>880</v>
       </c>
       <c r="D439" t="s">
         <v>9</v>
@@ -10636,10 +10636,10 @@
     </row>
     <row r="440" spans="1:4">
       <c r="A440" t="s">
+        <v>880</v>
+      </c>
+      <c r="B440" t="s">
         <v>881</v>
-      </c>
-      <c r="B440" t="s">
-        <v>882</v>
       </c>
       <c r="D440" t="s">
         <v>9</v>
@@ -10647,10 +10647,10 @@
     </row>
     <row r="441" spans="1:4">
       <c r="A441" t="s">
+        <v>882</v>
+      </c>
+      <c r="B441" t="s">
         <v>883</v>
-      </c>
-      <c r="B441" t="s">
-        <v>884</v>
       </c>
       <c r="D441" t="s">
         <v>9</v>
@@ -10658,10 +10658,10 @@
     </row>
     <row r="442" spans="1:4">
       <c r="A442" t="s">
+        <v>884</v>
+      </c>
+      <c r="B442" t="s">
         <v>885</v>
-      </c>
-      <c r="B442" t="s">
-        <v>886</v>
       </c>
       <c r="D442" t="s">
         <v>9</v>
@@ -10669,10 +10669,10 @@
     </row>
     <row r="443" spans="1:4">
       <c r="A443" t="s">
+        <v>886</v>
+      </c>
+      <c r="B443" t="s">
         <v>887</v>
-      </c>
-      <c r="B443" t="s">
-        <v>888</v>
       </c>
       <c r="D443" t="s">
         <v>9</v>
@@ -10680,10 +10680,10 @@
     </row>
     <row r="444" spans="1:4">
       <c r="A444" t="s">
+        <v>888</v>
+      </c>
+      <c r="B444" t="s">
         <v>889</v>
-      </c>
-      <c r="B444" t="s">
-        <v>890</v>
       </c>
       <c r="D444" t="s">
         <v>9</v>
@@ -10691,10 +10691,10 @@
     </row>
     <row r="445" spans="1:4">
       <c r="A445" t="s">
+        <v>890</v>
+      </c>
+      <c r="B445" t="s">
         <v>891</v>
-      </c>
-      <c r="B445" t="s">
-        <v>892</v>
       </c>
       <c r="D445" t="s">
         <v>9</v>
@@ -10702,10 +10702,10 @@
     </row>
     <row r="446" spans="1:4">
       <c r="A446" t="s">
+        <v>892</v>
+      </c>
+      <c r="B446" t="s">
         <v>893</v>
-      </c>
-      <c r="B446" t="s">
-        <v>894</v>
       </c>
       <c r="D446" t="s">
         <v>9</v>
@@ -10713,10 +10713,10 @@
     </row>
     <row r="447" spans="1:4">
       <c r="A447" t="s">
+        <v>894</v>
+      </c>
+      <c r="B447" t="s">
         <v>895</v>
-      </c>
-      <c r="B447" t="s">
-        <v>896</v>
       </c>
       <c r="D447" t="s">
         <v>9</v>
@@ -10724,10 +10724,10 @@
     </row>
     <row r="448" spans="1:4">
       <c r="A448" t="s">
+        <v>896</v>
+      </c>
+      <c r="B448" t="s">
         <v>897</v>
-      </c>
-      <c r="B448" t="s">
-        <v>898</v>
       </c>
       <c r="D448" t="s">
         <v>9</v>
@@ -10735,10 +10735,10 @@
     </row>
     <row r="449" spans="1:4">
       <c r="A449" t="s">
+        <v>898</v>
+      </c>
+      <c r="B449" t="s">
         <v>899</v>
-      </c>
-      <c r="B449" t="s">
-        <v>900</v>
       </c>
       <c r="D449" t="s">
         <v>9</v>
@@ -10746,10 +10746,10 @@
     </row>
     <row r="450" spans="1:4">
       <c r="A450" t="s">
+        <v>900</v>
+      </c>
+      <c r="B450" t="s">
         <v>901</v>
-      </c>
-      <c r="B450" t="s">
-        <v>902</v>
       </c>
       <c r="D450" t="s">
         <v>9</v>
@@ -10757,10 +10757,10 @@
     </row>
     <row r="451" spans="1:4">
       <c r="A451" t="s">
+        <v>902</v>
+      </c>
+      <c r="B451" t="s">
         <v>903</v>
-      </c>
-      <c r="B451" t="s">
-        <v>904</v>
       </c>
       <c r="D451" t="s">
         <v>9</v>
@@ -10768,10 +10768,10 @@
     </row>
     <row r="452" spans="1:4">
       <c r="A452" t="s">
+        <v>904</v>
+      </c>
+      <c r="B452" t="s">
         <v>905</v>
-      </c>
-      <c r="B452" t="s">
-        <v>906</v>
       </c>
       <c r="D452" t="s">
         <v>9</v>
@@ -10779,10 +10779,10 @@
     </row>
     <row r="453" spans="1:4">
       <c r="A453" t="s">
+        <v>906</v>
+      </c>
+      <c r="B453" t="s">
         <v>907</v>
-      </c>
-      <c r="B453" t="s">
-        <v>908</v>
       </c>
       <c r="D453" t="s">
         <v>9</v>
@@ -10790,10 +10790,10 @@
     </row>
     <row r="454" spans="1:4">
       <c r="A454" t="s">
+        <v>908</v>
+      </c>
+      <c r="B454" t="s">
         <v>909</v>
-      </c>
-      <c r="B454" t="s">
-        <v>910</v>
       </c>
       <c r="D454" t="s">
         <v>9</v>
@@ -10801,10 +10801,10 @@
     </row>
     <row r="455" spans="1:4">
       <c r="A455" t="s">
+        <v>910</v>
+      </c>
+      <c r="B455" t="s">
         <v>911</v>
-      </c>
-      <c r="B455" t="s">
-        <v>912</v>
       </c>
       <c r="D455" t="s">
         <v>9</v>
@@ -10812,10 +10812,10 @@
     </row>
     <row r="456" spans="1:4">
       <c r="A456" t="s">
+        <v>912</v>
+      </c>
+      <c r="B456" t="s">
         <v>913</v>
-      </c>
-      <c r="B456" t="s">
-        <v>914</v>
       </c>
       <c r="D456" t="s">
         <v>9</v>
@@ -10823,10 +10823,10 @@
     </row>
     <row r="457" spans="1:4">
       <c r="A457" t="s">
+        <v>914</v>
+      </c>
+      <c r="B457" t="s">
         <v>915</v>
-      </c>
-      <c r="B457" t="s">
-        <v>916</v>
       </c>
       <c r="D457" t="s">
         <v>9</v>
@@ -10834,10 +10834,10 @@
     </row>
     <row r="458" spans="1:4">
       <c r="A458" t="s">
+        <v>916</v>
+      </c>
+      <c r="B458" t="s">
         <v>917</v>
-      </c>
-      <c r="B458" t="s">
-        <v>918</v>
       </c>
       <c r="D458" t="s">
         <v>9</v>
@@ -10845,10 +10845,10 @@
     </row>
     <row r="459" spans="1:4">
       <c r="A459" t="s">
+        <v>918</v>
+      </c>
+      <c r="B459" t="s">
         <v>919</v>
-      </c>
-      <c r="B459" t="s">
-        <v>920</v>
       </c>
       <c r="D459" t="s">
         <v>9</v>
@@ -10856,10 +10856,10 @@
     </row>
     <row r="460" spans="1:4">
       <c r="A460" t="s">
+        <v>920</v>
+      </c>
+      <c r="B460" t="s">
         <v>921</v>
-      </c>
-      <c r="B460" t="s">
-        <v>922</v>
       </c>
       <c r="D460" t="s">
         <v>9</v>
@@ -10867,10 +10867,10 @@
     </row>
     <row r="461" spans="1:4">
       <c r="A461" t="s">
+        <v>922</v>
+      </c>
+      <c r="B461" t="s">
         <v>923</v>
-      </c>
-      <c r="B461" t="s">
-        <v>924</v>
       </c>
       <c r="D461" t="s">
         <v>9</v>
@@ -10878,10 +10878,10 @@
     </row>
     <row r="462" spans="1:4">
       <c r="A462" t="s">
+        <v>924</v>
+      </c>
+      <c r="B462" t="s">
         <v>925</v>
-      </c>
-      <c r="B462" t="s">
-        <v>926</v>
       </c>
       <c r="D462" t="s">
         <v>9</v>
@@ -10889,10 +10889,10 @@
     </row>
     <row r="463" spans="1:4">
       <c r="A463" t="s">
+        <v>926</v>
+      </c>
+      <c r="B463" t="s">
         <v>927</v>
-      </c>
-      <c r="B463" t="s">
-        <v>928</v>
       </c>
       <c r="D463" t="s">
         <v>9</v>
@@ -10900,10 +10900,10 @@
     </row>
     <row r="464" spans="1:4">
       <c r="A464" t="s">
+        <v>928</v>
+      </c>
+      <c r="B464" t="s">
         <v>929</v>
-      </c>
-      <c r="B464" t="s">
-        <v>930</v>
       </c>
       <c r="D464" t="s">
         <v>9</v>
@@ -10911,10 +10911,10 @@
     </row>
     <row r="465" spans="1:4">
       <c r="A465" t="s">
+        <v>930</v>
+      </c>
+      <c r="B465" t="s">
         <v>931</v>
-      </c>
-      <c r="B465" t="s">
-        <v>932</v>
       </c>
       <c r="D465" t="s">
         <v>9</v>
@@ -10922,10 +10922,10 @@
     </row>
     <row r="466" spans="1:4">
       <c r="A466" t="s">
+        <v>932</v>
+      </c>
+      <c r="B466" t="s">
         <v>933</v>
-      </c>
-      <c r="B466" t="s">
-        <v>934</v>
       </c>
       <c r="D466" t="s">
         <v>9</v>
@@ -10933,10 +10933,10 @@
     </row>
     <row r="467" spans="1:4">
       <c r="A467" t="s">
+        <v>934</v>
+      </c>
+      <c r="B467" t="s">
         <v>935</v>
-      </c>
-      <c r="B467" t="s">
-        <v>936</v>
       </c>
       <c r="D467" t="s">
         <v>9</v>
@@ -10944,10 +10944,10 @@
     </row>
     <row r="468" spans="1:4">
       <c r="A468" t="s">
+        <v>936</v>
+      </c>
+      <c r="B468" t="s">
         <v>937</v>
-      </c>
-      <c r="B468" t="s">
-        <v>938</v>
       </c>
       <c r="D468" t="s">
         <v>9</v>
@@ -10955,10 +10955,10 @@
     </row>
     <row r="469" spans="1:4">
       <c r="A469" t="s">
+        <v>938</v>
+      </c>
+      <c r="B469" t="s">
         <v>939</v>
-      </c>
-      <c r="B469" t="s">
-        <v>940</v>
       </c>
       <c r="D469" t="s">
         <v>9</v>
@@ -10966,10 +10966,10 @@
     </row>
     <row r="470" spans="1:4">
       <c r="A470" t="s">
+        <v>940</v>
+      </c>
+      <c r="B470" t="s">
         <v>941</v>
-      </c>
-      <c r="B470" t="s">
-        <v>942</v>
       </c>
       <c r="D470" t="s">
         <v>9</v>
@@ -10977,10 +10977,10 @@
     </row>
     <row r="471" spans="1:4">
       <c r="A471" t="s">
+        <v>942</v>
+      </c>
+      <c r="B471" t="s">
         <v>943</v>
-      </c>
-      <c r="B471" t="s">
-        <v>944</v>
       </c>
       <c r="D471" t="s">
         <v>9</v>
@@ -10988,10 +10988,10 @@
     </row>
     <row r="472" spans="1:4">
       <c r="A472" t="s">
+        <v>944</v>
+      </c>
+      <c r="B472" t="s">
         <v>945</v>
-      </c>
-      <c r="B472" t="s">
-        <v>946</v>
       </c>
       <c r="D472" t="s">
         <v>9</v>
@@ -10999,10 +10999,10 @@
     </row>
     <row r="473" spans="1:4">
       <c r="A473" t="s">
+        <v>946</v>
+      </c>
+      <c r="B473" t="s">
         <v>947</v>
-      </c>
-      <c r="B473" t="s">
-        <v>948</v>
       </c>
       <c r="D473" t="s">
         <v>9</v>
@@ -11010,10 +11010,10 @@
     </row>
     <row r="474" spans="1:4">
       <c r="A474" t="s">
+        <v>948</v>
+      </c>
+      <c r="B474" t="s">
         <v>949</v>
-      </c>
-      <c r="B474" t="s">
-        <v>950</v>
       </c>
       <c r="D474" t="s">
         <v>9</v>
@@ -11021,10 +11021,10 @@
     </row>
     <row r="475" spans="1:4">
       <c r="A475" t="s">
+        <v>950</v>
+      </c>
+      <c r="B475" t="s">
         <v>951</v>
-      </c>
-      <c r="B475" t="s">
-        <v>952</v>
       </c>
       <c r="D475" t="s">
         <v>9</v>
@@ -11032,10 +11032,10 @@
     </row>
     <row r="476" spans="1:4">
       <c r="A476" t="s">
+        <v>952</v>
+      </c>
+      <c r="B476" t="s">
         <v>953</v>
-      </c>
-      <c r="B476" t="s">
-        <v>954</v>
       </c>
       <c r="D476" t="s">
         <v>9</v>
@@ -11043,10 +11043,10 @@
     </row>
     <row r="477" spans="1:4">
       <c r="A477" t="s">
+        <v>954</v>
+      </c>
+      <c r="B477" t="s">
         <v>955</v>
-      </c>
-      <c r="B477" t="s">
-        <v>956</v>
       </c>
       <c r="D477" t="s">
         <v>9</v>
@@ -11054,10 +11054,10 @@
     </row>
     <row r="478" spans="1:4">
       <c r="A478" t="s">
+        <v>956</v>
+      </c>
+      <c r="B478" t="s">
         <v>957</v>
-      </c>
-      <c r="B478" t="s">
-        <v>958</v>
       </c>
       <c r="D478" t="s">
         <v>9</v>
@@ -11065,10 +11065,10 @@
     </row>
     <row r="479" spans="1:4">
       <c r="A479" t="s">
+        <v>958</v>
+      </c>
+      <c r="B479" t="s">
         <v>959</v>
-      </c>
-      <c r="B479" t="s">
-        <v>960</v>
       </c>
       <c r="D479" t="s">
         <v>9</v>
@@ -11076,10 +11076,10 @@
     </row>
     <row r="480" spans="1:4">
       <c r="A480" t="s">
+        <v>960</v>
+      </c>
+      <c r="B480" t="s">
         <v>961</v>
-      </c>
-      <c r="B480" t="s">
-        <v>962</v>
       </c>
       <c r="D480" t="s">
         <v>9</v>
@@ -11087,10 +11087,10 @@
     </row>
     <row r="481" spans="1:4">
       <c r="A481" t="s">
+        <v>962</v>
+      </c>
+      <c r="B481" t="s">
         <v>963</v>
-      </c>
-      <c r="B481" t="s">
-        <v>964</v>
       </c>
       <c r="D481" t="s">
         <v>9</v>
@@ -11098,10 +11098,10 @@
     </row>
     <row r="482" spans="1:4">
       <c r="A482" t="s">
+        <v>964</v>
+      </c>
+      <c r="B482" t="s">
         <v>965</v>
-      </c>
-      <c r="B482" t="s">
-        <v>966</v>
       </c>
       <c r="D482" t="s">
         <v>9</v>
@@ -11109,10 +11109,10 @@
     </row>
     <row r="483" spans="1:4">
       <c r="A483" t="s">
+        <v>966</v>
+      </c>
+      <c r="B483" t="s">
         <v>967</v>
-      </c>
-      <c r="B483" t="s">
-        <v>968</v>
       </c>
       <c r="D483" t="s">
         <v>9</v>
@@ -11120,10 +11120,10 @@
     </row>
     <row r="484" spans="1:4">
       <c r="A484" t="s">
+        <v>968</v>
+      </c>
+      <c r="B484" t="s">
         <v>969</v>
-      </c>
-      <c r="B484" t="s">
-        <v>970</v>
       </c>
       <c r="D484" t="s">
         <v>9</v>
@@ -11131,10 +11131,10 @@
     </row>
     <row r="485" spans="1:4">
       <c r="A485" t="s">
+        <v>970</v>
+      </c>
+      <c r="B485" t="s">
         <v>971</v>
-      </c>
-      <c r="B485" t="s">
-        <v>972</v>
       </c>
       <c r="D485" t="s">
         <v>9</v>
@@ -11142,10 +11142,10 @@
     </row>
     <row r="486" spans="1:4">
       <c r="A486" t="s">
+        <v>972</v>
+      </c>
+      <c r="B486" t="s">
         <v>973</v>
-      </c>
-      <c r="B486" t="s">
-        <v>974</v>
       </c>
       <c r="D486" t="s">
         <v>9</v>
@@ -11153,10 +11153,10 @@
     </row>
     <row r="487" spans="1:4">
       <c r="A487" t="s">
+        <v>974</v>
+      </c>
+      <c r="B487" t="s">
         <v>975</v>
-      </c>
-      <c r="B487" t="s">
-        <v>976</v>
       </c>
       <c r="D487" t="s">
         <v>9</v>
@@ -11164,10 +11164,10 @@
     </row>
     <row r="488" spans="1:4">
       <c r="A488" t="s">
+        <v>976</v>
+      </c>
+      <c r="B488" t="s">
         <v>977</v>
-      </c>
-      <c r="B488" t="s">
-        <v>978</v>
       </c>
       <c r="D488" t="s">
         <v>9</v>
@@ -11175,10 +11175,10 @@
     </row>
     <row r="489" spans="1:4">
       <c r="A489" t="s">
+        <v>978</v>
+      </c>
+      <c r="B489" t="s">
         <v>979</v>
-      </c>
-      <c r="B489" t="s">
-        <v>980</v>
       </c>
       <c r="D489" t="s">
         <v>9</v>
@@ -11186,10 +11186,10 @@
     </row>
     <row r="490" spans="1:4">
       <c r="A490" t="s">
+        <v>980</v>
+      </c>
+      <c r="B490" t="s">
         <v>981</v>
-      </c>
-      <c r="B490" t="s">
-        <v>982</v>
       </c>
       <c r="D490" t="s">
         <v>9</v>
@@ -11197,10 +11197,10 @@
     </row>
     <row r="491" spans="1:4">
       <c r="A491" t="s">
+        <v>982</v>
+      </c>
+      <c r="B491" t="s">
         <v>983</v>
-      </c>
-      <c r="B491" t="s">
-        <v>984</v>
       </c>
       <c r="D491" t="s">
         <v>9</v>
@@ -11208,10 +11208,10 @@
     </row>
     <row r="492" spans="1:4">
       <c r="A492" t="s">
+        <v>984</v>
+      </c>
+      <c r="B492" t="s">
         <v>985</v>
-      </c>
-      <c r="B492" t="s">
-        <v>986</v>
       </c>
       <c r="D492" t="s">
         <v>9</v>
@@ -11219,10 +11219,10 @@
     </row>
     <row r="493" spans="1:4">
       <c r="A493" t="s">
+        <v>986</v>
+      </c>
+      <c r="B493" t="s">
         <v>987</v>
-      </c>
-      <c r="B493" t="s">
-        <v>988</v>
       </c>
       <c r="D493" t="s">
         <v>9</v>
@@ -11230,10 +11230,10 @@
     </row>
     <row r="494" spans="1:4">
       <c r="A494" t="s">
+        <v>988</v>
+      </c>
+      <c r="B494" t="s">
         <v>989</v>
-      </c>
-      <c r="B494" t="s">
-        <v>990</v>
       </c>
       <c r="D494" t="s">
         <v>9</v>
@@ -11241,10 +11241,10 @@
     </row>
     <row r="495" spans="1:4">
       <c r="A495" t="s">
+        <v>990</v>
+      </c>
+      <c r="B495" t="s">
         <v>991</v>
-      </c>
-      <c r="B495" t="s">
-        <v>992</v>
       </c>
       <c r="D495" t="s">
         <v>9</v>
@@ -11252,10 +11252,10 @@
     </row>
     <row r="496" spans="1:4">
       <c r="A496" t="s">
+        <v>992</v>
+      </c>
+      <c r="B496" t="s">
         <v>993</v>
-      </c>
-      <c r="B496" t="s">
-        <v>994</v>
       </c>
       <c r="D496" t="s">
         <v>9</v>
@@ -11263,10 +11263,10 @@
     </row>
     <row r="497" spans="1:4">
       <c r="A497" t="s">
+        <v>994</v>
+      </c>
+      <c r="B497" t="s">
         <v>995</v>
-      </c>
-      <c r="B497" t="s">
-        <v>996</v>
       </c>
       <c r="D497" t="s">
         <v>9</v>
@@ -11274,10 +11274,10 @@
     </row>
     <row r="498" spans="1:4">
       <c r="A498" t="s">
+        <v>996</v>
+      </c>
+      <c r="B498" t="s">
         <v>997</v>
-      </c>
-      <c r="B498" t="s">
-        <v>998</v>
       </c>
       <c r="D498" t="s">
         <v>9</v>
@@ -11285,10 +11285,10 @@
     </row>
     <row r="499" spans="1:4">
       <c r="A499" t="s">
+        <v>998</v>
+      </c>
+      <c r="B499" t="s">
         <v>999</v>
-      </c>
-      <c r="B499" t="s">
-        <v>1000</v>
       </c>
       <c r="D499" t="s">
         <v>9</v>
@@ -11296,10 +11296,10 @@
     </row>
     <row r="500" spans="1:4">
       <c r="A500" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B500" t="s">
         <v>1001</v>
-      </c>
-      <c r="B500" t="s">
-        <v>1002</v>
       </c>
       <c r="D500" t="s">
         <v>9</v>
@@ -11307,10 +11307,10 @@
     </row>
     <row r="501" spans="1:4">
       <c r="A501" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B501" t="s">
         <v>1003</v>
-      </c>
-      <c r="B501" t="s">
-        <v>1004</v>
       </c>
       <c r="D501" t="s">
         <v>9</v>
@@ -11318,10 +11318,10 @@
     </row>
     <row r="502" spans="1:4">
       <c r="A502" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B502" t="s">
         <v>1005</v>
-      </c>
-      <c r="B502" t="s">
-        <v>1006</v>
       </c>
       <c r="D502" t="s">
         <v>9</v>
@@ -11329,10 +11329,10 @@
     </row>
     <row r="503" spans="1:4">
       <c r="A503" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B503" t="s">
         <v>1007</v>
-      </c>
-      <c r="B503" t="s">
-        <v>1008</v>
       </c>
       <c r="D503" t="s">
         <v>9</v>
@@ -11340,10 +11340,10 @@
     </row>
     <row r="504" spans="1:4">
       <c r="A504" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B504" t="s">
         <v>1009</v>
-      </c>
-      <c r="B504" t="s">
-        <v>1010</v>
       </c>
       <c r="D504" t="s">
         <v>9</v>
@@ -11351,10 +11351,10 @@
     </row>
     <row r="505" spans="1:4">
       <c r="A505" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B505" t="s">
         <v>1011</v>
-      </c>
-      <c r="B505" t="s">
-        <v>1012</v>
       </c>
       <c r="D505" t="s">
         <v>9</v>
@@ -11362,10 +11362,10 @@
     </row>
     <row r="506" spans="1:4">
       <c r="A506" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B506" t="s">
         <v>1013</v>
-      </c>
-      <c r="B506" t="s">
-        <v>1014</v>
       </c>
       <c r="D506" t="s">
         <v>9</v>
@@ -11373,10 +11373,10 @@
     </row>
     <row r="507" spans="1:4">
       <c r="A507" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B507" t="s">
         <v>1015</v>
-      </c>
-      <c r="B507" t="s">
-        <v>1016</v>
       </c>
       <c r="D507" t="s">
         <v>9</v>
@@ -11384,10 +11384,10 @@
     </row>
     <row r="508" spans="1:4">
       <c r="A508" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B508" t="s">
         <v>1017</v>
-      </c>
-      <c r="B508" t="s">
-        <v>1018</v>
       </c>
       <c r="D508" t="s">
         <v>9</v>
@@ -11395,10 +11395,10 @@
     </row>
     <row r="509" spans="1:4">
       <c r="A509" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B509" t="s">
         <v>1019</v>
-      </c>
-      <c r="B509" t="s">
-        <v>1020</v>
       </c>
       <c r="D509" t="s">
         <v>9</v>
@@ -11406,10 +11406,10 @@
     </row>
     <row r="510" spans="1:4">
       <c r="A510" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B510" t="s">
         <v>1021</v>
-      </c>
-      <c r="B510" t="s">
-        <v>1022</v>
       </c>
       <c r="D510" t="s">
         <v>9</v>
@@ -11417,10 +11417,10 @@
     </row>
     <row r="511" spans="1:4">
       <c r="A511" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B511" t="s">
         <v>1023</v>
-      </c>
-      <c r="B511" t="s">
-        <v>1024</v>
       </c>
       <c r="D511" t="s">
         <v>9</v>
@@ -11428,10 +11428,10 @@
     </row>
     <row r="512" spans="1:4">
       <c r="A512" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B512" t="s">
         <v>1025</v>
-      </c>
-      <c r="B512" t="s">
-        <v>1026</v>
       </c>
       <c r="D512" t="s">
         <v>9</v>
@@ -11439,10 +11439,10 @@
     </row>
     <row r="513" spans="1:4">
       <c r="A513" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B513" t="s">
         <v>1027</v>
-      </c>
-      <c r="B513" t="s">
-        <v>1028</v>
       </c>
       <c r="D513" t="s">
         <v>9</v>
@@ -11450,10 +11450,10 @@
     </row>
     <row r="514" spans="1:4">
       <c r="A514" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B514" t="s">
         <v>1029</v>
-      </c>
-      <c r="B514" t="s">
-        <v>1030</v>
       </c>
       <c r="D514" t="s">
         <v>9</v>
@@ -11461,10 +11461,10 @@
     </row>
     <row r="515" spans="1:4">
       <c r="A515" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B515" t="s">
         <v>1031</v>
-      </c>
-      <c r="B515" t="s">
-        <v>1032</v>
       </c>
       <c r="D515" t="s">
         <v>9</v>
@@ -11472,10 +11472,10 @@
     </row>
     <row r="516" spans="1:4">
       <c r="A516" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B516" t="s">
         <v>1033</v>
-      </c>
-      <c r="B516" t="s">
-        <v>1034</v>
       </c>
       <c r="D516" t="s">
         <v>9</v>
@@ -11483,10 +11483,10 @@
     </row>
     <row r="517" spans="1:4">
       <c r="A517" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B517" t="s">
         <v>1035</v>
-      </c>
-      <c r="B517" t="s">
-        <v>1036</v>
       </c>
       <c r="D517" t="s">
         <v>9</v>
@@ -11494,10 +11494,10 @@
     </row>
     <row r="518" spans="1:4">
       <c r="A518" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B518" t="s">
         <v>1037</v>
-      </c>
-      <c r="B518" t="s">
-        <v>1038</v>
       </c>
       <c r="D518" t="s">
         <v>9</v>
@@ -11505,10 +11505,10 @@
     </row>
     <row r="519" spans="1:4">
       <c r="A519" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B519" t="s">
         <v>1039</v>
-      </c>
-      <c r="B519" t="s">
-        <v>1040</v>
       </c>
       <c r="D519" t="s">
         <v>9</v>
@@ -11516,10 +11516,10 @@
     </row>
     <row r="520" spans="1:4">
       <c r="A520" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B520" t="s">
         <v>1041</v>
-      </c>
-      <c r="B520" t="s">
-        <v>1042</v>
       </c>
       <c r="D520" t="s">
         <v>9</v>
@@ -11527,10 +11527,10 @@
     </row>
     <row r="521" spans="1:4">
       <c r="A521" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B521" t="s">
         <v>1043</v>
-      </c>
-      <c r="B521" t="s">
-        <v>1044</v>
       </c>
       <c r="D521" t="s">
         <v>9</v>
@@ -11538,10 +11538,10 @@
     </row>
     <row r="522" spans="1:4">
       <c r="A522" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B522" t="s">
         <v>1045</v>
-      </c>
-      <c r="B522" t="s">
-        <v>1046</v>
       </c>
       <c r="D522" t="s">
         <v>9</v>
@@ -11549,10 +11549,10 @@
     </row>
     <row r="523" spans="1:4">
       <c r="A523" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B523" t="s">
         <v>1047</v>
-      </c>
-      <c r="B523" t="s">
-        <v>1048</v>
       </c>
       <c r="D523" t="s">
         <v>9</v>
@@ -11560,10 +11560,10 @@
     </row>
     <row r="524" spans="1:4">
       <c r="A524" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B524" t="s">
         <v>1049</v>
-      </c>
-      <c r="B524" t="s">
-        <v>1050</v>
       </c>
       <c r="D524" t="s">
         <v>9</v>
@@ -11571,10 +11571,10 @@
     </row>
     <row r="525" spans="1:4">
       <c r="A525" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B525" t="s">
         <v>1051</v>
-      </c>
-      <c r="B525" t="s">
-        <v>1052</v>
       </c>
       <c r="D525" t="s">
         <v>9</v>
@@ -11582,10 +11582,10 @@
     </row>
     <row r="526" spans="1:4">
       <c r="A526" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B526" t="s">
         <v>1053</v>
-      </c>
-      <c r="B526" t="s">
-        <v>1054</v>
       </c>
       <c r="D526" t="s">
         <v>9</v>
@@ -11593,10 +11593,10 @@
     </row>
     <row r="527" spans="1:4">
       <c r="A527" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B527" t="s">
         <v>1055</v>
-      </c>
-      <c r="B527" t="s">
-        <v>1056</v>
       </c>
       <c r="D527" t="s">
         <v>9</v>
@@ -11604,10 +11604,10 @@
     </row>
     <row r="528" spans="1:4">
       <c r="A528" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B528" t="s">
         <v>1057</v>
-      </c>
-      <c r="B528" t="s">
-        <v>1058</v>
       </c>
       <c r="D528" t="s">
         <v>9</v>
@@ -11615,10 +11615,10 @@
     </row>
     <row r="529" spans="1:4">
       <c r="A529" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B529" t="s">
         <v>1059</v>
-      </c>
-      <c r="B529" t="s">
-        <v>1060</v>
       </c>
       <c r="D529" t="s">
         <v>9</v>
@@ -11626,10 +11626,10 @@
     </row>
     <row r="530" spans="1:4">
       <c r="A530" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B530" t="s">
         <v>1061</v>
-      </c>
-      <c r="B530" t="s">
-        <v>1062</v>
       </c>
       <c r="D530" t="s">
         <v>9</v>
@@ -11637,10 +11637,10 @@
     </row>
     <row r="531" spans="1:4">
       <c r="A531" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B531" t="s">
         <v>1063</v>
-      </c>
-      <c r="B531" t="s">
-        <v>1064</v>
       </c>
       <c r="D531" t="s">
         <v>9</v>
@@ -11648,10 +11648,10 @@
     </row>
     <row r="532" spans="1:4">
       <c r="A532" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B532" t="s">
         <v>1065</v>
-      </c>
-      <c r="B532" t="s">
-        <v>1066</v>
       </c>
       <c r="D532" t="s">
         <v>9</v>
@@ -11659,10 +11659,10 @@
     </row>
     <row r="533" spans="1:4">
       <c r="A533" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B533" t="s">
         <v>1067</v>
-      </c>
-      <c r="B533" t="s">
-        <v>1068</v>
       </c>
       <c r="D533" t="s">
         <v>9</v>
@@ -11670,10 +11670,10 @@
     </row>
     <row r="534" spans="1:4">
       <c r="A534" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B534" t="s">
         <v>1069</v>
-      </c>
-      <c r="B534" t="s">
-        <v>1070</v>
       </c>
       <c r="D534" t="s">
         <v>9</v>
@@ -11681,10 +11681,10 @@
     </row>
     <row r="535" spans="1:4">
       <c r="A535" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B535" t="s">
         <v>1071</v>
-      </c>
-      <c r="B535" t="s">
-        <v>1072</v>
       </c>
       <c r="D535" t="s">
         <v>9</v>
@@ -11692,10 +11692,10 @@
     </row>
     <row r="536" spans="1:4">
       <c r="A536" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B536" t="s">
         <v>1073</v>
-      </c>
-      <c r="B536" t="s">
-        <v>1074</v>
       </c>
       <c r="D536" t="s">
         <v>9</v>
@@ -11703,10 +11703,10 @@
     </row>
     <row r="537" spans="1:4">
       <c r="A537" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B537" t="s">
         <v>1075</v>
-      </c>
-      <c r="B537" t="s">
-        <v>1076</v>
       </c>
       <c r="D537" t="s">
         <v>9</v>
@@ -11714,10 +11714,10 @@
     </row>
     <row r="538" spans="1:4">
       <c r="A538" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B538" t="s">
         <v>1077</v>
-      </c>
-      <c r="B538" t="s">
-        <v>1078</v>
       </c>
       <c r="D538" t="s">
         <v>9</v>
@@ -11725,10 +11725,10 @@
     </row>
     <row r="539" spans="1:4">
       <c r="A539" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B539" t="s">
         <v>1079</v>
-      </c>
-      <c r="B539" t="s">
-        <v>1080</v>
       </c>
       <c r="D539" t="s">
         <v>9</v>
@@ -11736,10 +11736,10 @@
     </row>
     <row r="540" spans="1:4">
       <c r="A540" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B540" t="s">
         <v>1081</v>
-      </c>
-      <c r="B540" t="s">
-        <v>1082</v>
       </c>
       <c r="D540" t="s">
         <v>9</v>
@@ -11747,10 +11747,10 @@
     </row>
     <row r="541" spans="1:4">
       <c r="A541" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B541" t="s">
         <v>1083</v>
-      </c>
-      <c r="B541" t="s">
-        <v>1084</v>
       </c>
       <c r="D541" t="s">
         <v>9</v>
@@ -11758,10 +11758,10 @@
     </row>
     <row r="542" spans="1:4">
       <c r="A542" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B542" t="s">
         <v>1085</v>
-      </c>
-      <c r="B542" t="s">
-        <v>1086</v>
       </c>
       <c r="D542" t="s">
         <v>9</v>
@@ -11769,10 +11769,10 @@
     </row>
     <row r="543" spans="1:4">
       <c r="A543" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B543" t="s">
         <v>1087</v>
-      </c>
-      <c r="B543" t="s">
-        <v>1088</v>
       </c>
       <c r="D543" t="s">
         <v>9</v>
@@ -11780,10 +11780,10 @@
     </row>
     <row r="544" spans="1:4">
       <c r="A544" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B544" t="s">
         <v>1089</v>
-      </c>
-      <c r="B544" t="s">
-        <v>1090</v>
       </c>
       <c r="D544" t="s">
         <v>9</v>
@@ -11791,10 +11791,10 @@
     </row>
     <row r="545" spans="1:4">
       <c r="A545" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B545" t="s">
         <v>1091</v>
-      </c>
-      <c r="B545" t="s">
-        <v>1092</v>
       </c>
       <c r="D545" t="s">
         <v>9</v>
@@ -11802,10 +11802,10 @@
     </row>
     <row r="546" spans="1:4">
       <c r="A546" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B546" t="s">
         <v>1093</v>
-      </c>
-      <c r="B546" t="s">
-        <v>1094</v>
       </c>
       <c r="D546" t="s">
         <v>9</v>
@@ -11813,10 +11813,10 @@
     </row>
     <row r="547" spans="1:4">
       <c r="A547" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B547" t="s">
         <v>1095</v>
-      </c>
-      <c r="B547" t="s">
-        <v>1096</v>
       </c>
       <c r="D547" t="s">
         <v>9</v>
@@ -11824,10 +11824,10 @@
     </row>
     <row r="548" spans="1:4">
       <c r="A548" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B548" t="s">
         <v>1097</v>
-      </c>
-      <c r="B548" t="s">
-        <v>1098</v>
       </c>
       <c r="D548" t="s">
         <v>9</v>
@@ -11835,10 +11835,10 @@
     </row>
     <row r="549" spans="1:4">
       <c r="A549" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B549" t="s">
         <v>1099</v>
-      </c>
-      <c r="B549" t="s">
-        <v>1100</v>
       </c>
       <c r="D549" t="s">
         <v>9</v>
@@ -11846,10 +11846,10 @@
     </row>
     <row r="550" spans="1:4">
       <c r="A550" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B550" t="s">
         <v>1101</v>
-      </c>
-      <c r="B550" t="s">
-        <v>1102</v>
       </c>
       <c r="D550" t="s">
         <v>9</v>
@@ -11857,10 +11857,10 @@
     </row>
     <row r="551" spans="1:4">
       <c r="A551" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B551" t="s">
         <v>1103</v>
-      </c>
-      <c r="B551" t="s">
-        <v>1104</v>
       </c>
       <c r="D551" t="s">
         <v>9</v>
@@ -11868,10 +11868,10 @@
     </row>
     <row r="552" spans="1:4">
       <c r="A552" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B552" t="s">
         <v>1105</v>
-      </c>
-      <c r="B552" t="s">
-        <v>1106</v>
       </c>
       <c r="D552" t="s">
         <v>9</v>
@@ -11879,10 +11879,10 @@
     </row>
     <row r="553" spans="1:4">
       <c r="A553" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B553" t="s">
         <v>1107</v>
-      </c>
-      <c r="B553" t="s">
-        <v>1108</v>
       </c>
       <c r="D553" t="s">
         <v>9</v>
@@ -11890,10 +11890,10 @@
     </row>
     <row r="554" spans="1:4">
       <c r="A554" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B554" t="s">
         <v>1109</v>
-      </c>
-      <c r="B554" t="s">
-        <v>1110</v>
       </c>
       <c r="D554" t="s">
         <v>9</v>
@@ -11901,10 +11901,10 @@
     </row>
     <row r="555" spans="1:4">
       <c r="A555" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B555" t="s">
         <v>1111</v>
-      </c>
-      <c r="B555" t="s">
-        <v>1112</v>
       </c>
       <c r="D555" t="s">
         <v>9</v>
@@ -11912,10 +11912,10 @@
     </row>
     <row r="556" spans="1:4">
       <c r="A556" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B556" t="s">
         <v>1113</v>
-      </c>
-      <c r="B556" t="s">
-        <v>1114</v>
       </c>
       <c r="D556" t="s">
         <v>9</v>
@@ -11923,10 +11923,10 @@
     </row>
     <row r="557" spans="1:4">
       <c r="A557" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B557" t="s">
         <v>1115</v>
-      </c>
-      <c r="B557" t="s">
-        <v>1116</v>
       </c>
       <c r="D557" t="s">
         <v>9</v>
@@ -11934,10 +11934,10 @@
     </row>
     <row r="558" spans="1:4">
       <c r="A558" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B558" t="s">
         <v>1117</v>
-      </c>
-      <c r="B558" t="s">
-        <v>1118</v>
       </c>
       <c r="D558" t="s">
         <v>9</v>
@@ -11945,10 +11945,10 @@
     </row>
     <row r="559" spans="1:4">
       <c r="A559" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B559" t="s">
         <v>1119</v>
-      </c>
-      <c r="B559" t="s">
-        <v>1120</v>
       </c>
       <c r="D559" t="s">
         <v>9</v>
@@ -11956,10 +11956,10 @@
     </row>
     <row r="560" spans="1:4">
       <c r="A560" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B560" t="s">
         <v>1121</v>
-      </c>
-      <c r="B560" t="s">
-        <v>1122</v>
       </c>
       <c r="D560" t="s">
         <v>9</v>
@@ -11967,10 +11967,10 @@
     </row>
     <row r="561" spans="1:4">
       <c r="A561" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B561" t="s">
         <v>1123</v>
-      </c>
-      <c r="B561" t="s">
-        <v>1124</v>
       </c>
       <c r="D561" t="s">
         <v>9</v>
@@ -11978,10 +11978,10 @@
     </row>
     <row r="562" spans="1:4">
       <c r="A562" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B562" t="s">
         <v>1125</v>
-      </c>
-      <c r="B562" t="s">
-        <v>1126</v>
       </c>
       <c r="D562" t="s">
         <v>9</v>
@@ -11989,10 +11989,10 @@
     </row>
     <row r="563" spans="1:4">
       <c r="A563" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B563" t="s">
         <v>1127</v>
-      </c>
-      <c r="B563" t="s">
-        <v>1128</v>
       </c>
       <c r="D563" t="s">
         <v>9</v>
@@ -12000,10 +12000,10 @@
     </row>
     <row r="564" spans="1:4">
       <c r="A564" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B564" t="s">
         <v>1129</v>
-      </c>
-      <c r="B564" t="s">
-        <v>1130</v>
       </c>
       <c r="D564" t="s">
         <v>9</v>
@@ -12011,10 +12011,10 @@
     </row>
     <row r="565" spans="1:4">
       <c r="A565" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B565" t="s">
         <v>1131</v>
-      </c>
-      <c r="B565" t="s">
-        <v>1132</v>
       </c>
       <c r="D565" t="s">
         <v>9</v>
@@ -12022,10 +12022,10 @@
     </row>
     <row r="566" spans="1:4">
       <c r="A566" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B566" t="s">
         <v>1133</v>
-      </c>
-      <c r="B566" t="s">
-        <v>1134</v>
       </c>
       <c r="D566" t="s">
         <v>9</v>
@@ -12033,10 +12033,10 @@
     </row>
     <row r="567" spans="1:4">
       <c r="A567" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B567" t="s">
         <v>1135</v>
-      </c>
-      <c r="B567" t="s">
-        <v>1136</v>
       </c>
       <c r="D567" t="s">
         <v>9</v>
@@ -12044,10 +12044,10 @@
     </row>
     <row r="568" spans="1:4">
       <c r="A568" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B568" t="s">
         <v>1137</v>
-      </c>
-      <c r="B568" t="s">
-        <v>1138</v>
       </c>
       <c r="D568" t="s">
         <v>9</v>
@@ -12055,10 +12055,10 @@
     </row>
     <row r="569" spans="1:4">
       <c r="A569" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B569" t="s">
         <v>1139</v>
-      </c>
-      <c r="B569" t="s">
-        <v>1140</v>
       </c>
       <c r="D569" t="s">
         <v>9</v>
@@ -12066,10 +12066,10 @@
     </row>
     <row r="570" spans="1:4">
       <c r="A570" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B570" t="s">
         <v>1141</v>
-      </c>
-      <c r="B570" t="s">
-        <v>1142</v>
       </c>
       <c r="D570" t="s">
         <v>9</v>
@@ -12077,10 +12077,10 @@
     </row>
     <row r="571" spans="1:4">
       <c r="A571" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B571" t="s">
         <v>1143</v>
-      </c>
-      <c r="B571" t="s">
-        <v>1144</v>
       </c>
       <c r="D571" t="s">
         <v>9</v>
@@ -12088,10 +12088,10 @@
     </row>
     <row r="572" spans="1:4">
       <c r="A572" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B572" t="s">
         <v>1145</v>
-      </c>
-      <c r="B572" t="s">
-        <v>1146</v>
       </c>
       <c r="D572" t="s">
         <v>9</v>
@@ -12099,10 +12099,10 @@
     </row>
     <row r="573" spans="1:4">
       <c r="A573" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B573" t="s">
         <v>1147</v>
-      </c>
-      <c r="B573" t="s">
-        <v>1148</v>
       </c>
       <c r="D573" t="s">
         <v>9</v>
@@ -12110,10 +12110,10 @@
     </row>
     <row r="574" spans="1:4">
       <c r="A574" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B574" t="s">
         <v>1149</v>
-      </c>
-      <c r="B574" t="s">
-        <v>1150</v>
       </c>
       <c r="D574" t="s">
         <v>9</v>
@@ -12121,10 +12121,10 @@
     </row>
     <row r="575" spans="1:4">
       <c r="A575" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B575" t="s">
         <v>1151</v>
-      </c>
-      <c r="B575" t="s">
-        <v>1152</v>
       </c>
       <c r="D575" t="s">
         <v>9</v>
@@ -12132,10 +12132,10 @@
     </row>
     <row r="576" spans="1:4">
       <c r="A576" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B576" t="s">
         <v>1153</v>
-      </c>
-      <c r="B576" t="s">
-        <v>1154</v>
       </c>
       <c r="D576" t="s">
         <v>9</v>
@@ -12143,10 +12143,10 @@
     </row>
     <row r="577" spans="1:4">
       <c r="A577" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B577" t="s">
         <v>1155</v>
-      </c>
-      <c r="B577" t="s">
-        <v>1156</v>
       </c>
       <c r="D577" t="s">
         <v>9</v>
@@ -12154,10 +12154,10 @@
     </row>
     <row r="578" spans="1:4">
       <c r="A578" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B578" t="s">
         <v>1157</v>
-      </c>
-      <c r="B578" t="s">
-        <v>1158</v>
       </c>
       <c r="D578" t="s">
         <v>9</v>
@@ -12165,10 +12165,10 @@
     </row>
     <row r="579" spans="1:4">
       <c r="A579" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B579" t="s">
         <v>1159</v>
-      </c>
-      <c r="B579" t="s">
-        <v>1160</v>
       </c>
       <c r="D579" t="s">
         <v>9</v>
@@ -12176,10 +12176,10 @@
     </row>
     <row r="580" spans="1:4">
       <c r="A580" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B580" t="s">
         <v>1161</v>
-      </c>
-      <c r="B580" t="s">
-        <v>1162</v>
       </c>
       <c r="D580" t="s">
         <v>9</v>
@@ -12187,10 +12187,10 @@
     </row>
     <row r="581" spans="1:4">
       <c r="A581" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B581" t="s">
         <v>1163</v>
-      </c>
-      <c r="B581" t="s">
-        <v>1164</v>
       </c>
       <c r="D581" t="s">
         <v>9</v>
@@ -12198,10 +12198,10 @@
     </row>
     <row r="582" spans="1:4">
       <c r="A582" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B582" t="s">
         <v>1165</v>
-      </c>
-      <c r="B582" t="s">
-        <v>1166</v>
       </c>
       <c r="D582" t="s">
         <v>9</v>
@@ -12209,10 +12209,10 @@
     </row>
     <row r="583" spans="1:4">
       <c r="A583" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B583" t="s">
         <v>1167</v>
-      </c>
-      <c r="B583" t="s">
-        <v>1168</v>
       </c>
       <c r="D583" t="s">
         <v>9</v>
@@ -12220,10 +12220,10 @@
     </row>
     <row r="584" spans="1:4">
       <c r="A584" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B584" t="s">
         <v>1169</v>
-      </c>
-      <c r="B584" t="s">
-        <v>1170</v>
       </c>
       <c r="D584" t="s">
         <v>9</v>
@@ -12231,10 +12231,10 @@
     </row>
     <row r="585" spans="1:4">
       <c r="A585" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B585" t="s">
         <v>1171</v>
-      </c>
-      <c r="B585" t="s">
-        <v>1172</v>
       </c>
       <c r="D585" t="s">
         <v>9</v>
@@ -12242,10 +12242,10 @@
     </row>
     <row r="586" spans="1:4">
       <c r="A586" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B586" t="s">
         <v>1173</v>
-      </c>
-      <c r="B586" t="s">
-        <v>1174</v>
       </c>
       <c r="D586" t="s">
         <v>9</v>
@@ -12253,10 +12253,10 @@
     </row>
     <row r="587" spans="1:4">
       <c r="A587" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B587" t="s">
         <v>1175</v>
-      </c>
-      <c r="B587" t="s">
-        <v>1176</v>
       </c>
       <c r="D587" t="s">
         <v>9</v>
@@ -12264,10 +12264,10 @@
     </row>
     <row r="588" spans="1:4">
       <c r="A588" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B588" t="s">
         <v>1177</v>
-      </c>
-      <c r="B588" t="s">
-        <v>1178</v>
       </c>
       <c r="D588" t="s">
         <v>9</v>
@@ -12275,10 +12275,10 @@
     </row>
     <row r="589" spans="1:4">
       <c r="A589" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B589" t="s">
         <v>1179</v>
-      </c>
-      <c r="B589" t="s">
-        <v>1180</v>
       </c>
       <c r="D589" t="s">
         <v>9</v>
@@ -12286,10 +12286,10 @@
     </row>
     <row r="590" spans="1:4">
       <c r="A590" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B590" t="s">
         <v>1181</v>
-      </c>
-      <c r="B590" t="s">
-        <v>1182</v>
       </c>
       <c r="D590" t="s">
         <v>9</v>
@@ -12297,10 +12297,10 @@
     </row>
     <row r="591" spans="1:4">
       <c r="A591" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B591" t="s">
         <v>1183</v>
-      </c>
-      <c r="B591" t="s">
-        <v>1184</v>
       </c>
       <c r="D591" t="s">
         <v>9</v>
@@ -12308,10 +12308,10 @@
     </row>
     <row r="592" spans="1:4">
       <c r="A592" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B592" t="s">
         <v>1185</v>
-      </c>
-      <c r="B592" t="s">
-        <v>1186</v>
       </c>
       <c r="D592" t="s">
         <v>9</v>
@@ -12319,10 +12319,10 @@
     </row>
     <row r="593" spans="1:4">
       <c r="A593" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B593" t="s">
         <v>1187</v>
-      </c>
-      <c r="B593" t="s">
-        <v>1188</v>
       </c>
       <c r="D593" t="s">
         <v>9</v>
@@ -12330,10 +12330,10 @@
     </row>
     <row r="594" spans="1:4">
       <c r="A594" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B594" t="s">
         <v>1189</v>
-      </c>
-      <c r="B594" t="s">
-        <v>1190</v>
       </c>
       <c r="D594" t="s">
         <v>9</v>
@@ -12341,10 +12341,10 @@
     </row>
     <row r="595" spans="1:4">
       <c r="A595" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B595" t="s">
         <v>1191</v>
-      </c>
-      <c r="B595" t="s">
-        <v>1192</v>
       </c>
       <c r="D595" t="s">
         <v>9</v>
@@ -12352,10 +12352,10 @@
     </row>
     <row r="596" spans="1:4">
       <c r="A596" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B596" t="s">
         <v>1193</v>
-      </c>
-      <c r="B596" t="s">
-        <v>1194</v>
       </c>
       <c r="D596" t="s">
         <v>9</v>
@@ -12363,10 +12363,10 @@
     </row>
     <row r="597" spans="1:4">
       <c r="A597" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B597" t="s">
         <v>1195</v>
-      </c>
-      <c r="B597" t="s">
-        <v>1196</v>
       </c>
       <c r="D597" t="s">
         <v>9</v>
@@ -12374,10 +12374,10 @@
     </row>
     <row r="598" spans="1:4">
       <c r="A598" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B598" t="s">
         <v>1197</v>
-      </c>
-      <c r="B598" t="s">
-        <v>1198</v>
       </c>
       <c r="D598" t="s">
         <v>9</v>
@@ -12385,10 +12385,10 @@
     </row>
     <row r="599" spans="1:4">
       <c r="A599" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B599" t="s">
         <v>1199</v>
-      </c>
-      <c r="B599" t="s">
-        <v>1200</v>
       </c>
       <c r="D599" t="s">
         <v>9</v>
@@ -12396,10 +12396,10 @@
     </row>
     <row r="600" spans="1:4">
       <c r="A600" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B600" t="s">
         <v>1201</v>
-      </c>
-      <c r="B600" t="s">
-        <v>1202</v>
       </c>
       <c r="D600" t="s">
         <v>9</v>
@@ -12407,10 +12407,10 @@
     </row>
     <row r="601" spans="1:4">
       <c r="A601" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B601" t="s">
         <v>1203</v>
-      </c>
-      <c r="B601" t="s">
-        <v>1204</v>
       </c>
       <c r="D601" t="s">
         <v>9</v>
@@ -12418,10 +12418,10 @@
     </row>
     <row r="602" spans="1:4">
       <c r="A602" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B602" t="s">
         <v>1205</v>
-      </c>
-      <c r="B602" t="s">
-        <v>1206</v>
       </c>
       <c r="D602" t="s">
         <v>9</v>
@@ -12429,10 +12429,10 @@
     </row>
     <row r="603" spans="1:4">
       <c r="A603" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B603" t="s">
         <v>1207</v>
-      </c>
-      <c r="B603" t="s">
-        <v>1208</v>
       </c>
       <c r="D603" t="s">
         <v>9</v>
@@ -12440,10 +12440,10 @@
     </row>
     <row r="604" spans="1:4">
       <c r="A604" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B604" t="s">
         <v>1209</v>
-      </c>
-      <c r="B604" t="s">
-        <v>1210</v>
       </c>
       <c r="D604" t="s">
         <v>9</v>
@@ -12451,10 +12451,10 @@
     </row>
     <row r="605" spans="1:4">
       <c r="A605" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B605" t="s">
         <v>1211</v>
-      </c>
-      <c r="B605" t="s">
-        <v>1212</v>
       </c>
       <c r="D605" t="s">
         <v>9</v>
@@ -12462,10 +12462,10 @@
     </row>
     <row r="606" spans="1:4">
       <c r="A606" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B606" t="s">
         <v>1213</v>
-      </c>
-      <c r="B606" t="s">
-        <v>1214</v>
       </c>
       <c r="D606" t="s">
         <v>9</v>
@@ -12473,10 +12473,10 @@
     </row>
     <row r="607" spans="1:4">
       <c r="A607" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B607" t="s">
         <v>1215</v>
-      </c>
-      <c r="B607" t="s">
-        <v>1216</v>
       </c>
       <c r="D607" t="s">
         <v>9</v>
@@ -12484,10 +12484,10 @@
     </row>
     <row r="608" spans="1:4">
       <c r="A608" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B608" t="s">
         <v>1217</v>
-      </c>
-      <c r="B608" t="s">
-        <v>1218</v>
       </c>
       <c r="D608" t="s">
         <v>9</v>
@@ -12495,10 +12495,10 @@
     </row>
     <row r="609" spans="1:4">
       <c r="A609" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B609" t="s">
         <v>1219</v>
-      </c>
-      <c r="B609" t="s">
-        <v>1220</v>
       </c>
       <c r="D609" t="s">
         <v>9</v>
@@ -12506,10 +12506,10 @@
     </row>
     <row r="610" spans="1:4">
       <c r="A610" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B610" t="s">
         <v>1221</v>
-      </c>
-      <c r="B610" t="s">
-        <v>1222</v>
       </c>
       <c r="D610" t="s">
         <v>9</v>
@@ -12517,10 +12517,10 @@
     </row>
     <row r="611" spans="1:4">
       <c r="A611" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B611" t="s">
         <v>1223</v>
-      </c>
-      <c r="B611" t="s">
-        <v>1224</v>
       </c>
       <c r="D611" t="s">
         <v>9</v>
@@ -12528,10 +12528,10 @@
     </row>
     <row r="612" spans="1:4">
       <c r="A612" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B612" t="s">
         <v>1225</v>
-      </c>
-      <c r="B612" t="s">
-        <v>1226</v>
       </c>
       <c r="D612" t="s">
         <v>9</v>
@@ -12539,10 +12539,10 @@
     </row>
     <row r="613" spans="1:4">
       <c r="A613" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B613" t="s">
         <v>1227</v>
-      </c>
-      <c r="B613" t="s">
-        <v>1228</v>
       </c>
       <c r="D613" t="s">
         <v>9</v>
@@ -12550,10 +12550,10 @@
     </row>
     <row r="614" spans="1:4">
       <c r="A614" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B614" t="s">
         <v>1229</v>
-      </c>
-      <c r="B614" t="s">
-        <v>1230</v>
       </c>
       <c r="D614" t="s">
         <v>9</v>
@@ -12561,10 +12561,10 @@
     </row>
     <row r="615" spans="1:4">
       <c r="A615" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B615" t="s">
         <v>1231</v>
-      </c>
-      <c r="B615" t="s">
-        <v>1232</v>
       </c>
       <c r="D615" t="s">
         <v>9</v>
@@ -12572,10 +12572,10 @@
     </row>
     <row r="616" spans="1:4">
       <c r="A616" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B616" t="s">
         <v>1233</v>
-      </c>
-      <c r="B616" t="s">
-        <v>1234</v>
       </c>
       <c r="D616" t="s">
         <v>9</v>
@@ -12583,10 +12583,10 @@
     </row>
     <row r="617" spans="1:4">
       <c r="A617" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B617" t="s">
         <v>1235</v>
-      </c>
-      <c r="B617" t="s">
-        <v>1236</v>
       </c>
       <c r="D617" t="s">
         <v>9</v>
@@ -12594,10 +12594,10 @@
     </row>
     <row r="618" spans="1:4">
       <c r="A618" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B618" t="s">
         <v>1237</v>
-      </c>
-      <c r="B618" t="s">
-        <v>1238</v>
       </c>
       <c r="D618" t="s">
         <v>9</v>
@@ -12605,10 +12605,10 @@
     </row>
     <row r="619" spans="1:4">
       <c r="A619" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B619" t="s">
         <v>1239</v>
-      </c>
-      <c r="B619" t="s">
-        <v>1240</v>
       </c>
       <c r="D619" t="s">
         <v>9</v>
@@ -12616,10 +12616,10 @@
     </row>
     <row r="620" spans="1:4">
       <c r="A620" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B620" t="s">
         <v>1241</v>
-      </c>
-      <c r="B620" t="s">
-        <v>1242</v>
       </c>
       <c r="D620" t="s">
         <v>9</v>
@@ -12627,10 +12627,10 @@
     </row>
     <row r="621" spans="1:4">
       <c r="A621" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B621" t="s">
         <v>1243</v>
-      </c>
-      <c r="B621" t="s">
-        <v>1244</v>
       </c>
       <c r="D621" t="s">
         <v>9</v>
@@ -12638,10 +12638,10 @@
     </row>
     <row r="622" spans="1:4">
       <c r="A622" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B622" t="s">
         <v>1245</v>
-      </c>
-      <c r="B622" t="s">
-        <v>1246</v>
       </c>
       <c r="D622" t="s">
         <v>9</v>
@@ -12649,10 +12649,10 @@
     </row>
     <row r="623" spans="1:4">
       <c r="A623" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B623" t="s">
         <v>1247</v>
-      </c>
-      <c r="B623" t="s">
-        <v>1248</v>
       </c>
       <c r="D623" t="s">
         <v>9</v>
@@ -12660,10 +12660,10 @@
     </row>
     <row r="624" spans="1:4">
       <c r="A624" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B624" t="s">
         <v>1249</v>
-      </c>
-      <c r="B624" t="s">
-        <v>1250</v>
       </c>
       <c r="D624" t="s">
         <v>9</v>
@@ -12671,10 +12671,10 @@
     </row>
     <row r="625" spans="1:4">
       <c r="A625" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B625" t="s">
         <v>1251</v>
-      </c>
-      <c r="B625" t="s">
-        <v>1252</v>
       </c>
       <c r="D625" t="s">
         <v>9</v>
@@ -12682,10 +12682,10 @@
     </row>
     <row r="626" spans="1:4">
       <c r="A626" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B626" t="s">
         <v>1253</v>
-      </c>
-      <c r="B626" t="s">
-        <v>1254</v>
       </c>
       <c r="D626" t="s">
         <v>9</v>
@@ -12693,10 +12693,10 @@
     </row>
     <row r="627" spans="1:4">
       <c r="A627" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B627" t="s">
         <v>1255</v>
-      </c>
-      <c r="B627" t="s">
-        <v>1256</v>
       </c>
       <c r="D627" t="s">
         <v>9</v>
@@ -12704,10 +12704,10 @@
     </row>
     <row r="628" spans="1:4">
       <c r="A628" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B628" t="s">
         <v>1257</v>
-      </c>
-      <c r="B628" t="s">
-        <v>1258</v>
       </c>
       <c r="D628" t="s">
         <v>9</v>
@@ -12715,10 +12715,10 @@
     </row>
     <row r="629" spans="1:4">
       <c r="A629" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B629" t="s">
         <v>1259</v>
-      </c>
-      <c r="B629" t="s">
-        <v>1260</v>
       </c>
       <c r="D629" t="s">
         <v>9</v>
@@ -12726,10 +12726,10 @@
     </row>
     <row r="630" spans="1:4">
       <c r="A630" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B630" t="s">
         <v>1261</v>
-      </c>
-      <c r="B630" t="s">
-        <v>1262</v>
       </c>
       <c r="D630" t="s">
         <v>9</v>
@@ -12737,10 +12737,10 @@
     </row>
     <row r="631" spans="1:4">
       <c r="A631" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B631" t="s">
         <v>1263</v>
-      </c>
-      <c r="B631" t="s">
-        <v>1264</v>
       </c>
       <c r="D631" t="s">
         <v>9</v>
@@ -12748,10 +12748,10 @@
     </row>
     <row r="632" spans="1:4">
       <c r="A632" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B632" t="s">
         <v>1265</v>
-      </c>
-      <c r="B632" t="s">
-        <v>1266</v>
       </c>
       <c r="D632" t="s">
         <v>9</v>
@@ -12759,10 +12759,10 @@
     </row>
     <row r="633" spans="1:4">
       <c r="A633" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B633" t="s">
         <v>1267</v>
-      </c>
-      <c r="B633" t="s">
-        <v>1268</v>
       </c>
       <c r="D633" t="s">
         <v>9</v>
@@ -12770,10 +12770,10 @@
     </row>
     <row r="634" spans="1:4">
       <c r="A634" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B634" t="s">
         <v>1269</v>
-      </c>
-      <c r="B634" t="s">
-        <v>1270</v>
       </c>
       <c r="D634" t="s">
         <v>9</v>
@@ -12781,10 +12781,10 @@
     </row>
     <row r="635" spans="1:4">
       <c r="A635" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B635" t="s">
         <v>1271</v>
-      </c>
-      <c r="B635" t="s">
-        <v>1272</v>
       </c>
       <c r="D635" t="s">
         <v>9</v>
@@ -12792,10 +12792,10 @@
     </row>
     <row r="636" spans="1:4">
       <c r="A636" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B636" t="s">
         <v>1273</v>
-      </c>
-      <c r="B636" t="s">
-        <v>1274</v>
       </c>
       <c r="D636" t="s">
         <v>9</v>
@@ -12803,10 +12803,10 @@
     </row>
     <row r="637" spans="1:4">
       <c r="A637" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B637" t="s">
         <v>1275</v>
-      </c>
-      <c r="B637" t="s">
-        <v>1276</v>
       </c>
       <c r="D637" t="s">
         <v>9</v>
@@ -12814,10 +12814,10 @@
     </row>
     <row r="638" spans="1:4">
       <c r="A638" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B638" t="s">
         <v>1277</v>
-      </c>
-      <c r="B638" t="s">
-        <v>1278</v>
       </c>
       <c r="D638" t="s">
         <v>9</v>
@@ -12825,10 +12825,10 @@
     </row>
     <row r="639" spans="1:4">
       <c r="A639" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B639" t="s">
         <v>1279</v>
-      </c>
-      <c r="B639" t="s">
-        <v>1280</v>
       </c>
       <c r="D639" t="s">
         <v>9</v>
@@ -12836,10 +12836,10 @@
     </row>
     <row r="640" spans="1:4">
       <c r="A640" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B640" t="s">
         <v>1281</v>
-      </c>
-      <c r="B640" t="s">
-        <v>1282</v>
       </c>
       <c r="D640" t="s">
         <v>9</v>
@@ -12847,10 +12847,10 @@
     </row>
     <row r="641" spans="1:4">
       <c r="A641" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B641" t="s">
         <v>1283</v>
-      </c>
-      <c r="B641" t="s">
-        <v>1284</v>
       </c>
       <c r="D641" t="s">
         <v>9</v>
@@ -12858,10 +12858,10 @@
     </row>
     <row r="642" spans="1:4">
       <c r="A642" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B642" t="s">
         <v>1285</v>
-      </c>
-      <c r="B642" t="s">
-        <v>1286</v>
       </c>
       <c r="D642" t="s">
         <v>9</v>
@@ -12869,10 +12869,10 @@
     </row>
     <row r="643" spans="1:4">
       <c r="A643" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B643" t="s">
         <v>1287</v>
-      </c>
-      <c r="B643" t="s">
-        <v>1288</v>
       </c>
       <c r="D643" t="s">
         <v>9</v>
@@ -12880,10 +12880,10 @@
     </row>
     <row r="644" spans="1:4">
       <c r="A644" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B644" t="s">
         <v>1289</v>
-      </c>
-      <c r="B644" t="s">
-        <v>1290</v>
       </c>
       <c r="D644" t="s">
         <v>9</v>
@@ -12891,10 +12891,10 @@
     </row>
     <row r="645" spans="1:4">
       <c r="A645" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B645" t="s">
         <v>1291</v>
-      </c>
-      <c r="B645" t="s">
-        <v>1292</v>
       </c>
       <c r="D645" t="s">
         <v>9</v>
@@ -12902,10 +12902,10 @@
     </row>
     <row r="646" spans="1:4">
       <c r="A646" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B646" t="s">
         <v>1293</v>
-      </c>
-      <c r="B646" t="s">
-        <v>1294</v>
       </c>
       <c r="D646" t="s">
         <v>9</v>
@@ -12913,10 +12913,10 @@
     </row>
     <row r="647" spans="1:4">
       <c r="A647" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B647" t="s">
         <v>1295</v>
-      </c>
-      <c r="B647" t="s">
-        <v>1296</v>
       </c>
       <c r="D647" t="s">
         <v>9</v>
@@ -12924,10 +12924,10 @@
     </row>
     <row r="648" spans="1:4">
       <c r="A648" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B648" t="s">
         <v>1297</v>
-      </c>
-      <c r="B648" t="s">
-        <v>1298</v>
       </c>
       <c r="D648" t="s">
         <v>9</v>
@@ -12935,10 +12935,10 @@
     </row>
     <row r="649" spans="1:4">
       <c r="A649" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B649" t="s">
         <v>1299</v>
-      </c>
-      <c r="B649" t="s">
-        <v>1300</v>
       </c>
       <c r="D649" t="s">
         <v>9</v>
@@ -12946,10 +12946,10 @@
     </row>
     <row r="650" spans="1:4">
       <c r="A650" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B650" t="s">
         <v>1301</v>
-      </c>
-      <c r="B650" t="s">
-        <v>1302</v>
       </c>
       <c r="D650" t="s">
         <v>9</v>
@@ -12957,10 +12957,10 @@
     </row>
     <row r="651" spans="1:4">
       <c r="A651" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B651" t="s">
         <v>1303</v>
-      </c>
-      <c r="B651" t="s">
-        <v>1304</v>
       </c>
       <c r="D651" t="s">
         <v>9</v>
@@ -12968,10 +12968,10 @@
     </row>
     <row r="652" spans="1:4">
       <c r="A652" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B652" t="s">
         <v>1305</v>
-      </c>
-      <c r="B652" t="s">
-        <v>1306</v>
       </c>
       <c r="D652" t="s">
         <v>9</v>
@@ -12979,10 +12979,10 @@
     </row>
     <row r="653" spans="1:4">
       <c r="A653" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B653" t="s">
         <v>1307</v>
-      </c>
-      <c r="B653" t="s">
-        <v>1308</v>
       </c>
       <c r="D653" t="s">
         <v>9</v>
@@ -12990,10 +12990,10 @@
     </row>
     <row r="654" spans="1:4">
       <c r="A654" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B654" t="s">
         <v>1309</v>
-      </c>
-      <c r="B654" t="s">
-        <v>1310</v>
       </c>
       <c r="D654" t="s">
         <v>9</v>
@@ -13001,10 +13001,10 @@
     </row>
     <row r="655" spans="1:4">
       <c r="A655" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B655" t="s">
         <v>1311</v>
-      </c>
-      <c r="B655" t="s">
-        <v>1312</v>
       </c>
       <c r="D655" t="s">
         <v>9</v>
@@ -13012,10 +13012,10 @@
     </row>
     <row r="656" spans="1:4">
       <c r="A656" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B656" t="s">
         <v>1313</v>
-      </c>
-      <c r="B656" t="s">
-        <v>1314</v>
       </c>
       <c r="D656" t="s">
         <v>9</v>
@@ -13023,10 +13023,10 @@
     </row>
     <row r="657" spans="1:4">
       <c r="A657" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B657" t="s">
         <v>1315</v>
-      </c>
-      <c r="B657" t="s">
-        <v>1316</v>
       </c>
       <c r="D657" t="s">
         <v>9</v>
@@ -13034,10 +13034,10 @@
     </row>
     <row r="658" spans="1:4">
       <c r="A658" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B658" t="s">
         <v>1317</v>
-      </c>
-      <c r="B658" t="s">
-        <v>1318</v>
       </c>
       <c r="D658" t="s">
         <v>9</v>
@@ -13045,10 +13045,10 @@
     </row>
     <row r="659" spans="1:4">
       <c r="A659" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B659" t="s">
         <v>1319</v>
-      </c>
-      <c r="B659" t="s">
-        <v>1320</v>
       </c>
       <c r="D659" t="s">
         <v>9</v>
@@ -13056,10 +13056,10 @@
     </row>
     <row r="660" spans="1:4">
       <c r="A660" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B660" t="s">
         <v>1321</v>
-      </c>
-      <c r="B660" t="s">
-        <v>1322</v>
       </c>
       <c r="D660" t="s">
         <v>9</v>
@@ -13067,10 +13067,10 @@
     </row>
     <row r="661" spans="1:4">
       <c r="A661" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B661" t="s">
         <v>1323</v>
-      </c>
-      <c r="B661" t="s">
-        <v>1324</v>
       </c>
       <c r="D661" t="s">
         <v>9</v>
@@ -13078,10 +13078,10 @@
     </row>
     <row r="662" spans="1:4">
       <c r="A662" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B662" t="s">
         <v>1325</v>
-      </c>
-      <c r="B662" t="s">
-        <v>1326</v>
       </c>
       <c r="D662" t="s">
         <v>9</v>
@@ -13089,10 +13089,10 @@
     </row>
     <row r="663" spans="1:4">
       <c r="A663" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B663" t="s">
         <v>1327</v>
-      </c>
-      <c r="B663" t="s">
-        <v>1328</v>
       </c>
       <c r="D663" t="s">
         <v>9</v>
@@ -13100,10 +13100,10 @@
     </row>
     <row r="664" spans="1:4">
       <c r="A664" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B664" t="s">
         <v>1329</v>
-      </c>
-      <c r="B664" t="s">
-        <v>1330</v>
       </c>
       <c r="D664" t="s">
         <v>9</v>
@@ -13111,10 +13111,10 @@
     </row>
     <row r="665" spans="1:4">
       <c r="A665" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B665" t="s">
         <v>1331</v>
-      </c>
-      <c r="B665" t="s">
-        <v>1332</v>
       </c>
       <c r="D665" t="s">
         <v>9</v>
@@ -13122,10 +13122,10 @@
     </row>
     <row r="666" spans="1:4">
       <c r="A666" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B666" t="s">
         <v>1333</v>
-      </c>
-      <c r="B666" t="s">
-        <v>1334</v>
       </c>
       <c r="D666" t="s">
         <v>9</v>
@@ -13133,10 +13133,10 @@
     </row>
     <row r="667" spans="1:4">
       <c r="A667" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B667" t="s">
         <v>1335</v>
-      </c>
-      <c r="B667" t="s">
-        <v>1336</v>
       </c>
       <c r="D667" t="s">
         <v>9</v>
@@ -13144,10 +13144,10 @@
     </row>
     <row r="668" spans="1:4">
       <c r="A668" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B668" t="s">
         <v>1337</v>
-      </c>
-      <c r="B668" t="s">
-        <v>1338</v>
       </c>
       <c r="D668" t="s">
         <v>9</v>
@@ -13155,10 +13155,10 @@
     </row>
     <row r="669" spans="1:4">
       <c r="A669" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B669" t="s">
         <v>1339</v>
-      </c>
-      <c r="B669" t="s">
-        <v>1340</v>
       </c>
       <c r="D669" t="s">
         <v>9</v>
@@ -13166,10 +13166,10 @@
     </row>
     <row r="670" spans="1:4">
       <c r="A670" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B670" t="s">
         <v>1341</v>
-      </c>
-      <c r="B670" t="s">
-        <v>1342</v>
       </c>
       <c r="D670" t="s">
         <v>9</v>
@@ -13177,10 +13177,10 @@
     </row>
     <row r="671" spans="1:4">
       <c r="A671" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B671" t="s">
         <v>1343</v>
-      </c>
-      <c r="B671" t="s">
-        <v>1344</v>
       </c>
       <c r="D671" t="s">
         <v>9</v>
@@ -13188,10 +13188,10 @@
     </row>
     <row r="672" spans="1:4">
       <c r="A672" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B672" t="s">
         <v>1345</v>
-      </c>
-      <c r="B672" t="s">
-        <v>1346</v>
       </c>
       <c r="D672" t="s">
         <v>9</v>
@@ -13199,10 +13199,10 @@
     </row>
     <row r="673" spans="1:4">
       <c r="A673" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B673" t="s">
         <v>1347</v>
-      </c>
-      <c r="B673" t="s">
-        <v>1348</v>
       </c>
       <c r="D673" t="s">
         <v>9</v>
@@ -13210,10 +13210,10 @@
     </row>
     <row r="674" spans="1:4">
       <c r="A674" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B674" t="s">
         <v>1349</v>
-      </c>
-      <c r="B674" t="s">
-        <v>1350</v>
       </c>
       <c r="D674" t="s">
         <v>9</v>
@@ -13221,10 +13221,10 @@
     </row>
     <row r="675" spans="1:4">
       <c r="A675" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B675" t="s">
         <v>1351</v>
-      </c>
-      <c r="B675" t="s">
-        <v>1352</v>
       </c>
       <c r="D675" t="s">
         <v>9</v>
@@ -13232,10 +13232,10 @@
     </row>
     <row r="676" spans="1:4">
       <c r="A676" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B676" t="s">
         <v>1353</v>
-      </c>
-      <c r="B676" t="s">
-        <v>1354</v>
       </c>
       <c r="D676" t="s">
         <v>9</v>
@@ -13243,10 +13243,10 @@
     </row>
     <row r="677" spans="1:4">
       <c r="A677" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B677" t="s">
         <v>1355</v>
-      </c>
-      <c r="B677" t="s">
-        <v>1356</v>
       </c>
       <c r="D677" t="s">
         <v>9</v>
@@ -13254,10 +13254,10 @@
     </row>
     <row r="678" spans="1:4">
       <c r="A678" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B678" t="s">
         <v>1357</v>
-      </c>
-      <c r="B678" t="s">
-        <v>1358</v>
       </c>
       <c r="D678" t="s">
         <v>9</v>
@@ -13265,10 +13265,10 @@
     </row>
     <row r="679" spans="1:4">
       <c r="A679" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B679" t="s">
         <v>1359</v>
-      </c>
-      <c r="B679" t="s">
-        <v>1360</v>
       </c>
       <c r="D679" t="s">
         <v>9</v>
@@ -13276,10 +13276,10 @@
     </row>
     <row r="680" spans="1:4">
       <c r="A680" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B680" t="s">
         <v>1361</v>
-      </c>
-      <c r="B680" t="s">
-        <v>1362</v>
       </c>
       <c r="D680" t="s">
         <v>9</v>
@@ -13287,10 +13287,10 @@
     </row>
     <row r="681" spans="1:4">
       <c r="A681" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B681" t="s">
         <v>1363</v>
-      </c>
-      <c r="B681" t="s">
-        <v>1364</v>
       </c>
       <c r="D681" t="s">
         <v>9</v>
@@ -13298,10 +13298,10 @@
     </row>
     <row r="682" spans="1:4">
       <c r="A682" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B682" t="s">
         <v>1365</v>
-      </c>
-      <c r="B682" t="s">
-        <v>1366</v>
       </c>
       <c r="D682" t="s">
         <v>9</v>
@@ -13309,10 +13309,10 @@
     </row>
     <row r="683" spans="1:4">
       <c r="A683" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B683" t="s">
         <v>1367</v>
-      </c>
-      <c r="B683" t="s">
-        <v>1368</v>
       </c>
       <c r="D683" t="s">
         <v>9</v>
@@ -13320,10 +13320,10 @@
     </row>
     <row r="684" spans="1:4">
       <c r="A684" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B684" t="s">
         <v>1369</v>
-      </c>
-      <c r="B684" t="s">
-        <v>1370</v>
       </c>
       <c r="D684" t="s">
         <v>9</v>
@@ -13331,10 +13331,10 @@
     </row>
     <row r="685" spans="1:4">
       <c r="A685" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B685" t="s">
         <v>1371</v>
-      </c>
-      <c r="B685" t="s">
-        <v>1372</v>
       </c>
       <c r="D685" t="s">
         <v>9</v>
@@ -13342,10 +13342,10 @@
     </row>
     <row r="686" spans="1:4">
       <c r="A686" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B686" t="s">
         <v>1373</v>
-      </c>
-      <c r="B686" t="s">
-        <v>1374</v>
       </c>
       <c r="D686" t="s">
         <v>9</v>
@@ -13353,10 +13353,10 @@
     </row>
     <row r="687" spans="1:4">
       <c r="A687" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B687" t="s">
         <v>1375</v>
-      </c>
-      <c r="B687" t="s">
-        <v>1376</v>
       </c>
       <c r="D687" t="s">
         <v>9</v>
@@ -13364,10 +13364,10 @@
     </row>
     <row r="688" spans="1:4">
       <c r="A688" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B688" t="s">
         <v>1377</v>
-      </c>
-      <c r="B688" t="s">
-        <v>1378</v>
       </c>
       <c r="D688" t="s">
         <v>9</v>
@@ -13375,10 +13375,10 @@
     </row>
     <row r="689" spans="1:4">
       <c r="A689" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B689" t="s">
         <v>1379</v>
-      </c>
-      <c r="B689" t="s">
-        <v>1380</v>
       </c>
       <c r="D689" t="s">
         <v>9</v>
@@ -13386,10 +13386,10 @@
     </row>
     <row r="690" spans="1:4">
       <c r="A690" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B690" t="s">
         <v>1381</v>
-      </c>
-      <c r="B690" t="s">
-        <v>1382</v>
       </c>
       <c r="D690" t="s">
         <v>9</v>
@@ -13397,10 +13397,10 @@
     </row>
     <row r="691" spans="1:4">
       <c r="A691" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B691" t="s">
         <v>1383</v>
-      </c>
-      <c r="B691" t="s">
-        <v>1384</v>
       </c>
       <c r="D691" t="s">
         <v>9</v>
@@ -13408,10 +13408,10 @@
     </row>
     <row r="692" spans="1:4">
       <c r="A692" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B692" t="s">
         <v>1385</v>
-      </c>
-      <c r="B692" t="s">
-        <v>1386</v>
       </c>
       <c r="D692" t="s">
         <v>9</v>
@@ -13419,10 +13419,10 @@
     </row>
     <row r="693" spans="1:4">
       <c r="A693" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B693" t="s">
         <v>1387</v>
-      </c>
-      <c r="B693" t="s">
-        <v>1388</v>
       </c>
       <c r="D693" t="s">
         <v>9</v>
@@ -13430,10 +13430,10 @@
     </row>
     <row r="694" spans="1:4">
       <c r="A694" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B694" t="s">
         <v>1389</v>
-      </c>
-      <c r="B694" t="s">
-        <v>1390</v>
       </c>
       <c r="D694" t="s">
         <v>9</v>
@@ -13441,10 +13441,10 @@
     </row>
     <row r="695" spans="1:4">
       <c r="A695" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B695" t="s">
         <v>1391</v>
-      </c>
-      <c r="B695" t="s">
-        <v>1392</v>
       </c>
       <c r="D695" t="s">
         <v>9</v>
@@ -13452,10 +13452,10 @@
     </row>
     <row r="696" spans="1:4">
       <c r="A696" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B696" t="s">
         <v>1393</v>
-      </c>
-      <c r="B696" t="s">
-        <v>1394</v>
       </c>
       <c r="D696" t="s">
         <v>9</v>
@@ -13463,10 +13463,10 @@
     </row>
     <row r="697" spans="1:4">
       <c r="A697" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B697" t="s">
         <v>1395</v>
-      </c>
-      <c r="B697" t="s">
-        <v>1396</v>
       </c>
       <c r="D697" t="s">
         <v>9</v>
@@ -13474,10 +13474,10 @@
     </row>
     <row r="698" spans="1:4">
       <c r="A698" t="s">
+        <v>1396</v>
+      </c>
+      <c r="B698" t="s">
         <v>1397</v>
-      </c>
-      <c r="B698" t="s">
-        <v>1398</v>
       </c>
       <c r="D698" t="s">
         <v>9</v>
@@ -13485,10 +13485,10 @@
     </row>
     <row r="699" spans="1:4">
       <c r="A699" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B699" t="s">
         <v>1399</v>
-      </c>
-      <c r="B699" t="s">
-        <v>1400</v>
       </c>
       <c r="D699" t="s">
         <v>9</v>
@@ -13496,10 +13496,10 @@
     </row>
     <row r="700" spans="1:4">
       <c r="A700" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B700" t="s">
         <v>1401</v>
-      </c>
-      <c r="B700" t="s">
-        <v>1402</v>
       </c>
       <c r="D700" t="s">
         <v>9</v>
@@ -13507,10 +13507,10 @@
     </row>
     <row r="701" spans="1:4">
       <c r="A701" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B701" t="s">
         <v>1403</v>
-      </c>
-      <c r="B701" t="s">
-        <v>1404</v>
       </c>
       <c r="D701" t="s">
         <v>9</v>
@@ -13518,10 +13518,10 @@
     </row>
     <row r="702" spans="1:4">
       <c r="A702" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B702" t="s">
         <v>1405</v>
-      </c>
-      <c r="B702" t="s">
-        <v>1406</v>
       </c>
       <c r="D702" t="s">
         <v>9</v>
@@ -13529,10 +13529,10 @@
     </row>
     <row r="703" spans="1:4">
       <c r="A703" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B703" t="s">
         <v>1407</v>
-      </c>
-      <c r="B703" t="s">
-        <v>1408</v>
       </c>
       <c r="D703" t="s">
         <v>9</v>
@@ -13540,10 +13540,10 @@
     </row>
     <row r="704" spans="1:4">
       <c r="A704" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B704" t="s">
         <v>1409</v>
-      </c>
-      <c r="B704" t="s">
-        <v>1410</v>
       </c>
       <c r="D704" t="s">
         <v>9</v>
@@ -13551,10 +13551,10 @@
     </row>
     <row r="705" spans="1:4">
       <c r="A705" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B705" t="s">
         <v>1411</v>
-      </c>
-      <c r="B705" t="s">
-        <v>1412</v>
       </c>
       <c r="D705" t="s">
         <v>9</v>
@@ -13562,10 +13562,10 @@
     </row>
     <row r="706" spans="1:4">
       <c r="A706" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B706" t="s">
         <v>1413</v>
-      </c>
-      <c r="B706" t="s">
-        <v>1414</v>
       </c>
       <c r="D706" t="s">
         <v>9</v>
@@ -13573,10 +13573,10 @@
     </row>
     <row r="707" spans="1:4">
       <c r="A707" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B707" t="s">
         <v>1415</v>
-      </c>
-      <c r="B707" t="s">
-        <v>1416</v>
       </c>
       <c r="D707" t="s">
         <v>9</v>
@@ -13584,10 +13584,10 @@
     </row>
     <row r="708" spans="1:4">
       <c r="A708" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B708" t="s">
         <v>1417</v>
-      </c>
-      <c r="B708" t="s">
-        <v>1418</v>
       </c>
       <c r="D708" t="s">
         <v>9</v>
@@ -13595,10 +13595,10 @@
     </row>
     <row r="709" spans="1:4">
       <c r="A709" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B709" t="s">
         <v>1419</v>
-      </c>
-      <c r="B709" t="s">
-        <v>1420</v>
       </c>
       <c r="D709" t="s">
         <v>9</v>
@@ -13606,10 +13606,10 @@
     </row>
     <row r="710" spans="1:4">
       <c r="A710" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B710" t="s">
         <v>1421</v>
-      </c>
-      <c r="B710" t="s">
-        <v>1422</v>
       </c>
       <c r="D710" t="s">
         <v>9</v>
@@ -13617,10 +13617,10 @@
     </row>
     <row r="711" spans="1:4">
       <c r="A711" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B711" t="s">
         <v>1423</v>
-      </c>
-      <c r="B711" t="s">
-        <v>1424</v>
       </c>
       <c r="D711" t="s">
         <v>9</v>
@@ -13628,10 +13628,10 @@
     </row>
     <row r="712" spans="1:4">
       <c r="A712" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B712" t="s">
         <v>1425</v>
-      </c>
-      <c r="B712" t="s">
-        <v>1426</v>
       </c>
       <c r="D712" t="s">
         <v>9</v>
@@ -13639,10 +13639,10 @@
     </row>
     <row r="713" spans="1:4">
       <c r="A713" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B713" t="s">
         <v>1427</v>
-      </c>
-      <c r="B713" t="s">
-        <v>1428</v>
       </c>
       <c r="D713" t="s">
         <v>9</v>
@@ -13650,10 +13650,10 @@
     </row>
     <row r="714" spans="1:4">
       <c r="A714" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B714" t="s">
         <v>1429</v>
-      </c>
-      <c r="B714" t="s">
-        <v>1430</v>
       </c>
       <c r="D714" t="s">
         <v>9</v>
@@ -13661,10 +13661,10 @@
     </row>
     <row r="715" spans="1:4">
       <c r="A715" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B715" t="s">
         <v>1431</v>
-      </c>
-      <c r="B715" t="s">
-        <v>1432</v>
       </c>
       <c r="D715" t="s">
         <v>9</v>
@@ -13672,10 +13672,10 @@
     </row>
     <row r="716" spans="1:4">
       <c r="A716" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B716" t="s">
         <v>1433</v>
-      </c>
-      <c r="B716" t="s">
-        <v>1434</v>
       </c>
       <c r="D716" t="s">
         <v>9</v>
@@ -13683,10 +13683,10 @@
     </row>
     <row r="717" spans="1:4">
       <c r="A717" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B717" t="s">
         <v>1435</v>
-      </c>
-      <c r="B717" t="s">
-        <v>1436</v>
       </c>
       <c r="D717" t="s">
         <v>9</v>
@@ -13694,10 +13694,10 @@
     </row>
     <row r="718" spans="1:4">
       <c r="A718" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B718" t="s">
         <v>1437</v>
-      </c>
-      <c r="B718" t="s">
-        <v>1438</v>
       </c>
       <c r="D718" t="s">
         <v>9</v>
@@ -13705,10 +13705,10 @@
     </row>
     <row r="719" spans="1:4">
       <c r="A719" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B719" t="s">
         <v>1439</v>
-      </c>
-      <c r="B719" t="s">
-        <v>1440</v>
       </c>
       <c r="D719" t="s">
         <v>9</v>
@@ -13716,10 +13716,10 @@
     </row>
     <row r="720" spans="1:4">
       <c r="A720" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B720" t="s">
         <v>1441</v>
-      </c>
-      <c r="B720" t="s">
-        <v>1442</v>
       </c>
       <c r="D720" t="s">
         <v>9</v>
@@ -13727,10 +13727,10 @@
     </row>
     <row r="721" spans="1:4">
       <c r="A721" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B721" t="s">
         <v>1443</v>
-      </c>
-      <c r="B721" t="s">
-        <v>1444</v>
       </c>
       <c r="D721" t="s">
         <v>9</v>
@@ -13738,10 +13738,10 @@
     </row>
     <row r="722" spans="1:4">
       <c r="A722" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B722" t="s">
         <v>1445</v>
-      </c>
-      <c r="B722" t="s">
-        <v>1446</v>
       </c>
       <c r="D722" t="s">
         <v>9</v>
@@ -13749,10 +13749,10 @@
     </row>
     <row r="723" spans="1:4">
       <c r="A723" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B723" t="s">
         <v>1447</v>
-      </c>
-      <c r="B723" t="s">
-        <v>1448</v>
       </c>
       <c r="D723" t="s">
         <v>9</v>
@@ -13760,10 +13760,10 @@
     </row>
     <row r="724" spans="1:4">
       <c r="A724" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B724" t="s">
         <v>1449</v>
-      </c>
-      <c r="B724" t="s">
-        <v>1450</v>
       </c>
       <c r="D724" t="s">
         <v>9</v>
@@ -13771,10 +13771,10 @@
     </row>
     <row r="725" spans="1:4">
       <c r="A725" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B725" t="s">
         <v>1451</v>
-      </c>
-      <c r="B725" t="s">
-        <v>1452</v>
       </c>
       <c r="D725" t="s">
         <v>9</v>
@@ -13782,10 +13782,10 @@
     </row>
     <row r="726" spans="1:4">
       <c r="A726" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B726" t="s">
         <v>1453</v>
-      </c>
-      <c r="B726" t="s">
-        <v>1454</v>
       </c>
       <c r="D726" t="s">
         <v>9</v>
@@ -13793,10 +13793,10 @@
     </row>
     <row r="727" spans="1:4">
       <c r="A727" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B727" t="s">
         <v>1455</v>
-      </c>
-      <c r="B727" t="s">
-        <v>1456</v>
       </c>
       <c r="D727" t="s">
         <v>9</v>
@@ -13804,10 +13804,10 @@
     </row>
     <row r="728" spans="1:4">
       <c r="A728" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B728" t="s">
         <v>1457</v>
-      </c>
-      <c r="B728" t="s">
-        <v>1458</v>
       </c>
       <c r="D728" t="s">
         <v>9</v>
@@ -13815,10 +13815,10 @@
     </row>
     <row r="729" spans="1:4">
       <c r="A729" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B729" t="s">
         <v>1459</v>
-      </c>
-      <c r="B729" t="s">
-        <v>1460</v>
       </c>
       <c r="D729" t="s">
         <v>9</v>
@@ -13826,10 +13826,10 @@
     </row>
     <row r="730" spans="1:4">
       <c r="A730" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B730" t="s">
         <v>1461</v>
-      </c>
-      <c r="B730" t="s">
-        <v>1462</v>
       </c>
       <c r="D730" t="s">
         <v>9</v>
@@ -13837,10 +13837,10 @@
     </row>
     <row r="731" spans="1:4">
       <c r="A731" t="s">
+        <v>1462</v>
+      </c>
+      <c r="B731" t="s">
         <v>1463</v>
-      </c>
-      <c r="B731" t="s">
-        <v>1464</v>
       </c>
       <c r="D731" t="s">
         <v>9</v>
@@ -13848,10 +13848,10 @@
     </row>
     <row r="732" spans="1:4">
       <c r="A732" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B732" t="s">
         <v>1465</v>
-      </c>
-      <c r="B732" t="s">
-        <v>1466</v>
       </c>
       <c r="D732" t="s">
         <v>9</v>
@@ -13859,10 +13859,10 @@
     </row>
     <row r="733" spans="1:4">
       <c r="A733" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B733" t="s">
         <v>1467</v>
-      </c>
-      <c r="B733" t="s">
-        <v>1468</v>
       </c>
       <c r="D733" t="s">
         <v>9</v>
@@ -13870,10 +13870,10 @@
     </row>
     <row r="734" spans="1:4">
       <c r="A734" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B734" t="s">
         <v>1469</v>
-      </c>
-      <c r="B734" t="s">
-        <v>1470</v>
       </c>
       <c r="D734" t="s">
         <v>9</v>
@@ -13881,10 +13881,10 @@
     </row>
     <row r="735" spans="1:4">
       <c r="A735" t="s">
+        <v>1470</v>
+      </c>
+      <c r="B735" t="s">
         <v>1471</v>
-      </c>
-      <c r="B735" t="s">
-        <v>1472</v>
       </c>
       <c r="D735" t="s">
         <v>9</v>
@@ -13892,10 +13892,10 @@
     </row>
     <row r="736" spans="1:4">
       <c r="A736" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B736" t="s">
         <v>1473</v>
-      </c>
-      <c r="B736" t="s">
-        <v>1474</v>
       </c>
       <c r="D736" t="s">
         <v>9</v>
@@ -13903,10 +13903,10 @@
     </row>
     <row r="737" spans="1:4">
       <c r="A737" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B737" t="s">
         <v>1475</v>
-      </c>
-      <c r="B737" t="s">
-        <v>1476</v>
       </c>
       <c r="D737" t="s">
         <v>9</v>
@@ -13914,10 +13914,10 @@
     </row>
     <row r="738" spans="1:4">
       <c r="A738" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B738" t="s">
         <v>1477</v>
-      </c>
-      <c r="B738" t="s">
-        <v>1478</v>
       </c>
       <c r="D738" t="s">
         <v>9</v>
@@ -13925,10 +13925,10 @@
     </row>
     <row r="739" spans="1:4">
       <c r="A739" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B739" t="s">
         <v>1479</v>
-      </c>
-      <c r="B739" t="s">
-        <v>1480</v>
       </c>
       <c r="D739" t="s">
         <v>9</v>
@@ -13936,10 +13936,10 @@
     </row>
     <row r="740" spans="1:4">
       <c r="A740" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B740" t="s">
         <v>1481</v>
-      </c>
-      <c r="B740" t="s">
-        <v>1482</v>
       </c>
       <c r="D740" t="s">
         <v>9</v>
@@ -13947,10 +13947,10 @@
     </row>
     <row r="741" spans="1:4">
       <c r="A741" t="s">
+        <v>1482</v>
+      </c>
+      <c r="B741" t="s">
         <v>1483</v>
-      </c>
-      <c r="B741" t="s">
-        <v>1484</v>
       </c>
       <c r="D741" t="s">
         <v>9</v>
@@ -13958,10 +13958,10 @@
     </row>
     <row r="742" spans="1:4">
       <c r="A742" t="s">
+        <v>1484</v>
+      </c>
+      <c r="B742" t="s">
         <v>1485</v>
-      </c>
-      <c r="B742" t="s">
-        <v>1486</v>
       </c>
       <c r="D742" t="s">
         <v>9</v>
@@ -13969,10 +13969,10 @@
     </row>
     <row r="743" spans="1:4">
       <c r="A743" t="s">
+        <v>1486</v>
+      </c>
+      <c r="B743" t="s">
         <v>1487</v>
-      </c>
-      <c r="B743" t="s">
-        <v>1488</v>
       </c>
       <c r="D743" t="s">
         <v>9</v>
@@ -13980,10 +13980,10 @@
     </row>
     <row r="744" spans="1:4">
       <c r="A744" t="s">
+        <v>1488</v>
+      </c>
+      <c r="B744" t="s">
         <v>1489</v>
-      </c>
-      <c r="B744" t="s">
-        <v>1490</v>
       </c>
       <c r="D744" t="s">
         <v>9</v>
@@ -13991,10 +13991,10 @@
     </row>
     <row r="745" spans="1:4">
       <c r="A745" t="s">
+        <v>1490</v>
+      </c>
+      <c r="B745" t="s">
         <v>1491</v>
-      </c>
-      <c r="B745" t="s">
-        <v>1492</v>
       </c>
       <c r="D745" t="s">
         <v>9</v>
@@ -14002,10 +14002,10 @@
     </row>
     <row r="746" spans="1:4">
       <c r="A746" t="s">
+        <v>1492</v>
+      </c>
+      <c r="B746" t="s">
         <v>1493</v>
-      </c>
-      <c r="B746" t="s">
-        <v>1494</v>
       </c>
       <c r="D746" t="s">
         <v>9</v>
@@ -14013,10 +14013,10 @@
     </row>
     <row r="747" spans="1:4">
       <c r="A747" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B747" t="s">
         <v>1495</v>
-      </c>
-      <c r="B747" t="s">
-        <v>1496</v>
       </c>
       <c r="D747" t="s">
         <v>9</v>
@@ -14024,10 +14024,10 @@
     </row>
     <row r="748" spans="1:4">
       <c r="A748" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B748" t="s">
         <v>1497</v>
-      </c>
-      <c r="B748" t="s">
-        <v>1498</v>
       </c>
       <c r="D748" t="s">
         <v>9</v>
@@ -14035,10 +14035,10 @@
     </row>
     <row r="749" spans="1:4">
       <c r="A749" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B749" t="s">
         <v>1499</v>
-      </c>
-      <c r="B749" t="s">
-        <v>1500</v>
       </c>
       <c r="D749" t="s">
         <v>9</v>
@@ -14046,10 +14046,10 @@
     </row>
     <row r="750" spans="1:4">
       <c r="A750" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B750" t="s">
         <v>1501</v>
-      </c>
-      <c r="B750" t="s">
-        <v>1502</v>
       </c>
       <c r="D750" t="s">
         <v>9</v>
@@ -14057,10 +14057,10 @@
     </row>
     <row r="751" spans="1:4">
       <c r="A751" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B751" t="s">
         <v>1503</v>
-      </c>
-      <c r="B751" t="s">
-        <v>1504</v>
       </c>
       <c r="D751" t="s">
         <v>9</v>
@@ -14068,10 +14068,10 @@
     </row>
     <row r="752" spans="1:4">
       <c r="A752" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B752" t="s">
         <v>1505</v>
-      </c>
-      <c r="B752" t="s">
-        <v>1506</v>
       </c>
       <c r="D752" t="s">
         <v>9</v>
@@ -14079,10 +14079,10 @@
     </row>
     <row r="753" spans="1:4">
       <c r="A753" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B753" t="s">
         <v>1507</v>
-      </c>
-      <c r="B753" t="s">
-        <v>1508</v>
       </c>
       <c r="D753" t="s">
         <v>9</v>
@@ -14090,10 +14090,10 @@
     </row>
     <row r="754" spans="1:4">
       <c r="A754" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B754" t="s">
         <v>1509</v>
-      </c>
-      <c r="B754" t="s">
-        <v>1510</v>
       </c>
       <c r="D754" t="s">
         <v>9</v>
@@ -14101,10 +14101,10 @@
     </row>
     <row r="755" spans="1:4">
       <c r="A755" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B755" t="s">
         <v>1511</v>
-      </c>
-      <c r="B755" t="s">
-        <v>1512</v>
       </c>
       <c r="D755" t="s">
         <v>9</v>
@@ -14112,10 +14112,10 @@
     </row>
     <row r="756" spans="1:4">
       <c r="A756" t="s">
+        <v>1512</v>
+      </c>
+      <c r="B756" t="s">
         <v>1513</v>
-      </c>
-      <c r="B756" t="s">
-        <v>1514</v>
       </c>
       <c r="D756" t="s">
         <v>9</v>
@@ -14123,10 +14123,10 @@
     </row>
     <row r="757" spans="1:4">
       <c r="A757" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B757" t="s">
         <v>1515</v>
-      </c>
-      <c r="B757" t="s">
-        <v>1516</v>
       </c>
       <c r="D757" t="s">
         <v>9</v>
@@ -14134,10 +14134,10 @@
     </row>
     <row r="758" spans="1:4">
       <c r="A758" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B758" t="s">
         <v>1517</v>
-      </c>
-      <c r="B758" t="s">
-        <v>1518</v>
       </c>
       <c r="D758" t="s">
         <v>9</v>
@@ -14145,10 +14145,10 @@
     </row>
     <row r="759" spans="1:4">
       <c r="A759" t="s">
+        <v>1518</v>
+      </c>
+      <c r="B759" t="s">
         <v>1519</v>
-      </c>
-      <c r="B759" t="s">
-        <v>1520</v>
       </c>
       <c r="D759" t="s">
         <v>9</v>
@@ -14156,10 +14156,10 @@
     </row>
     <row r="760" spans="1:4">
       <c r="A760" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B760" t="s">
         <v>1521</v>
-      </c>
-      <c r="B760" t="s">
-        <v>1522</v>
       </c>
       <c r="D760" t="s">
         <v>9</v>
@@ -14167,10 +14167,10 @@
     </row>
     <row r="761" spans="1:4">
       <c r="A761" t="s">
+        <v>1522</v>
+      </c>
+      <c r="B761" t="s">
         <v>1523</v>
-      </c>
-      <c r="B761" t="s">
-        <v>1524</v>
       </c>
       <c r="D761" t="s">
         <v>9</v>
@@ -14178,10 +14178,10 @@
     </row>
     <row r="762" spans="1:4">
       <c r="A762" t="s">
+        <v>1524</v>
+      </c>
+      <c r="B762" t="s">
         <v>1525</v>
-      </c>
-      <c r="B762" t="s">
-        <v>1526</v>
       </c>
       <c r="D762" t="s">
         <v>9</v>
@@ -14189,10 +14189,10 @@
     </row>
     <row r="763" spans="1:4">
       <c r="A763" t="s">
+        <v>1526</v>
+      </c>
+      <c r="B763" t="s">
         <v>1527</v>
-      </c>
-      <c r="B763" t="s">
-        <v>1528</v>
       </c>
       <c r="D763" t="s">
         <v>9</v>
@@ -14200,10 +14200,10 @@
     </row>
     <row r="764" spans="1:4">
       <c r="A764" t="s">
+        <v>1528</v>
+      </c>
+      <c r="B764" t="s">
         <v>1529</v>
-      </c>
-      <c r="B764" t="s">
-        <v>1530</v>
       </c>
       <c r="D764" t="s">
         <v>9</v>
@@ -14211,10 +14211,10 @@
     </row>
     <row r="765" spans="1:4">
       <c r="A765" t="s">
+        <v>1530</v>
+      </c>
+      <c r="B765" t="s">
         <v>1531</v>
-      </c>
-      <c r="B765" t="s">
-        <v>1532</v>
       </c>
       <c r="D765" t="s">
         <v>9</v>
@@ -14222,10 +14222,10 @@
     </row>
     <row r="766" spans="1:4">
       <c r="A766" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B766" t="s">
         <v>1533</v>
-      </c>
-      <c r="B766" t="s">
-        <v>1534</v>
       </c>
       <c r="D766" t="s">
         <v>9</v>
@@ -14233,10 +14233,10 @@
     </row>
     <row r="767" spans="1:4">
       <c r="A767" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B767" t="s">
         <v>1535</v>
-      </c>
-      <c r="B767" t="s">
-        <v>1536</v>
       </c>
       <c r="D767" t="s">
         <v>9</v>
@@ -14244,10 +14244,10 @@
     </row>
     <row r="768" spans="1:4">
       <c r="A768" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B768" t="s">
         <v>1537</v>
-      </c>
-      <c r="B768" t="s">
-        <v>1538</v>
       </c>
       <c r="D768" t="s">
         <v>9</v>
@@ -14255,10 +14255,10 @@
     </row>
     <row r="769" spans="1:4">
       <c r="A769" t="s">
+        <v>1538</v>
+      </c>
+      <c r="B769" t="s">
         <v>1539</v>
-      </c>
-      <c r="B769" t="s">
-        <v>1540</v>
       </c>
       <c r="D769" t="s">
         <v>9</v>
@@ -14266,10 +14266,10 @@
     </row>
     <row r="770" spans="1:4">
       <c r="A770" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B770" t="s">
         <v>1541</v>
-      </c>
-      <c r="B770" t="s">
-        <v>1542</v>
       </c>
       <c r="D770" t="s">
         <v>9</v>
@@ -14277,10 +14277,10 @@
     </row>
     <row r="771" spans="1:4">
       <c r="A771" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B771" t="s">
         <v>1543</v>
-      </c>
-      <c r="B771" t="s">
-        <v>1544</v>
       </c>
       <c r="D771" t="s">
         <v>9</v>
@@ -14288,10 +14288,10 @@
     </row>
     <row r="772" spans="1:4">
       <c r="A772" t="s">
+        <v>1544</v>
+      </c>
+      <c r="B772" t="s">
         <v>1545</v>
-      </c>
-      <c r="B772" t="s">
-        <v>1546</v>
       </c>
       <c r="D772" t="s">
         <v>9</v>
@@ -14299,10 +14299,10 @@
     </row>
     <row r="773" spans="1:4">
       <c r="A773" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B773" t="s">
         <v>1547</v>
-      </c>
-      <c r="B773" t="s">
-        <v>1548</v>
       </c>
       <c r="D773" t="s">
         <v>9</v>
@@ -14310,10 +14310,10 @@
     </row>
     <row r="774" spans="1:4">
       <c r="A774" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B774" t="s">
         <v>1549</v>
-      </c>
-      <c r="B774" t="s">
-        <v>1550</v>
       </c>
       <c r="D774" t="s">
         <v>9</v>
@@ -14321,10 +14321,10 @@
     </row>
     <row r="775" spans="1:4">
       <c r="A775" t="s">
+        <v>1550</v>
+      </c>
+      <c r="B775" t="s">
         <v>1551</v>
-      </c>
-      <c r="B775" t="s">
-        <v>1552</v>
       </c>
       <c r="D775" t="s">
         <v>9</v>
@@ -14332,10 +14332,10 @@
     </row>
     <row r="776" spans="1:4">
       <c r="A776" t="s">
+        <v>1552</v>
+      </c>
+      <c r="B776" t="s">
         <v>1553</v>
-      </c>
-      <c r="B776" t="s">
-        <v>1554</v>
       </c>
       <c r="D776" t="s">
         <v>9</v>
@@ -14343,10 +14343,10 @@
     </row>
     <row r="777" spans="1:4">
       <c r="A777" t="s">
+        <v>1554</v>
+      </c>
+      <c r="B777" t="s">
         <v>1555</v>
-      </c>
-      <c r="B777" t="s">
-        <v>1556</v>
       </c>
       <c r="D777" t="s">
         <v>9</v>
@@ -14354,10 +14354,10 @@
     </row>
     <row r="778" spans="1:4">
       <c r="A778" t="s">
+        <v>1556</v>
+      </c>
+      <c r="B778" t="s">
         <v>1557</v>
-      </c>
-      <c r="B778" t="s">
-        <v>1558</v>
       </c>
       <c r="D778" t="s">
         <v>9</v>
@@ -14365,10 +14365,10 @@
     </row>
     <row r="779" spans="1:4">
       <c r="A779" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B779" t="s">
         <v>1559</v>
-      </c>
-      <c r="B779" t="s">
-        <v>1560</v>
       </c>
       <c r="D779" t="s">
         <v>9</v>
@@ -14376,10 +14376,10 @@
     </row>
     <row r="780" spans="1:4">
       <c r="A780" t="s">
+        <v>1560</v>
+      </c>
+      <c r="B780" t="s">
         <v>1561</v>
-      </c>
-      <c r="B780" t="s">
-        <v>1562</v>
       </c>
       <c r="D780" t="s">
         <v>9</v>
@@ -14387,10 +14387,10 @@
     </row>
     <row r="781" spans="1:4">
       <c r="A781" t="s">
+        <v>1562</v>
+      </c>
+      <c r="B781" t="s">
         <v>1563</v>
-      </c>
-      <c r="B781" t="s">
-        <v>1564</v>
       </c>
       <c r="D781" t="s">
         <v>9</v>
@@ -14398,10 +14398,10 @@
     </row>
     <row r="782" spans="1:4">
       <c r="A782" t="s">
+        <v>1564</v>
+      </c>
+      <c r="B782" t="s">
         <v>1565</v>
-      </c>
-      <c r="B782" t="s">
-        <v>1566</v>
       </c>
       <c r="D782" t="s">
         <v>9</v>
@@ -14409,10 +14409,10 @@
     </row>
     <row r="783" spans="1:4">
       <c r="A783" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B783" t="s">
         <v>1567</v>
-      </c>
-      <c r="B783" t="s">
-        <v>1568</v>
       </c>
       <c r="D783" t="s">
         <v>9</v>
@@ -14420,10 +14420,10 @@
     </row>
     <row r="784" spans="1:4">
       <c r="A784" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B784" t="s">
         <v>1569</v>
-      </c>
-      <c r="B784" t="s">
-        <v>1570</v>
       </c>
       <c r="D784" t="s">
         <v>9</v>
@@ -14431,10 +14431,10 @@
     </row>
     <row r="785" spans="1:4">
       <c r="A785" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B785" t="s">
         <v>1571</v>
-      </c>
-      <c r="B785" t="s">
-        <v>1572</v>
       </c>
       <c r="D785" t="s">
         <v>9</v>
@@ -14442,10 +14442,10 @@
     </row>
     <row r="786" spans="1:4">
       <c r="A786" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B786" t="s">
         <v>1573</v>
-      </c>
-      <c r="B786" t="s">
-        <v>1574</v>
       </c>
       <c r="D786" t="s">
         <v>9</v>
@@ -14453,10 +14453,10 @@
     </row>
     <row r="787" spans="1:4">
       <c r="A787" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B787" t="s">
         <v>1575</v>
-      </c>
-      <c r="B787" t="s">
-        <v>1576</v>
       </c>
       <c r="D787" t="s">
         <v>9</v>
@@ -14464,10 +14464,10 @@
     </row>
     <row r="788" spans="1:4">
       <c r="A788" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B788" t="s">
         <v>1577</v>
-      </c>
-      <c r="B788" t="s">
-        <v>1578</v>
       </c>
       <c r="D788" t="s">
         <v>9</v>
@@ -14475,10 +14475,10 @@
     </row>
     <row r="789" spans="1:4">
       <c r="A789" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B789" t="s">
         <v>1579</v>
-      </c>
-      <c r="B789" t="s">
-        <v>1580</v>
       </c>
       <c r="D789" t="s">
         <v>9</v>
@@ -14486,10 +14486,10 @@
     </row>
     <row r="790" spans="1:4">
       <c r="A790" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B790" t="s">
         <v>1581</v>
-      </c>
-      <c r="B790" t="s">
-        <v>1582</v>
       </c>
       <c r="D790" t="s">
         <v>9</v>
@@ -14497,10 +14497,10 @@
     </row>
     <row r="791" spans="1:4">
       <c r="A791" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B791" t="s">
         <v>1583</v>
-      </c>
-      <c r="B791" t="s">
-        <v>1584</v>
       </c>
       <c r="D791" t="s">
         <v>9</v>
@@ -14508,10 +14508,10 @@
     </row>
     <row r="792" spans="1:4">
       <c r="A792" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B792" t="s">
         <v>1585</v>
-      </c>
-      <c r="B792" t="s">
-        <v>1586</v>
       </c>
       <c r="D792" t="s">
         <v>9</v>
@@ -14519,10 +14519,10 @@
     </row>
     <row r="793" spans="1:4">
       <c r="A793" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B793" t="s">
         <v>1587</v>
-      </c>
-      <c r="B793" t="s">
-        <v>1588</v>
       </c>
       <c r="D793" t="s">
         <v>9</v>
@@ -14530,10 +14530,10 @@
     </row>
     <row r="794" spans="1:4">
       <c r="A794" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B794" t="s">
         <v>1589</v>
-      </c>
-      <c r="B794" t="s">
-        <v>1590</v>
       </c>
       <c r="D794" t="s">
         <v>9</v>
@@ -14541,10 +14541,10 @@
     </row>
     <row r="795" spans="1:4">
       <c r="A795" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B795" t="s">
         <v>1591</v>
-      </c>
-      <c r="B795" t="s">
-        <v>1592</v>
       </c>
       <c r="D795" t="s">
         <v>9</v>
@@ -14552,10 +14552,10 @@
     </row>
     <row r="796" spans="1:4">
       <c r="A796" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B796" t="s">
         <v>1593</v>
-      </c>
-      <c r="B796" t="s">
-        <v>1594</v>
       </c>
       <c r="D796" t="s">
         <v>9</v>
@@ -14563,10 +14563,10 @@
     </row>
     <row r="797" spans="1:4">
       <c r="A797" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B797" t="s">
         <v>1595</v>
-      </c>
-      <c r="B797" t="s">
-        <v>1596</v>
       </c>
       <c r="D797" t="s">
         <v>9</v>
@@ -14574,10 +14574,10 @@
     </row>
     <row r="798" spans="1:4">
       <c r="A798" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B798" t="s">
         <v>1597</v>
-      </c>
-      <c r="B798" t="s">
-        <v>1598</v>
       </c>
       <c r="D798" t="s">
         <v>9</v>
@@ -14585,10 +14585,10 @@
     </row>
     <row r="799" spans="1:4">
       <c r="A799" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B799" t="s">
         <v>1599</v>
-      </c>
-      <c r="B799" t="s">
-        <v>1600</v>
       </c>
       <c r="D799" t="s">
         <v>9</v>
@@ -14596,10 +14596,10 @@
     </row>
     <row r="800" spans="1:4">
       <c r="A800" t="s">
+        <v>1600</v>
+      </c>
+      <c r="B800" t="s">
         <v>1601</v>
-      </c>
-      <c r="B800" t="s">
-        <v>1602</v>
       </c>
       <c r="D800" t="s">
         <v>9</v>
@@ -14607,10 +14607,10 @@
     </row>
     <row r="801" spans="1:4">
       <c r="A801" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B801" t="s">
         <v>1603</v>
-      </c>
-      <c r="B801" t="s">
-        <v>1604</v>
       </c>
       <c r="D801" t="s">
         <v>9</v>
@@ -14618,10 +14618,10 @@
     </row>
     <row r="802" spans="1:4">
       <c r="A802" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B802" t="s">
         <v>1605</v>
-      </c>
-      <c r="B802" t="s">
-        <v>1606</v>
       </c>
       <c r="D802" t="s">
         <v>9</v>
@@ -14629,10 +14629,10 @@
     </row>
     <row r="803" spans="1:4">
       <c r="A803" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B803" t="s">
         <v>1607</v>
-      </c>
-      <c r="B803" t="s">
-        <v>1608</v>
       </c>
       <c r="D803" t="s">
         <v>9</v>
@@ -14640,10 +14640,10 @@
     </row>
     <row r="804" spans="1:4">
       <c r="A804" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B804" t="s">
         <v>1609</v>
-      </c>
-      <c r="B804" t="s">
-        <v>1610</v>
       </c>
       <c r="D804" t="s">
         <v>9</v>
@@ -14651,10 +14651,10 @@
     </row>
     <row r="805" spans="1:4">
       <c r="A805" t="s">
+        <v>1610</v>
+      </c>
+      <c r="B805" t="s">
         <v>1611</v>
-      </c>
-      <c r="B805" t="s">
-        <v>1612</v>
       </c>
       <c r="D805" t="s">
         <v>9</v>
@@ -14662,10 +14662,10 @@
     </row>
     <row r="806" spans="1:4">
       <c r="A806" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B806" t="s">
         <v>1613</v>
-      </c>
-      <c r="B806" t="s">
-        <v>1614</v>
       </c>
       <c r="D806" t="s">
         <v>9</v>
@@ -14673,10 +14673,10 @@
     </row>
     <row r="807" spans="1:4">
       <c r="A807" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B807" t="s">
         <v>1615</v>
-      </c>
-      <c r="B807" t="s">
-        <v>1616</v>
       </c>
       <c r="D807" t="s">
         <v>9</v>
@@ -14684,10 +14684,10 @@
     </row>
     <row r="808" spans="1:4">
       <c r="A808" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B808" t="s">
         <v>1617</v>
-      </c>
-      <c r="B808" t="s">
-        <v>1618</v>
       </c>
       <c r="D808" t="s">
         <v>9</v>
@@ -14695,10 +14695,10 @@
     </row>
     <row r="809" spans="1:4">
       <c r="A809" t="s">
+        <v>1618</v>
+      </c>
+      <c r="B809" t="s">
         <v>1619</v>
-      </c>
-      <c r="B809" t="s">
-        <v>1620</v>
       </c>
       <c r="D809" t="s">
         <v>9</v>
@@ -14706,10 +14706,10 @@
     </row>
     <row r="810" spans="1:4">
       <c r="A810" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B810" t="s">
         <v>1621</v>
-      </c>
-      <c r="B810" t="s">
-        <v>1622</v>
       </c>
       <c r="D810" t="s">
         <v>9</v>
@@ -14717,10 +14717,10 @@
     </row>
     <row r="811" spans="1:4">
       <c r="A811" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B811" t="s">
         <v>1623</v>
-      </c>
-      <c r="B811" t="s">
-        <v>1624</v>
       </c>
       <c r="D811" t="s">
         <v>9</v>
@@ -14728,10 +14728,10 @@
     </row>
     <row r="812" spans="1:4">
       <c r="A812" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B812" t="s">
         <v>1625</v>
-      </c>
-      <c r="B812" t="s">
-        <v>1626</v>
       </c>
       <c r="D812" t="s">
         <v>9</v>
@@ -14739,10 +14739,10 @@
     </row>
     <row r="813" spans="1:4">
       <c r="A813" t="s">
+        <v>1626</v>
+      </c>
+      <c r="B813" t="s">
         <v>1627</v>
-      </c>
-      <c r="B813" t="s">
-        <v>1628</v>
       </c>
       <c r="D813" t="s">
         <v>9</v>
@@ -14750,10 +14750,10 @@
     </row>
     <row r="814" spans="1:4">
       <c r="A814" t="s">
+        <v>1628</v>
+      </c>
+      <c r="B814" t="s">
         <v>1629</v>
-      </c>
-      <c r="B814" t="s">
-        <v>1630</v>
       </c>
       <c r="D814" t="s">
         <v>9</v>
@@ -14761,10 +14761,10 @@
     </row>
     <row r="815" spans="1:4">
       <c r="A815" t="s">
+        <v>1630</v>
+      </c>
+      <c r="B815" t="s">
         <v>1631</v>
-      </c>
-      <c r="B815" t="s">
-        <v>1632</v>
       </c>
       <c r="D815" t="s">
         <v>9</v>
@@ -14772,10 +14772,10 @@
     </row>
     <row r="816" spans="1:4">
       <c r="A816" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B816" t="s">
         <v>1633</v>
-      </c>
-      <c r="B816" t="s">
-        <v>1634</v>
       </c>
       <c r="D816" t="s">
         <v>9</v>
@@ -14783,10 +14783,10 @@
     </row>
     <row r="817" spans="1:4">
       <c r="A817" t="s">
+        <v>1634</v>
+      </c>
+      <c r="B817" t="s">
         <v>1635</v>
-      </c>
-      <c r="B817" t="s">
-        <v>1636</v>
       </c>
       <c r="D817" t="s">
         <v>9</v>
@@ -14794,10 +14794,10 @@
     </row>
     <row r="818" spans="1:4">
       <c r="A818" t="s">
+        <v>1636</v>
+      </c>
+      <c r="B818" t="s">
         <v>1637</v>
-      </c>
-      <c r="B818" t="s">
-        <v>1638</v>
       </c>
       <c r="D818" t="s">
         <v>9</v>
@@ -14805,10 +14805,10 @@
     </row>
     <row r="819" spans="1:4">
       <c r="A819" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B819" t="s">
         <v>1639</v>
-      </c>
-      <c r="B819" t="s">
-        <v>1640</v>
       </c>
       <c r="D819" t="s">
         <v>9</v>
@@ -14816,10 +14816,10 @@
     </row>
     <row r="820" spans="1:4">
       <c r="A820" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B820" t="s">
         <v>1641</v>
-      </c>
-      <c r="B820" t="s">
-        <v>1642</v>
       </c>
       <c r="D820" t="s">
         <v>9</v>
@@ -14827,10 +14827,10 @@
     </row>
     <row r="821" spans="1:4">
       <c r="A821" t="s">
+        <v>1642</v>
+      </c>
+      <c r="B821" t="s">
         <v>1643</v>
-      </c>
-      <c r="B821" t="s">
-        <v>1644</v>
       </c>
       <c r="D821" t="s">
         <v>9</v>
@@ -14838,10 +14838,10 @@
     </row>
     <row r="822" spans="1:4">
       <c r="A822" t="s">
+        <v>1644</v>
+      </c>
+      <c r="B822" t="s">
         <v>1645</v>
-      </c>
-      <c r="B822" t="s">
-        <v>1646</v>
       </c>
       <c r="D822" t="s">
         <v>9</v>
@@ -14849,10 +14849,10 @@
     </row>
     <row r="823" spans="1:4">
       <c r="A823" t="s">
+        <v>1646</v>
+      </c>
+      <c r="B823" t="s">
         <v>1647</v>
-      </c>
-      <c r="B823" t="s">
-        <v>1648</v>
       </c>
       <c r="D823" t="s">
         <v>9</v>
@@ -14860,10 +14860,10 @@
     </row>
     <row r="824" spans="1:4">
       <c r="A824" t="s">
+        <v>1648</v>
+      </c>
+      <c r="B824" t="s">
         <v>1649</v>
-      </c>
-      <c r="B824" t="s">
-        <v>1650</v>
       </c>
       <c r="D824" t="s">
         <v>9</v>
@@ -14871,10 +14871,10 @@
     </row>
     <row r="825" spans="1:4">
       <c r="A825" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B825" t="s">
         <v>1651</v>
-      </c>
-      <c r="B825" t="s">
-        <v>1652</v>
       </c>
       <c r="D825" t="s">
         <v>9</v>
@@ -14882,10 +14882,10 @@
     </row>
     <row r="826" spans="1:4">
       <c r="A826" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B826" t="s">
         <v>1653</v>
-      </c>
-      <c r="B826" t="s">
-        <v>1654</v>
       </c>
       <c r="D826" t="s">
         <v>9</v>
@@ -14893,10 +14893,10 @@
     </row>
     <row r="827" spans="1:4">
       <c r="A827" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B827" t="s">
         <v>1655</v>
-      </c>
-      <c r="B827" t="s">
-        <v>1656</v>
       </c>
       <c r="D827" t="s">
         <v>9</v>
@@ -14904,10 +14904,10 @@
     </row>
     <row r="828" spans="1:4">
       <c r="A828" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B828" t="s">
         <v>1657</v>
-      </c>
-      <c r="B828" t="s">
-        <v>1658</v>
       </c>
       <c r="D828" t="s">
         <v>9</v>
@@ -14915,10 +14915,10 @@
     </row>
     <row r="829" spans="1:4">
       <c r="A829" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B829" t="s">
         <v>1659</v>
-      </c>
-      <c r="B829" t="s">
-        <v>1660</v>
       </c>
       <c r="D829" t="s">
         <v>9</v>
@@ -14926,10 +14926,10 @@
     </row>
     <row r="830" spans="1:4">
       <c r="A830" t="s">
+        <v>1660</v>
+      </c>
+      <c r="B830" t="s">
         <v>1661</v>
-      </c>
-      <c r="B830" t="s">
-        <v>1662</v>
       </c>
       <c r="D830" t="s">
         <v>9</v>
@@ -14937,10 +14937,10 @@
     </row>
     <row r="831" spans="1:4">
       <c r="A831" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B831" t="s">
         <v>1663</v>
-      </c>
-      <c r="B831" t="s">
-        <v>1664</v>
       </c>
       <c r="D831" t="s">
         <v>9</v>
@@ -14948,10 +14948,10 @@
     </row>
     <row r="832" spans="1:4">
       <c r="A832" t="s">
+        <v>1664</v>
+      </c>
+      <c r="B832" t="s">
         <v>1665</v>
-      </c>
-      <c r="B832" t="s">
-        <v>1666</v>
       </c>
       <c r="D832" t="s">
         <v>9</v>
@@ -14959,10 +14959,10 @@
     </row>
     <row r="833" spans="1:4">
       <c r="A833" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B833" t="s">
         <v>1667</v>
-      </c>
-      <c r="B833" t="s">
-        <v>1668</v>
       </c>
       <c r="D833" t="s">
         <v>9</v>
@@ -14970,10 +14970,10 @@
     </row>
     <row r="834" spans="1:4">
       <c r="A834" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B834" t="s">
         <v>1669</v>
-      </c>
-      <c r="B834" t="s">
-        <v>1670</v>
       </c>
       <c r="D834" t="s">
         <v>9</v>
@@ -14981,10 +14981,10 @@
     </row>
     <row r="835" spans="1:4">
       <c r="A835" t="s">
+        <v>1670</v>
+      </c>
+      <c r="B835" t="s">
         <v>1671</v>
-      </c>
-      <c r="B835" t="s">
-        <v>1672</v>
       </c>
       <c r="D835" t="s">
         <v>9</v>
@@ -14992,10 +14992,10 @@
     </row>
     <row r="836" spans="1:4">
       <c r="A836" t="s">
+        <v>1672</v>
+      </c>
+      <c r="B836" t="s">
         <v>1673</v>
-      </c>
-      <c r="B836" t="s">
-        <v>1674</v>
       </c>
       <c r="D836" t="s">
         <v>9</v>
@@ -15003,10 +15003,10 @@
     </row>
     <row r="837" spans="1:4">
       <c r="A837" t="s">
+        <v>1674</v>
+      </c>
+      <c r="B837" t="s">
         <v>1675</v>
-      </c>
-      <c r="B837" t="s">
-        <v>1676</v>
       </c>
       <c r="D837" t="s">
         <v>9</v>
@@ -15014,10 +15014,10 @@
     </row>
     <row r="838" spans="1:4">
       <c r="A838" t="s">
+        <v>1676</v>
+      </c>
+      <c r="B838" t="s">
         <v>1677</v>
-      </c>
-      <c r="B838" t="s">
-        <v>1678</v>
       </c>
       <c r="D838" t="s">
         <v>9</v>
@@ -15025,10 +15025,10 @@
     </row>
     <row r="839" spans="1:4">
       <c r="A839" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B839" t="s">
         <v>1679</v>
-      </c>
-      <c r="B839" t="s">
-        <v>1680</v>
       </c>
       <c r="D839" t="s">
         <v>9</v>
@@ -15036,10 +15036,10 @@
     </row>
     <row r="840" spans="1:4">
       <c r="A840" t="s">
+        <v>1680</v>
+      </c>
+      <c r="B840" t="s">
         <v>1681</v>
-      </c>
-      <c r="B840" t="s">
-        <v>1682</v>
       </c>
       <c r="D840" t="s">
         <v>9</v>
@@ -15047,10 +15047,10 @@
     </row>
     <row r="841" spans="1:4">
       <c r="A841" t="s">
+        <v>1682</v>
+      </c>
+      <c r="B841" t="s">
         <v>1683</v>
-      </c>
-      <c r="B841" t="s">
-        <v>1684</v>
       </c>
       <c r="D841" t="s">
         <v>9</v>
@@ -15058,10 +15058,10 @@
     </row>
     <row r="842" spans="1:4">
       <c r="A842" t="s">
+        <v>1684</v>
+      </c>
+      <c r="B842" t="s">
         <v>1685</v>
-      </c>
-      <c r="B842" t="s">
-        <v>1686</v>
       </c>
       <c r="D842" t="s">
         <v>9</v>
@@ -15069,10 +15069,10 @@
     </row>
     <row r="843" spans="1:4">
       <c r="A843" t="s">
+        <v>1686</v>
+      </c>
+      <c r="B843" t="s">
         <v>1687</v>
-      </c>
-      <c r="B843" t="s">
-        <v>1688</v>
       </c>
       <c r="D843" t="s">
         <v>9</v>
@@ -15080,10 +15080,10 @@
     </row>
     <row r="844" spans="1:4">
       <c r="A844" t="s">
+        <v>1688</v>
+      </c>
+      <c r="B844" t="s">
         <v>1689</v>
-      </c>
-      <c r="B844" t="s">
-        <v>1690</v>
       </c>
       <c r="D844" t="s">
         <v>9</v>
@@ -15091,10 +15091,10 @@
     </row>
     <row r="845" spans="1:4">
       <c r="A845" t="s">
+        <v>1690</v>
+      </c>
+      <c r="B845" t="s">
         <v>1691</v>
-      </c>
-      <c r="B845" t="s">
-        <v>1692</v>
       </c>
       <c r="D845" t="s">
         <v>9</v>
@@ -15102,10 +15102,10 @@
     </row>
     <row r="846" spans="1:4">
       <c r="A846" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B846" t="s">
         <v>1693</v>
-      </c>
-      <c r="B846" t="s">
-        <v>1694</v>
       </c>
       <c r="D846" t="s">
         <v>9</v>
@@ -15113,10 +15113,10 @@
     </row>
     <row r="847" spans="1:4">
       <c r="A847" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B847" t="s">
         <v>1695</v>
-      </c>
-      <c r="B847" t="s">
-        <v>1696</v>
       </c>
       <c r="D847" t="s">
         <v>9</v>
@@ -15124,10 +15124,10 @@
     </row>
     <row r="848" spans="1:4">
       <c r="A848" t="s">
+        <v>1696</v>
+      </c>
+      <c r="B848" t="s">
         <v>1697</v>
-      </c>
-      <c r="B848" t="s">
-        <v>1698</v>
       </c>
       <c r="D848" t="s">
         <v>9</v>
@@ -15135,10 +15135,10 @@
     </row>
     <row r="849" spans="1:4">
       <c r="A849" t="s">
+        <v>1698</v>
+      </c>
+      <c r="B849" t="s">
         <v>1699</v>
-      </c>
-      <c r="B849" t="s">
-        <v>1700</v>
       </c>
       <c r="D849" t="s">
         <v>9</v>
@@ -15146,10 +15146,10 @@
     </row>
     <row r="850" spans="1:4">
       <c r="A850" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B850" t="s">
         <v>1701</v>
-      </c>
-      <c r="B850" t="s">
-        <v>1702</v>
       </c>
       <c r="D850" t="s">
         <v>9</v>
@@ -15157,10 +15157,10 @@
     </row>
     <row r="851" spans="1:4">
       <c r="A851" t="s">
+        <v>1702</v>
+      </c>
+      <c r="B851" t="s">
         <v>1703</v>
-      </c>
-      <c r="B851" t="s">
-        <v>1704</v>
       </c>
       <c r="D851" t="s">
         <v>9</v>
@@ -15168,10 +15168,10 @@
     </row>
     <row r="852" spans="1:4">
       <c r="A852" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B852" t="s">
         <v>1705</v>
-      </c>
-      <c r="B852" t="s">
-        <v>1706</v>
       </c>
       <c r="D852" t="s">
         <v>9</v>
@@ -15179,10 +15179,10 @@
     </row>
     <row r="853" spans="1:4">
       <c r="A853" t="s">
+        <v>1706</v>
+      </c>
+      <c r="B853" t="s">
         <v>1707</v>
-      </c>
-      <c r="B853" t="s">
-        <v>1708</v>
       </c>
       <c r="D853" t="s">
         <v>9</v>
@@ -15190,10 +15190,10 @@
     </row>
     <row r="854" spans="1:4">
       <c r="A854" t="s">
+        <v>1708</v>
+      </c>
+      <c r="B854" t="s">
         <v>1709</v>
-      </c>
-      <c r="B854" t="s">
-        <v>1710</v>
       </c>
       <c r="D854" t="s">
         <v>9</v>
@@ -15201,10 +15201,10 @@
     </row>
     <row r="855" spans="1:4">
       <c r="A855" t="s">
+        <v>1710</v>
+      </c>
+      <c r="B855" t="s">
         <v>1711</v>
-      </c>
-      <c r="B855" t="s">
-        <v>1712</v>
       </c>
       <c r="D855" t="s">
         <v>9</v>
@@ -15212,10 +15212,10 @@
     </row>
     <row r="856" spans="1:4">
       <c r="A856" t="s">
+        <v>1712</v>
+      </c>
+      <c r="B856" t="s">
         <v>1713</v>
-      </c>
-      <c r="B856" t="s">
-        <v>1714</v>
       </c>
       <c r="D856" t="s">
         <v>9</v>
@@ -15223,10 +15223,10 @@
     </row>
     <row r="857" spans="1:4">
       <c r="A857" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B857" t="s">
         <v>1715</v>
-      </c>
-      <c r="B857" t="s">
-        <v>1716</v>
       </c>
       <c r="D857" t="s">
         <v>9</v>
@@ -15234,10 +15234,10 @@
     </row>
     <row r="858" spans="1:4">
       <c r="A858" t="s">
+        <v>1716</v>
+      </c>
+      <c r="B858" t="s">
         <v>1717</v>
-      </c>
-      <c r="B858" t="s">
-        <v>1718</v>
       </c>
       <c r="D858" t="s">
         <v>9</v>
@@ -15245,10 +15245,10 @@
     </row>
     <row r="859" spans="1:4">
       <c r="A859" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B859" t="s">
         <v>1719</v>
-      </c>
-      <c r="B859" t="s">
-        <v>1720</v>
       </c>
       <c r="D859" t="s">
         <v>9</v>
@@ -15256,10 +15256,10 @@
     </row>
     <row r="860" spans="1:4">
       <c r="A860" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B860" t="s">
         <v>1721</v>
-      </c>
-      <c r="B860" t="s">
-        <v>1722</v>
       </c>
       <c r="D860" t="s">
         <v>9</v>
@@ -15267,10 +15267,10 @@
     </row>
     <row r="861" spans="1:4">
       <c r="A861" t="s">
+        <v>1722</v>
+      </c>
+      <c r="B861" t="s">
         <v>1723</v>
-      </c>
-      <c r="B861" t="s">
-        <v>1724</v>
       </c>
       <c r="D861" t="s">
         <v>9</v>
@@ -15278,10 +15278,10 @@
     </row>
     <row r="862" spans="1:4">
       <c r="A862" t="s">
+        <v>1724</v>
+      </c>
+      <c r="B862" t="s">
         <v>1725</v>
-      </c>
-      <c r="B862" t="s">
-        <v>1726</v>
       </c>
       <c r="D862" t="s">
         <v>9</v>
@@ -15289,10 +15289,10 @@
     </row>
     <row r="863" spans="1:4">
       <c r="A863" t="s">
+        <v>1726</v>
+      </c>
+      <c r="B863" t="s">
         <v>1727</v>
-      </c>
-      <c r="B863" t="s">
-        <v>1728</v>
       </c>
       <c r="D863" t="s">
         <v>9</v>
@@ -15300,10 +15300,10 @@
     </row>
     <row r="864" spans="1:4">
       <c r="A864" t="s">
+        <v>1728</v>
+      </c>
+      <c r="B864" t="s">
         <v>1729</v>
-      </c>
-      <c r="B864" t="s">
-        <v>1730</v>
       </c>
       <c r="D864" t="s">
         <v>9</v>
@@ -15311,10 +15311,10 @@
     </row>
     <row r="865" spans="1:4">
       <c r="A865" t="s">
+        <v>1730</v>
+      </c>
+      <c r="B865" t="s">
         <v>1731</v>
-      </c>
-      <c r="B865" t="s">
-        <v>1732</v>
       </c>
       <c r="D865" t="s">
         <v>9</v>
@@ -15322,10 +15322,10 @@
     </row>
     <row r="866" spans="1:4">
       <c r="A866" t="s">
+        <v>1732</v>
+      </c>
+      <c r="B866" t="s">
         <v>1733</v>
-      </c>
-      <c r="B866" t="s">
-        <v>1734</v>
       </c>
       <c r="D866" t="s">
         <v>9</v>
@@ -15333,10 +15333,10 @@
     </row>
     <row r="867" spans="1:4">
       <c r="A867" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B867" t="s">
         <v>1735</v>
-      </c>
-      <c r="B867" t="s">
-        <v>1736</v>
       </c>
       <c r="D867" t="s">
         <v>9</v>
@@ -15344,10 +15344,10 @@
     </row>
     <row r="868" spans="1:4">
       <c r="A868" t="s">
+        <v>1736</v>
+      </c>
+      <c r="B868" t="s">
         <v>1737</v>
-      </c>
-      <c r="B868" t="s">
-        <v>1738</v>
       </c>
       <c r="D868" t="s">
         <v>9</v>
@@ -15355,10 +15355,10 @@
     </row>
     <row r="869" spans="1:4">
       <c r="A869" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B869" t="s">
         <v>1739</v>
-      </c>
-      <c r="B869" t="s">
-        <v>1740</v>
       </c>
       <c r="D869" t="s">
         <v>9</v>
@@ -15366,10 +15366,10 @@
     </row>
     <row r="870" spans="1:4">
       <c r="A870" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B870" t="s">
         <v>1741</v>
-      </c>
-      <c r="B870" t="s">
-        <v>1742</v>
       </c>
       <c r="D870" t="s">
         <v>9</v>
@@ -15377,10 +15377,10 @@
     </row>
     <row r="871" spans="1:4">
       <c r="A871" t="s">
+        <v>1742</v>
+      </c>
+      <c r="B871" t="s">
         <v>1743</v>
-      </c>
-      <c r="B871" t="s">
-        <v>1744</v>
       </c>
       <c r="D871" t="s">
         <v>9</v>
@@ -15388,10 +15388,10 @@
     </row>
     <row r="872" spans="1:4">
       <c r="A872" t="s">
+        <v>1744</v>
+      </c>
+      <c r="B872" t="s">
         <v>1745</v>
-      </c>
-      <c r="B872" t="s">
-        <v>1746</v>
       </c>
       <c r="D872" t="s">
         <v>9</v>
@@ -15399,10 +15399,10 @@
     </row>
     <row r="873" spans="1:4">
       <c r="A873" t="s">
+        <v>1746</v>
+      </c>
+      <c r="B873" t="s">
         <v>1747</v>
-      </c>
-      <c r="B873" t="s">
-        <v>1748</v>
       </c>
       <c r="D873" t="s">
         <v>9</v>
@@ -15410,10 +15410,10 @@
     </row>
     <row r="874" spans="1:4">
       <c r="A874" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B874" t="s">
         <v>1749</v>
-      </c>
-      <c r="B874" t="s">
-        <v>1750</v>
       </c>
       <c r="D874" t="s">
         <v>9</v>
@@ -15421,10 +15421,10 @@
     </row>
     <row r="875" spans="1:4">
       <c r="A875" t="s">
+        <v>1750</v>
+      </c>
+      <c r="B875" t="s">
         <v>1751</v>
-      </c>
-      <c r="B875" t="s">
-        <v>1752</v>
       </c>
       <c r="D875" t="s">
         <v>9</v>
@@ -15432,10 +15432,10 @@
     </row>
     <row r="876" spans="1:4">
       <c r="A876" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B876" t="s">
         <v>1753</v>
-      </c>
-      <c r="B876" t="s">
-        <v>1754</v>
       </c>
       <c r="D876" t="s">
         <v>9</v>
@@ -15443,10 +15443,10 @@
     </row>
     <row r="877" spans="1:4">
       <c r="A877" t="s">
+        <v>1754</v>
+      </c>
+      <c r="B877" t="s">
         <v>1755</v>
-      </c>
-      <c r="B877" t="s">
-        <v>1756</v>
       </c>
       <c r="D877" t="s">
         <v>9</v>
@@ -15454,10 +15454,10 @@
     </row>
     <row r="878" spans="1:4">
       <c r="A878" t="s">
+        <v>1756</v>
+      </c>
+      <c r="B878" t="s">
         <v>1757</v>
-      </c>
-      <c r="B878" t="s">
-        <v>1758</v>
       </c>
       <c r="D878" t="s">
         <v>9</v>
@@ -15465,10 +15465,10 @@
     </row>
     <row r="879" spans="1:4">
       <c r="A879" t="s">
+        <v>1758</v>
+      </c>
+      <c r="B879" t="s">
         <v>1759</v>
-      </c>
-      <c r="B879" t="s">
-        <v>1760</v>
       </c>
       <c r="D879" t="s">
         <v>9</v>
@@ -15476,10 +15476,10 @@
     </row>
     <row r="880" spans="1:4">
       <c r="A880" t="s">
+        <v>1760</v>
+      </c>
+      <c r="B880" t="s">
         <v>1761</v>
-      </c>
-      <c r="B880" t="s">
-        <v>1762</v>
       </c>
       <c r="D880" t="s">
         <v>9</v>
@@ -15487,10 +15487,10 @@
     </row>
     <row r="881" spans="1:4">
       <c r="A881" t="s">
+        <v>1762</v>
+      </c>
+      <c r="B881" t="s">
         <v>1763</v>
-      </c>
-      <c r="B881" t="s">
-        <v>1764</v>
       </c>
       <c r="D881" t="s">
         <v>9</v>
@@ -15498,10 +15498,10 @@
     </row>
     <row r="882" spans="1:4">
       <c r="A882" t="s">
+        <v>1764</v>
+      </c>
+      <c r="B882" t="s">
         <v>1765</v>
-      </c>
-      <c r="B882" t="s">
-        <v>1766</v>
       </c>
       <c r="D882" t="s">
         <v>9</v>
@@ -15509,10 +15509,10 @@
     </row>
     <row r="883" spans="1:4">
       <c r="A883" t="s">
+        <v>1766</v>
+      </c>
+      <c r="B883" t="s">
         <v>1767</v>
-      </c>
-      <c r="B883" t="s">
-        <v>1768</v>
       </c>
       <c r="D883" t="s">
         <v>9</v>
@@ -15520,10 +15520,10 @@
     </row>
     <row r="884" spans="1:4">
       <c r="A884" t="s">
+        <v>1768</v>
+      </c>
+      <c r="B884" t="s">
         <v>1769</v>
-      </c>
-      <c r="B884" t="s">
-        <v>1770</v>
       </c>
       <c r="D884" t="s">
         <v>9</v>
@@ -15531,10 +15531,10 @@
     </row>
     <row r="885" spans="1:4">
       <c r="A885" t="s">
+        <v>1770</v>
+      </c>
+      <c r="B885" t="s">
         <v>1771</v>
-      </c>
-      <c r="B885" t="s">
-        <v>1772</v>
       </c>
       <c r="D885" t="s">
         <v>9</v>
@@ -15542,10 +15542,10 @@
     </row>
     <row r="886" spans="1:4">
       <c r="A886" t="s">
+        <v>1772</v>
+      </c>
+      <c r="B886" t="s">
         <v>1773</v>
-      </c>
-      <c r="B886" t="s">
-        <v>1774</v>
       </c>
       <c r="D886" t="s">
         <v>9</v>
@@ -15553,10 +15553,10 @@
     </row>
     <row r="887" spans="1:4">
       <c r="A887" t="s">
+        <v>1774</v>
+      </c>
+      <c r="B887" t="s">
         <v>1775</v>
-      </c>
-      <c r="B887" t="s">
-        <v>1776</v>
       </c>
       <c r="D887" t="s">
         <v>9</v>
@@ -15564,10 +15564,10 @@
     </row>
     <row r="888" spans="1:4">
       <c r="A888" t="s">
+        <v>1776</v>
+      </c>
+      <c r="B888" t="s">
         <v>1777</v>
-      </c>
-      <c r="B888" t="s">
-        <v>1778</v>
       </c>
       <c r="D888" t="s">
         <v>9</v>
@@ -15575,10 +15575,10 @@
     </row>
     <row r="889" spans="1:4">
       <c r="A889" t="s">
+        <v>1778</v>
+      </c>
+      <c r="B889" t="s">
         <v>1779</v>
-      </c>
-      <c r="B889" t="s">
-        <v>1780</v>
       </c>
       <c r="D889" t="s">
         <v>9</v>
@@ -15586,10 +15586,10 @@
     </row>
     <row r="890" spans="1:4">
       <c r="A890" t="s">
+        <v>1780</v>
+      </c>
+      <c r="B890" t="s">
         <v>1781</v>
-      </c>
-      <c r="B890" t="s">
-        <v>1782</v>
       </c>
       <c r="D890" t="s">
         <v>9</v>
@@ -15597,10 +15597,10 @@
     </row>
     <row r="891" spans="1:4">
       <c r="A891" t="s">
+        <v>1782</v>
+      </c>
+      <c r="B891" t="s">
         <v>1783</v>
-      </c>
-      <c r="B891" t="s">
-        <v>1784</v>
       </c>
       <c r="D891" t="s">
         <v>9</v>
@@ -15608,10 +15608,10 @@
     </row>
     <row r="892" spans="1:4">
       <c r="A892" t="s">
+        <v>1784</v>
+      </c>
+      <c r="B892" t="s">
         <v>1785</v>
-      </c>
-      <c r="B892" t="s">
-        <v>1786</v>
       </c>
       <c r="D892" t="s">
         <v>9</v>
@@ -15619,10 +15619,10 @@
     </row>
     <row r="893" spans="1:4">
       <c r="A893" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B893" t="s">
         <v>1787</v>
-      </c>
-      <c r="B893" t="s">
-        <v>1788</v>
       </c>
       <c r="D893" t="s">
         <v>9</v>
@@ -15630,10 +15630,10 @@
     </row>
     <row r="894" spans="1:4">
       <c r="A894" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B894" t="s">
         <v>1789</v>
-      </c>
-      <c r="B894" t="s">
-        <v>1790</v>
       </c>
       <c r="D894" t="s">
         <v>9</v>
@@ -15641,10 +15641,10 @@
     </row>
     <row r="895" spans="1:4">
       <c r="A895" t="s">
+        <v>1790</v>
+      </c>
+      <c r="B895" t="s">
         <v>1791</v>
-      </c>
-      <c r="B895" t="s">
-        <v>1792</v>
       </c>
       <c r="D895" t="s">
         <v>9</v>
@@ -15652,10 +15652,10 @@
     </row>
     <row r="896" spans="1:4">
       <c r="A896" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="B896" t="s">
-        <v>1794</v>
+        <v>1791</v>
       </c>
       <c r="D896" t="s">
         <v>9</v>
@@ -15663,10 +15663,10 @@
     </row>
     <row r="897" spans="1:4">
       <c r="A897" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="B897" t="s">
-        <v>1796</v>
+        <v>1794</v>
       </c>
       <c r="D897" t="s">
         <v>9</v>
@@ -15674,10 +15674,10 @@
     </row>
     <row r="898" spans="1:4">
       <c r="A898" t="s">
-        <v>1797</v>
+        <v>1795</v>
       </c>
       <c r="B898" t="s">
-        <v>1798</v>
+        <v>1796</v>
       </c>
       <c r="D898" t="s">
         <v>9</v>
@@ -15685,10 +15685,10 @@
     </row>
     <row r="899" spans="1:4">
       <c r="A899" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
       <c r="B899" t="s">
-        <v>1800</v>
+        <v>1798</v>
       </c>
       <c r="D899" t="s">
         <v>9</v>
@@ -15696,10 +15696,10 @@
     </row>
     <row r="900" spans="1:4">
       <c r="A900" t="s">
-        <v>1801</v>
+        <v>1799</v>
       </c>
       <c r="B900" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="D900" t="s">
         <v>9</v>
@@ -15707,10 +15707,10 @@
     </row>
     <row r="901" spans="1:4">
       <c r="A901" t="s">
-        <v>1803</v>
+        <v>1801</v>
       </c>
       <c r="B901" t="s">
-        <v>1804</v>
+        <v>1802</v>
       </c>
       <c r="D901" t="s">
         <v>9</v>
@@ -15718,10 +15718,10 @@
     </row>
     <row r="902" spans="1:4">
       <c r="A902" t="s">
-        <v>1805</v>
+        <v>1803</v>
       </c>
       <c r="B902" t="s">
-        <v>1806</v>
+        <v>1804</v>
       </c>
       <c r="D902" t="s">
         <v>9</v>
@@ -15729,10 +15729,10 @@
     </row>
     <row r="903" spans="1:4">
       <c r="A903" t="s">
-        <v>1807</v>
+        <v>1805</v>
       </c>
       <c r="B903" t="s">
-        <v>1808</v>
+        <v>1806</v>
       </c>
       <c r="D903" t="s">
         <v>9</v>
@@ -15740,10 +15740,10 @@
     </row>
     <row r="904" spans="1:4">
       <c r="A904" t="s">
-        <v>1809</v>
+        <v>1807</v>
       </c>
       <c r="B904" t="s">
-        <v>1810</v>
+        <v>1808</v>
       </c>
       <c r="D904" t="s">
         <v>9</v>
@@ -15751,10 +15751,10 @@
     </row>
     <row r="905" spans="1:4">
       <c r="A905" t="s">
-        <v>1811</v>
+        <v>1809</v>
       </c>
       <c r="B905" t="s">
-        <v>1812</v>
+        <v>1810</v>
       </c>
       <c r="D905" t="s">
         <v>9</v>
@@ -15762,12 +15762,23 @@
     </row>
     <row r="906" spans="1:4">
       <c r="A906" t="s">
+        <v>1811</v>
+      </c>
+      <c r="B906" t="s">
+        <v>1812</v>
+      </c>
+      <c r="D906" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="907" spans="1:4">
+      <c r="A907" t="s">
         <v>1813</v>
       </c>
-      <c r="B906" t="s">
+      <c r="B907" t="s">
         <v>1814</v>
       </c>
-      <c r="D906" t="s">
+      <c r="D907" t="s">
         <v>9</v>
       </c>
     </row>

--- a/api/1/clv1/codelist/HumanitarianPlan.xlsx
+++ b/api/1/clv1/codelist/HumanitarianPlan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2725" uniqueCount="1815">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2815" uniqueCount="1845">
   <si>
     <t>code</t>
   </si>
@@ -2467,6 +2467,12 @@
     <t>Congo Plan de Réponse Humanitaire 2017</t>
   </si>
   <si>
+    <t>RAIAATGBHSBLMKNAMAFSXMTCAVGB17</t>
+  </si>
+  <si>
+    <t>HBGD17</t>
+  </si>
+  <si>
     <t>HSSD17</t>
   </si>
   <si>
@@ -2686,6 +2692,15 @@
     <t>Occupied Palestinian Territory Humanitarian Response Plan 2016</t>
   </si>
   <si>
+    <t>RGRCHRVMKDSRBSVNTUR16</t>
+  </si>
+  <si>
+    <t>RBFACMRGMBMLIMRTNERNGASENTCD16</t>
+  </si>
+  <si>
+    <t>Sahel Region Call for Humanitarian Aid 2016</t>
+  </si>
+  <si>
     <t>HSSD16</t>
   </si>
   <si>
@@ -2695,9 +2710,6 @@
     <t>HXSHL16</t>
   </si>
   <si>
-    <t>Sahel Region Call for Humanitarian Aid 2016</t>
-  </si>
-  <si>
     <t>HSEN16</t>
   </si>
   <si>
@@ -2878,6 +2890,12 @@
     <t>Occupied Palestinian Territory Strategic Response Plan 2015</t>
   </si>
   <si>
+    <t>RBFACMRGMBMLIMRTNERNGASENTCD15</t>
+  </si>
+  <si>
+    <t>Sahel Region Call for Humanitarian Aid 2015</t>
+  </si>
+  <si>
     <t>HSSD15</t>
   </si>
   <si>
@@ -2887,9 +2905,6 @@
     <t>HXSHL15</t>
   </si>
   <si>
-    <t>Sahel Region Call for Humanitarian Aid 2015</t>
-  </si>
-  <si>
     <t>HSEN15</t>
   </si>
   <si>
@@ -3094,6 +3109,12 @@
     <t>République du Congo Plan de Réponse 2014</t>
   </si>
   <si>
+    <t>RBFACMRGMBMLIMRTNERNGASENTCD14</t>
+  </si>
+  <si>
+    <t>Sahel Region Strategic Response Plan 2014</t>
+  </si>
+  <si>
     <t>HSSD14</t>
   </si>
   <si>
@@ -3103,9 +3124,6 @@
     <t>HXSHL14</t>
   </si>
   <si>
-    <t>Sahel Region Strategic Response Plan 2014</t>
-  </si>
-  <si>
     <t>HSEN14</t>
   </si>
   <si>
@@ -3652,12 +3670,15 @@
     <t>Haiti Humanitarian Appeal (Revised) (January - December 2010)</t>
   </si>
   <si>
+    <t>CIRQ10</t>
+  </si>
+  <si>
+    <t>Iraq Humanitarian Action Plan 2010</t>
+  </si>
+  <si>
     <t>OIRQ10</t>
   </si>
   <si>
-    <t>Iraq Humanitarian Action Plan 2010</t>
-  </si>
-  <si>
     <t>CKEN10</t>
   </si>
   <si>
@@ -3688,12 +3709,15 @@
     <t>Pakistan Floods Relief and Early Recovery Response Plan (Revised) (August 2010 - July 2011)</t>
   </si>
   <si>
+    <t>CPAK10</t>
+  </si>
+  <si>
+    <t>Pakistan Humanitarian Response Plan (February - December 2010)</t>
+  </si>
+  <si>
     <t>OPAK10</t>
   </si>
   <si>
-    <t>Pakistan Humanitarian Response Plan (February - December 2010)</t>
-  </si>
-  <si>
     <t>OXIRQREG10</t>
   </si>
   <si>
@@ -3712,12 +3736,15 @@
     <t>Somalia 2010</t>
   </si>
   <si>
+    <t>CLKA10</t>
+  </si>
+  <si>
+    <t>Sri Lanka Common Humanitarian Action Plan 2010</t>
+  </si>
+  <si>
     <t>OLKA10</t>
   </si>
   <si>
-    <t>Sri Lanka Common Humanitarian Action Plan 2010</t>
-  </si>
-  <si>
     <t>CSDN10</t>
   </si>
   <si>
@@ -3730,12 +3757,15 @@
     <t>Uganda 2010</t>
   </si>
   <si>
+    <t>RBENBFACIVGHAGINGNBLBRMLIMRTNERNGASENSLETGO10</t>
+  </si>
+  <si>
+    <t>West Africa 2010</t>
+  </si>
+  <si>
     <t>CXWAF10</t>
   </si>
   <si>
-    <t>West Africa 2010</t>
-  </si>
-  <si>
     <t>CYEM10</t>
   </si>
   <si>
@@ -3796,12 +3826,15 @@
     <t>Indonesia West Sumatra Earthquake Humanitarian Response Plan 2009</t>
   </si>
   <si>
+    <t>RIRQ09</t>
+  </si>
+  <si>
+    <t>Iraq and the region 2009</t>
+  </si>
+  <si>
     <t>CIRQ09</t>
   </si>
   <si>
-    <t>Iraq and the region 2009</t>
-  </si>
-  <si>
     <t>CKEN09</t>
   </si>
   <si>
@@ -3886,12 +3919,15 @@
     <t>Uganda 2009</t>
   </si>
   <si>
+    <t>RBENBFACIVGHAGINGNBLBRMLIMRTNERSENSLETGO09</t>
+  </si>
+  <si>
+    <t>West Africa 2009</t>
+  </si>
+  <si>
     <t>CXWAF09</t>
   </si>
   <si>
-    <t>West Africa 2009</t>
-  </si>
-  <si>
     <t>FYEM09</t>
   </si>
   <si>
@@ -4006,12 +4042,15 @@
     <t>Lao PDR Joint Appeal for Flood Recovery and Rehabilitation 2008</t>
   </si>
   <si>
+    <t>OLBR08</t>
+  </si>
+  <si>
+    <t>Liberia Critical Humanitarian Gaps 2008</t>
+  </si>
+  <si>
     <t>CLBR08</t>
   </si>
   <si>
-    <t>Liberia Critical Humanitarian Gaps 2008</t>
-  </si>
-  <si>
     <t>FMDG08</t>
   </si>
   <si>
@@ -4084,12 +4123,15 @@
     <t>Uganda 2008</t>
   </si>
   <si>
+    <t>RBENBFAGHAGINGMBGNBLBRMLIMRTNERSENSLETGO08</t>
+  </si>
+  <si>
+    <t>West Africa 2008</t>
+  </si>
+  <si>
     <t>CXWAF08</t>
   </si>
   <si>
-    <t>West Africa 2008</t>
-  </si>
-  <si>
     <t>FYEM0809</t>
   </si>
   <si>
@@ -4258,12 +4300,15 @@
     <t>Somalia 2007</t>
   </si>
   <si>
+    <t>CLKA07</t>
+  </si>
+  <si>
+    <t>Sri Lanka Common Humanitarian Action Plan 2007</t>
+  </si>
+  <si>
     <t>OLKA07</t>
   </si>
   <si>
-    <t>Sri Lanka Common Humanitarian Action Plan 2007</t>
-  </si>
-  <si>
     <t>FSDN0708</t>
   </si>
   <si>
@@ -4300,12 +4345,15 @@
     <t>Uganda Floods Flash Appeal 2007</t>
   </si>
   <si>
+    <t>RBENBFACIVCPVGHAGINGNBLBRMLIMRTNERSENSLETGO07</t>
+  </si>
+  <si>
+    <t>West Africa 2007</t>
+  </si>
+  <si>
     <t>CXWAF07</t>
   </si>
   <si>
-    <t>West Africa 2007</t>
-  </si>
-  <si>
     <t>FZMB07</t>
   </si>
   <si>
@@ -4498,12 +4546,15 @@
     <t>Uganda 2006</t>
   </si>
   <si>
+    <t>RBFAGNBMLIMRTNERSENTGO06</t>
+  </si>
+  <si>
+    <t>West Africa 2006</t>
+  </si>
+  <si>
     <t>CXWAF06</t>
   </si>
   <si>
-    <t>West Africa 2006</t>
-  </si>
-  <si>
     <t>CZWE06</t>
   </si>
   <si>
@@ -4582,6 +4633,12 @@
     <t>Eritrea 2005</t>
   </si>
   <si>
+    <t>R05</t>
+  </si>
+  <si>
+    <t>Indian Ocean Earthquake-Tsunami  2005</t>
+  </si>
+  <si>
     <t>CXGLR05</t>
   </si>
   <si>
@@ -4609,9 +4666,6 @@
     <t>FXINDTSU05</t>
   </si>
   <si>
-    <t>Indian Ocean Earthquake-Tsunami  2005</t>
-  </si>
-  <si>
     <t>FMWI0506</t>
   </si>
   <si>
@@ -4636,6 +4690,18 @@
     <t>Somalia 2005</t>
   </si>
   <si>
+    <t>R0506</t>
+  </si>
+  <si>
+    <t>West and Central Africa Region Cholera 2005</t>
+  </si>
+  <si>
+    <t>OSDN05</t>
+  </si>
+  <si>
+    <t>Sudan - Humanitarian &amp; Recovery Components of the 2005 Work Plan</t>
+  </si>
+  <si>
     <t>FXSASIA0506</t>
   </si>
   <si>
@@ -4645,9 +4711,6 @@
     <t>CSDN05</t>
   </si>
   <si>
-    <t>Sudan - Humanitarian &amp; Recovery Components of the 2005 Work Plan</t>
-  </si>
-  <si>
     <t>CUGA05</t>
   </si>
   <si>
@@ -4663,9 +4726,6 @@
     <t>FXWAF0506</t>
   </si>
   <si>
-    <t>West and Central Africa Region Cholera 2005</t>
-  </si>
-  <si>
     <t>CPSE05</t>
   </si>
   <si>
@@ -4720,6 +4780,12 @@
     <t>Chechnya and Neighbouring Republics (RF) 2004</t>
   </si>
   <si>
+    <t>R04</t>
+  </si>
+  <si>
+    <t>West Africa Sub-Regional 2004</t>
+  </si>
+  <si>
     <t>CCIV04</t>
   </si>
   <si>
@@ -4849,9 +4915,6 @@
     <t>CXWAF04</t>
   </si>
   <si>
-    <t>West Africa Sub-Regional 2004</t>
-  </si>
-  <si>
     <t>CZWE04</t>
   </si>
   <si>
@@ -4900,18 +4963,24 @@
     <t>Colombia (HAP) 2003</t>
   </si>
   <si>
+    <t>RCIV03</t>
+  </si>
+  <si>
+    <t>Cote d'Ivoire + 5 2003</t>
+  </si>
+  <si>
+    <t>RCIV0203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Côte d'Ivoire and the West Africa Sub-Region 2002-2003 </t>
+  </si>
+  <si>
     <t>CCIV03</t>
   </si>
   <si>
-    <t>Cote d'Ivoire + 5 2003</t>
-  </si>
-  <si>
     <t>FCIV0203</t>
   </si>
   <si>
-    <t xml:space="preserve">Côte d'Ivoire and the West Africa Sub-Region 2002-2003 </t>
-  </si>
-  <si>
     <t>CPRK03</t>
   </si>
   <si>
@@ -4930,12 +4999,15 @@
     <t>Eritrea 2003</t>
   </si>
   <si>
+    <t>R03</t>
+  </si>
+  <si>
+    <t>Great Lakes Region and Central Africa 2003</t>
+  </si>
+  <si>
     <t>CXGLR03</t>
   </si>
   <si>
-    <t>Great Lakes Region and Central Africa 2003</t>
-  </si>
-  <si>
     <t>CGIN03</t>
   </si>
   <si>
@@ -4966,12 +5038,15 @@
     <t>Humanitarian Crisis in Southern Africa - MOZAMBIQUE (July 2003 - June 2004)</t>
   </si>
   <si>
+    <t>R0304</t>
+  </si>
+  <si>
+    <t>Humanitarian Crisis in Southern Africa - REGION (July 2003 - June 2004)</t>
+  </si>
+  <si>
     <t>CXSAF0304</t>
   </si>
   <si>
-    <t>Humanitarian Crisis in Southern Africa - REGION (July 2003 - June 2004)</t>
-  </si>
-  <si>
     <t>CSWZ0304</t>
   </si>
   <si>
@@ -4996,12 +5071,15 @@
     <t>Indonesia 2003</t>
   </si>
   <si>
+    <t>FIRQ03</t>
+  </si>
+  <si>
+    <t>Iraq Crisis 2003</t>
+  </si>
+  <si>
     <t>CIRQ03</t>
   </si>
   <si>
-    <t>Iraq Crisis 2003</t>
-  </si>
-  <si>
     <t>CLBR03</t>
   </si>
   <si>
@@ -5086,6 +5164,12 @@
     <t>Eritrea 2002</t>
   </si>
   <si>
+    <t>R02</t>
+  </si>
+  <si>
+    <t>West Africa 2002</t>
+  </si>
+  <si>
     <t>CXGLR02</t>
   </si>
   <si>
@@ -5110,12 +5194,15 @@
     <t>Humanitarian Crisis in Southern Africa 2002 - MALAWI</t>
   </si>
   <si>
+    <t>R0203</t>
+  </si>
+  <si>
+    <t>Humanitarian Crisis in Southern Africa 2002 - REGION</t>
+  </si>
+  <si>
     <t>CXSAF0203</t>
   </si>
   <si>
-    <t>Humanitarian Crisis in Southern Africa 2002 - REGION</t>
-  </si>
-  <si>
     <t>CSWZ0203</t>
   </si>
   <si>
@@ -5215,9 +5302,6 @@
     <t>CXWAF02</t>
   </si>
   <si>
-    <t>West Africa 2002</t>
-  </si>
-  <si>
     <t>CAFG01</t>
   </si>
   <si>
@@ -5254,6 +5338,12 @@
     <t>Djibouti Drought 2001</t>
   </si>
   <si>
+    <t>R01</t>
+  </si>
+  <si>
+    <t>West Africa 2001</t>
+  </si>
+  <si>
     <t>OXHAF01</t>
   </si>
   <si>
@@ -5353,9 +5443,6 @@
     <t>CXWAF01</t>
   </si>
   <si>
-    <t>West Africa 2001</t>
-  </si>
-  <si>
     <t>CAGO00</t>
   </si>
   <si>
@@ -5447,6 +5534,9 @@
   </si>
   <si>
     <t>East Timor Consolidated Inter Agency Appeal 2000</t>
+  </si>
+  <si>
+    <t>R00</t>
   </si>
   <si>
     <t>CRUS9900</t>
@@ -5790,7 +5880,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G907"/>
+  <dimension ref="A1:G937"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -10287,7 +10377,7 @@
         <v>817</v>
       </c>
       <c r="B408" t="s">
-        <v>818</v>
+        <v>788</v>
       </c>
       <c r="D408" t="s">
         <v>9</v>
@@ -10295,10 +10385,10 @@
     </row>
     <row r="409" spans="1:4">
       <c r="A409" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B409" t="s">
-        <v>820</v>
+        <v>762</v>
       </c>
       <c r="D409" t="s">
         <v>9</v>
@@ -10306,10 +10396,10 @@
     </row>
     <row r="410" spans="1:4">
       <c r="A410" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B410" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="D410" t="s">
         <v>9</v>
@@ -10317,10 +10407,10 @@
     </row>
     <row r="411" spans="1:4">
       <c r="A411" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="B411" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="D411" t="s">
         <v>9</v>
@@ -10328,10 +10418,10 @@
     </row>
     <row r="412" spans="1:4">
       <c r="A412" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="B412" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="D412" t="s">
         <v>9</v>
@@ -10339,10 +10429,10 @@
     </row>
     <row r="413" spans="1:4">
       <c r="A413" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B413" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="D413" t="s">
         <v>9</v>
@@ -10350,10 +10440,10 @@
     </row>
     <row r="414" spans="1:4">
       <c r="A414" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="B414" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="D414" t="s">
         <v>9</v>
@@ -10361,10 +10451,10 @@
     </row>
     <row r="415" spans="1:4">
       <c r="A415" t="s">
+        <v>829</v>
+      </c>
+      <c r="B415" t="s">
         <v>830</v>
-      </c>
-      <c r="B415" t="s">
-        <v>831</v>
       </c>
       <c r="D415" t="s">
         <v>9</v>
@@ -10372,10 +10462,10 @@
     </row>
     <row r="416" spans="1:4">
       <c r="A416" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B416" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="D416" t="s">
         <v>9</v>
@@ -10383,10 +10473,10 @@
     </row>
     <row r="417" spans="1:4">
       <c r="A417" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B417" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D417" t="s">
         <v>9</v>
@@ -10394,10 +10484,10 @@
     </row>
     <row r="418" spans="1:4">
       <c r="A418" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B418" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="D418" t="s">
         <v>9</v>
@@ -10405,10 +10495,10 @@
     </row>
     <row r="419" spans="1:4">
       <c r="A419" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B419" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="D419" t="s">
         <v>9</v>
@@ -10416,10 +10506,10 @@
     </row>
     <row r="420" spans="1:4">
       <c r="A420" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="B420" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="D420" t="s">
         <v>9</v>
@@ -10427,10 +10517,10 @@
     </row>
     <row r="421" spans="1:4">
       <c r="A421" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B421" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="D421" t="s">
         <v>9</v>
@@ -10438,10 +10528,10 @@
     </row>
     <row r="422" spans="1:4">
       <c r="A422" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B422" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="D422" t="s">
         <v>9</v>
@@ -10449,10 +10539,10 @@
     </row>
     <row r="423" spans="1:4">
       <c r="A423" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="B423" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="D423" t="s">
         <v>9</v>
@@ -10460,10 +10550,10 @@
     </row>
     <row r="424" spans="1:4">
       <c r="A424" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B424" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="D424" t="s">
         <v>9</v>
@@ -10471,10 +10561,10 @@
     </row>
     <row r="425" spans="1:4">
       <c r="A425" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B425" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="D425" t="s">
         <v>9</v>
@@ -10482,10 +10572,10 @@
     </row>
     <row r="426" spans="1:4">
       <c r="A426" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B426" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="D426" t="s">
         <v>9</v>
@@ -10493,10 +10583,10 @@
     </row>
     <row r="427" spans="1:4">
       <c r="A427" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="B427" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="D427" t="s">
         <v>9</v>
@@ -10504,10 +10594,10 @@
     </row>
     <row r="428" spans="1:4">
       <c r="A428" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="B428" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="D428" t="s">
         <v>9</v>
@@ -10515,10 +10605,10 @@
     </row>
     <row r="429" spans="1:4">
       <c r="A429" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B429" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="D429" t="s">
         <v>9</v>
@@ -10526,10 +10616,10 @@
     </row>
     <row r="430" spans="1:4">
       <c r="A430" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B430" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="D430" t="s">
         <v>9</v>
@@ -10537,10 +10627,10 @@
     </row>
     <row r="431" spans="1:4">
       <c r="A431" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B431" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="D431" t="s">
         <v>9</v>
@@ -10548,10 +10638,10 @@
     </row>
     <row r="432" spans="1:4">
       <c r="A432" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B432" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="D432" t="s">
         <v>9</v>
@@ -10559,10 +10649,10 @@
     </row>
     <row r="433" spans="1:4">
       <c r="A433" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="B433" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="D433" t="s">
         <v>9</v>
@@ -10570,10 +10660,10 @@
     </row>
     <row r="434" spans="1:4">
       <c r="A434" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="B434" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="D434" t="s">
         <v>9</v>
@@ -10581,10 +10671,10 @@
     </row>
     <row r="435" spans="1:4">
       <c r="A435" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B435" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="D435" t="s">
         <v>9</v>
@@ -10592,10 +10682,10 @@
     </row>
     <row r="436" spans="1:4">
       <c r="A436" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="B436" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="D436" t="s">
         <v>9</v>
@@ -10603,10 +10693,10 @@
     </row>
     <row r="437" spans="1:4">
       <c r="A437" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="B437" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="D437" t="s">
         <v>9</v>
@@ -10614,10 +10704,10 @@
     </row>
     <row r="438" spans="1:4">
       <c r="A438" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="B438" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="D438" t="s">
         <v>9</v>
@@ -10625,10 +10715,10 @@
     </row>
     <row r="439" spans="1:4">
       <c r="A439" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="B439" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="D439" t="s">
         <v>9</v>
@@ -10636,10 +10726,10 @@
     </row>
     <row r="440" spans="1:4">
       <c r="A440" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B440" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="D440" t="s">
         <v>9</v>
@@ -10647,10 +10737,10 @@
     </row>
     <row r="441" spans="1:4">
       <c r="A441" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B441" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="D441" t="s">
         <v>9</v>
@@ -10658,10 +10748,10 @@
     </row>
     <row r="442" spans="1:4">
       <c r="A442" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B442" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="D442" t="s">
         <v>9</v>
@@ -10669,10 +10759,10 @@
     </row>
     <row r="443" spans="1:4">
       <c r="A443" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B443" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="D443" t="s">
         <v>9</v>
@@ -10680,10 +10770,10 @@
     </row>
     <row r="444" spans="1:4">
       <c r="A444" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B444" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="D444" t="s">
         <v>9</v>
@@ -10691,10 +10781,10 @@
     </row>
     <row r="445" spans="1:4">
       <c r="A445" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="B445" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="D445" t="s">
         <v>9</v>
@@ -10702,10 +10792,10 @@
     </row>
     <row r="446" spans="1:4">
       <c r="A446" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="B446" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="D446" t="s">
         <v>9</v>
@@ -10713,10 +10803,10 @@
     </row>
     <row r="447" spans="1:4">
       <c r="A447" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B447" t="s">
-        <v>895</v>
+        <v>837</v>
       </c>
       <c r="D447" t="s">
         <v>9</v>
@@ -10724,10 +10814,10 @@
     </row>
     <row r="448" spans="1:4">
       <c r="A448" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="B448" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="D448" t="s">
         <v>9</v>
@@ -10735,10 +10825,10 @@
     </row>
     <row r="449" spans="1:4">
       <c r="A449" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="B449" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="D449" t="s">
         <v>9</v>
@@ -10746,10 +10836,10 @@
     </row>
     <row r="450" spans="1:4">
       <c r="A450" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="B450" t="s">
-        <v>901</v>
+        <v>894</v>
       </c>
       <c r="D450" t="s">
         <v>9</v>
@@ -10757,10 +10847,10 @@
     </row>
     <row r="451" spans="1:4">
       <c r="A451" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="B451" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="D451" t="s">
         <v>9</v>
@@ -10768,10 +10858,10 @@
     </row>
     <row r="452" spans="1:4">
       <c r="A452" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="B452" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="D452" t="s">
         <v>9</v>
@@ -10779,10 +10869,10 @@
     </row>
     <row r="453" spans="1:4">
       <c r="A453" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="B453" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="D453" t="s">
         <v>9</v>
@@ -10790,10 +10880,10 @@
     </row>
     <row r="454" spans="1:4">
       <c r="A454" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="B454" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="D454" t="s">
         <v>9</v>
@@ -10801,10 +10891,10 @@
     </row>
     <row r="455" spans="1:4">
       <c r="A455" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B455" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="D455" t="s">
         <v>9</v>
@@ -10812,10 +10902,10 @@
     </row>
     <row r="456" spans="1:4">
       <c r="A456" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="B456" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="D456" t="s">
         <v>9</v>
@@ -10823,10 +10913,10 @@
     </row>
     <row r="457" spans="1:4">
       <c r="A457" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="B457" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="D457" t="s">
         <v>9</v>
@@ -10834,10 +10924,10 @@
     </row>
     <row r="458" spans="1:4">
       <c r="A458" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="B458" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="D458" t="s">
         <v>9</v>
@@ -10845,10 +10935,10 @@
     </row>
     <row r="459" spans="1:4">
       <c r="A459" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="B459" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="D459" t="s">
         <v>9</v>
@@ -10856,10 +10946,10 @@
     </row>
     <row r="460" spans="1:4">
       <c r="A460" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="B460" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="D460" t="s">
         <v>9</v>
@@ -10867,10 +10957,10 @@
     </row>
     <row r="461" spans="1:4">
       <c r="A461" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="B461" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="D461" t="s">
         <v>9</v>
@@ -10878,10 +10968,10 @@
     </row>
     <row r="462" spans="1:4">
       <c r="A462" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="B462" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="D462" t="s">
         <v>9</v>
@@ -10889,10 +10979,10 @@
     </row>
     <row r="463" spans="1:4">
       <c r="A463" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="B463" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D463" t="s">
         <v>9</v>
@@ -10900,10 +10990,10 @@
     </row>
     <row r="464" spans="1:4">
       <c r="A464" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="B464" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="D464" t="s">
         <v>9</v>
@@ -10911,10 +11001,10 @@
     </row>
     <row r="465" spans="1:4">
       <c r="A465" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="B465" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="D465" t="s">
         <v>9</v>
@@ -10922,10 +11012,10 @@
     </row>
     <row r="466" spans="1:4">
       <c r="A466" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="B466" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="D466" t="s">
         <v>9</v>
@@ -10933,10 +11023,10 @@
     </row>
     <row r="467" spans="1:4">
       <c r="A467" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="B467" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="D467" t="s">
         <v>9</v>
@@ -10944,10 +11034,10 @@
     </row>
     <row r="468" spans="1:4">
       <c r="A468" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="B468" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="D468" t="s">
         <v>9</v>
@@ -10955,10 +11045,10 @@
     </row>
     <row r="469" spans="1:4">
       <c r="A469" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="B469" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="D469" t="s">
         <v>9</v>
@@ -10966,10 +11056,10 @@
     </row>
     <row r="470" spans="1:4">
       <c r="A470" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="B470" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="D470" t="s">
         <v>9</v>
@@ -10977,10 +11067,10 @@
     </row>
     <row r="471" spans="1:4">
       <c r="A471" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="B471" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="D471" t="s">
         <v>9</v>
@@ -10988,10 +11078,10 @@
     </row>
     <row r="472" spans="1:4">
       <c r="A472" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="B472" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="D472" t="s">
         <v>9</v>
@@ -10999,10 +11089,10 @@
     </row>
     <row r="473" spans="1:4">
       <c r="A473" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="B473" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="D473" t="s">
         <v>9</v>
@@ -11010,10 +11100,10 @@
     </row>
     <row r="474" spans="1:4">
       <c r="A474" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="B474" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="D474" t="s">
         <v>9</v>
@@ -11021,10 +11111,10 @@
     </row>
     <row r="475" spans="1:4">
       <c r="A475" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="B475" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="D475" t="s">
         <v>9</v>
@@ -11032,10 +11122,10 @@
     </row>
     <row r="476" spans="1:4">
       <c r="A476" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="B476" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="D476" t="s">
         <v>9</v>
@@ -11043,10 +11133,10 @@
     </row>
     <row r="477" spans="1:4">
       <c r="A477" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="B477" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="D477" t="s">
         <v>9</v>
@@ -11054,10 +11144,10 @@
     </row>
     <row r="478" spans="1:4">
       <c r="A478" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="B478" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="D478" t="s">
         <v>9</v>
@@ -11065,10 +11155,10 @@
     </row>
     <row r="479" spans="1:4">
       <c r="A479" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="B479" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="D479" t="s">
         <v>9</v>
@@ -11076,10 +11166,10 @@
     </row>
     <row r="480" spans="1:4">
       <c r="A480" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="B480" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="D480" t="s">
         <v>9</v>
@@ -11087,10 +11177,10 @@
     </row>
     <row r="481" spans="1:4">
       <c r="A481" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="B481" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="D481" t="s">
         <v>9</v>
@@ -11098,10 +11188,10 @@
     </row>
     <row r="482" spans="1:4">
       <c r="A482" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="B482" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="D482" t="s">
         <v>9</v>
@@ -11109,10 +11199,10 @@
     </row>
     <row r="483" spans="1:4">
       <c r="A483" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="B483" t="s">
-        <v>967</v>
+        <v>959</v>
       </c>
       <c r="D483" t="s">
         <v>9</v>
@@ -11120,10 +11210,10 @@
     </row>
     <row r="484" spans="1:4">
       <c r="A484" t="s">
-        <v>968</v>
+        <v>963</v>
       </c>
       <c r="B484" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="D484" t="s">
         <v>9</v>
@@ -11131,10 +11221,10 @@
     </row>
     <row r="485" spans="1:4">
       <c r="A485" t="s">
-        <v>970</v>
+        <v>965</v>
       </c>
       <c r="B485" t="s">
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="D485" t="s">
         <v>9</v>
@@ -11142,10 +11232,10 @@
     </row>
     <row r="486" spans="1:4">
       <c r="A486" t="s">
-        <v>972</v>
+        <v>967</v>
       </c>
       <c r="B486" t="s">
-        <v>973</v>
+        <v>968</v>
       </c>
       <c r="D486" t="s">
         <v>9</v>
@@ -11153,10 +11243,10 @@
     </row>
     <row r="487" spans="1:4">
       <c r="A487" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="B487" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="D487" t="s">
         <v>9</v>
@@ -11164,10 +11254,10 @@
     </row>
     <row r="488" spans="1:4">
       <c r="A488" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="B488" t="s">
-        <v>977</v>
+        <v>972</v>
       </c>
       <c r="D488" t="s">
         <v>9</v>
@@ -11175,10 +11265,10 @@
     </row>
     <row r="489" spans="1:4">
       <c r="A489" t="s">
-        <v>978</v>
+        <v>973</v>
       </c>
       <c r="B489" t="s">
-        <v>979</v>
+        <v>974</v>
       </c>
       <c r="D489" t="s">
         <v>9</v>
@@ -11186,10 +11276,10 @@
     </row>
     <row r="490" spans="1:4">
       <c r="A490" t="s">
-        <v>980</v>
+        <v>975</v>
       </c>
       <c r="B490" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
       <c r="D490" t="s">
         <v>9</v>
@@ -11197,10 +11287,10 @@
     </row>
     <row r="491" spans="1:4">
       <c r="A491" t="s">
-        <v>982</v>
+        <v>977</v>
       </c>
       <c r="B491" t="s">
-        <v>983</v>
+        <v>978</v>
       </c>
       <c r="D491" t="s">
         <v>9</v>
@@ -11208,10 +11298,10 @@
     </row>
     <row r="492" spans="1:4">
       <c r="A492" t="s">
-        <v>984</v>
+        <v>979</v>
       </c>
       <c r="B492" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="D492" t="s">
         <v>9</v>
@@ -11219,10 +11309,10 @@
     </row>
     <row r="493" spans="1:4">
       <c r="A493" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="B493" t="s">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="D493" t="s">
         <v>9</v>
@@ -11230,10 +11320,10 @@
     </row>
     <row r="494" spans="1:4">
       <c r="A494" t="s">
-        <v>988</v>
+        <v>983</v>
       </c>
       <c r="B494" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="D494" t="s">
         <v>9</v>
@@ -11241,10 +11331,10 @@
     </row>
     <row r="495" spans="1:4">
       <c r="A495" t="s">
-        <v>990</v>
+        <v>985</v>
       </c>
       <c r="B495" t="s">
-        <v>991</v>
+        <v>986</v>
       </c>
       <c r="D495" t="s">
         <v>9</v>
@@ -11252,10 +11342,10 @@
     </row>
     <row r="496" spans="1:4">
       <c r="A496" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="B496" t="s">
-        <v>993</v>
+        <v>988</v>
       </c>
       <c r="D496" t="s">
         <v>9</v>
@@ -11263,10 +11353,10 @@
     </row>
     <row r="497" spans="1:4">
       <c r="A497" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="B497" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="D497" t="s">
         <v>9</v>
@@ -11274,10 +11364,10 @@
     </row>
     <row r="498" spans="1:4">
       <c r="A498" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="B498" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="D498" t="s">
         <v>9</v>
@@ -11285,10 +11375,10 @@
     </row>
     <row r="499" spans="1:4">
       <c r="A499" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="B499" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="D499" t="s">
         <v>9</v>
@@ -11296,10 +11386,10 @@
     </row>
     <row r="500" spans="1:4">
       <c r="A500" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="B500" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="D500" t="s">
         <v>9</v>
@@ -11307,10 +11397,10 @@
     </row>
     <row r="501" spans="1:4">
       <c r="A501" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
       <c r="B501" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
       <c r="D501" t="s">
         <v>9</v>
@@ -11318,10 +11408,10 @@
     </row>
     <row r="502" spans="1:4">
       <c r="A502" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="B502" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="D502" t="s">
         <v>9</v>
@@ -11329,10 +11419,10 @@
     </row>
     <row r="503" spans="1:4">
       <c r="A503" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="B503" t="s">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="D503" t="s">
         <v>9</v>
@@ -11340,10 +11430,10 @@
     </row>
     <row r="504" spans="1:4">
       <c r="A504" t="s">
-        <v>1008</v>
+        <v>1003</v>
       </c>
       <c r="B504" t="s">
-        <v>1009</v>
+        <v>1004</v>
       </c>
       <c r="D504" t="s">
         <v>9</v>
@@ -11351,10 +11441,10 @@
     </row>
     <row r="505" spans="1:4">
       <c r="A505" t="s">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="B505" t="s">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="D505" t="s">
         <v>9</v>
@@ -11362,10 +11452,10 @@
     </row>
     <row r="506" spans="1:4">
       <c r="A506" t="s">
-        <v>1012</v>
+        <v>1007</v>
       </c>
       <c r="B506" t="s">
-        <v>1013</v>
+        <v>1008</v>
       </c>
       <c r="D506" t="s">
         <v>9</v>
@@ -11373,10 +11463,10 @@
     </row>
     <row r="507" spans="1:4">
       <c r="A507" t="s">
-        <v>1014</v>
+        <v>1009</v>
       </c>
       <c r="B507" t="s">
-        <v>1015</v>
+        <v>1010</v>
       </c>
       <c r="D507" t="s">
         <v>9</v>
@@ -11384,10 +11474,10 @@
     </row>
     <row r="508" spans="1:4">
       <c r="A508" t="s">
-        <v>1016</v>
+        <v>1011</v>
       </c>
       <c r="B508" t="s">
-        <v>1017</v>
+        <v>1012</v>
       </c>
       <c r="D508" t="s">
         <v>9</v>
@@ -11395,10 +11485,10 @@
     </row>
     <row r="509" spans="1:4">
       <c r="A509" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="B509" t="s">
-        <v>1019</v>
+        <v>1014</v>
       </c>
       <c r="D509" t="s">
         <v>9</v>
@@ -11406,10 +11496,10 @@
     </row>
     <row r="510" spans="1:4">
       <c r="A510" t="s">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="B510" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="D510" t="s">
         <v>9</v>
@@ -11417,10 +11507,10 @@
     </row>
     <row r="511" spans="1:4">
       <c r="A511" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="B511" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="D511" t="s">
         <v>9</v>
@@ -11428,10 +11518,10 @@
     </row>
     <row r="512" spans="1:4">
       <c r="A512" t="s">
-        <v>1024</v>
+        <v>1019</v>
       </c>
       <c r="B512" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
       <c r="D512" t="s">
         <v>9</v>
@@ -11439,10 +11529,10 @@
     </row>
     <row r="513" spans="1:4">
       <c r="A513" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="B513" t="s">
-        <v>1027</v>
+        <v>1022</v>
       </c>
       <c r="D513" t="s">
         <v>9</v>
@@ -11450,10 +11540,10 @@
     </row>
     <row r="514" spans="1:4">
       <c r="A514" t="s">
-        <v>1028</v>
+        <v>1023</v>
       </c>
       <c r="B514" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="D514" t="s">
         <v>9</v>
@@ -11461,10 +11551,10 @@
     </row>
     <row r="515" spans="1:4">
       <c r="A515" t="s">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="B515" t="s">
-        <v>1031</v>
+        <v>1026</v>
       </c>
       <c r="D515" t="s">
         <v>9</v>
@@ -11472,10 +11562,10 @@
     </row>
     <row r="516" spans="1:4">
       <c r="A516" t="s">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="B516" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="D516" t="s">
         <v>9</v>
@@ -11483,10 +11573,10 @@
     </row>
     <row r="517" spans="1:4">
       <c r="A517" t="s">
-        <v>1034</v>
+        <v>1029</v>
       </c>
       <c r="B517" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="D517" t="s">
         <v>9</v>
@@ -11494,10 +11584,10 @@
     </row>
     <row r="518" spans="1:4">
       <c r="A518" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="B518" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="D518" t="s">
         <v>9</v>
@@ -11505,10 +11595,10 @@
     </row>
     <row r="519" spans="1:4">
       <c r="A519" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="B519" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="D519" t="s">
         <v>9</v>
@@ -11516,10 +11606,10 @@
     </row>
     <row r="520" spans="1:4">
       <c r="A520" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="B520" t="s">
-        <v>1041</v>
+        <v>1032</v>
       </c>
       <c r="D520" t="s">
         <v>9</v>
@@ -11527,10 +11617,10 @@
     </row>
     <row r="521" spans="1:4">
       <c r="A521" t="s">
-        <v>1042</v>
+        <v>1036</v>
       </c>
       <c r="B521" t="s">
-        <v>1043</v>
+        <v>1037</v>
       </c>
       <c r="D521" t="s">
         <v>9</v>
@@ -11538,10 +11628,10 @@
     </row>
     <row r="522" spans="1:4">
       <c r="A522" t="s">
-        <v>1044</v>
+        <v>1038</v>
       </c>
       <c r="B522" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
       <c r="D522" t="s">
         <v>9</v>
@@ -11549,10 +11639,10 @@
     </row>
     <row r="523" spans="1:4">
       <c r="A523" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="B523" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
       <c r="D523" t="s">
         <v>9</v>
@@ -11560,10 +11650,10 @@
     </row>
     <row r="524" spans="1:4">
       <c r="A524" t="s">
-        <v>1048</v>
+        <v>1042</v>
       </c>
       <c r="B524" t="s">
-        <v>1049</v>
+        <v>1043</v>
       </c>
       <c r="D524" t="s">
         <v>9</v>
@@ -11571,10 +11661,10 @@
     </row>
     <row r="525" spans="1:4">
       <c r="A525" t="s">
-        <v>1050</v>
+        <v>1044</v>
       </c>
       <c r="B525" t="s">
-        <v>1051</v>
+        <v>1045</v>
       </c>
       <c r="D525" t="s">
         <v>9</v>
@@ -11582,10 +11672,10 @@
     </row>
     <row r="526" spans="1:4">
       <c r="A526" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
       <c r="B526" t="s">
-        <v>1053</v>
+        <v>1047</v>
       </c>
       <c r="D526" t="s">
         <v>9</v>
@@ -11593,10 +11683,10 @@
     </row>
     <row r="527" spans="1:4">
       <c r="A527" t="s">
-        <v>1054</v>
+        <v>1048</v>
       </c>
       <c r="B527" t="s">
-        <v>1055</v>
+        <v>1049</v>
       </c>
       <c r="D527" t="s">
         <v>9</v>
@@ -11604,10 +11694,10 @@
     </row>
     <row r="528" spans="1:4">
       <c r="A528" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="B528" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="D528" t="s">
         <v>9</v>
@@ -11615,10 +11705,10 @@
     </row>
     <row r="529" spans="1:4">
       <c r="A529" t="s">
-        <v>1058</v>
+        <v>1052</v>
       </c>
       <c r="B529" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="D529" t="s">
         <v>9</v>
@@ -11626,10 +11716,10 @@
     </row>
     <row r="530" spans="1:4">
       <c r="A530" t="s">
-        <v>1060</v>
+        <v>1054</v>
       </c>
       <c r="B530" t="s">
-        <v>1061</v>
+        <v>1055</v>
       </c>
       <c r="D530" t="s">
         <v>9</v>
@@ -11637,10 +11727,10 @@
     </row>
     <row r="531" spans="1:4">
       <c r="A531" t="s">
-        <v>1062</v>
+        <v>1056</v>
       </c>
       <c r="B531" t="s">
-        <v>1063</v>
+        <v>1057</v>
       </c>
       <c r="D531" t="s">
         <v>9</v>
@@ -11648,10 +11738,10 @@
     </row>
     <row r="532" spans="1:4">
       <c r="A532" t="s">
-        <v>1064</v>
+        <v>1058</v>
       </c>
       <c r="B532" t="s">
-        <v>1065</v>
+        <v>1059</v>
       </c>
       <c r="D532" t="s">
         <v>9</v>
@@ -11659,10 +11749,10 @@
     </row>
     <row r="533" spans="1:4">
       <c r="A533" t="s">
-        <v>1066</v>
+        <v>1060</v>
       </c>
       <c r="B533" t="s">
-        <v>1067</v>
+        <v>1061</v>
       </c>
       <c r="D533" t="s">
         <v>9</v>
@@ -11670,10 +11760,10 @@
     </row>
     <row r="534" spans="1:4">
       <c r="A534" t="s">
-        <v>1068</v>
+        <v>1062</v>
       </c>
       <c r="B534" t="s">
-        <v>1069</v>
+        <v>1063</v>
       </c>
       <c r="D534" t="s">
         <v>9</v>
@@ -11681,10 +11771,10 @@
     </row>
     <row r="535" spans="1:4">
       <c r="A535" t="s">
-        <v>1070</v>
+        <v>1064</v>
       </c>
       <c r="B535" t="s">
-        <v>1071</v>
+        <v>1065</v>
       </c>
       <c r="D535" t="s">
         <v>9</v>
@@ -11692,10 +11782,10 @@
     </row>
     <row r="536" spans="1:4">
       <c r="A536" t="s">
-        <v>1072</v>
+        <v>1066</v>
       </c>
       <c r="B536" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="D536" t="s">
         <v>9</v>
@@ -11703,10 +11793,10 @@
     </row>
     <row r="537" spans="1:4">
       <c r="A537" t="s">
-        <v>1074</v>
+        <v>1068</v>
       </c>
       <c r="B537" t="s">
-        <v>1075</v>
+        <v>1069</v>
       </c>
       <c r="D537" t="s">
         <v>9</v>
@@ -11714,10 +11804,10 @@
     </row>
     <row r="538" spans="1:4">
       <c r="A538" t="s">
-        <v>1076</v>
+        <v>1070</v>
       </c>
       <c r="B538" t="s">
-        <v>1077</v>
+        <v>1071</v>
       </c>
       <c r="D538" t="s">
         <v>9</v>
@@ -11725,10 +11815,10 @@
     </row>
     <row r="539" spans="1:4">
       <c r="A539" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="B539" t="s">
-        <v>1079</v>
+        <v>1073</v>
       </c>
       <c r="D539" t="s">
         <v>9</v>
@@ -11736,10 +11826,10 @@
     </row>
     <row r="540" spans="1:4">
       <c r="A540" t="s">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="B540" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
       <c r="D540" t="s">
         <v>9</v>
@@ -11747,10 +11837,10 @@
     </row>
     <row r="541" spans="1:4">
       <c r="A541" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
       <c r="B541" t="s">
-        <v>1083</v>
+        <v>1077</v>
       </c>
       <c r="D541" t="s">
         <v>9</v>
@@ -11758,10 +11848,10 @@
     </row>
     <row r="542" spans="1:4">
       <c r="A542" t="s">
-        <v>1084</v>
+        <v>1078</v>
       </c>
       <c r="B542" t="s">
-        <v>1085</v>
+        <v>1079</v>
       </c>
       <c r="D542" t="s">
         <v>9</v>
@@ -11769,10 +11859,10 @@
     </row>
     <row r="543" spans="1:4">
       <c r="A543" t="s">
-        <v>1086</v>
+        <v>1080</v>
       </c>
       <c r="B543" t="s">
-        <v>1087</v>
+        <v>1081</v>
       </c>
       <c r="D543" t="s">
         <v>9</v>
@@ -11780,10 +11870,10 @@
     </row>
     <row r="544" spans="1:4">
       <c r="A544" t="s">
-        <v>1088</v>
+        <v>1082</v>
       </c>
       <c r="B544" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="D544" t="s">
         <v>9</v>
@@ -11791,10 +11881,10 @@
     </row>
     <row r="545" spans="1:4">
       <c r="A545" t="s">
-        <v>1090</v>
+        <v>1084</v>
       </c>
       <c r="B545" t="s">
-        <v>1091</v>
+        <v>1085</v>
       </c>
       <c r="D545" t="s">
         <v>9</v>
@@ -11802,10 +11892,10 @@
     </row>
     <row r="546" spans="1:4">
       <c r="A546" t="s">
-        <v>1092</v>
+        <v>1086</v>
       </c>
       <c r="B546" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="D546" t="s">
         <v>9</v>
@@ -11813,10 +11903,10 @@
     </row>
     <row r="547" spans="1:4">
       <c r="A547" t="s">
-        <v>1094</v>
+        <v>1088</v>
       </c>
       <c r="B547" t="s">
-        <v>1095</v>
+        <v>1089</v>
       </c>
       <c r="D547" t="s">
         <v>9</v>
@@ -11824,10 +11914,10 @@
     </row>
     <row r="548" spans="1:4">
       <c r="A548" t="s">
-        <v>1096</v>
+        <v>1090</v>
       </c>
       <c r="B548" t="s">
-        <v>1097</v>
+        <v>1091</v>
       </c>
       <c r="D548" t="s">
         <v>9</v>
@@ -11835,10 +11925,10 @@
     </row>
     <row r="549" spans="1:4">
       <c r="A549" t="s">
-        <v>1098</v>
+        <v>1092</v>
       </c>
       <c r="B549" t="s">
-        <v>1099</v>
+        <v>1093</v>
       </c>
       <c r="D549" t="s">
         <v>9</v>
@@ -11846,10 +11936,10 @@
     </row>
     <row r="550" spans="1:4">
       <c r="A550" t="s">
-        <v>1100</v>
+        <v>1094</v>
       </c>
       <c r="B550" t="s">
-        <v>1101</v>
+        <v>1095</v>
       </c>
       <c r="D550" t="s">
         <v>9</v>
@@ -11857,10 +11947,10 @@
     </row>
     <row r="551" spans="1:4">
       <c r="A551" t="s">
-        <v>1102</v>
+        <v>1096</v>
       </c>
       <c r="B551" t="s">
-        <v>1103</v>
+        <v>1097</v>
       </c>
       <c r="D551" t="s">
         <v>9</v>
@@ -11868,10 +11958,10 @@
     </row>
     <row r="552" spans="1:4">
       <c r="A552" t="s">
-        <v>1104</v>
+        <v>1098</v>
       </c>
       <c r="B552" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="D552" t="s">
         <v>9</v>
@@ -11879,10 +11969,10 @@
     </row>
     <row r="553" spans="1:4">
       <c r="A553" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
       <c r="B553" t="s">
-        <v>1107</v>
+        <v>1101</v>
       </c>
       <c r="D553" t="s">
         <v>9</v>
@@ -11890,10 +11980,10 @@
     </row>
     <row r="554" spans="1:4">
       <c r="A554" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
       <c r="B554" t="s">
-        <v>1109</v>
+        <v>1103</v>
       </c>
       <c r="D554" t="s">
         <v>9</v>
@@ -11901,10 +11991,10 @@
     </row>
     <row r="555" spans="1:4">
       <c r="A555" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
       <c r="B555" t="s">
-        <v>1111</v>
+        <v>1105</v>
       </c>
       <c r="D555" t="s">
         <v>9</v>
@@ -11912,10 +12002,10 @@
     </row>
     <row r="556" spans="1:4">
       <c r="A556" t="s">
-        <v>1112</v>
+        <v>1106</v>
       </c>
       <c r="B556" t="s">
-        <v>1113</v>
+        <v>1107</v>
       </c>
       <c r="D556" t="s">
         <v>9</v>
@@ -11923,10 +12013,10 @@
     </row>
     <row r="557" spans="1:4">
       <c r="A557" t="s">
-        <v>1114</v>
+        <v>1108</v>
       </c>
       <c r="B557" t="s">
-        <v>1115</v>
+        <v>1109</v>
       </c>
       <c r="D557" t="s">
         <v>9</v>
@@ -11934,10 +12024,10 @@
     </row>
     <row r="558" spans="1:4">
       <c r="A558" t="s">
-        <v>1116</v>
+        <v>1110</v>
       </c>
       <c r="B558" t="s">
-        <v>1117</v>
+        <v>1111</v>
       </c>
       <c r="D558" t="s">
         <v>9</v>
@@ -11945,10 +12035,10 @@
     </row>
     <row r="559" spans="1:4">
       <c r="A559" t="s">
-        <v>1118</v>
+        <v>1112</v>
       </c>
       <c r="B559" t="s">
-        <v>1119</v>
+        <v>1113</v>
       </c>
       <c r="D559" t="s">
         <v>9</v>
@@ -11956,10 +12046,10 @@
     </row>
     <row r="560" spans="1:4">
       <c r="A560" t="s">
-        <v>1120</v>
+        <v>1114</v>
       </c>
       <c r="B560" t="s">
-        <v>1121</v>
+        <v>1115</v>
       </c>
       <c r="D560" t="s">
         <v>9</v>
@@ -11967,10 +12057,10 @@
     </row>
     <row r="561" spans="1:4">
       <c r="A561" t="s">
-        <v>1122</v>
+        <v>1116</v>
       </c>
       <c r="B561" t="s">
-        <v>1123</v>
+        <v>1117</v>
       </c>
       <c r="D561" t="s">
         <v>9</v>
@@ -11978,10 +12068,10 @@
     </row>
     <row r="562" spans="1:4">
       <c r="A562" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
       <c r="B562" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
       <c r="D562" t="s">
         <v>9</v>
@@ -11989,10 +12079,10 @@
     </row>
     <row r="563" spans="1:4">
       <c r="A563" t="s">
-        <v>1126</v>
+        <v>1120</v>
       </c>
       <c r="B563" t="s">
-        <v>1127</v>
+        <v>1121</v>
       </c>
       <c r="D563" t="s">
         <v>9</v>
@@ -12000,10 +12090,10 @@
     </row>
     <row r="564" spans="1:4">
       <c r="A564" t="s">
-        <v>1128</v>
+        <v>1122</v>
       </c>
       <c r="B564" t="s">
-        <v>1129</v>
+        <v>1123</v>
       </c>
       <c r="D564" t="s">
         <v>9</v>
@@ -12011,10 +12101,10 @@
     </row>
     <row r="565" spans="1:4">
       <c r="A565" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="B565" t="s">
-        <v>1131</v>
+        <v>1125</v>
       </c>
       <c r="D565" t="s">
         <v>9</v>
@@ -12022,10 +12112,10 @@
     </row>
     <row r="566" spans="1:4">
       <c r="A566" t="s">
-        <v>1132</v>
+        <v>1126</v>
       </c>
       <c r="B566" t="s">
-        <v>1133</v>
+        <v>1127</v>
       </c>
       <c r="D566" t="s">
         <v>9</v>
@@ -12033,10 +12123,10 @@
     </row>
     <row r="567" spans="1:4">
       <c r="A567" t="s">
-        <v>1134</v>
+        <v>1128</v>
       </c>
       <c r="B567" t="s">
-        <v>1135</v>
+        <v>1129</v>
       </c>
       <c r="D567" t="s">
         <v>9</v>
@@ -12044,10 +12134,10 @@
     </row>
     <row r="568" spans="1:4">
       <c r="A568" t="s">
-        <v>1136</v>
+        <v>1130</v>
       </c>
       <c r="B568" t="s">
-        <v>1137</v>
+        <v>1131</v>
       </c>
       <c r="D568" t="s">
         <v>9</v>
@@ -12055,10 +12145,10 @@
     </row>
     <row r="569" spans="1:4">
       <c r="A569" t="s">
-        <v>1138</v>
+        <v>1132</v>
       </c>
       <c r="B569" t="s">
-        <v>1139</v>
+        <v>1133</v>
       </c>
       <c r="D569" t="s">
         <v>9</v>
@@ -12066,10 +12156,10 @@
     </row>
     <row r="570" spans="1:4">
       <c r="A570" t="s">
-        <v>1140</v>
+        <v>1134</v>
       </c>
       <c r="B570" t="s">
-        <v>1141</v>
+        <v>1135</v>
       </c>
       <c r="D570" t="s">
         <v>9</v>
@@ -12077,10 +12167,10 @@
     </row>
     <row r="571" spans="1:4">
       <c r="A571" t="s">
-        <v>1142</v>
+        <v>1136</v>
       </c>
       <c r="B571" t="s">
-        <v>1143</v>
+        <v>1137</v>
       </c>
       <c r="D571" t="s">
         <v>9</v>
@@ -12088,10 +12178,10 @@
     </row>
     <row r="572" spans="1:4">
       <c r="A572" t="s">
-        <v>1144</v>
+        <v>1138</v>
       </c>
       <c r="B572" t="s">
-        <v>1145</v>
+        <v>1139</v>
       </c>
       <c r="D572" t="s">
         <v>9</v>
@@ -12099,10 +12189,10 @@
     </row>
     <row r="573" spans="1:4">
       <c r="A573" t="s">
-        <v>1146</v>
+        <v>1140</v>
       </c>
       <c r="B573" t="s">
-        <v>1147</v>
+        <v>1141</v>
       </c>
       <c r="D573" t="s">
         <v>9</v>
@@ -12110,10 +12200,10 @@
     </row>
     <row r="574" spans="1:4">
       <c r="A574" t="s">
-        <v>1148</v>
+        <v>1142</v>
       </c>
       <c r="B574" t="s">
-        <v>1149</v>
+        <v>1143</v>
       </c>
       <c r="D574" t="s">
         <v>9</v>
@@ -12121,10 +12211,10 @@
     </row>
     <row r="575" spans="1:4">
       <c r="A575" t="s">
-        <v>1150</v>
+        <v>1144</v>
       </c>
       <c r="B575" t="s">
-        <v>1151</v>
+        <v>1145</v>
       </c>
       <c r="D575" t="s">
         <v>9</v>
@@ -12132,10 +12222,10 @@
     </row>
     <row r="576" spans="1:4">
       <c r="A576" t="s">
-        <v>1152</v>
+        <v>1146</v>
       </c>
       <c r="B576" t="s">
-        <v>1153</v>
+        <v>1147</v>
       </c>
       <c r="D576" t="s">
         <v>9</v>
@@ -12143,10 +12233,10 @@
     </row>
     <row r="577" spans="1:4">
       <c r="A577" t="s">
-        <v>1154</v>
+        <v>1148</v>
       </c>
       <c r="B577" t="s">
-        <v>1155</v>
+        <v>1149</v>
       </c>
       <c r="D577" t="s">
         <v>9</v>
@@ -12154,10 +12244,10 @@
     </row>
     <row r="578" spans="1:4">
       <c r="A578" t="s">
-        <v>1156</v>
+        <v>1150</v>
       </c>
       <c r="B578" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="D578" t="s">
         <v>9</v>
@@ -12165,10 +12255,10 @@
     </row>
     <row r="579" spans="1:4">
       <c r="A579" t="s">
-        <v>1158</v>
+        <v>1152</v>
       </c>
       <c r="B579" t="s">
-        <v>1159</v>
+        <v>1153</v>
       </c>
       <c r="D579" t="s">
         <v>9</v>
@@ -12176,10 +12266,10 @@
     </row>
     <row r="580" spans="1:4">
       <c r="A580" t="s">
-        <v>1160</v>
+        <v>1154</v>
       </c>
       <c r="B580" t="s">
-        <v>1161</v>
+        <v>1155</v>
       </c>
       <c r="D580" t="s">
         <v>9</v>
@@ -12187,10 +12277,10 @@
     </row>
     <row r="581" spans="1:4">
       <c r="A581" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
       <c r="B581" t="s">
-        <v>1163</v>
+        <v>1157</v>
       </c>
       <c r="D581" t="s">
         <v>9</v>
@@ -12198,10 +12288,10 @@
     </row>
     <row r="582" spans="1:4">
       <c r="A582" t="s">
-        <v>1164</v>
+        <v>1158</v>
       </c>
       <c r="B582" t="s">
-        <v>1165</v>
+        <v>1159</v>
       </c>
       <c r="D582" t="s">
         <v>9</v>
@@ -12209,10 +12299,10 @@
     </row>
     <row r="583" spans="1:4">
       <c r="A583" t="s">
-        <v>1166</v>
+        <v>1160</v>
       </c>
       <c r="B583" t="s">
-        <v>1167</v>
+        <v>1161</v>
       </c>
       <c r="D583" t="s">
         <v>9</v>
@@ -12220,10 +12310,10 @@
     </row>
     <row r="584" spans="1:4">
       <c r="A584" t="s">
-        <v>1168</v>
+        <v>1162</v>
       </c>
       <c r="B584" t="s">
-        <v>1169</v>
+        <v>1163</v>
       </c>
       <c r="D584" t="s">
         <v>9</v>
@@ -12231,10 +12321,10 @@
     </row>
     <row r="585" spans="1:4">
       <c r="A585" t="s">
-        <v>1170</v>
+        <v>1164</v>
       </c>
       <c r="B585" t="s">
-        <v>1171</v>
+        <v>1165</v>
       </c>
       <c r="D585" t="s">
         <v>9</v>
@@ -12242,10 +12332,10 @@
     </row>
     <row r="586" spans="1:4">
       <c r="A586" t="s">
-        <v>1172</v>
+        <v>1166</v>
       </c>
       <c r="B586" t="s">
-        <v>1173</v>
+        <v>1167</v>
       </c>
       <c r="D586" t="s">
         <v>9</v>
@@ -12253,10 +12343,10 @@
     </row>
     <row r="587" spans="1:4">
       <c r="A587" t="s">
-        <v>1174</v>
+        <v>1168</v>
       </c>
       <c r="B587" t="s">
-        <v>1175</v>
+        <v>1169</v>
       </c>
       <c r="D587" t="s">
         <v>9</v>
@@ -12264,10 +12354,10 @@
     </row>
     <row r="588" spans="1:4">
       <c r="A588" t="s">
-        <v>1176</v>
+        <v>1170</v>
       </c>
       <c r="B588" t="s">
-        <v>1177</v>
+        <v>1171</v>
       </c>
       <c r="D588" t="s">
         <v>9</v>
@@ -12275,10 +12365,10 @@
     </row>
     <row r="589" spans="1:4">
       <c r="A589" t="s">
-        <v>1178</v>
+        <v>1172</v>
       </c>
       <c r="B589" t="s">
-        <v>1179</v>
+        <v>1173</v>
       </c>
       <c r="D589" t="s">
         <v>9</v>
@@ -12286,10 +12376,10 @@
     </row>
     <row r="590" spans="1:4">
       <c r="A590" t="s">
-        <v>1180</v>
+        <v>1174</v>
       </c>
       <c r="B590" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="D590" t="s">
         <v>9</v>
@@ -12297,10 +12387,10 @@
     </row>
     <row r="591" spans="1:4">
       <c r="A591" t="s">
-        <v>1182</v>
+        <v>1176</v>
       </c>
       <c r="B591" t="s">
-        <v>1183</v>
+        <v>1177</v>
       </c>
       <c r="D591" t="s">
         <v>9</v>
@@ -12308,10 +12398,10 @@
     </row>
     <row r="592" spans="1:4">
       <c r="A592" t="s">
-        <v>1184</v>
+        <v>1178</v>
       </c>
       <c r="B592" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
       <c r="D592" t="s">
         <v>9</v>
@@ -12319,10 +12409,10 @@
     </row>
     <row r="593" spans="1:4">
       <c r="A593" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="B593" t="s">
-        <v>1187</v>
+        <v>1181</v>
       </c>
       <c r="D593" t="s">
         <v>9</v>
@@ -12330,10 +12420,10 @@
     </row>
     <row r="594" spans="1:4">
       <c r="A594" t="s">
-        <v>1188</v>
+        <v>1182</v>
       </c>
       <c r="B594" t="s">
-        <v>1189</v>
+        <v>1183</v>
       </c>
       <c r="D594" t="s">
         <v>9</v>
@@ -12341,10 +12431,10 @@
     </row>
     <row r="595" spans="1:4">
       <c r="A595" t="s">
-        <v>1190</v>
+        <v>1184</v>
       </c>
       <c r="B595" t="s">
-        <v>1191</v>
+        <v>1185</v>
       </c>
       <c r="D595" t="s">
         <v>9</v>
@@ -12352,10 +12442,10 @@
     </row>
     <row r="596" spans="1:4">
       <c r="A596" t="s">
-        <v>1192</v>
+        <v>1186</v>
       </c>
       <c r="B596" t="s">
-        <v>1193</v>
+        <v>1187</v>
       </c>
       <c r="D596" t="s">
         <v>9</v>
@@ -12363,10 +12453,10 @@
     </row>
     <row r="597" spans="1:4">
       <c r="A597" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="B597" t="s">
-        <v>1195</v>
+        <v>1189</v>
       </c>
       <c r="D597" t="s">
         <v>9</v>
@@ -12374,10 +12464,10 @@
     </row>
     <row r="598" spans="1:4">
       <c r="A598" t="s">
-        <v>1196</v>
+        <v>1190</v>
       </c>
       <c r="B598" t="s">
-        <v>1197</v>
+        <v>1191</v>
       </c>
       <c r="D598" t="s">
         <v>9</v>
@@ -12385,10 +12475,10 @@
     </row>
     <row r="599" spans="1:4">
       <c r="A599" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="B599" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="D599" t="s">
         <v>9</v>
@@ -12396,10 +12486,10 @@
     </row>
     <row r="600" spans="1:4">
       <c r="A600" t="s">
-        <v>1200</v>
+        <v>1194</v>
       </c>
       <c r="B600" t="s">
-        <v>1201</v>
+        <v>1195</v>
       </c>
       <c r="D600" t="s">
         <v>9</v>
@@ -12407,10 +12497,10 @@
     </row>
     <row r="601" spans="1:4">
       <c r="A601" t="s">
-        <v>1202</v>
+        <v>1196</v>
       </c>
       <c r="B601" t="s">
-        <v>1203</v>
+        <v>1197</v>
       </c>
       <c r="D601" t="s">
         <v>9</v>
@@ -12418,10 +12508,10 @@
     </row>
     <row r="602" spans="1:4">
       <c r="A602" t="s">
-        <v>1204</v>
+        <v>1198</v>
       </c>
       <c r="B602" t="s">
-        <v>1205</v>
+        <v>1199</v>
       </c>
       <c r="D602" t="s">
         <v>9</v>
@@ -12429,10 +12519,10 @@
     </row>
     <row r="603" spans="1:4">
       <c r="A603" t="s">
-        <v>1206</v>
+        <v>1200</v>
       </c>
       <c r="B603" t="s">
-        <v>1207</v>
+        <v>1201</v>
       </c>
       <c r="D603" t="s">
         <v>9</v>
@@ -12440,10 +12530,10 @@
     </row>
     <row r="604" spans="1:4">
       <c r="A604" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
       <c r="B604" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="D604" t="s">
         <v>9</v>
@@ -12451,10 +12541,10 @@
     </row>
     <row r="605" spans="1:4">
       <c r="A605" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="B605" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="D605" t="s">
         <v>9</v>
@@ -12462,10 +12552,10 @@
     </row>
     <row r="606" spans="1:4">
       <c r="A606" t="s">
-        <v>1212</v>
+        <v>1206</v>
       </c>
       <c r="B606" t="s">
-        <v>1213</v>
+        <v>1207</v>
       </c>
       <c r="D606" t="s">
         <v>9</v>
@@ -12473,10 +12563,10 @@
     </row>
     <row r="607" spans="1:4">
       <c r="A607" t="s">
-        <v>1214</v>
+        <v>1208</v>
       </c>
       <c r="B607" t="s">
-        <v>1215</v>
+        <v>1209</v>
       </c>
       <c r="D607" t="s">
         <v>9</v>
@@ -12484,10 +12574,10 @@
     </row>
     <row r="608" spans="1:4">
       <c r="A608" t="s">
-        <v>1216</v>
+        <v>1210</v>
       </c>
       <c r="B608" t="s">
-        <v>1217</v>
+        <v>1211</v>
       </c>
       <c r="D608" t="s">
         <v>9</v>
@@ -12495,10 +12585,10 @@
     </row>
     <row r="609" spans="1:4">
       <c r="A609" t="s">
-        <v>1218</v>
+        <v>1212</v>
       </c>
       <c r="B609" t="s">
-        <v>1219</v>
+        <v>1213</v>
       </c>
       <c r="D609" t="s">
         <v>9</v>
@@ -12506,10 +12596,10 @@
     </row>
     <row r="610" spans="1:4">
       <c r="A610" t="s">
-        <v>1220</v>
+        <v>1214</v>
       </c>
       <c r="B610" t="s">
-        <v>1221</v>
+        <v>1215</v>
       </c>
       <c r="D610" t="s">
         <v>9</v>
@@ -12517,10 +12607,10 @@
     </row>
     <row r="611" spans="1:4">
       <c r="A611" t="s">
-        <v>1222</v>
+        <v>1216</v>
       </c>
       <c r="B611" t="s">
-        <v>1223</v>
+        <v>1217</v>
       </c>
       <c r="D611" t="s">
         <v>9</v>
@@ -12528,10 +12618,10 @@
     </row>
     <row r="612" spans="1:4">
       <c r="A612" t="s">
-        <v>1224</v>
+        <v>1218</v>
       </c>
       <c r="B612" t="s">
-        <v>1225</v>
+        <v>1219</v>
       </c>
       <c r="D612" t="s">
         <v>9</v>
@@ -12539,10 +12629,10 @@
     </row>
     <row r="613" spans="1:4">
       <c r="A613" t="s">
-        <v>1226</v>
+        <v>1220</v>
       </c>
       <c r="B613" t="s">
-        <v>1227</v>
+        <v>1219</v>
       </c>
       <c r="D613" t="s">
         <v>9</v>
@@ -12550,10 +12640,10 @@
     </row>
     <row r="614" spans="1:4">
       <c r="A614" t="s">
-        <v>1228</v>
+        <v>1221</v>
       </c>
       <c r="B614" t="s">
-        <v>1229</v>
+        <v>1222</v>
       </c>
       <c r="D614" t="s">
         <v>9</v>
@@ -12561,10 +12651,10 @@
     </row>
     <row r="615" spans="1:4">
       <c r="A615" t="s">
-        <v>1230</v>
+        <v>1223</v>
       </c>
       <c r="B615" t="s">
-        <v>1231</v>
+        <v>1224</v>
       </c>
       <c r="D615" t="s">
         <v>9</v>
@@ -12572,10 +12662,10 @@
     </row>
     <row r="616" spans="1:4">
       <c r="A616" t="s">
-        <v>1232</v>
+        <v>1225</v>
       </c>
       <c r="B616" t="s">
-        <v>1233</v>
+        <v>1226</v>
       </c>
       <c r="D616" t="s">
         <v>9</v>
@@ -12583,10 +12673,10 @@
     </row>
     <row r="617" spans="1:4">
       <c r="A617" t="s">
-        <v>1234</v>
+        <v>1227</v>
       </c>
       <c r="B617" t="s">
-        <v>1235</v>
+        <v>1228</v>
       </c>
       <c r="D617" t="s">
         <v>9</v>
@@ -12594,10 +12684,10 @@
     </row>
     <row r="618" spans="1:4">
       <c r="A618" t="s">
-        <v>1236</v>
+        <v>1229</v>
       </c>
       <c r="B618" t="s">
-        <v>1237</v>
+        <v>1230</v>
       </c>
       <c r="D618" t="s">
         <v>9</v>
@@ -12605,10 +12695,10 @@
     </row>
     <row r="619" spans="1:4">
       <c r="A619" t="s">
-        <v>1238</v>
+        <v>1231</v>
       </c>
       <c r="B619" t="s">
-        <v>1239</v>
+        <v>1232</v>
       </c>
       <c r="D619" t="s">
         <v>9</v>
@@ -12616,10 +12706,10 @@
     </row>
     <row r="620" spans="1:4">
       <c r="A620" t="s">
-        <v>1240</v>
+        <v>1233</v>
       </c>
       <c r="B620" t="s">
-        <v>1241</v>
+        <v>1232</v>
       </c>
       <c r="D620" t="s">
         <v>9</v>
@@ -12627,10 +12717,10 @@
     </row>
     <row r="621" spans="1:4">
       <c r="A621" t="s">
-        <v>1242</v>
+        <v>1234</v>
       </c>
       <c r="B621" t="s">
-        <v>1243</v>
+        <v>1235</v>
       </c>
       <c r="D621" t="s">
         <v>9</v>
@@ -12638,10 +12728,10 @@
     </row>
     <row r="622" spans="1:4">
       <c r="A622" t="s">
-        <v>1244</v>
+        <v>1236</v>
       </c>
       <c r="B622" t="s">
-        <v>1245</v>
+        <v>1237</v>
       </c>
       <c r="D622" t="s">
         <v>9</v>
@@ -12649,10 +12739,10 @@
     </row>
     <row r="623" spans="1:4">
       <c r="A623" t="s">
-        <v>1246</v>
+        <v>1238</v>
       </c>
       <c r="B623" t="s">
-        <v>1247</v>
+        <v>1239</v>
       </c>
       <c r="D623" t="s">
         <v>9</v>
@@ -12660,10 +12750,10 @@
     </row>
     <row r="624" spans="1:4">
       <c r="A624" t="s">
-        <v>1248</v>
+        <v>1240</v>
       </c>
       <c r="B624" t="s">
-        <v>1249</v>
+        <v>1241</v>
       </c>
       <c r="D624" t="s">
         <v>9</v>
@@ -12671,10 +12761,10 @@
     </row>
     <row r="625" spans="1:4">
       <c r="A625" t="s">
-        <v>1250</v>
+        <v>1242</v>
       </c>
       <c r="B625" t="s">
-        <v>1251</v>
+        <v>1241</v>
       </c>
       <c r="D625" t="s">
         <v>9</v>
@@ -12682,10 +12772,10 @@
     </row>
     <row r="626" spans="1:4">
       <c r="A626" t="s">
-        <v>1252</v>
+        <v>1243</v>
       </c>
       <c r="B626" t="s">
-        <v>1253</v>
+        <v>1244</v>
       </c>
       <c r="D626" t="s">
         <v>9</v>
@@ -12693,10 +12783,10 @@
     </row>
     <row r="627" spans="1:4">
       <c r="A627" t="s">
-        <v>1254</v>
+        <v>1245</v>
       </c>
       <c r="B627" t="s">
-        <v>1255</v>
+        <v>1246</v>
       </c>
       <c r="D627" t="s">
         <v>9</v>
@@ -12704,10 +12794,10 @@
     </row>
     <row r="628" spans="1:4">
       <c r="A628" t="s">
-        <v>1256</v>
+        <v>1247</v>
       </c>
       <c r="B628" t="s">
-        <v>1257</v>
+        <v>1248</v>
       </c>
       <c r="D628" t="s">
         <v>9</v>
@@ -12715,10 +12805,10 @@
     </row>
     <row r="629" spans="1:4">
       <c r="A629" t="s">
-        <v>1258</v>
+        <v>1249</v>
       </c>
       <c r="B629" t="s">
-        <v>1259</v>
+        <v>1248</v>
       </c>
       <c r="D629" t="s">
         <v>9</v>
@@ -12726,10 +12816,10 @@
     </row>
     <row r="630" spans="1:4">
       <c r="A630" t="s">
-        <v>1260</v>
+        <v>1250</v>
       </c>
       <c r="B630" t="s">
-        <v>1261</v>
+        <v>1251</v>
       </c>
       <c r="D630" t="s">
         <v>9</v>
@@ -12737,10 +12827,10 @@
     </row>
     <row r="631" spans="1:4">
       <c r="A631" t="s">
-        <v>1262</v>
+        <v>1252</v>
       </c>
       <c r="B631" t="s">
-        <v>1263</v>
+        <v>1253</v>
       </c>
       <c r="D631" t="s">
         <v>9</v>
@@ -12748,10 +12838,10 @@
     </row>
     <row r="632" spans="1:4">
       <c r="A632" t="s">
-        <v>1264</v>
+        <v>1254</v>
       </c>
       <c r="B632" t="s">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="D632" t="s">
         <v>9</v>
@@ -12759,10 +12849,10 @@
     </row>
     <row r="633" spans="1:4">
       <c r="A633" t="s">
-        <v>1266</v>
+        <v>1256</v>
       </c>
       <c r="B633" t="s">
-        <v>1267</v>
+        <v>1257</v>
       </c>
       <c r="D633" t="s">
         <v>9</v>
@@ -12770,10 +12860,10 @@
     </row>
     <row r="634" spans="1:4">
       <c r="A634" t="s">
-        <v>1268</v>
+        <v>1258</v>
       </c>
       <c r="B634" t="s">
-        <v>1269</v>
+        <v>1259</v>
       </c>
       <c r="D634" t="s">
         <v>9</v>
@@ -12781,10 +12871,10 @@
     </row>
     <row r="635" spans="1:4">
       <c r="A635" t="s">
-        <v>1270</v>
+        <v>1260</v>
       </c>
       <c r="B635" t="s">
-        <v>1271</v>
+        <v>1261</v>
       </c>
       <c r="D635" t="s">
         <v>9</v>
@@ -12792,10 +12882,10 @@
     </row>
     <row r="636" spans="1:4">
       <c r="A636" t="s">
-        <v>1272</v>
+        <v>1262</v>
       </c>
       <c r="B636" t="s">
-        <v>1273</v>
+        <v>1263</v>
       </c>
       <c r="D636" t="s">
         <v>9</v>
@@ -12803,10 +12893,10 @@
     </row>
     <row r="637" spans="1:4">
       <c r="A637" t="s">
-        <v>1274</v>
+        <v>1264</v>
       </c>
       <c r="B637" t="s">
-        <v>1275</v>
+        <v>1265</v>
       </c>
       <c r="D637" t="s">
         <v>9</v>
@@ -12814,10 +12904,10 @@
     </row>
     <row r="638" spans="1:4">
       <c r="A638" t="s">
-        <v>1276</v>
+        <v>1266</v>
       </c>
       <c r="B638" t="s">
-        <v>1277</v>
+        <v>1267</v>
       </c>
       <c r="D638" t="s">
         <v>9</v>
@@ -12825,10 +12915,10 @@
     </row>
     <row r="639" spans="1:4">
       <c r="A639" t="s">
-        <v>1278</v>
+        <v>1268</v>
       </c>
       <c r="B639" t="s">
-        <v>1279</v>
+        <v>1269</v>
       </c>
       <c r="D639" t="s">
         <v>9</v>
@@ -12836,10 +12926,10 @@
     </row>
     <row r="640" spans="1:4">
       <c r="A640" t="s">
-        <v>1280</v>
+        <v>1270</v>
       </c>
       <c r="B640" t="s">
-        <v>1281</v>
+        <v>1271</v>
       </c>
       <c r="D640" t="s">
         <v>9</v>
@@ -12847,10 +12937,10 @@
     </row>
     <row r="641" spans="1:4">
       <c r="A641" t="s">
-        <v>1282</v>
+        <v>1272</v>
       </c>
       <c r="B641" t="s">
-        <v>1283</v>
+        <v>1271</v>
       </c>
       <c r="D641" t="s">
         <v>9</v>
@@ -12858,10 +12948,10 @@
     </row>
     <row r="642" spans="1:4">
       <c r="A642" t="s">
-        <v>1284</v>
+        <v>1273</v>
       </c>
       <c r="B642" t="s">
-        <v>1285</v>
+        <v>1274</v>
       </c>
       <c r="D642" t="s">
         <v>9</v>
@@ -12869,10 +12959,10 @@
     </row>
     <row r="643" spans="1:4">
       <c r="A643" t="s">
-        <v>1286</v>
+        <v>1275</v>
       </c>
       <c r="B643" t="s">
-        <v>1287</v>
+        <v>1276</v>
       </c>
       <c r="D643" t="s">
         <v>9</v>
@@ -12880,10 +12970,10 @@
     </row>
     <row r="644" spans="1:4">
       <c r="A644" t="s">
-        <v>1288</v>
+        <v>1277</v>
       </c>
       <c r="B644" t="s">
-        <v>1289</v>
+        <v>1278</v>
       </c>
       <c r="D644" t="s">
         <v>9</v>
@@ -12891,10 +12981,10 @@
     </row>
     <row r="645" spans="1:4">
       <c r="A645" t="s">
-        <v>1290</v>
+        <v>1279</v>
       </c>
       <c r="B645" t="s">
-        <v>1291</v>
+        <v>1280</v>
       </c>
       <c r="D645" t="s">
         <v>9</v>
@@ -12902,10 +12992,10 @@
     </row>
     <row r="646" spans="1:4">
       <c r="A646" t="s">
-        <v>1292</v>
+        <v>1281</v>
       </c>
       <c r="B646" t="s">
-        <v>1293</v>
+        <v>1282</v>
       </c>
       <c r="D646" t="s">
         <v>9</v>
@@ -12913,10 +13003,10 @@
     </row>
     <row r="647" spans="1:4">
       <c r="A647" t="s">
-        <v>1294</v>
+        <v>1283</v>
       </c>
       <c r="B647" t="s">
-        <v>1295</v>
+        <v>1284</v>
       </c>
       <c r="D647" t="s">
         <v>9</v>
@@ -12924,10 +13014,10 @@
     </row>
     <row r="648" spans="1:4">
       <c r="A648" t="s">
-        <v>1296</v>
+        <v>1285</v>
       </c>
       <c r="B648" t="s">
-        <v>1297</v>
+        <v>1286</v>
       </c>
       <c r="D648" t="s">
         <v>9</v>
@@ -12935,10 +13025,10 @@
     </row>
     <row r="649" spans="1:4">
       <c r="A649" t="s">
-        <v>1298</v>
+        <v>1287</v>
       </c>
       <c r="B649" t="s">
-        <v>1299</v>
+        <v>1288</v>
       </c>
       <c r="D649" t="s">
         <v>9</v>
@@ -12946,10 +13036,10 @@
     </row>
     <row r="650" spans="1:4">
       <c r="A650" t="s">
-        <v>1300</v>
+        <v>1289</v>
       </c>
       <c r="B650" t="s">
-        <v>1301</v>
+        <v>1290</v>
       </c>
       <c r="D650" t="s">
         <v>9</v>
@@ -12957,10 +13047,10 @@
     </row>
     <row r="651" spans="1:4">
       <c r="A651" t="s">
-        <v>1302</v>
+        <v>1291</v>
       </c>
       <c r="B651" t="s">
-        <v>1303</v>
+        <v>1292</v>
       </c>
       <c r="D651" t="s">
         <v>9</v>
@@ -12968,10 +13058,10 @@
     </row>
     <row r="652" spans="1:4">
       <c r="A652" t="s">
-        <v>1304</v>
+        <v>1293</v>
       </c>
       <c r="B652" t="s">
-        <v>1305</v>
+        <v>1294</v>
       </c>
       <c r="D652" t="s">
         <v>9</v>
@@ -12979,10 +13069,10 @@
     </row>
     <row r="653" spans="1:4">
       <c r="A653" t="s">
-        <v>1306</v>
+        <v>1295</v>
       </c>
       <c r="B653" t="s">
-        <v>1307</v>
+        <v>1296</v>
       </c>
       <c r="D653" t="s">
         <v>9</v>
@@ -12990,10 +13080,10 @@
     </row>
     <row r="654" spans="1:4">
       <c r="A654" t="s">
-        <v>1308</v>
+        <v>1297</v>
       </c>
       <c r="B654" t="s">
-        <v>1309</v>
+        <v>1298</v>
       </c>
       <c r="D654" t="s">
         <v>9</v>
@@ -13001,10 +13091,10 @@
     </row>
     <row r="655" spans="1:4">
       <c r="A655" t="s">
-        <v>1310</v>
+        <v>1299</v>
       </c>
       <c r="B655" t="s">
-        <v>1311</v>
+        <v>1300</v>
       </c>
       <c r="D655" t="s">
         <v>9</v>
@@ -13012,10 +13102,10 @@
     </row>
     <row r="656" spans="1:4">
       <c r="A656" t="s">
-        <v>1312</v>
+        <v>1301</v>
       </c>
       <c r="B656" t="s">
-        <v>1313</v>
+        <v>1302</v>
       </c>
       <c r="D656" t="s">
         <v>9</v>
@@ -13023,10 +13113,10 @@
     </row>
     <row r="657" spans="1:4">
       <c r="A657" t="s">
-        <v>1314</v>
+        <v>1303</v>
       </c>
       <c r="B657" t="s">
-        <v>1315</v>
+        <v>1302</v>
       </c>
       <c r="D657" t="s">
         <v>9</v>
@@ -13034,10 +13124,10 @@
     </row>
     <row r="658" spans="1:4">
       <c r="A658" t="s">
-        <v>1316</v>
+        <v>1304</v>
       </c>
       <c r="B658" t="s">
-        <v>1317</v>
+        <v>1305</v>
       </c>
       <c r="D658" t="s">
         <v>9</v>
@@ -13045,10 +13135,10 @@
     </row>
     <row r="659" spans="1:4">
       <c r="A659" t="s">
-        <v>1318</v>
+        <v>1306</v>
       </c>
       <c r="B659" t="s">
-        <v>1319</v>
+        <v>1307</v>
       </c>
       <c r="D659" t="s">
         <v>9</v>
@@ -13056,10 +13146,10 @@
     </row>
     <row r="660" spans="1:4">
       <c r="A660" t="s">
-        <v>1320</v>
+        <v>1308</v>
       </c>
       <c r="B660" t="s">
-        <v>1321</v>
+        <v>1309</v>
       </c>
       <c r="D660" t="s">
         <v>9</v>
@@ -13067,10 +13157,10 @@
     </row>
     <row r="661" spans="1:4">
       <c r="A661" t="s">
-        <v>1322</v>
+        <v>1310</v>
       </c>
       <c r="B661" t="s">
-        <v>1323</v>
+        <v>1311</v>
       </c>
       <c r="D661" t="s">
         <v>9</v>
@@ -13078,10 +13168,10 @@
     </row>
     <row r="662" spans="1:4">
       <c r="A662" t="s">
-        <v>1324</v>
+        <v>1312</v>
       </c>
       <c r="B662" t="s">
-        <v>1325</v>
+        <v>1313</v>
       </c>
       <c r="D662" t="s">
         <v>9</v>
@@ -13089,10 +13179,10 @@
     </row>
     <row r="663" spans="1:4">
       <c r="A663" t="s">
-        <v>1326</v>
+        <v>1314</v>
       </c>
       <c r="B663" t="s">
-        <v>1327</v>
+        <v>1315</v>
       </c>
       <c r="D663" t="s">
         <v>9</v>
@@ -13100,10 +13190,10 @@
     </row>
     <row r="664" spans="1:4">
       <c r="A664" t="s">
-        <v>1328</v>
+        <v>1316</v>
       </c>
       <c r="B664" t="s">
-        <v>1329</v>
+        <v>1317</v>
       </c>
       <c r="D664" t="s">
         <v>9</v>
@@ -13111,10 +13201,10 @@
     </row>
     <row r="665" spans="1:4">
       <c r="A665" t="s">
-        <v>1330</v>
+        <v>1318</v>
       </c>
       <c r="B665" t="s">
-        <v>1331</v>
+        <v>1319</v>
       </c>
       <c r="D665" t="s">
         <v>9</v>
@@ -13122,10 +13212,10 @@
     </row>
     <row r="666" spans="1:4">
       <c r="A666" t="s">
-        <v>1332</v>
+        <v>1320</v>
       </c>
       <c r="B666" t="s">
-        <v>1333</v>
+        <v>1321</v>
       </c>
       <c r="D666" t="s">
         <v>9</v>
@@ -13133,10 +13223,10 @@
     </row>
     <row r="667" spans="1:4">
       <c r="A667" t="s">
-        <v>1334</v>
+        <v>1322</v>
       </c>
       <c r="B667" t="s">
-        <v>1335</v>
+        <v>1323</v>
       </c>
       <c r="D667" t="s">
         <v>9</v>
@@ -13144,10 +13234,10 @@
     </row>
     <row r="668" spans="1:4">
       <c r="A668" t="s">
-        <v>1336</v>
+        <v>1324</v>
       </c>
       <c r="B668" t="s">
-        <v>1337</v>
+        <v>1325</v>
       </c>
       <c r="D668" t="s">
         <v>9</v>
@@ -13155,10 +13245,10 @@
     </row>
     <row r="669" spans="1:4">
       <c r="A669" t="s">
-        <v>1338</v>
+        <v>1326</v>
       </c>
       <c r="B669" t="s">
-        <v>1339</v>
+        <v>1327</v>
       </c>
       <c r="D669" t="s">
         <v>9</v>
@@ -13166,10 +13256,10 @@
     </row>
     <row r="670" spans="1:4">
       <c r="A670" t="s">
-        <v>1340</v>
+        <v>1328</v>
       </c>
       <c r="B670" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
       <c r="D670" t="s">
         <v>9</v>
@@ -13177,10 +13267,10 @@
     </row>
     <row r="671" spans="1:4">
       <c r="A671" t="s">
-        <v>1342</v>
+        <v>1330</v>
       </c>
       <c r="B671" t="s">
-        <v>1343</v>
+        <v>1331</v>
       </c>
       <c r="D671" t="s">
         <v>9</v>
@@ -13188,10 +13278,10 @@
     </row>
     <row r="672" spans="1:4">
       <c r="A672" t="s">
-        <v>1344</v>
+        <v>1332</v>
       </c>
       <c r="B672" t="s">
-        <v>1345</v>
+        <v>1333</v>
       </c>
       <c r="D672" t="s">
         <v>9</v>
@@ -13199,10 +13289,10 @@
     </row>
     <row r="673" spans="1:4">
       <c r="A673" t="s">
-        <v>1346</v>
+        <v>1334</v>
       </c>
       <c r="B673" t="s">
-        <v>1347</v>
+        <v>1335</v>
       </c>
       <c r="D673" t="s">
         <v>9</v>
@@ -13210,10 +13300,10 @@
     </row>
     <row r="674" spans="1:4">
       <c r="A674" t="s">
-        <v>1348</v>
+        <v>1336</v>
       </c>
       <c r="B674" t="s">
-        <v>1349</v>
+        <v>1337</v>
       </c>
       <c r="D674" t="s">
         <v>9</v>
@@ -13221,10 +13311,10 @@
     </row>
     <row r="675" spans="1:4">
       <c r="A675" t="s">
-        <v>1350</v>
+        <v>1338</v>
       </c>
       <c r="B675" t="s">
-        <v>1351</v>
+        <v>1339</v>
       </c>
       <c r="D675" t="s">
         <v>9</v>
@@ -13232,10 +13322,10 @@
     </row>
     <row r="676" spans="1:4">
       <c r="A676" t="s">
-        <v>1352</v>
+        <v>1340</v>
       </c>
       <c r="B676" t="s">
-        <v>1353</v>
+        <v>1341</v>
       </c>
       <c r="D676" t="s">
         <v>9</v>
@@ -13243,10 +13333,10 @@
     </row>
     <row r="677" spans="1:4">
       <c r="A677" t="s">
-        <v>1354</v>
+        <v>1342</v>
       </c>
       <c r="B677" t="s">
-        <v>1355</v>
+        <v>1343</v>
       </c>
       <c r="D677" t="s">
         <v>9</v>
@@ -13254,10 +13344,10 @@
     </row>
     <row r="678" spans="1:4">
       <c r="A678" t="s">
-        <v>1356</v>
+        <v>1344</v>
       </c>
       <c r="B678" t="s">
-        <v>1357</v>
+        <v>1343</v>
       </c>
       <c r="D678" t="s">
         <v>9</v>
@@ -13265,10 +13355,10 @@
     </row>
     <row r="679" spans="1:4">
       <c r="A679" t="s">
-        <v>1358</v>
+        <v>1345</v>
       </c>
       <c r="B679" t="s">
-        <v>1359</v>
+        <v>1346</v>
       </c>
       <c r="D679" t="s">
         <v>9</v>
@@ -13276,10 +13366,10 @@
     </row>
     <row r="680" spans="1:4">
       <c r="A680" t="s">
-        <v>1360</v>
+        <v>1347</v>
       </c>
       <c r="B680" t="s">
-        <v>1361</v>
+        <v>1348</v>
       </c>
       <c r="D680" t="s">
         <v>9</v>
@@ -13287,10 +13377,10 @@
     </row>
     <row r="681" spans="1:4">
       <c r="A681" t="s">
-        <v>1362</v>
+        <v>1349</v>
       </c>
       <c r="B681" t="s">
-        <v>1363</v>
+        <v>1350</v>
       </c>
       <c r="D681" t="s">
         <v>9</v>
@@ -13298,10 +13388,10 @@
     </row>
     <row r="682" spans="1:4">
       <c r="A682" t="s">
-        <v>1364</v>
+        <v>1351</v>
       </c>
       <c r="B682" t="s">
-        <v>1365</v>
+        <v>1352</v>
       </c>
       <c r="D682" t="s">
         <v>9</v>
@@ -13309,10 +13399,10 @@
     </row>
     <row r="683" spans="1:4">
       <c r="A683" t="s">
-        <v>1366</v>
+        <v>1353</v>
       </c>
       <c r="B683" t="s">
-        <v>1367</v>
+        <v>1354</v>
       </c>
       <c r="D683" t="s">
         <v>9</v>
@@ -13320,10 +13410,10 @@
     </row>
     <row r="684" spans="1:4">
       <c r="A684" t="s">
-        <v>1368</v>
+        <v>1355</v>
       </c>
       <c r="B684" t="s">
-        <v>1369</v>
+        <v>1356</v>
       </c>
       <c r="D684" t="s">
         <v>9</v>
@@ -13331,10 +13421,10 @@
     </row>
     <row r="685" spans="1:4">
       <c r="A685" t="s">
-        <v>1370</v>
+        <v>1357</v>
       </c>
       <c r="B685" t="s">
-        <v>1371</v>
+        <v>1358</v>
       </c>
       <c r="D685" t="s">
         <v>9</v>
@@ -13342,10 +13432,10 @@
     </row>
     <row r="686" spans="1:4">
       <c r="A686" t="s">
-        <v>1372</v>
+        <v>1359</v>
       </c>
       <c r="B686" t="s">
-        <v>1373</v>
+        <v>1360</v>
       </c>
       <c r="D686" t="s">
         <v>9</v>
@@ -13353,10 +13443,10 @@
     </row>
     <row r="687" spans="1:4">
       <c r="A687" t="s">
-        <v>1374</v>
+        <v>1361</v>
       </c>
       <c r="B687" t="s">
-        <v>1375</v>
+        <v>1362</v>
       </c>
       <c r="D687" t="s">
         <v>9</v>
@@ -13364,10 +13454,10 @@
     </row>
     <row r="688" spans="1:4">
       <c r="A688" t="s">
-        <v>1376</v>
+        <v>1363</v>
       </c>
       <c r="B688" t="s">
-        <v>1377</v>
+        <v>1364</v>
       </c>
       <c r="D688" t="s">
         <v>9</v>
@@ -13375,10 +13465,10 @@
     </row>
     <row r="689" spans="1:4">
       <c r="A689" t="s">
-        <v>1378</v>
+        <v>1365</v>
       </c>
       <c r="B689" t="s">
-        <v>1379</v>
+        <v>1366</v>
       </c>
       <c r="D689" t="s">
         <v>9</v>
@@ -13386,10 +13476,10 @@
     </row>
     <row r="690" spans="1:4">
       <c r="A690" t="s">
-        <v>1380</v>
+        <v>1367</v>
       </c>
       <c r="B690" t="s">
-        <v>1381</v>
+        <v>1368</v>
       </c>
       <c r="D690" t="s">
         <v>9</v>
@@ -13397,10 +13487,10 @@
     </row>
     <row r="691" spans="1:4">
       <c r="A691" t="s">
-        <v>1382</v>
+        <v>1369</v>
       </c>
       <c r="B691" t="s">
-        <v>1383</v>
+        <v>1370</v>
       </c>
       <c r="D691" t="s">
         <v>9</v>
@@ -13408,10 +13498,10 @@
     </row>
     <row r="692" spans="1:4">
       <c r="A692" t="s">
-        <v>1384</v>
+        <v>1371</v>
       </c>
       <c r="B692" t="s">
-        <v>1385</v>
+        <v>1370</v>
       </c>
       <c r="D692" t="s">
         <v>9</v>
@@ -13419,10 +13509,10 @@
     </row>
     <row r="693" spans="1:4">
       <c r="A693" t="s">
-        <v>1386</v>
+        <v>1372</v>
       </c>
       <c r="B693" t="s">
-        <v>1387</v>
+        <v>1373</v>
       </c>
       <c r="D693" t="s">
         <v>9</v>
@@ -13430,10 +13520,10 @@
     </row>
     <row r="694" spans="1:4">
       <c r="A694" t="s">
-        <v>1388</v>
+        <v>1374</v>
       </c>
       <c r="B694" t="s">
-        <v>1389</v>
+        <v>1375</v>
       </c>
       <c r="D694" t="s">
         <v>9</v>
@@ -13441,10 +13531,10 @@
     </row>
     <row r="695" spans="1:4">
       <c r="A695" t="s">
-        <v>1390</v>
+        <v>1376</v>
       </c>
       <c r="B695" t="s">
-        <v>1391</v>
+        <v>1377</v>
       </c>
       <c r="D695" t="s">
         <v>9</v>
@@ -13452,10 +13542,10 @@
     </row>
     <row r="696" spans="1:4">
       <c r="A696" t="s">
-        <v>1392</v>
+        <v>1378</v>
       </c>
       <c r="B696" t="s">
-        <v>1393</v>
+        <v>1379</v>
       </c>
       <c r="D696" t="s">
         <v>9</v>
@@ -13463,10 +13553,10 @@
     </row>
     <row r="697" spans="1:4">
       <c r="A697" t="s">
-        <v>1394</v>
+        <v>1380</v>
       </c>
       <c r="B697" t="s">
-        <v>1395</v>
+        <v>1381</v>
       </c>
       <c r="D697" t="s">
         <v>9</v>
@@ -13474,10 +13564,10 @@
     </row>
     <row r="698" spans="1:4">
       <c r="A698" t="s">
-        <v>1396</v>
+        <v>1382</v>
       </c>
       <c r="B698" t="s">
-        <v>1397</v>
+        <v>1383</v>
       </c>
       <c r="D698" t="s">
         <v>9</v>
@@ -13485,10 +13575,10 @@
     </row>
     <row r="699" spans="1:4">
       <c r="A699" t="s">
-        <v>1398</v>
+        <v>1384</v>
       </c>
       <c r="B699" t="s">
-        <v>1399</v>
+        <v>1385</v>
       </c>
       <c r="D699" t="s">
         <v>9</v>
@@ -13496,10 +13586,10 @@
     </row>
     <row r="700" spans="1:4">
       <c r="A700" t="s">
-        <v>1400</v>
+        <v>1386</v>
       </c>
       <c r="B700" t="s">
-        <v>1401</v>
+        <v>1387</v>
       </c>
       <c r="D700" t="s">
         <v>9</v>
@@ -13507,10 +13597,10 @@
     </row>
     <row r="701" spans="1:4">
       <c r="A701" t="s">
-        <v>1402</v>
+        <v>1388</v>
       </c>
       <c r="B701" t="s">
-        <v>1403</v>
+        <v>1389</v>
       </c>
       <c r="D701" t="s">
         <v>9</v>
@@ -13518,10 +13608,10 @@
     </row>
     <row r="702" spans="1:4">
       <c r="A702" t="s">
-        <v>1404</v>
+        <v>1390</v>
       </c>
       <c r="B702" t="s">
-        <v>1405</v>
+        <v>1391</v>
       </c>
       <c r="D702" t="s">
         <v>9</v>
@@ -13529,10 +13619,10 @@
     </row>
     <row r="703" spans="1:4">
       <c r="A703" t="s">
-        <v>1406</v>
+        <v>1392</v>
       </c>
       <c r="B703" t="s">
-        <v>1407</v>
+        <v>1393</v>
       </c>
       <c r="D703" t="s">
         <v>9</v>
@@ -13540,10 +13630,10 @@
     </row>
     <row r="704" spans="1:4">
       <c r="A704" t="s">
-        <v>1408</v>
+        <v>1394</v>
       </c>
       <c r="B704" t="s">
-        <v>1409</v>
+        <v>1395</v>
       </c>
       <c r="D704" t="s">
         <v>9</v>
@@ -13551,10 +13641,10 @@
     </row>
     <row r="705" spans="1:4">
       <c r="A705" t="s">
-        <v>1410</v>
+        <v>1396</v>
       </c>
       <c r="B705" t="s">
-        <v>1411</v>
+        <v>1397</v>
       </c>
       <c r="D705" t="s">
         <v>9</v>
@@ -13562,10 +13652,10 @@
     </row>
     <row r="706" spans="1:4">
       <c r="A706" t="s">
-        <v>1412</v>
+        <v>1398</v>
       </c>
       <c r="B706" t="s">
-        <v>1413</v>
+        <v>1399</v>
       </c>
       <c r="D706" t="s">
         <v>9</v>
@@ -13573,10 +13663,10 @@
     </row>
     <row r="707" spans="1:4">
       <c r="A707" t="s">
-        <v>1414</v>
+        <v>1400</v>
       </c>
       <c r="B707" t="s">
-        <v>1415</v>
+        <v>1401</v>
       </c>
       <c r="D707" t="s">
         <v>9</v>
@@ -13584,10 +13674,10 @@
     </row>
     <row r="708" spans="1:4">
       <c r="A708" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B708" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
       <c r="D708" t="s">
         <v>9</v>
@@ -13595,10 +13685,10 @@
     </row>
     <row r="709" spans="1:4">
       <c r="A709" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="B709" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="D709" t="s">
         <v>9</v>
@@ -13606,10 +13696,10 @@
     </row>
     <row r="710" spans="1:4">
       <c r="A710" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B710" t="s">
-        <v>1421</v>
+        <v>1407</v>
       </c>
       <c r="D710" t="s">
         <v>9</v>
@@ -13617,10 +13707,10 @@
     </row>
     <row r="711" spans="1:4">
       <c r="A711" t="s">
-        <v>1422</v>
+        <v>1408</v>
       </c>
       <c r="B711" t="s">
-        <v>1423</v>
+        <v>1409</v>
       </c>
       <c r="D711" t="s">
         <v>9</v>
@@ -13628,10 +13718,10 @@
     </row>
     <row r="712" spans="1:4">
       <c r="A712" t="s">
-        <v>1424</v>
+        <v>1410</v>
       </c>
       <c r="B712" t="s">
-        <v>1425</v>
+        <v>1411</v>
       </c>
       <c r="D712" t="s">
         <v>9</v>
@@ -13639,10 +13729,10 @@
     </row>
     <row r="713" spans="1:4">
       <c r="A713" t="s">
-        <v>1426</v>
+        <v>1412</v>
       </c>
       <c r="B713" t="s">
-        <v>1427</v>
+        <v>1413</v>
       </c>
       <c r="D713" t="s">
         <v>9</v>
@@ -13650,10 +13740,10 @@
     </row>
     <row r="714" spans="1:4">
       <c r="A714" t="s">
-        <v>1428</v>
+        <v>1414</v>
       </c>
       <c r="B714" t="s">
-        <v>1429</v>
+        <v>1415</v>
       </c>
       <c r="D714" t="s">
         <v>9</v>
@@ -13661,10 +13751,10 @@
     </row>
     <row r="715" spans="1:4">
       <c r="A715" t="s">
-        <v>1430</v>
+        <v>1416</v>
       </c>
       <c r="B715" t="s">
-        <v>1431</v>
+        <v>1417</v>
       </c>
       <c r="D715" t="s">
         <v>9</v>
@@ -13672,10 +13762,10 @@
     </row>
     <row r="716" spans="1:4">
       <c r="A716" t="s">
-        <v>1432</v>
+        <v>1418</v>
       </c>
       <c r="B716" t="s">
-        <v>1433</v>
+        <v>1419</v>
       </c>
       <c r="D716" t="s">
         <v>9</v>
@@ -13683,10 +13773,10 @@
     </row>
     <row r="717" spans="1:4">
       <c r="A717" t="s">
-        <v>1434</v>
+        <v>1420</v>
       </c>
       <c r="B717" t="s">
-        <v>1435</v>
+        <v>1421</v>
       </c>
       <c r="D717" t="s">
         <v>9</v>
@@ -13694,10 +13784,10 @@
     </row>
     <row r="718" spans="1:4">
       <c r="A718" t="s">
-        <v>1436</v>
+        <v>1422</v>
       </c>
       <c r="B718" t="s">
-        <v>1437</v>
+        <v>1423</v>
       </c>
       <c r="D718" t="s">
         <v>9</v>
@@ -13705,10 +13795,10 @@
     </row>
     <row r="719" spans="1:4">
       <c r="A719" t="s">
-        <v>1438</v>
+        <v>1424</v>
       </c>
       <c r="B719" t="s">
-        <v>1439</v>
+        <v>1425</v>
       </c>
       <c r="D719" t="s">
         <v>9</v>
@@ -13716,10 +13806,10 @@
     </row>
     <row r="720" spans="1:4">
       <c r="A720" t="s">
-        <v>1440</v>
+        <v>1426</v>
       </c>
       <c r="B720" t="s">
-        <v>1441</v>
+        <v>1427</v>
       </c>
       <c r="D720" t="s">
         <v>9</v>
@@ -13727,10 +13817,10 @@
     </row>
     <row r="721" spans="1:4">
       <c r="A721" t="s">
-        <v>1442</v>
+        <v>1428</v>
       </c>
       <c r="B721" t="s">
-        <v>1443</v>
+        <v>1429</v>
       </c>
       <c r="D721" t="s">
         <v>9</v>
@@ -13738,10 +13828,10 @@
     </row>
     <row r="722" spans="1:4">
       <c r="A722" t="s">
-        <v>1444</v>
+        <v>1430</v>
       </c>
       <c r="B722" t="s">
-        <v>1445</v>
+        <v>1429</v>
       </c>
       <c r="D722" t="s">
         <v>9</v>
@@ -13749,10 +13839,10 @@
     </row>
     <row r="723" spans="1:4">
       <c r="A723" t="s">
-        <v>1446</v>
+        <v>1431</v>
       </c>
       <c r="B723" t="s">
-        <v>1447</v>
+        <v>1432</v>
       </c>
       <c r="D723" t="s">
         <v>9</v>
@@ -13760,10 +13850,10 @@
     </row>
     <row r="724" spans="1:4">
       <c r="A724" t="s">
-        <v>1448</v>
+        <v>1433</v>
       </c>
       <c r="B724" t="s">
-        <v>1449</v>
+        <v>1434</v>
       </c>
       <c r="D724" t="s">
         <v>9</v>
@@ -13771,10 +13861,10 @@
     </row>
     <row r="725" spans="1:4">
       <c r="A725" t="s">
-        <v>1450</v>
+        <v>1435</v>
       </c>
       <c r="B725" t="s">
-        <v>1451</v>
+        <v>1436</v>
       </c>
       <c r="D725" t="s">
         <v>9</v>
@@ -13782,10 +13872,10 @@
     </row>
     <row r="726" spans="1:4">
       <c r="A726" t="s">
-        <v>1452</v>
+        <v>1437</v>
       </c>
       <c r="B726" t="s">
-        <v>1453</v>
+        <v>1438</v>
       </c>
       <c r="D726" t="s">
         <v>9</v>
@@ -13793,10 +13883,10 @@
     </row>
     <row r="727" spans="1:4">
       <c r="A727" t="s">
-        <v>1454</v>
+        <v>1439</v>
       </c>
       <c r="B727" t="s">
-        <v>1455</v>
+        <v>1440</v>
       </c>
       <c r="D727" t="s">
         <v>9</v>
@@ -13804,10 +13894,10 @@
     </row>
     <row r="728" spans="1:4">
       <c r="A728" t="s">
-        <v>1456</v>
+        <v>1441</v>
       </c>
       <c r="B728" t="s">
-        <v>1457</v>
+        <v>1442</v>
       </c>
       <c r="D728" t="s">
         <v>9</v>
@@ -13815,10 +13905,10 @@
     </row>
     <row r="729" spans="1:4">
       <c r="A729" t="s">
-        <v>1458</v>
+        <v>1443</v>
       </c>
       <c r="B729" t="s">
-        <v>1459</v>
+        <v>1444</v>
       </c>
       <c r="D729" t="s">
         <v>9</v>
@@ -13826,10 +13916,10 @@
     </row>
     <row r="730" spans="1:4">
       <c r="A730" t="s">
-        <v>1460</v>
+        <v>1445</v>
       </c>
       <c r="B730" t="s">
-        <v>1461</v>
+        <v>1444</v>
       </c>
       <c r="D730" t="s">
         <v>9</v>
@@ -13837,10 +13927,10 @@
     </row>
     <row r="731" spans="1:4">
       <c r="A731" t="s">
-        <v>1462</v>
+        <v>1446</v>
       </c>
       <c r="B731" t="s">
-        <v>1463</v>
+        <v>1447</v>
       </c>
       <c r="D731" t="s">
         <v>9</v>
@@ -13848,10 +13938,10 @@
     </row>
     <row r="732" spans="1:4">
       <c r="A732" t="s">
-        <v>1464</v>
+        <v>1448</v>
       </c>
       <c r="B732" t="s">
-        <v>1465</v>
+        <v>1449</v>
       </c>
       <c r="D732" t="s">
         <v>9</v>
@@ -13859,10 +13949,10 @@
     </row>
     <row r="733" spans="1:4">
       <c r="A733" t="s">
-        <v>1466</v>
+        <v>1450</v>
       </c>
       <c r="B733" t="s">
-        <v>1467</v>
+        <v>1451</v>
       </c>
       <c r="D733" t="s">
         <v>9</v>
@@ -13870,10 +13960,10 @@
     </row>
     <row r="734" spans="1:4">
       <c r="A734" t="s">
-        <v>1468</v>
+        <v>1452</v>
       </c>
       <c r="B734" t="s">
-        <v>1469</v>
+        <v>1453</v>
       </c>
       <c r="D734" t="s">
         <v>9</v>
@@ -13881,10 +13971,10 @@
     </row>
     <row r="735" spans="1:4">
       <c r="A735" t="s">
-        <v>1470</v>
+        <v>1454</v>
       </c>
       <c r="B735" t="s">
-        <v>1471</v>
+        <v>1455</v>
       </c>
       <c r="D735" t="s">
         <v>9</v>
@@ -13892,10 +13982,10 @@
     </row>
     <row r="736" spans="1:4">
       <c r="A736" t="s">
-        <v>1472</v>
+        <v>1456</v>
       </c>
       <c r="B736" t="s">
-        <v>1473</v>
+        <v>1457</v>
       </c>
       <c r="D736" t="s">
         <v>9</v>
@@ -13903,10 +13993,10 @@
     </row>
     <row r="737" spans="1:4">
       <c r="A737" t="s">
-        <v>1474</v>
+        <v>1458</v>
       </c>
       <c r="B737" t="s">
-        <v>1475</v>
+        <v>1459</v>
       </c>
       <c r="D737" t="s">
         <v>9</v>
@@ -13914,10 +14004,10 @@
     </row>
     <row r="738" spans="1:4">
       <c r="A738" t="s">
-        <v>1476</v>
+        <v>1460</v>
       </c>
       <c r="B738" t="s">
-        <v>1477</v>
+        <v>1461</v>
       </c>
       <c r="D738" t="s">
         <v>9</v>
@@ -13925,10 +14015,10 @@
     </row>
     <row r="739" spans="1:4">
       <c r="A739" t="s">
-        <v>1478</v>
+        <v>1462</v>
       </c>
       <c r="B739" t="s">
-        <v>1479</v>
+        <v>1463</v>
       </c>
       <c r="D739" t="s">
         <v>9</v>
@@ -13936,10 +14026,10 @@
     </row>
     <row r="740" spans="1:4">
       <c r="A740" t="s">
-        <v>1480</v>
+        <v>1464</v>
       </c>
       <c r="B740" t="s">
-        <v>1481</v>
+        <v>1465</v>
       </c>
       <c r="D740" t="s">
         <v>9</v>
@@ -13947,10 +14037,10 @@
     </row>
     <row r="741" spans="1:4">
       <c r="A741" t="s">
-        <v>1482</v>
+        <v>1466</v>
       </c>
       <c r="B741" t="s">
-        <v>1483</v>
+        <v>1467</v>
       </c>
       <c r="D741" t="s">
         <v>9</v>
@@ -13958,10 +14048,10 @@
     </row>
     <row r="742" spans="1:4">
       <c r="A742" t="s">
-        <v>1484</v>
+        <v>1468</v>
       </c>
       <c r="B742" t="s">
-        <v>1485</v>
+        <v>1469</v>
       </c>
       <c r="D742" t="s">
         <v>9</v>
@@ -13969,10 +14059,10 @@
     </row>
     <row r="743" spans="1:4">
       <c r="A743" t="s">
-        <v>1486</v>
+        <v>1470</v>
       </c>
       <c r="B743" t="s">
-        <v>1487</v>
+        <v>1471</v>
       </c>
       <c r="D743" t="s">
         <v>9</v>
@@ -13980,10 +14070,10 @@
     </row>
     <row r="744" spans="1:4">
       <c r="A744" t="s">
-        <v>1488</v>
+        <v>1472</v>
       </c>
       <c r="B744" t="s">
-        <v>1489</v>
+        <v>1473</v>
       </c>
       <c r="D744" t="s">
         <v>9</v>
@@ -13991,10 +14081,10 @@
     </row>
     <row r="745" spans="1:4">
       <c r="A745" t="s">
-        <v>1490</v>
+        <v>1474</v>
       </c>
       <c r="B745" t="s">
-        <v>1491</v>
+        <v>1475</v>
       </c>
       <c r="D745" t="s">
         <v>9</v>
@@ -14002,10 +14092,10 @@
     </row>
     <row r="746" spans="1:4">
       <c r="A746" t="s">
-        <v>1492</v>
+        <v>1476</v>
       </c>
       <c r="B746" t="s">
-        <v>1493</v>
+        <v>1477</v>
       </c>
       <c r="D746" t="s">
         <v>9</v>
@@ -14013,10 +14103,10 @@
     </row>
     <row r="747" spans="1:4">
       <c r="A747" t="s">
-        <v>1494</v>
+        <v>1478</v>
       </c>
       <c r="B747" t="s">
-        <v>1495</v>
+        <v>1479</v>
       </c>
       <c r="D747" t="s">
         <v>9</v>
@@ -14024,10 +14114,10 @@
     </row>
     <row r="748" spans="1:4">
       <c r="A748" t="s">
-        <v>1496</v>
+        <v>1480</v>
       </c>
       <c r="B748" t="s">
-        <v>1497</v>
+        <v>1481</v>
       </c>
       <c r="D748" t="s">
         <v>9</v>
@@ -14035,10 +14125,10 @@
     </row>
     <row r="749" spans="1:4">
       <c r="A749" t="s">
-        <v>1498</v>
+        <v>1482</v>
       </c>
       <c r="B749" t="s">
-        <v>1499</v>
+        <v>1483</v>
       </c>
       <c r="D749" t="s">
         <v>9</v>
@@ -14046,10 +14136,10 @@
     </row>
     <row r="750" spans="1:4">
       <c r="A750" t="s">
-        <v>1500</v>
+        <v>1484</v>
       </c>
       <c r="B750" t="s">
-        <v>1501</v>
+        <v>1485</v>
       </c>
       <c r="D750" t="s">
         <v>9</v>
@@ -14057,10 +14147,10 @@
     </row>
     <row r="751" spans="1:4">
       <c r="A751" t="s">
-        <v>1502</v>
+        <v>1486</v>
       </c>
       <c r="B751" t="s">
-        <v>1503</v>
+        <v>1487</v>
       </c>
       <c r="D751" t="s">
         <v>9</v>
@@ -14068,10 +14158,10 @@
     </row>
     <row r="752" spans="1:4">
       <c r="A752" t="s">
-        <v>1504</v>
+        <v>1488</v>
       </c>
       <c r="B752" t="s">
-        <v>1505</v>
+        <v>1489</v>
       </c>
       <c r="D752" t="s">
         <v>9</v>
@@ -14079,10 +14169,10 @@
     </row>
     <row r="753" spans="1:4">
       <c r="A753" t="s">
-        <v>1506</v>
+        <v>1490</v>
       </c>
       <c r="B753" t="s">
-        <v>1507</v>
+        <v>1491</v>
       </c>
       <c r="D753" t="s">
         <v>9</v>
@@ -14090,10 +14180,10 @@
     </row>
     <row r="754" spans="1:4">
       <c r="A754" t="s">
-        <v>1508</v>
+        <v>1492</v>
       </c>
       <c r="B754" t="s">
-        <v>1509</v>
+        <v>1493</v>
       </c>
       <c r="D754" t="s">
         <v>9</v>
@@ -14101,10 +14191,10 @@
     </row>
     <row r="755" spans="1:4">
       <c r="A755" t="s">
-        <v>1510</v>
+        <v>1494</v>
       </c>
       <c r="B755" t="s">
-        <v>1511</v>
+        <v>1495</v>
       </c>
       <c r="D755" t="s">
         <v>9</v>
@@ -14112,10 +14202,10 @@
     </row>
     <row r="756" spans="1:4">
       <c r="A756" t="s">
-        <v>1512</v>
+        <v>1496</v>
       </c>
       <c r="B756" t="s">
-        <v>1513</v>
+        <v>1497</v>
       </c>
       <c r="D756" t="s">
         <v>9</v>
@@ -14123,10 +14213,10 @@
     </row>
     <row r="757" spans="1:4">
       <c r="A757" t="s">
-        <v>1514</v>
+        <v>1498</v>
       </c>
       <c r="B757" t="s">
-        <v>1515</v>
+        <v>1499</v>
       </c>
       <c r="D757" t="s">
         <v>9</v>
@@ -14134,10 +14224,10 @@
     </row>
     <row r="758" spans="1:4">
       <c r="A758" t="s">
-        <v>1516</v>
+        <v>1500</v>
       </c>
       <c r="B758" t="s">
-        <v>1517</v>
+        <v>1501</v>
       </c>
       <c r="D758" t="s">
         <v>9</v>
@@ -14145,10 +14235,10 @@
     </row>
     <row r="759" spans="1:4">
       <c r="A759" t="s">
-        <v>1518</v>
+        <v>1502</v>
       </c>
       <c r="B759" t="s">
-        <v>1519</v>
+        <v>1503</v>
       </c>
       <c r="D759" t="s">
         <v>9</v>
@@ -14156,10 +14246,10 @@
     </row>
     <row r="760" spans="1:4">
       <c r="A760" t="s">
-        <v>1520</v>
+        <v>1504</v>
       </c>
       <c r="B760" t="s">
-        <v>1521</v>
+        <v>1505</v>
       </c>
       <c r="D760" t="s">
         <v>9</v>
@@ -14167,10 +14257,10 @@
     </row>
     <row r="761" spans="1:4">
       <c r="A761" t="s">
-        <v>1522</v>
+        <v>1506</v>
       </c>
       <c r="B761" t="s">
-        <v>1523</v>
+        <v>1507</v>
       </c>
       <c r="D761" t="s">
         <v>9</v>
@@ -14178,10 +14268,10 @@
     </row>
     <row r="762" spans="1:4">
       <c r="A762" t="s">
-        <v>1524</v>
+        <v>1508</v>
       </c>
       <c r="B762" t="s">
-        <v>1525</v>
+        <v>1509</v>
       </c>
       <c r="D762" t="s">
         <v>9</v>
@@ -14189,10 +14279,10 @@
     </row>
     <row r="763" spans="1:4">
       <c r="A763" t="s">
-        <v>1526</v>
+        <v>1510</v>
       </c>
       <c r="B763" t="s">
-        <v>1527</v>
+        <v>1511</v>
       </c>
       <c r="D763" t="s">
         <v>9</v>
@@ -14200,10 +14290,10 @@
     </row>
     <row r="764" spans="1:4">
       <c r="A764" t="s">
-        <v>1528</v>
+        <v>1512</v>
       </c>
       <c r="B764" t="s">
-        <v>1529</v>
+        <v>1511</v>
       </c>
       <c r="D764" t="s">
         <v>9</v>
@@ -14211,10 +14301,10 @@
     </row>
     <row r="765" spans="1:4">
       <c r="A765" t="s">
-        <v>1530</v>
+        <v>1513</v>
       </c>
       <c r="B765" t="s">
-        <v>1531</v>
+        <v>1514</v>
       </c>
       <c r="D765" t="s">
         <v>9</v>
@@ -14222,10 +14312,10 @@
     </row>
     <row r="766" spans="1:4">
       <c r="A766" t="s">
-        <v>1532</v>
+        <v>1515</v>
       </c>
       <c r="B766" t="s">
-        <v>1533</v>
+        <v>1516</v>
       </c>
       <c r="D766" t="s">
         <v>9</v>
@@ -14233,10 +14323,10 @@
     </row>
     <row r="767" spans="1:4">
       <c r="A767" t="s">
-        <v>1534</v>
+        <v>1517</v>
       </c>
       <c r="B767" t="s">
-        <v>1535</v>
+        <v>1518</v>
       </c>
       <c r="D767" t="s">
         <v>9</v>
@@ -14244,10 +14334,10 @@
     </row>
     <row r="768" spans="1:4">
       <c r="A768" t="s">
-        <v>1536</v>
+        <v>1519</v>
       </c>
       <c r="B768" t="s">
-        <v>1537</v>
+        <v>1520</v>
       </c>
       <c r="D768" t="s">
         <v>9</v>
@@ -14255,10 +14345,10 @@
     </row>
     <row r="769" spans="1:4">
       <c r="A769" t="s">
-        <v>1538</v>
+        <v>1521</v>
       </c>
       <c r="B769" t="s">
-        <v>1539</v>
+        <v>1522</v>
       </c>
       <c r="D769" t="s">
         <v>9</v>
@@ -14266,10 +14356,10 @@
     </row>
     <row r="770" spans="1:4">
       <c r="A770" t="s">
-        <v>1540</v>
+        <v>1523</v>
       </c>
       <c r="B770" t="s">
-        <v>1541</v>
+        <v>1524</v>
       </c>
       <c r="D770" t="s">
         <v>9</v>
@@ -14277,10 +14367,10 @@
     </row>
     <row r="771" spans="1:4">
       <c r="A771" t="s">
-        <v>1542</v>
+        <v>1525</v>
       </c>
       <c r="B771" t="s">
-        <v>1543</v>
+        <v>1526</v>
       </c>
       <c r="D771" t="s">
         <v>9</v>
@@ -14288,10 +14378,10 @@
     </row>
     <row r="772" spans="1:4">
       <c r="A772" t="s">
-        <v>1544</v>
+        <v>1527</v>
       </c>
       <c r="B772" t="s">
-        <v>1545</v>
+        <v>1528</v>
       </c>
       <c r="D772" t="s">
         <v>9</v>
@@ -14299,10 +14389,10 @@
     </row>
     <row r="773" spans="1:4">
       <c r="A773" t="s">
-        <v>1546</v>
+        <v>1529</v>
       </c>
       <c r="B773" t="s">
-        <v>1547</v>
+        <v>1530</v>
       </c>
       <c r="D773" t="s">
         <v>9</v>
@@ -14310,10 +14400,10 @@
     </row>
     <row r="774" spans="1:4">
       <c r="A774" t="s">
-        <v>1548</v>
+        <v>1531</v>
       </c>
       <c r="B774" t="s">
-        <v>1549</v>
+        <v>1532</v>
       </c>
       <c r="D774" t="s">
         <v>9</v>
@@ -14321,10 +14411,10 @@
     </row>
     <row r="775" spans="1:4">
       <c r="A775" t="s">
-        <v>1550</v>
+        <v>1533</v>
       </c>
       <c r="B775" t="s">
-        <v>1551</v>
+        <v>1534</v>
       </c>
       <c r="D775" t="s">
         <v>9</v>
@@ -14332,10 +14422,10 @@
     </row>
     <row r="776" spans="1:4">
       <c r="A776" t="s">
-        <v>1552</v>
+        <v>1535</v>
       </c>
       <c r="B776" t="s">
-        <v>1553</v>
+        <v>1536</v>
       </c>
       <c r="D776" t="s">
         <v>9</v>
@@ -14343,10 +14433,10 @@
     </row>
     <row r="777" spans="1:4">
       <c r="A777" t="s">
-        <v>1554</v>
+        <v>1537</v>
       </c>
       <c r="B777" t="s">
-        <v>1555</v>
+        <v>1538</v>
       </c>
       <c r="D777" t="s">
         <v>9</v>
@@ -14354,10 +14444,10 @@
     </row>
     <row r="778" spans="1:4">
       <c r="A778" t="s">
-        <v>1556</v>
+        <v>1539</v>
       </c>
       <c r="B778" t="s">
-        <v>1557</v>
+        <v>1540</v>
       </c>
       <c r="D778" t="s">
         <v>9</v>
@@ -14365,10 +14455,10 @@
     </row>
     <row r="779" spans="1:4">
       <c r="A779" t="s">
-        <v>1558</v>
+        <v>1541</v>
       </c>
       <c r="B779" t="s">
-        <v>1559</v>
+        <v>1542</v>
       </c>
       <c r="D779" t="s">
         <v>9</v>
@@ -14376,10 +14466,10 @@
     </row>
     <row r="780" spans="1:4">
       <c r="A780" t="s">
-        <v>1560</v>
+        <v>1543</v>
       </c>
       <c r="B780" t="s">
-        <v>1561</v>
+        <v>1544</v>
       </c>
       <c r="D780" t="s">
         <v>9</v>
@@ -14387,10 +14477,10 @@
     </row>
     <row r="781" spans="1:4">
       <c r="A781" t="s">
-        <v>1562</v>
+        <v>1545</v>
       </c>
       <c r="B781" t="s">
-        <v>1563</v>
+        <v>1546</v>
       </c>
       <c r="D781" t="s">
         <v>9</v>
@@ -14398,10 +14488,10 @@
     </row>
     <row r="782" spans="1:4">
       <c r="A782" t="s">
-        <v>1564</v>
+        <v>1547</v>
       </c>
       <c r="B782" t="s">
-        <v>1565</v>
+        <v>1548</v>
       </c>
       <c r="D782" t="s">
         <v>9</v>
@@ -14409,10 +14499,10 @@
     </row>
     <row r="783" spans="1:4">
       <c r="A783" t="s">
-        <v>1566</v>
+        <v>1549</v>
       </c>
       <c r="B783" t="s">
-        <v>1567</v>
+        <v>1540</v>
       </c>
       <c r="D783" t="s">
         <v>9</v>
@@ -14420,10 +14510,10 @@
     </row>
     <row r="784" spans="1:4">
       <c r="A784" t="s">
-        <v>1568</v>
+        <v>1550</v>
       </c>
       <c r="B784" t="s">
-        <v>1569</v>
+        <v>1551</v>
       </c>
       <c r="D784" t="s">
         <v>9</v>
@@ -14431,10 +14521,10 @@
     </row>
     <row r="785" spans="1:4">
       <c r="A785" t="s">
-        <v>1570</v>
+        <v>1552</v>
       </c>
       <c r="B785" t="s">
-        <v>1571</v>
+        <v>1553</v>
       </c>
       <c r="D785" t="s">
         <v>9</v>
@@ -14442,10 +14532,10 @@
     </row>
     <row r="786" spans="1:4">
       <c r="A786" t="s">
-        <v>1572</v>
+        <v>1554</v>
       </c>
       <c r="B786" t="s">
-        <v>1573</v>
+        <v>1555</v>
       </c>
       <c r="D786" t="s">
         <v>9</v>
@@ -14453,10 +14543,10 @@
     </row>
     <row r="787" spans="1:4">
       <c r="A787" t="s">
-        <v>1574</v>
+        <v>1556</v>
       </c>
       <c r="B787" t="s">
-        <v>1575</v>
+        <v>1557</v>
       </c>
       <c r="D787" t="s">
         <v>9</v>
@@ -14464,10 +14554,10 @@
     </row>
     <row r="788" spans="1:4">
       <c r="A788" t="s">
-        <v>1576</v>
+        <v>1558</v>
       </c>
       <c r="B788" t="s">
-        <v>1577</v>
+        <v>1559</v>
       </c>
       <c r="D788" t="s">
         <v>9</v>
@@ -14475,10 +14565,10 @@
     </row>
     <row r="789" spans="1:4">
       <c r="A789" t="s">
-        <v>1578</v>
+        <v>1560</v>
       </c>
       <c r="B789" t="s">
-        <v>1579</v>
+        <v>1561</v>
       </c>
       <c r="D789" t="s">
         <v>9</v>
@@ -14486,10 +14576,10 @@
     </row>
     <row r="790" spans="1:4">
       <c r="A790" t="s">
-        <v>1580</v>
+        <v>1562</v>
       </c>
       <c r="B790" t="s">
-        <v>1581</v>
+        <v>1563</v>
       </c>
       <c r="D790" t="s">
         <v>9</v>
@@ -14497,10 +14587,10 @@
     </row>
     <row r="791" spans="1:4">
       <c r="A791" t="s">
-        <v>1582</v>
+        <v>1564</v>
       </c>
       <c r="B791" t="s">
-        <v>1583</v>
+        <v>1561</v>
       </c>
       <c r="D791" t="s">
         <v>9</v>
@@ -14508,10 +14598,10 @@
     </row>
     <row r="792" spans="1:4">
       <c r="A792" t="s">
-        <v>1584</v>
+        <v>1565</v>
       </c>
       <c r="B792" t="s">
-        <v>1585</v>
+        <v>1566</v>
       </c>
       <c r="D792" t="s">
         <v>9</v>
@@ -14519,10 +14609,10 @@
     </row>
     <row r="793" spans="1:4">
       <c r="A793" t="s">
-        <v>1586</v>
+        <v>1567</v>
       </c>
       <c r="B793" t="s">
-        <v>1587</v>
+        <v>1568</v>
       </c>
       <c r="D793" t="s">
         <v>9</v>
@@ -14530,10 +14620,10 @@
     </row>
     <row r="794" spans="1:4">
       <c r="A794" t="s">
-        <v>1588</v>
+        <v>1569</v>
       </c>
       <c r="B794" t="s">
-        <v>1589</v>
+        <v>1559</v>
       </c>
       <c r="D794" t="s">
         <v>9</v>
@@ -14541,10 +14631,10 @@
     </row>
     <row r="795" spans="1:4">
       <c r="A795" t="s">
-        <v>1590</v>
+        <v>1570</v>
       </c>
       <c r="B795" t="s">
-        <v>1591</v>
+        <v>1571</v>
       </c>
       <c r="D795" t="s">
         <v>9</v>
@@ -14552,10 +14642,10 @@
     </row>
     <row r="796" spans="1:4">
       <c r="A796" t="s">
-        <v>1592</v>
+        <v>1572</v>
       </c>
       <c r="B796" t="s">
-        <v>1593</v>
+        <v>1573</v>
       </c>
       <c r="D796" t="s">
         <v>9</v>
@@ -14563,10 +14653,10 @@
     </row>
     <row r="797" spans="1:4">
       <c r="A797" t="s">
-        <v>1594</v>
+        <v>1574</v>
       </c>
       <c r="B797" t="s">
-        <v>1595</v>
+        <v>1575</v>
       </c>
       <c r="D797" t="s">
         <v>9</v>
@@ -14574,10 +14664,10 @@
     </row>
     <row r="798" spans="1:4">
       <c r="A798" t="s">
-        <v>1596</v>
+        <v>1576</v>
       </c>
       <c r="B798" t="s">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="D798" t="s">
         <v>9</v>
@@ -14585,10 +14675,10 @@
     </row>
     <row r="799" spans="1:4">
       <c r="A799" t="s">
-        <v>1598</v>
+        <v>1578</v>
       </c>
       <c r="B799" t="s">
-        <v>1599</v>
+        <v>1579</v>
       </c>
       <c r="D799" t="s">
         <v>9</v>
@@ -14596,10 +14686,10 @@
     </row>
     <row r="800" spans="1:4">
       <c r="A800" t="s">
-        <v>1600</v>
+        <v>1580</v>
       </c>
       <c r="B800" t="s">
-        <v>1601</v>
+        <v>1581</v>
       </c>
       <c r="D800" t="s">
         <v>9</v>
@@ -14607,10 +14697,10 @@
     </row>
     <row r="801" spans="1:4">
       <c r="A801" t="s">
-        <v>1602</v>
+        <v>1582</v>
       </c>
       <c r="B801" t="s">
-        <v>1603</v>
+        <v>1583</v>
       </c>
       <c r="D801" t="s">
         <v>9</v>
@@ -14618,10 +14708,10 @@
     </row>
     <row r="802" spans="1:4">
       <c r="A802" t="s">
-        <v>1604</v>
+        <v>1584</v>
       </c>
       <c r="B802" t="s">
-        <v>1605</v>
+        <v>1585</v>
       </c>
       <c r="D802" t="s">
         <v>9</v>
@@ -14629,10 +14719,10 @@
     </row>
     <row r="803" spans="1:4">
       <c r="A803" t="s">
-        <v>1606</v>
+        <v>1586</v>
       </c>
       <c r="B803" t="s">
-        <v>1607</v>
+        <v>1587</v>
       </c>
       <c r="D803" t="s">
         <v>9</v>
@@ -14640,10 +14730,10 @@
     </row>
     <row r="804" spans="1:4">
       <c r="A804" t="s">
-        <v>1608</v>
+        <v>1588</v>
       </c>
       <c r="B804" t="s">
-        <v>1609</v>
+        <v>1589</v>
       </c>
       <c r="D804" t="s">
         <v>9</v>
@@ -14651,10 +14741,10 @@
     </row>
     <row r="805" spans="1:4">
       <c r="A805" t="s">
-        <v>1610</v>
+        <v>1590</v>
       </c>
       <c r="B805" t="s">
-        <v>1611</v>
+        <v>1591</v>
       </c>
       <c r="D805" t="s">
         <v>9</v>
@@ -14662,10 +14752,10 @@
     </row>
     <row r="806" spans="1:4">
       <c r="A806" t="s">
-        <v>1612</v>
+        <v>1592</v>
       </c>
       <c r="B806" t="s">
-        <v>1613</v>
+        <v>1593</v>
       </c>
       <c r="D806" t="s">
         <v>9</v>
@@ -14673,10 +14763,10 @@
     </row>
     <row r="807" spans="1:4">
       <c r="A807" t="s">
-        <v>1614</v>
+        <v>1594</v>
       </c>
       <c r="B807" t="s">
-        <v>1615</v>
+        <v>1595</v>
       </c>
       <c r="D807" t="s">
         <v>9</v>
@@ -14684,10 +14774,10 @@
     </row>
     <row r="808" spans="1:4">
       <c r="A808" t="s">
-        <v>1616</v>
+        <v>1596</v>
       </c>
       <c r="B808" t="s">
-        <v>1617</v>
+        <v>1597</v>
       </c>
       <c r="D808" t="s">
         <v>9</v>
@@ -14695,10 +14785,10 @@
     </row>
     <row r="809" spans="1:4">
       <c r="A809" t="s">
-        <v>1618</v>
+        <v>1598</v>
       </c>
       <c r="B809" t="s">
-        <v>1619</v>
+        <v>1599</v>
       </c>
       <c r="D809" t="s">
         <v>9</v>
@@ -14706,10 +14796,10 @@
     </row>
     <row r="810" spans="1:4">
       <c r="A810" t="s">
-        <v>1620</v>
+        <v>1600</v>
       </c>
       <c r="B810" t="s">
-        <v>1621</v>
+        <v>1601</v>
       </c>
       <c r="D810" t="s">
         <v>9</v>
@@ -14717,10 +14807,10 @@
     </row>
     <row r="811" spans="1:4">
       <c r="A811" t="s">
-        <v>1622</v>
+        <v>1602</v>
       </c>
       <c r="B811" t="s">
-        <v>1623</v>
+        <v>1603</v>
       </c>
       <c r="D811" t="s">
         <v>9</v>
@@ -14728,10 +14818,10 @@
     </row>
     <row r="812" spans="1:4">
       <c r="A812" t="s">
-        <v>1624</v>
+        <v>1604</v>
       </c>
       <c r="B812" t="s">
-        <v>1625</v>
+        <v>1605</v>
       </c>
       <c r="D812" t="s">
         <v>9</v>
@@ -14739,10 +14829,10 @@
     </row>
     <row r="813" spans="1:4">
       <c r="A813" t="s">
-        <v>1626</v>
+        <v>1606</v>
       </c>
       <c r="B813" t="s">
-        <v>1627</v>
+        <v>1607</v>
       </c>
       <c r="D813" t="s">
         <v>9</v>
@@ -14750,10 +14840,10 @@
     </row>
     <row r="814" spans="1:4">
       <c r="A814" t="s">
-        <v>1628</v>
+        <v>1608</v>
       </c>
       <c r="B814" t="s">
-        <v>1629</v>
+        <v>1609</v>
       </c>
       <c r="D814" t="s">
         <v>9</v>
@@ -14761,10 +14851,10 @@
     </row>
     <row r="815" spans="1:4">
       <c r="A815" t="s">
-        <v>1630</v>
+        <v>1610</v>
       </c>
       <c r="B815" t="s">
-        <v>1631</v>
+        <v>1611</v>
       </c>
       <c r="D815" t="s">
         <v>9</v>
@@ -14772,10 +14862,10 @@
     </row>
     <row r="816" spans="1:4">
       <c r="A816" t="s">
-        <v>1632</v>
+        <v>1612</v>
       </c>
       <c r="B816" t="s">
-        <v>1633</v>
+        <v>1613</v>
       </c>
       <c r="D816" t="s">
         <v>9</v>
@@ -14783,10 +14873,10 @@
     </row>
     <row r="817" spans="1:4">
       <c r="A817" t="s">
-        <v>1634</v>
+        <v>1614</v>
       </c>
       <c r="B817" t="s">
-        <v>1635</v>
+        <v>1615</v>
       </c>
       <c r="D817" t="s">
         <v>9</v>
@@ -14794,10 +14884,10 @@
     </row>
     <row r="818" spans="1:4">
       <c r="A818" t="s">
-        <v>1636</v>
+        <v>1616</v>
       </c>
       <c r="B818" t="s">
-        <v>1637</v>
+        <v>1617</v>
       </c>
       <c r="D818" t="s">
         <v>9</v>
@@ -14805,10 +14895,10 @@
     </row>
     <row r="819" spans="1:4">
       <c r="A819" t="s">
-        <v>1638</v>
+        <v>1618</v>
       </c>
       <c r="B819" t="s">
-        <v>1639</v>
+        <v>1619</v>
       </c>
       <c r="D819" t="s">
         <v>9</v>
@@ -14816,10 +14906,10 @@
     </row>
     <row r="820" spans="1:4">
       <c r="A820" t="s">
-        <v>1640</v>
+        <v>1620</v>
       </c>
       <c r="B820" t="s">
-        <v>1641</v>
+        <v>1621</v>
       </c>
       <c r="D820" t="s">
         <v>9</v>
@@ -14827,10 +14917,10 @@
     </row>
     <row r="821" spans="1:4">
       <c r="A821" t="s">
-        <v>1642</v>
+        <v>1622</v>
       </c>
       <c r="B821" t="s">
-        <v>1643</v>
+        <v>1623</v>
       </c>
       <c r="D821" t="s">
         <v>9</v>
@@ -14838,10 +14928,10 @@
     </row>
     <row r="822" spans="1:4">
       <c r="A822" t="s">
-        <v>1644</v>
+        <v>1624</v>
       </c>
       <c r="B822" t="s">
-        <v>1645</v>
+        <v>1625</v>
       </c>
       <c r="D822" t="s">
         <v>9</v>
@@ -14849,10 +14939,10 @@
     </row>
     <row r="823" spans="1:4">
       <c r="A823" t="s">
-        <v>1646</v>
+        <v>1626</v>
       </c>
       <c r="B823" t="s">
-        <v>1647</v>
+        <v>1627</v>
       </c>
       <c r="D823" t="s">
         <v>9</v>
@@ -14860,10 +14950,10 @@
     </row>
     <row r="824" spans="1:4">
       <c r="A824" t="s">
-        <v>1648</v>
+        <v>1628</v>
       </c>
       <c r="B824" t="s">
-        <v>1649</v>
+        <v>1629</v>
       </c>
       <c r="D824" t="s">
         <v>9</v>
@@ -14871,10 +14961,10 @@
     </row>
     <row r="825" spans="1:4">
       <c r="A825" t="s">
-        <v>1650</v>
+        <v>1630</v>
       </c>
       <c r="B825" t="s">
-        <v>1651</v>
+        <v>1631</v>
       </c>
       <c r="D825" t="s">
         <v>9</v>
@@ -14882,10 +14972,10 @@
     </row>
     <row r="826" spans="1:4">
       <c r="A826" t="s">
-        <v>1652</v>
+        <v>1632</v>
       </c>
       <c r="B826" t="s">
-        <v>1653</v>
+        <v>1589</v>
       </c>
       <c r="D826" t="s">
         <v>9</v>
@@ -14893,10 +14983,10 @@
     </row>
     <row r="827" spans="1:4">
       <c r="A827" t="s">
-        <v>1654</v>
+        <v>1633</v>
       </c>
       <c r="B827" t="s">
-        <v>1655</v>
+        <v>1634</v>
       </c>
       <c r="D827" t="s">
         <v>9</v>
@@ -14904,10 +14994,10 @@
     </row>
     <row r="828" spans="1:4">
       <c r="A828" t="s">
-        <v>1656</v>
+        <v>1635</v>
       </c>
       <c r="B828" t="s">
-        <v>1657</v>
+        <v>1636</v>
       </c>
       <c r="D828" t="s">
         <v>9</v>
@@ -14915,10 +15005,10 @@
     </row>
     <row r="829" spans="1:4">
       <c r="A829" t="s">
-        <v>1658</v>
+        <v>1637</v>
       </c>
       <c r="B829" t="s">
-        <v>1659</v>
+        <v>1638</v>
       </c>
       <c r="D829" t="s">
         <v>9</v>
@@ -14926,10 +15016,10 @@
     </row>
     <row r="830" spans="1:4">
       <c r="A830" t="s">
-        <v>1660</v>
+        <v>1639</v>
       </c>
       <c r="B830" t="s">
-        <v>1661</v>
+        <v>1640</v>
       </c>
       <c r="D830" t="s">
         <v>9</v>
@@ -14937,10 +15027,10 @@
     </row>
     <row r="831" spans="1:4">
       <c r="A831" t="s">
-        <v>1662</v>
+        <v>1641</v>
       </c>
       <c r="B831" t="s">
-        <v>1663</v>
+        <v>1642</v>
       </c>
       <c r="D831" t="s">
         <v>9</v>
@@ -14948,10 +15038,10 @@
     </row>
     <row r="832" spans="1:4">
       <c r="A832" t="s">
-        <v>1664</v>
+        <v>1643</v>
       </c>
       <c r="B832" t="s">
-        <v>1665</v>
+        <v>1644</v>
       </c>
       <c r="D832" t="s">
         <v>9</v>
@@ -14959,10 +15049,10 @@
     </row>
     <row r="833" spans="1:4">
       <c r="A833" t="s">
-        <v>1666</v>
+        <v>1645</v>
       </c>
       <c r="B833" t="s">
-        <v>1667</v>
+        <v>1646</v>
       </c>
       <c r="D833" t="s">
         <v>9</v>
@@ -14970,10 +15060,10 @@
     </row>
     <row r="834" spans="1:4">
       <c r="A834" t="s">
-        <v>1668</v>
+        <v>1647</v>
       </c>
       <c r="B834" t="s">
-        <v>1669</v>
+        <v>1648</v>
       </c>
       <c r="D834" t="s">
         <v>9</v>
@@ -14981,10 +15071,10 @@
     </row>
     <row r="835" spans="1:4">
       <c r="A835" t="s">
-        <v>1670</v>
+        <v>1649</v>
       </c>
       <c r="B835" t="s">
-        <v>1671</v>
+        <v>1650</v>
       </c>
       <c r="D835" t="s">
         <v>9</v>
@@ -14992,10 +15082,10 @@
     </row>
     <row r="836" spans="1:4">
       <c r="A836" t="s">
-        <v>1672</v>
+        <v>1651</v>
       </c>
       <c r="B836" t="s">
-        <v>1673</v>
+        <v>1652</v>
       </c>
       <c r="D836" t="s">
         <v>9</v>
@@ -15003,10 +15093,10 @@
     </row>
     <row r="837" spans="1:4">
       <c r="A837" t="s">
-        <v>1674</v>
+        <v>1653</v>
       </c>
       <c r="B837" t="s">
-        <v>1675</v>
+        <v>1650</v>
       </c>
       <c r="D837" t="s">
         <v>9</v>
@@ -15014,10 +15104,10 @@
     </row>
     <row r="838" spans="1:4">
       <c r="A838" t="s">
-        <v>1676</v>
+        <v>1654</v>
       </c>
       <c r="B838" t="s">
-        <v>1677</v>
+        <v>1652</v>
       </c>
       <c r="D838" t="s">
         <v>9</v>
@@ -15025,10 +15115,10 @@
     </row>
     <row r="839" spans="1:4">
       <c r="A839" t="s">
-        <v>1678</v>
+        <v>1655</v>
       </c>
       <c r="B839" t="s">
-        <v>1679</v>
+        <v>1656</v>
       </c>
       <c r="D839" t="s">
         <v>9</v>
@@ -15036,10 +15126,10 @@
     </row>
     <row r="840" spans="1:4">
       <c r="A840" t="s">
-        <v>1680</v>
+        <v>1657</v>
       </c>
       <c r="B840" t="s">
-        <v>1681</v>
+        <v>1658</v>
       </c>
       <c r="D840" t="s">
         <v>9</v>
@@ -15047,10 +15137,10 @@
     </row>
     <row r="841" spans="1:4">
       <c r="A841" t="s">
-        <v>1682</v>
+        <v>1659</v>
       </c>
       <c r="B841" t="s">
-        <v>1683</v>
+        <v>1660</v>
       </c>
       <c r="D841" t="s">
         <v>9</v>
@@ -15058,10 +15148,10 @@
     </row>
     <row r="842" spans="1:4">
       <c r="A842" t="s">
-        <v>1684</v>
+        <v>1661</v>
       </c>
       <c r="B842" t="s">
-        <v>1685</v>
+        <v>1662</v>
       </c>
       <c r="D842" t="s">
         <v>9</v>
@@ -15069,10 +15159,10 @@
     </row>
     <row r="843" spans="1:4">
       <c r="A843" t="s">
-        <v>1686</v>
+        <v>1663</v>
       </c>
       <c r="B843" t="s">
-        <v>1687</v>
+        <v>1662</v>
       </c>
       <c r="D843" t="s">
         <v>9</v>
@@ -15080,10 +15170,10 @@
     </row>
     <row r="844" spans="1:4">
       <c r="A844" t="s">
-        <v>1688</v>
+        <v>1664</v>
       </c>
       <c r="B844" t="s">
-        <v>1689</v>
+        <v>1665</v>
       </c>
       <c r="D844" t="s">
         <v>9</v>
@@ -15091,10 +15181,10 @@
     </row>
     <row r="845" spans="1:4">
       <c r="A845" t="s">
-        <v>1690</v>
+        <v>1666</v>
       </c>
       <c r="B845" t="s">
-        <v>1691</v>
+        <v>1667</v>
       </c>
       <c r="D845" t="s">
         <v>9</v>
@@ -15102,10 +15192,10 @@
     </row>
     <row r="846" spans="1:4">
       <c r="A846" t="s">
-        <v>1692</v>
+        <v>1668</v>
       </c>
       <c r="B846" t="s">
-        <v>1693</v>
+        <v>1669</v>
       </c>
       <c r="D846" t="s">
         <v>9</v>
@@ -15113,10 +15203,10 @@
     </row>
     <row r="847" spans="1:4">
       <c r="A847" t="s">
-        <v>1694</v>
+        <v>1670</v>
       </c>
       <c r="B847" t="s">
-        <v>1695</v>
+        <v>1671</v>
       </c>
       <c r="D847" t="s">
         <v>9</v>
@@ -15124,10 +15214,10 @@
     </row>
     <row r="848" spans="1:4">
       <c r="A848" t="s">
-        <v>1696</v>
+        <v>1672</v>
       </c>
       <c r="B848" t="s">
-        <v>1697</v>
+        <v>1673</v>
       </c>
       <c r="D848" t="s">
         <v>9</v>
@@ -15135,10 +15225,10 @@
     </row>
     <row r="849" spans="1:4">
       <c r="A849" t="s">
-        <v>1698</v>
+        <v>1674</v>
       </c>
       <c r="B849" t="s">
-        <v>1699</v>
+        <v>1675</v>
       </c>
       <c r="D849" t="s">
         <v>9</v>
@@ -15146,10 +15236,10 @@
     </row>
     <row r="850" spans="1:4">
       <c r="A850" t="s">
-        <v>1700</v>
+        <v>1676</v>
       </c>
       <c r="B850" t="s">
-        <v>1701</v>
+        <v>1675</v>
       </c>
       <c r="D850" t="s">
         <v>9</v>
@@ -15157,10 +15247,10 @@
     </row>
     <row r="851" spans="1:4">
       <c r="A851" t="s">
-        <v>1702</v>
+        <v>1677</v>
       </c>
       <c r="B851" t="s">
-        <v>1703</v>
+        <v>1678</v>
       </c>
       <c r="D851" t="s">
         <v>9</v>
@@ -15168,10 +15258,10 @@
     </row>
     <row r="852" spans="1:4">
       <c r="A852" t="s">
-        <v>1704</v>
+        <v>1679</v>
       </c>
       <c r="B852" t="s">
-        <v>1705</v>
+        <v>1680</v>
       </c>
       <c r="D852" t="s">
         <v>9</v>
@@ -15179,10 +15269,10 @@
     </row>
     <row r="853" spans="1:4">
       <c r="A853" t="s">
-        <v>1706</v>
+        <v>1681</v>
       </c>
       <c r="B853" t="s">
-        <v>1707</v>
+        <v>1682</v>
       </c>
       <c r="D853" t="s">
         <v>9</v>
@@ -15190,10 +15280,10 @@
     </row>
     <row r="854" spans="1:4">
       <c r="A854" t="s">
-        <v>1708</v>
+        <v>1683</v>
       </c>
       <c r="B854" t="s">
-        <v>1709</v>
+        <v>1684</v>
       </c>
       <c r="D854" t="s">
         <v>9</v>
@@ -15201,10 +15291,10 @@
     </row>
     <row r="855" spans="1:4">
       <c r="A855" t="s">
-        <v>1710</v>
+        <v>1685</v>
       </c>
       <c r="B855" t="s">
-        <v>1711</v>
+        <v>1686</v>
       </c>
       <c r="D855" t="s">
         <v>9</v>
@@ -15212,10 +15302,10 @@
     </row>
     <row r="856" spans="1:4">
       <c r="A856" t="s">
-        <v>1712</v>
+        <v>1687</v>
       </c>
       <c r="B856" t="s">
-        <v>1713</v>
+        <v>1686</v>
       </c>
       <c r="D856" t="s">
         <v>9</v>
@@ -15223,10 +15313,10 @@
     </row>
     <row r="857" spans="1:4">
       <c r="A857" t="s">
-        <v>1714</v>
+        <v>1688</v>
       </c>
       <c r="B857" t="s">
-        <v>1715</v>
+        <v>1689</v>
       </c>
       <c r="D857" t="s">
         <v>9</v>
@@ -15234,10 +15324,10 @@
     </row>
     <row r="858" spans="1:4">
       <c r="A858" t="s">
-        <v>1716</v>
+        <v>1690</v>
       </c>
       <c r="B858" t="s">
-        <v>1717</v>
+        <v>1691</v>
       </c>
       <c r="D858" t="s">
         <v>9</v>
@@ -15245,10 +15335,10 @@
     </row>
     <row r="859" spans="1:4">
       <c r="A859" t="s">
-        <v>1718</v>
+        <v>1692</v>
       </c>
       <c r="B859" t="s">
-        <v>1719</v>
+        <v>1693</v>
       </c>
       <c r="D859" t="s">
         <v>9</v>
@@ -15256,10 +15346,10 @@
     </row>
     <row r="860" spans="1:4">
       <c r="A860" t="s">
-        <v>1720</v>
+        <v>1694</v>
       </c>
       <c r="B860" t="s">
-        <v>1721</v>
+        <v>1695</v>
       </c>
       <c r="D860" t="s">
         <v>9</v>
@@ -15267,10 +15357,10 @@
     </row>
     <row r="861" spans="1:4">
       <c r="A861" t="s">
-        <v>1722</v>
+        <v>1696</v>
       </c>
       <c r="B861" t="s">
-        <v>1723</v>
+        <v>1697</v>
       </c>
       <c r="D861" t="s">
         <v>9</v>
@@ -15278,10 +15368,10 @@
     </row>
     <row r="862" spans="1:4">
       <c r="A862" t="s">
-        <v>1724</v>
+        <v>1698</v>
       </c>
       <c r="B862" t="s">
-        <v>1725</v>
+        <v>1699</v>
       </c>
       <c r="D862" t="s">
         <v>9</v>
@@ -15289,10 +15379,10 @@
     </row>
     <row r="863" spans="1:4">
       <c r="A863" t="s">
-        <v>1726</v>
+        <v>1700</v>
       </c>
       <c r="B863" t="s">
-        <v>1727</v>
+        <v>1701</v>
       </c>
       <c r="D863" t="s">
         <v>9</v>
@@ -15300,10 +15390,10 @@
     </row>
     <row r="864" spans="1:4">
       <c r="A864" t="s">
-        <v>1728</v>
+        <v>1702</v>
       </c>
       <c r="B864" t="s">
-        <v>1729</v>
+        <v>1703</v>
       </c>
       <c r="D864" t="s">
         <v>9</v>
@@ -15311,10 +15401,10 @@
     </row>
     <row r="865" spans="1:4">
       <c r="A865" t="s">
-        <v>1730</v>
+        <v>1704</v>
       </c>
       <c r="B865" t="s">
-        <v>1731</v>
+        <v>1705</v>
       </c>
       <c r="D865" t="s">
         <v>9</v>
@@ -15322,10 +15412,10 @@
     </row>
     <row r="866" spans="1:4">
       <c r="A866" t="s">
-        <v>1732</v>
+        <v>1706</v>
       </c>
       <c r="B866" t="s">
-        <v>1733</v>
+        <v>1707</v>
       </c>
       <c r="D866" t="s">
         <v>9</v>
@@ -15333,10 +15423,10 @@
     </row>
     <row r="867" spans="1:4">
       <c r="A867" t="s">
-        <v>1734</v>
+        <v>1708</v>
       </c>
       <c r="B867" t="s">
-        <v>1735</v>
+        <v>1709</v>
       </c>
       <c r="D867" t="s">
         <v>9</v>
@@ -15344,10 +15434,10 @@
     </row>
     <row r="868" spans="1:4">
       <c r="A868" t="s">
-        <v>1736</v>
+        <v>1710</v>
       </c>
       <c r="B868" t="s">
-        <v>1737</v>
+        <v>1711</v>
       </c>
       <c r="D868" t="s">
         <v>9</v>
@@ -15355,10 +15445,10 @@
     </row>
     <row r="869" spans="1:4">
       <c r="A869" t="s">
-        <v>1738</v>
+        <v>1712</v>
       </c>
       <c r="B869" t="s">
-        <v>1739</v>
+        <v>1713</v>
       </c>
       <c r="D869" t="s">
         <v>9</v>
@@ -15366,10 +15456,10 @@
     </row>
     <row r="870" spans="1:4">
       <c r="A870" t="s">
-        <v>1740</v>
+        <v>1714</v>
       </c>
       <c r="B870" t="s">
-        <v>1741</v>
+        <v>1715</v>
       </c>
       <c r="D870" t="s">
         <v>9</v>
@@ -15377,10 +15467,10 @@
     </row>
     <row r="871" spans="1:4">
       <c r="A871" t="s">
-        <v>1742</v>
+        <v>1716</v>
       </c>
       <c r="B871" t="s">
-        <v>1743</v>
+        <v>1717</v>
       </c>
       <c r="D871" t="s">
         <v>9</v>
@@ -15388,10 +15478,10 @@
     </row>
     <row r="872" spans="1:4">
       <c r="A872" t="s">
-        <v>1744</v>
+        <v>1718</v>
       </c>
       <c r="B872" t="s">
-        <v>1745</v>
+        <v>1719</v>
       </c>
       <c r="D872" t="s">
         <v>9</v>
@@ -15399,10 +15489,10 @@
     </row>
     <row r="873" spans="1:4">
       <c r="A873" t="s">
-        <v>1746</v>
+        <v>1720</v>
       </c>
       <c r="B873" t="s">
-        <v>1747</v>
+        <v>1721</v>
       </c>
       <c r="D873" t="s">
         <v>9</v>
@@ -15410,10 +15500,10 @@
     </row>
     <row r="874" spans="1:4">
       <c r="A874" t="s">
-        <v>1748</v>
+        <v>1722</v>
       </c>
       <c r="B874" t="s">
-        <v>1749</v>
+        <v>1723</v>
       </c>
       <c r="D874" t="s">
         <v>9</v>
@@ -15421,10 +15511,10 @@
     </row>
     <row r="875" spans="1:4">
       <c r="A875" t="s">
-        <v>1750</v>
+        <v>1724</v>
       </c>
       <c r="B875" t="s">
-        <v>1751</v>
+        <v>1725</v>
       </c>
       <c r="D875" t="s">
         <v>9</v>
@@ -15432,10 +15522,10 @@
     </row>
     <row r="876" spans="1:4">
       <c r="A876" t="s">
-        <v>1752</v>
+        <v>1726</v>
       </c>
       <c r="B876" t="s">
-        <v>1753</v>
+        <v>1727</v>
       </c>
       <c r="D876" t="s">
         <v>9</v>
@@ -15443,10 +15533,10 @@
     </row>
     <row r="877" spans="1:4">
       <c r="A877" t="s">
-        <v>1754</v>
+        <v>1728</v>
       </c>
       <c r="B877" t="s">
-        <v>1755</v>
+        <v>1727</v>
       </c>
       <c r="D877" t="s">
         <v>9</v>
@@ -15454,10 +15544,10 @@
     </row>
     <row r="878" spans="1:4">
       <c r="A878" t="s">
-        <v>1756</v>
+        <v>1729</v>
       </c>
       <c r="B878" t="s">
-        <v>1757</v>
+        <v>1730</v>
       </c>
       <c r="D878" t="s">
         <v>9</v>
@@ -15465,10 +15555,10 @@
     </row>
     <row r="879" spans="1:4">
       <c r="A879" t="s">
-        <v>1758</v>
+        <v>1731</v>
       </c>
       <c r="B879" t="s">
-        <v>1759</v>
+        <v>1732</v>
       </c>
       <c r="D879" t="s">
         <v>9</v>
@@ -15476,10 +15566,10 @@
     </row>
     <row r="880" spans="1:4">
       <c r="A880" t="s">
-        <v>1760</v>
+        <v>1733</v>
       </c>
       <c r="B880" t="s">
-        <v>1761</v>
+        <v>1734</v>
       </c>
       <c r="D880" t="s">
         <v>9</v>
@@ -15487,10 +15577,10 @@
     </row>
     <row r="881" spans="1:4">
       <c r="A881" t="s">
-        <v>1762</v>
+        <v>1735</v>
       </c>
       <c r="B881" t="s">
-        <v>1763</v>
+        <v>1736</v>
       </c>
       <c r="D881" t="s">
         <v>9</v>
@@ -15498,10 +15588,10 @@
     </row>
     <row r="882" spans="1:4">
       <c r="A882" t="s">
-        <v>1764</v>
+        <v>1737</v>
       </c>
       <c r="B882" t="s">
-        <v>1765</v>
+        <v>1738</v>
       </c>
       <c r="D882" t="s">
         <v>9</v>
@@ -15509,10 +15599,10 @@
     </row>
     <row r="883" spans="1:4">
       <c r="A883" t="s">
-        <v>1766</v>
+        <v>1739</v>
       </c>
       <c r="B883" t="s">
-        <v>1767</v>
+        <v>1740</v>
       </c>
       <c r="D883" t="s">
         <v>9</v>
@@ -15520,10 +15610,10 @@
     </row>
     <row r="884" spans="1:4">
       <c r="A884" t="s">
-        <v>1768</v>
+        <v>1741</v>
       </c>
       <c r="B884" t="s">
-        <v>1769</v>
+        <v>1742</v>
       </c>
       <c r="D884" t="s">
         <v>9</v>
@@ -15531,10 +15621,10 @@
     </row>
     <row r="885" spans="1:4">
       <c r="A885" t="s">
-        <v>1770</v>
+        <v>1743</v>
       </c>
       <c r="B885" t="s">
-        <v>1771</v>
+        <v>1744</v>
       </c>
       <c r="D885" t="s">
         <v>9</v>
@@ -15542,10 +15632,10 @@
     </row>
     <row r="886" spans="1:4">
       <c r="A886" t="s">
-        <v>1772</v>
+        <v>1745</v>
       </c>
       <c r="B886" t="s">
-        <v>1773</v>
+        <v>1746</v>
       </c>
       <c r="D886" t="s">
         <v>9</v>
@@ -15553,10 +15643,10 @@
     </row>
     <row r="887" spans="1:4">
       <c r="A887" t="s">
-        <v>1774</v>
+        <v>1747</v>
       </c>
       <c r="B887" t="s">
-        <v>1775</v>
+        <v>1748</v>
       </c>
       <c r="D887" t="s">
         <v>9</v>
@@ -15564,10 +15654,10 @@
     </row>
     <row r="888" spans="1:4">
       <c r="A888" t="s">
-        <v>1776</v>
+        <v>1749</v>
       </c>
       <c r="B888" t="s">
-        <v>1777</v>
+        <v>1750</v>
       </c>
       <c r="D888" t="s">
         <v>9</v>
@@ -15575,10 +15665,10 @@
     </row>
     <row r="889" spans="1:4">
       <c r="A889" t="s">
-        <v>1778</v>
+        <v>1751</v>
       </c>
       <c r="B889" t="s">
-        <v>1779</v>
+        <v>1752</v>
       </c>
       <c r="D889" t="s">
         <v>9</v>
@@ -15586,10 +15676,10 @@
     </row>
     <row r="890" spans="1:4">
       <c r="A890" t="s">
-        <v>1780</v>
+        <v>1753</v>
       </c>
       <c r="B890" t="s">
-        <v>1781</v>
+        <v>1754</v>
       </c>
       <c r="D890" t="s">
         <v>9</v>
@@ -15597,10 +15687,10 @@
     </row>
     <row r="891" spans="1:4">
       <c r="A891" t="s">
-        <v>1782</v>
+        <v>1755</v>
       </c>
       <c r="B891" t="s">
-        <v>1783</v>
+        <v>1756</v>
       </c>
       <c r="D891" t="s">
         <v>9</v>
@@ -15608,10 +15698,10 @@
     </row>
     <row r="892" spans="1:4">
       <c r="A892" t="s">
-        <v>1784</v>
+        <v>1757</v>
       </c>
       <c r="B892" t="s">
-        <v>1785</v>
+        <v>1758</v>
       </c>
       <c r="D892" t="s">
         <v>9</v>
@@ -15619,10 +15709,10 @@
     </row>
     <row r="893" spans="1:4">
       <c r="A893" t="s">
-        <v>1786</v>
+        <v>1759</v>
       </c>
       <c r="B893" t="s">
-        <v>1787</v>
+        <v>1760</v>
       </c>
       <c r="D893" t="s">
         <v>9</v>
@@ -15630,10 +15720,10 @@
     </row>
     <row r="894" spans="1:4">
       <c r="A894" t="s">
-        <v>1788</v>
+        <v>1761</v>
       </c>
       <c r="B894" t="s">
-        <v>1789</v>
+        <v>1717</v>
       </c>
       <c r="D894" t="s">
         <v>9</v>
@@ -15641,10 +15731,10 @@
     </row>
     <row r="895" spans="1:4">
       <c r="A895" t="s">
-        <v>1790</v>
+        <v>1762</v>
       </c>
       <c r="B895" t="s">
-        <v>1791</v>
+        <v>1763</v>
       </c>
       <c r="D895" t="s">
         <v>9</v>
@@ -15652,10 +15742,10 @@
     </row>
     <row r="896" spans="1:4">
       <c r="A896" t="s">
-        <v>1792</v>
+        <v>1764</v>
       </c>
       <c r="B896" t="s">
-        <v>1791</v>
+        <v>1765</v>
       </c>
       <c r="D896" t="s">
         <v>9</v>
@@ -15663,10 +15753,10 @@
     </row>
     <row r="897" spans="1:4">
       <c r="A897" t="s">
-        <v>1793</v>
+        <v>1766</v>
       </c>
       <c r="B897" t="s">
-        <v>1794</v>
+        <v>1767</v>
       </c>
       <c r="D897" t="s">
         <v>9</v>
@@ -15674,10 +15764,10 @@
     </row>
     <row r="898" spans="1:4">
       <c r="A898" t="s">
-        <v>1795</v>
+        <v>1768</v>
       </c>
       <c r="B898" t="s">
-        <v>1796</v>
+        <v>1769</v>
       </c>
       <c r="D898" t="s">
         <v>9</v>
@@ -15685,10 +15775,10 @@
     </row>
     <row r="899" spans="1:4">
       <c r="A899" t="s">
-        <v>1797</v>
+        <v>1770</v>
       </c>
       <c r="B899" t="s">
-        <v>1798</v>
+        <v>1771</v>
       </c>
       <c r="D899" t="s">
         <v>9</v>
@@ -15696,10 +15786,10 @@
     </row>
     <row r="900" spans="1:4">
       <c r="A900" t="s">
-        <v>1799</v>
+        <v>1772</v>
       </c>
       <c r="B900" t="s">
-        <v>1800</v>
+        <v>1773</v>
       </c>
       <c r="D900" t="s">
         <v>9</v>
@@ -15707,10 +15797,10 @@
     </row>
     <row r="901" spans="1:4">
       <c r="A901" t="s">
-        <v>1801</v>
+        <v>1774</v>
       </c>
       <c r="B901" t="s">
-        <v>1802</v>
+        <v>1775</v>
       </c>
       <c r="D901" t="s">
         <v>9</v>
@@ -15718,10 +15808,10 @@
     </row>
     <row r="902" spans="1:4">
       <c r="A902" t="s">
-        <v>1803</v>
+        <v>1776</v>
       </c>
       <c r="B902" t="s">
-        <v>1804</v>
+        <v>1777</v>
       </c>
       <c r="D902" t="s">
         <v>9</v>
@@ -15729,10 +15819,10 @@
     </row>
     <row r="903" spans="1:4">
       <c r="A903" t="s">
-        <v>1805</v>
+        <v>1778</v>
       </c>
       <c r="B903" t="s">
-        <v>1806</v>
+        <v>1779</v>
       </c>
       <c r="D903" t="s">
         <v>9</v>
@@ -15740,10 +15830,10 @@
     </row>
     <row r="904" spans="1:4">
       <c r="A904" t="s">
-        <v>1807</v>
+        <v>1780</v>
       </c>
       <c r="B904" t="s">
-        <v>1808</v>
+        <v>1781</v>
       </c>
       <c r="D904" t="s">
         <v>9</v>
@@ -15751,10 +15841,10 @@
     </row>
     <row r="905" spans="1:4">
       <c r="A905" t="s">
-        <v>1809</v>
+        <v>1782</v>
       </c>
       <c r="B905" t="s">
-        <v>1810</v>
+        <v>1783</v>
       </c>
       <c r="D905" t="s">
         <v>9</v>
@@ -15762,10 +15852,10 @@
     </row>
     <row r="906" spans="1:4">
       <c r="A906" t="s">
-        <v>1811</v>
+        <v>1784</v>
       </c>
       <c r="B906" t="s">
-        <v>1812</v>
+        <v>1785</v>
       </c>
       <c r="D906" t="s">
         <v>9</v>
@@ -15773,12 +15863,342 @@
     </row>
     <row r="907" spans="1:4">
       <c r="A907" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B907" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D907" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="908" spans="1:4">
+      <c r="A908" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B908" t="s">
+        <v>1789</v>
+      </c>
+      <c r="D908" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="909" spans="1:4">
+      <c r="A909" t="s">
+        <v>1790</v>
+      </c>
+      <c r="B909" t="s">
+        <v>1791</v>
+      </c>
+      <c r="D909" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="910" spans="1:4">
+      <c r="A910" t="s">
+        <v>1792</v>
+      </c>
+      <c r="B910" t="s">
+        <v>1793</v>
+      </c>
+      <c r="D910" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="911" spans="1:4">
+      <c r="A911" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B911" t="s">
+        <v>1795</v>
+      </c>
+      <c r="D911" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="912" spans="1:4">
+      <c r="A912" t="s">
+        <v>1796</v>
+      </c>
+      <c r="B912" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D912" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="913" spans="1:4">
+      <c r="A913" t="s">
+        <v>1798</v>
+      </c>
+      <c r="B913" t="s">
+        <v>1799</v>
+      </c>
+      <c r="D913" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="914" spans="1:4">
+      <c r="A914" t="s">
+        <v>1800</v>
+      </c>
+      <c r="B914" t="s">
+        <v>1801</v>
+      </c>
+      <c r="D914" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="915" spans="1:4">
+      <c r="A915" t="s">
+        <v>1802</v>
+      </c>
+      <c r="B915" t="s">
+        <v>1803</v>
+      </c>
+      <c r="D915" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="916" spans="1:4">
+      <c r="A916" t="s">
+        <v>1804</v>
+      </c>
+      <c r="B916" t="s">
+        <v>1805</v>
+      </c>
+      <c r="D916" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="917" spans="1:4">
+      <c r="A917" t="s">
+        <v>1806</v>
+      </c>
+      <c r="B917" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D917" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="918" spans="1:4">
+      <c r="A918" t="s">
+        <v>1808</v>
+      </c>
+      <c r="B918" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D918" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="919" spans="1:4">
+      <c r="A919" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B919" t="s">
+        <v>1810</v>
+      </c>
+      <c r="D919" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="920" spans="1:4">
+      <c r="A920" t="s">
+        <v>1811</v>
+      </c>
+      <c r="B920" t="s">
+        <v>1812</v>
+      </c>
+      <c r="D920" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="921" spans="1:4">
+      <c r="A921" t="s">
         <v>1813</v>
       </c>
-      <c r="B907" t="s">
+      <c r="B921" t="s">
         <v>1814</v>
       </c>
-      <c r="D907" t="s">
+      <c r="D921" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="922" spans="1:4">
+      <c r="A922" t="s">
+        <v>1815</v>
+      </c>
+      <c r="B922" t="s">
+        <v>1816</v>
+      </c>
+      <c r="D922" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="923" spans="1:4">
+      <c r="A923" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B923" t="s">
+        <v>1818</v>
+      </c>
+      <c r="D923" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="924" spans="1:4">
+      <c r="A924" t="s">
+        <v>1819</v>
+      </c>
+      <c r="B924" t="s">
+        <v>1820</v>
+      </c>
+      <c r="D924" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="925" spans="1:4">
+      <c r="A925" t="s">
+        <v>1821</v>
+      </c>
+      <c r="B925" t="s">
+        <v>1820</v>
+      </c>
+      <c r="D925" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="926" spans="1:4">
+      <c r="A926" t="s">
+        <v>1822</v>
+      </c>
+      <c r="B926" t="s">
+        <v>1823</v>
+      </c>
+      <c r="D926" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="927" spans="1:4">
+      <c r="A927" t="s">
+        <v>1824</v>
+      </c>
+      <c r="B927" t="s">
+        <v>1825</v>
+      </c>
+      <c r="D927" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="928" spans="1:4">
+      <c r="A928" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B928" t="s">
+        <v>1827</v>
+      </c>
+      <c r="D928" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="929" spans="1:4">
+      <c r="A929" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B929" t="s">
+        <v>1829</v>
+      </c>
+      <c r="D929" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="930" spans="1:4">
+      <c r="A930" t="s">
+        <v>1830</v>
+      </c>
+      <c r="B930" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D930" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="931" spans="1:4">
+      <c r="A931" t="s">
+        <v>1832</v>
+      </c>
+      <c r="B931" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D931" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="932" spans="1:4">
+      <c r="A932" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B932" t="s">
+        <v>1835</v>
+      </c>
+      <c r="D932" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="933" spans="1:4">
+      <c r="A933" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B933" t="s">
+        <v>1837</v>
+      </c>
+      <c r="D933" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="934" spans="1:4">
+      <c r="A934" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B934" t="s">
+        <v>1839</v>
+      </c>
+      <c r="D934" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="935" spans="1:4">
+      <c r="A935" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B935" t="s">
+        <v>1829</v>
+      </c>
+      <c r="D935" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="936" spans="1:4">
+      <c r="A936" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B936" t="s">
+        <v>1842</v>
+      </c>
+      <c r="D936" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="937" spans="1:4">
+      <c r="A937" t="s">
+        <v>1843</v>
+      </c>
+      <c r="B937" t="s">
+        <v>1844</v>
+      </c>
+      <c r="D937" t="s">
         <v>9</v>
       </c>
     </row>

--- a/api/1/clv1/codelist/HumanitarianPlan.xlsx
+++ b/api/1/clv1/codelist/HumanitarianPlan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2815" uniqueCount="1845">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2818" uniqueCount="1847">
   <si>
     <t>code</t>
   </si>
@@ -283,7 +283,13 @@
     <t>OVNM25</t>
   </si>
   <si>
-    <t>Viet Nam Joint Response Plan for Typhoon Yagi and Floods 2025</t>
+    <t>Viet Nam 24-25 Joint Response Plan for Typhoon Yagi and Floods 2025</t>
+  </si>
+  <si>
+    <t>OVNM25a</t>
+  </si>
+  <si>
+    <t>Viet Nam 25-26 Joint Response Plan multiple Typhoons and Floods 2025</t>
   </si>
   <si>
     <t>HYEM25</t>
@@ -589,7 +595,7 @@
     <t>OVNM24</t>
   </si>
   <si>
-    <t>Viet Nam  Joint Response Plan for Typhoon Yagi and Floods 2024</t>
+    <t>Viet Nam 24-25 Joint Response Plan for Typhoon Yagi and Floods 2024</t>
   </si>
   <si>
     <t>HYEM24</t>
@@ -5880,7 +5886,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G937"/>
+  <dimension ref="A1:G938"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -7264,7 +7270,7 @@
         <v>254</v>
       </c>
       <c r="B125" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D125" t="s">
         <v>9</v>
@@ -7272,10 +7278,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" t="s">
+        <v>256</v>
+      </c>
+      <c r="B126" t="s">
         <v>255</v>
-      </c>
-      <c r="B126" t="s">
-        <v>256</v>
       </c>
       <c r="D126" t="s">
         <v>9</v>
@@ -7803,7 +7809,7 @@
         <v>351</v>
       </c>
       <c r="B174" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D174" t="s">
         <v>9</v>
@@ -7811,10 +7817,10 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" t="s">
+        <v>353</v>
+      </c>
+      <c r="B175" t="s">
         <v>352</v>
-      </c>
-      <c r="B175" t="s">
-        <v>353</v>
       </c>
       <c r="D175" t="s">
         <v>9</v>
@@ -8419,7 +8425,7 @@
         <v>462</v>
       </c>
       <c r="B230" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D230" t="s">
         <v>9</v>
@@ -8427,10 +8433,10 @@
     </row>
     <row r="231" spans="1:4">
       <c r="A231" t="s">
+        <v>464</v>
+      </c>
+      <c r="B231" t="s">
         <v>463</v>
-      </c>
-      <c r="B231" t="s">
-        <v>464</v>
       </c>
       <c r="D231" t="s">
         <v>9</v>
@@ -10377,7 +10383,7 @@
         <v>817</v>
       </c>
       <c r="B408" t="s">
-        <v>788</v>
+        <v>818</v>
       </c>
       <c r="D408" t="s">
         <v>9</v>
@@ -10385,10 +10391,10 @@
     </row>
     <row r="409" spans="1:4">
       <c r="A409" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B409" t="s">
-        <v>762</v>
+        <v>790</v>
       </c>
       <c r="D409" t="s">
         <v>9</v>
@@ -10396,10 +10402,10 @@
     </row>
     <row r="410" spans="1:4">
       <c r="A410" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B410" t="s">
-        <v>820</v>
+        <v>764</v>
       </c>
       <c r="D410" t="s">
         <v>9</v>
@@ -10465,7 +10471,7 @@
         <v>831</v>
       </c>
       <c r="B416" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="D416" t="s">
         <v>9</v>
@@ -10473,10 +10479,10 @@
     </row>
     <row r="417" spans="1:4">
       <c r="A417" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B417" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="D417" t="s">
         <v>9</v>
@@ -10806,7 +10812,7 @@
         <v>892</v>
       </c>
       <c r="B447" t="s">
-        <v>837</v>
+        <v>893</v>
       </c>
       <c r="D447" t="s">
         <v>9</v>
@@ -10814,10 +10820,10 @@
     </row>
     <row r="448" spans="1:4">
       <c r="A448" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B448" t="s">
-        <v>894</v>
+        <v>839</v>
       </c>
       <c r="D448" t="s">
         <v>9</v>
@@ -10839,7 +10845,7 @@
         <v>897</v>
       </c>
       <c r="B450" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="D450" t="s">
         <v>9</v>
@@ -10847,10 +10853,10 @@
     </row>
     <row r="451" spans="1:4">
       <c r="A451" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B451" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="D451" t="s">
         <v>9</v>
@@ -11202,7 +11208,7 @@
         <v>962</v>
       </c>
       <c r="B483" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="D483" t="s">
         <v>9</v>
@@ -11210,10 +11216,10 @@
     </row>
     <row r="484" spans="1:4">
       <c r="A484" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B484" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="D484" t="s">
         <v>9</v>
@@ -11609,7 +11615,7 @@
         <v>1035</v>
       </c>
       <c r="B520" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D520" t="s">
         <v>9</v>
@@ -11617,10 +11623,10 @@
     </row>
     <row r="521" spans="1:4">
       <c r="A521" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B521" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="D521" t="s">
         <v>9</v>
@@ -12632,7 +12638,7 @@
         <v>1220</v>
       </c>
       <c r="B613" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="D613" t="s">
         <v>9</v>
@@ -12640,10 +12646,10 @@
     </row>
     <row r="614" spans="1:4">
       <c r="A614" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B614" t="s">
         <v>1221</v>
-      </c>
-      <c r="B614" t="s">
-        <v>1222</v>
       </c>
       <c r="D614" t="s">
         <v>9</v>
@@ -12709,7 +12715,7 @@
         <v>1233</v>
       </c>
       <c r="B620" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="D620" t="s">
         <v>9</v>
@@ -12717,10 +12723,10 @@
     </row>
     <row r="621" spans="1:4">
       <c r="A621" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B621" t="s">
         <v>1234</v>
-      </c>
-      <c r="B621" t="s">
-        <v>1235</v>
       </c>
       <c r="D621" t="s">
         <v>9</v>
@@ -12764,7 +12770,7 @@
         <v>1242</v>
       </c>
       <c r="B625" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="D625" t="s">
         <v>9</v>
@@ -12772,10 +12778,10 @@
     </row>
     <row r="626" spans="1:4">
       <c r="A626" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B626" t="s">
         <v>1243</v>
-      </c>
-      <c r="B626" t="s">
-        <v>1244</v>
       </c>
       <c r="D626" t="s">
         <v>9</v>
@@ -12808,7 +12814,7 @@
         <v>1249</v>
       </c>
       <c r="B629" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="D629" t="s">
         <v>9</v>
@@ -12816,10 +12822,10 @@
     </row>
     <row r="630" spans="1:4">
       <c r="A630" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B630" t="s">
         <v>1250</v>
-      </c>
-      <c r="B630" t="s">
-        <v>1251</v>
       </c>
       <c r="D630" t="s">
         <v>9</v>
@@ -12940,7 +12946,7 @@
         <v>1272</v>
       </c>
       <c r="B641" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="D641" t="s">
         <v>9</v>
@@ -12948,10 +12954,10 @@
     </row>
     <row r="642" spans="1:4">
       <c r="A642" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B642" t="s">
         <v>1273</v>
-      </c>
-      <c r="B642" t="s">
-        <v>1274</v>
       </c>
       <c r="D642" t="s">
         <v>9</v>
@@ -13116,7 +13122,7 @@
         <v>1303</v>
       </c>
       <c r="B657" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="D657" t="s">
         <v>9</v>
@@ -13124,10 +13130,10 @@
     </row>
     <row r="658" spans="1:4">
       <c r="A658" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B658" t="s">
         <v>1304</v>
-      </c>
-      <c r="B658" t="s">
-        <v>1305</v>
       </c>
       <c r="D658" t="s">
         <v>9</v>
@@ -13347,7 +13353,7 @@
         <v>1344</v>
       </c>
       <c r="B678" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="D678" t="s">
         <v>9</v>
@@ -13355,10 +13361,10 @@
     </row>
     <row r="679" spans="1:4">
       <c r="A679" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B679" t="s">
         <v>1345</v>
-      </c>
-      <c r="B679" t="s">
-        <v>1346</v>
       </c>
       <c r="D679" t="s">
         <v>9</v>
@@ -13501,7 +13507,7 @@
         <v>1371</v>
       </c>
       <c r="B692" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="D692" t="s">
         <v>9</v>
@@ -13509,10 +13515,10 @@
     </row>
     <row r="693" spans="1:4">
       <c r="A693" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B693" t="s">
         <v>1372</v>
-      </c>
-      <c r="B693" t="s">
-        <v>1373</v>
       </c>
       <c r="D693" t="s">
         <v>9</v>
@@ -13831,7 +13837,7 @@
         <v>1430</v>
       </c>
       <c r="B722" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="D722" t="s">
         <v>9</v>
@@ -13839,10 +13845,10 @@
     </row>
     <row r="723" spans="1:4">
       <c r="A723" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B723" t="s">
         <v>1431</v>
-      </c>
-      <c r="B723" t="s">
-        <v>1432</v>
       </c>
       <c r="D723" t="s">
         <v>9</v>
@@ -13919,7 +13925,7 @@
         <v>1445</v>
       </c>
       <c r="B730" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="D730" t="s">
         <v>9</v>
@@ -13927,10 +13933,10 @@
     </row>
     <row r="731" spans="1:4">
       <c r="A731" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B731" t="s">
         <v>1446</v>
-      </c>
-      <c r="B731" t="s">
-        <v>1447</v>
       </c>
       <c r="D731" t="s">
         <v>9</v>
@@ -14293,7 +14299,7 @@
         <v>1512</v>
       </c>
       <c r="B764" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="D764" t="s">
         <v>9</v>
@@ -14301,10 +14307,10 @@
     </row>
     <row r="765" spans="1:4">
       <c r="A765" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B765" t="s">
         <v>1513</v>
-      </c>
-      <c r="B765" t="s">
-        <v>1514</v>
       </c>
       <c r="D765" t="s">
         <v>9</v>
@@ -14502,7 +14508,7 @@
         <v>1549</v>
       </c>
       <c r="B783" t="s">
-        <v>1540</v>
+        <v>1550</v>
       </c>
       <c r="D783" t="s">
         <v>9</v>
@@ -14510,10 +14516,10 @@
     </row>
     <row r="784" spans="1:4">
       <c r="A784" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B784" t="s">
-        <v>1551</v>
+        <v>1542</v>
       </c>
       <c r="D784" t="s">
         <v>9</v>
@@ -14590,7 +14596,7 @@
         <v>1564</v>
       </c>
       <c r="B791" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
       <c r="D791" t="s">
         <v>9</v>
@@ -14598,10 +14604,10 @@
     </row>
     <row r="792" spans="1:4">
       <c r="A792" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="B792" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="D792" t="s">
         <v>9</v>
@@ -14623,7 +14629,7 @@
         <v>1569</v>
       </c>
       <c r="B794" t="s">
-        <v>1559</v>
+        <v>1570</v>
       </c>
       <c r="D794" t="s">
         <v>9</v>
@@ -14631,10 +14637,10 @@
     </row>
     <row r="795" spans="1:4">
       <c r="A795" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="B795" t="s">
-        <v>1571</v>
+        <v>1561</v>
       </c>
       <c r="D795" t="s">
         <v>9</v>
@@ -14975,7 +14981,7 @@
         <v>1632</v>
       </c>
       <c r="B826" t="s">
-        <v>1589</v>
+        <v>1633</v>
       </c>
       <c r="D826" t="s">
         <v>9</v>
@@ -14983,10 +14989,10 @@
     </row>
     <row r="827" spans="1:4">
       <c r="A827" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="B827" t="s">
-        <v>1634</v>
+        <v>1591</v>
       </c>
       <c r="D827" t="s">
         <v>9</v>
@@ -15096,7 +15102,7 @@
         <v>1653</v>
       </c>
       <c r="B837" t="s">
-        <v>1650</v>
+        <v>1654</v>
       </c>
       <c r="D837" t="s">
         <v>9</v>
@@ -15104,7 +15110,7 @@
     </row>
     <row r="838" spans="1:4">
       <c r="A838" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="B838" t="s">
         <v>1652</v>
@@ -15115,10 +15121,10 @@
     </row>
     <row r="839" spans="1:4">
       <c r="A839" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="B839" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="D839" t="s">
         <v>9</v>
@@ -15162,7 +15168,7 @@
         <v>1663</v>
       </c>
       <c r="B843" t="s">
-        <v>1662</v>
+        <v>1664</v>
       </c>
       <c r="D843" t="s">
         <v>9</v>
@@ -15170,10 +15176,10 @@
     </row>
     <row r="844" spans="1:4">
       <c r="A844" t="s">
+        <v>1665</v>
+      </c>
+      <c r="B844" t="s">
         <v>1664</v>
-      </c>
-      <c r="B844" t="s">
-        <v>1665</v>
       </c>
       <c r="D844" t="s">
         <v>9</v>
@@ -15239,7 +15245,7 @@
         <v>1676</v>
       </c>
       <c r="B850" t="s">
-        <v>1675</v>
+        <v>1677</v>
       </c>
       <c r="D850" t="s">
         <v>9</v>
@@ -15247,10 +15253,10 @@
     </row>
     <row r="851" spans="1:4">
       <c r="A851" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B851" t="s">
         <v>1677</v>
-      </c>
-      <c r="B851" t="s">
-        <v>1678</v>
       </c>
       <c r="D851" t="s">
         <v>9</v>
@@ -15305,7 +15311,7 @@
         <v>1687</v>
       </c>
       <c r="B856" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="D856" t="s">
         <v>9</v>
@@ -15313,10 +15319,10 @@
     </row>
     <row r="857" spans="1:4">
       <c r="A857" t="s">
+        <v>1689</v>
+      </c>
+      <c r="B857" t="s">
         <v>1688</v>
-      </c>
-      <c r="B857" t="s">
-        <v>1689</v>
       </c>
       <c r="D857" t="s">
         <v>9</v>
@@ -15536,7 +15542,7 @@
         <v>1728</v>
       </c>
       <c r="B877" t="s">
-        <v>1727</v>
+        <v>1729</v>
       </c>
       <c r="D877" t="s">
         <v>9</v>
@@ -15544,10 +15550,10 @@
     </row>
     <row r="878" spans="1:4">
       <c r="A878" t="s">
+        <v>1730</v>
+      </c>
+      <c r="B878" t="s">
         <v>1729</v>
-      </c>
-      <c r="B878" t="s">
-        <v>1730</v>
       </c>
       <c r="D878" t="s">
         <v>9</v>
@@ -15723,7 +15729,7 @@
         <v>1761</v>
       </c>
       <c r="B894" t="s">
-        <v>1717</v>
+        <v>1762</v>
       </c>
       <c r="D894" t="s">
         <v>9</v>
@@ -15731,10 +15737,10 @@
     </row>
     <row r="895" spans="1:4">
       <c r="A895" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="B895" t="s">
-        <v>1763</v>
+        <v>1719</v>
       </c>
       <c r="D895" t="s">
         <v>9</v>
@@ -15987,7 +15993,7 @@
         <v>1808</v>
       </c>
       <c r="B918" t="s">
-        <v>1775</v>
+        <v>1809</v>
       </c>
       <c r="D918" t="s">
         <v>9</v>
@@ -15995,10 +16001,10 @@
     </row>
     <row r="919" spans="1:4">
       <c r="A919" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="B919" t="s">
-        <v>1810</v>
+        <v>1777</v>
       </c>
       <c r="D919" t="s">
         <v>9</v>
@@ -16064,7 +16070,7 @@
         <v>1821</v>
       </c>
       <c r="B925" t="s">
-        <v>1820</v>
+        <v>1822</v>
       </c>
       <c r="D925" t="s">
         <v>9</v>
@@ -16072,10 +16078,10 @@
     </row>
     <row r="926" spans="1:4">
       <c r="A926" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B926" t="s">
         <v>1822</v>
-      </c>
-      <c r="B926" t="s">
-        <v>1823</v>
       </c>
       <c r="D926" t="s">
         <v>9</v>
@@ -16174,7 +16180,7 @@
         <v>1840</v>
       </c>
       <c r="B935" t="s">
-        <v>1829</v>
+        <v>1841</v>
       </c>
       <c r="D935" t="s">
         <v>9</v>
@@ -16182,10 +16188,10 @@
     </row>
     <row r="936" spans="1:4">
       <c r="A936" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="B936" t="s">
-        <v>1842</v>
+        <v>1831</v>
       </c>
       <c r="D936" t="s">
         <v>9</v>
@@ -16199,6 +16205,17 @@
         <v>1844</v>
       </c>
       <c r="D937" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="938" spans="1:4">
+      <c r="A938" t="s">
+        <v>1845</v>
+      </c>
+      <c r="B938" t="s">
+        <v>1846</v>
+      </c>
+      <c r="D938" t="s">
         <v>9</v>
       </c>
     </row>

--- a/api/1/clv1/codelist/HumanitarianPlan.xlsx
+++ b/api/1/clv1/codelist/HumanitarianPlan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2818" uniqueCount="1847">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2914" uniqueCount="1910">
   <si>
     <t>code</t>
   </si>
@@ -37,15 +37,195 @@
     <t>category-description</t>
   </si>
   <si>
+    <t>HAFG26</t>
+  </si>
+  <si>
+    <t>Afghanistan Humanitarian Needs and Response Plan 2026</t>
+  </si>
+  <si>
+    <t>en</t>
+  </si>
+  <si>
+    <t>HBFA26</t>
+  </si>
+  <si>
+    <t>Burkina Faso Besoins Humanitaires et Plan de Réponse 2026</t>
+  </si>
+  <si>
+    <t>HCMR26</t>
+  </si>
+  <si>
+    <t>Cameroon Humanitarian Needs and Response Plan 2026</t>
+  </si>
+  <si>
+    <t>HCOL26</t>
+  </si>
+  <si>
+    <t>Colombia Necesidades Humanitarias y Plan de Respuesta 2026</t>
+  </si>
+  <si>
+    <t>FPSE26</t>
+  </si>
+  <si>
+    <t>Escalation of Hostilities in the OPT Flash Appeal 2026</t>
+  </si>
+  <si>
+    <t>HHTI26</t>
+  </si>
+  <si>
+    <t>Haiti Besoins Humanitaires et Plan de Réponse 2026</t>
+  </si>
+  <si>
+    <t>HMLI26</t>
+  </si>
+  <si>
+    <t>Mali Besoins Humanitaires et Plan de Réponse 2026</t>
+  </si>
+  <si>
+    <t>HMOZ26</t>
+  </si>
+  <si>
+    <t>Mozambique Humanitarian Needs and Response Plan 2026</t>
+  </si>
+  <si>
+    <t>HMMR26</t>
+  </si>
+  <si>
+    <t>Myanmar Humanitarian Needs and Response Plan 2026</t>
+  </si>
+  <si>
+    <t>HNER26</t>
+  </si>
+  <si>
+    <t>Niger Besoins Humanitaires et Plan de Réponse 2026</t>
+  </si>
+  <si>
+    <t>HNGA26</t>
+  </si>
+  <si>
+    <t>Nigeria Humanitarian Needs and Response Plan 2026</t>
+  </si>
+  <si>
+    <t>OPAK26</t>
+  </si>
+  <si>
+    <t>Pakistan Floods Support Plan 2026</t>
+  </si>
+  <si>
+    <t>RREG26</t>
+  </si>
+  <si>
+    <t>Regional Migrant Response Plan for Horn of Africa to Yemen and Southern Africa 2026</t>
+  </si>
+  <si>
+    <t>RBGD26</t>
+  </si>
+  <si>
+    <t>Rohingya Humanitarian Crisis Joint Response Plan 2026</t>
+  </si>
+  <si>
+    <t>HCAF26</t>
+  </si>
+  <si>
+    <t>République Centrafricaine Besoins Humanitaires et Plan de Réponse 2026</t>
+  </si>
+  <si>
+    <t>HCOD26</t>
+  </si>
+  <si>
+    <t>République Démocratique du Congo Besoins Humanitaires et Plan de Réponse 2026</t>
+  </si>
+  <si>
+    <t>HSOM26</t>
+  </si>
+  <si>
+    <t>Somalia Humanitarian Needs and Response Plan 2026</t>
+  </si>
+  <si>
+    <t>HSSD26</t>
+  </si>
+  <si>
+    <t>South Sudan Humanitarian Needs and Response Plan 2026</t>
+  </si>
+  <si>
+    <t>OLKA2526</t>
+  </si>
+  <si>
+    <t>Sri Lanka Humanitarian Priorities Plan Cyclone Ditwa 2026</t>
+  </si>
+  <si>
+    <t>RREG26a</t>
+  </si>
+  <si>
+    <t>Sudan Emergency: Regional Refugee Response Plan 2026</t>
+  </si>
+  <si>
+    <t>HSDN26</t>
+  </si>
+  <si>
+    <t>Sudan Humanitarian Needs and Response Plan 2026</t>
+  </si>
+  <si>
+    <t>HSYR26</t>
+  </si>
+  <si>
+    <t>Syrian Arab Republic Humanitarian Response Priorities 2026</t>
+  </si>
+  <si>
+    <t>RJORLBNTUR26</t>
+  </si>
+  <si>
+    <t>Syrian Arab Republic Regional Refugee and Resilience Plan (3RP) 2026</t>
+  </si>
+  <si>
+    <t>HTCD26</t>
+  </si>
+  <si>
+    <t>Tchad Besoins Humanitaires et Plan de Réponse 2026</t>
+  </si>
+  <si>
+    <t>RUGA26</t>
+  </si>
+  <si>
+    <t>Uganda Regional Refugee Response Plan 2026</t>
+  </si>
+  <si>
+    <t>HUKR26</t>
+  </si>
+  <si>
+    <t>Ukraine Humanitarian Needs and Response Plan 2026</t>
+  </si>
+  <si>
+    <t>HVEN26</t>
+  </si>
+  <si>
+    <t>Venezuela Plan de Respuesta Humanitaria 2026</t>
+  </si>
+  <si>
+    <t>RREG26b</t>
+  </si>
+  <si>
+    <t>Venezuela Regional Refugee and Migrant Response Plan (RMRP) 2026</t>
+  </si>
+  <si>
+    <t>OVNM26</t>
+  </si>
+  <si>
+    <t>Viet Nam 25-26 Joint Response Plan Multiple Typhoons and Floods 2026</t>
+  </si>
+  <si>
+    <t>HYEM26</t>
+  </si>
+  <si>
+    <t>Yemen Humanitarian Needs and Response Plan 2026</t>
+  </si>
+  <si>
     <t>HAFG25</t>
   </si>
   <si>
     <t>Afghanistan Humanitarian Needs and Response Plan 2025</t>
   </si>
   <si>
-    <t>en</t>
-  </si>
-  <si>
     <t>RIRNPAK25</t>
   </si>
   <si>
@@ -172,6 +352,12 @@
     <t>Nigeria Humanitarian Needs and Response Plan 2025</t>
   </si>
   <si>
+    <t>OPAK25</t>
+  </si>
+  <si>
+    <t>Pakistan Floods Support Plan 2025</t>
+  </si>
+  <si>
     <t>OPHL25</t>
   </si>
   <si>
@@ -280,16 +466,19 @@
     <t>Venezuela Regional Refugee and Migrant Response Plan (RMRP) 2025</t>
   </si>
   <si>
+    <t>OVNM25b</t>
+  </si>
+  <si>
+    <t>Viet Nam 24-25 Joint Response Plan for Typhoon Yagi and Floods 2025</t>
+  </si>
+  <si>
     <t>OVNM25</t>
   </si>
   <si>
-    <t>Viet Nam 24-25 Joint Response Plan for Typhoon Yagi and Floods 2025</t>
-  </si>
-  <si>
     <t>OVNM25a</t>
   </si>
   <si>
-    <t>Viet Nam 25-26 Joint Response Plan multiple Typhoons and Floods 2025</t>
+    <t>Viet Nam 25-26 Joint Response Plan Multiple Typhoons and Floods 2025</t>
   </si>
   <si>
     <t>HYEM25</t>
@@ -5886,7 +6075,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G938"/>
+  <dimension ref="A1:G970"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -6709,7 +6898,7 @@
         <v>152</v>
       </c>
       <c r="B74" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D74" t="s">
         <v>9</v>
@@ -6717,10 +6906,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
+        <v>153</v>
+      </c>
+      <c r="B75" t="s">
         <v>154</v>
-      </c>
-      <c r="B75" t="s">
-        <v>155</v>
       </c>
       <c r="D75" t="s">
         <v>9</v>
@@ -6728,10 +6917,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
+        <v>155</v>
+      </c>
+      <c r="B76" t="s">
         <v>156</v>
-      </c>
-      <c r="B76" t="s">
-        <v>157</v>
       </c>
       <c r="D76" t="s">
         <v>9</v>
@@ -6739,10 +6928,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
+        <v>157</v>
+      </c>
+      <c r="B77" t="s">
         <v>158</v>
-      </c>
-      <c r="B77" t="s">
-        <v>159</v>
       </c>
       <c r="D77" t="s">
         <v>9</v>
@@ -6750,10 +6939,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
+        <v>159</v>
+      </c>
+      <c r="B78" t="s">
         <v>160</v>
-      </c>
-      <c r="B78" t="s">
-        <v>161</v>
       </c>
       <c r="D78" t="s">
         <v>9</v>
@@ -6761,10 +6950,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
+        <v>161</v>
+      </c>
+      <c r="B79" t="s">
         <v>162</v>
-      </c>
-      <c r="B79" t="s">
-        <v>163</v>
       </c>
       <c r="D79" t="s">
         <v>9</v>
@@ -6772,10 +6961,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
+        <v>163</v>
+      </c>
+      <c r="B80" t="s">
         <v>164</v>
-      </c>
-      <c r="B80" t="s">
-        <v>165</v>
       </c>
       <c r="D80" t="s">
         <v>9</v>
@@ -6783,10 +6972,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
+        <v>165</v>
+      </c>
+      <c r="B81" t="s">
         <v>166</v>
-      </c>
-      <c r="B81" t="s">
-        <v>167</v>
       </c>
       <c r="D81" t="s">
         <v>9</v>
@@ -6794,10 +6983,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
+        <v>167</v>
+      </c>
+      <c r="B82" t="s">
         <v>168</v>
-      </c>
-      <c r="B82" t="s">
-        <v>169</v>
       </c>
       <c r="D82" t="s">
         <v>9</v>
@@ -6805,10 +6994,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
+        <v>169</v>
+      </c>
+      <c r="B83" t="s">
         <v>170</v>
-      </c>
-      <c r="B83" t="s">
-        <v>171</v>
       </c>
       <c r="D83" t="s">
         <v>9</v>
@@ -6816,10 +7005,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
+        <v>171</v>
+      </c>
+      <c r="B84" t="s">
         <v>172</v>
-      </c>
-      <c r="B84" t="s">
-        <v>173</v>
       </c>
       <c r="D84" t="s">
         <v>9</v>
@@ -6827,10 +7016,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
+        <v>173</v>
+      </c>
+      <c r="B85" t="s">
         <v>174</v>
-      </c>
-      <c r="B85" t="s">
-        <v>175</v>
       </c>
       <c r="D85" t="s">
         <v>9</v>
@@ -6838,10 +7027,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
+        <v>175</v>
+      </c>
+      <c r="B86" t="s">
         <v>176</v>
-      </c>
-      <c r="B86" t="s">
-        <v>177</v>
       </c>
       <c r="D86" t="s">
         <v>9</v>
@@ -6849,10 +7038,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
+        <v>177</v>
+      </c>
+      <c r="B87" t="s">
         <v>178</v>
-      </c>
-      <c r="B87" t="s">
-        <v>179</v>
       </c>
       <c r="D87" t="s">
         <v>9</v>
@@ -6860,10 +7049,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
+        <v>179</v>
+      </c>
+      <c r="B88" t="s">
         <v>180</v>
-      </c>
-      <c r="B88" t="s">
-        <v>181</v>
       </c>
       <c r="D88" t="s">
         <v>9</v>
@@ -6871,10 +7060,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
+        <v>181</v>
+      </c>
+      <c r="B89" t="s">
         <v>182</v>
-      </c>
-      <c r="B89" t="s">
-        <v>183</v>
       </c>
       <c r="D89" t="s">
         <v>9</v>
@@ -6882,10 +7071,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
+        <v>183</v>
+      </c>
+      <c r="B90" t="s">
         <v>184</v>
-      </c>
-      <c r="B90" t="s">
-        <v>185</v>
       </c>
       <c r="D90" t="s">
         <v>9</v>
@@ -6893,10 +7082,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
+        <v>185</v>
+      </c>
+      <c r="B91" t="s">
         <v>186</v>
-      </c>
-      <c r="B91" t="s">
-        <v>187</v>
       </c>
       <c r="D91" t="s">
         <v>9</v>
@@ -6904,10 +7093,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
+        <v>187</v>
+      </c>
+      <c r="B92" t="s">
         <v>188</v>
-      </c>
-      <c r="B92" t="s">
-        <v>189</v>
       </c>
       <c r="D92" t="s">
         <v>9</v>
@@ -6915,10 +7104,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
+        <v>189</v>
+      </c>
+      <c r="B93" t="s">
         <v>190</v>
-      </c>
-      <c r="B93" t="s">
-        <v>191</v>
       </c>
       <c r="D93" t="s">
         <v>9</v>
@@ -6926,10 +7115,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
+        <v>191</v>
+      </c>
+      <c r="B94" t="s">
         <v>192</v>
-      </c>
-      <c r="B94" t="s">
-        <v>193</v>
       </c>
       <c r="D94" t="s">
         <v>9</v>
@@ -6937,10 +7126,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
+        <v>193</v>
+      </c>
+      <c r="B95" t="s">
         <v>194</v>
-      </c>
-      <c r="B95" t="s">
-        <v>195</v>
       </c>
       <c r="D95" t="s">
         <v>9</v>
@@ -6948,10 +7137,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
+        <v>195</v>
+      </c>
+      <c r="B96" t="s">
         <v>196</v>
-      </c>
-      <c r="B96" t="s">
-        <v>197</v>
       </c>
       <c r="D96" t="s">
         <v>9</v>
@@ -6959,10 +7148,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
+        <v>197</v>
+      </c>
+      <c r="B97" t="s">
         <v>198</v>
-      </c>
-      <c r="B97" t="s">
-        <v>199</v>
       </c>
       <c r="D97" t="s">
         <v>9</v>
@@ -6970,10 +7159,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
+        <v>199</v>
+      </c>
+      <c r="B98" t="s">
         <v>200</v>
-      </c>
-      <c r="B98" t="s">
-        <v>201</v>
       </c>
       <c r="D98" t="s">
         <v>9</v>
@@ -6981,10 +7170,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
+        <v>201</v>
+      </c>
+      <c r="B99" t="s">
         <v>202</v>
-      </c>
-      <c r="B99" t="s">
-        <v>203</v>
       </c>
       <c r="D99" t="s">
         <v>9</v>
@@ -6992,10 +7181,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
+        <v>203</v>
+      </c>
+      <c r="B100" t="s">
         <v>204</v>
-      </c>
-      <c r="B100" t="s">
-        <v>205</v>
       </c>
       <c r="D100" t="s">
         <v>9</v>
@@ -7003,10 +7192,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
+        <v>205</v>
+      </c>
+      <c r="B101" t="s">
         <v>206</v>
-      </c>
-      <c r="B101" t="s">
-        <v>207</v>
       </c>
       <c r="D101" t="s">
         <v>9</v>
@@ -7014,10 +7203,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
+        <v>207</v>
+      </c>
+      <c r="B102" t="s">
         <v>208</v>
-      </c>
-      <c r="B102" t="s">
-        <v>209</v>
       </c>
       <c r="D102" t="s">
         <v>9</v>
@@ -7025,10 +7214,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
+        <v>209</v>
+      </c>
+      <c r="B103" t="s">
         <v>210</v>
-      </c>
-      <c r="B103" t="s">
-        <v>211</v>
       </c>
       <c r="D103" t="s">
         <v>9</v>
@@ -7036,10 +7225,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
+        <v>211</v>
+      </c>
+      <c r="B104" t="s">
         <v>212</v>
-      </c>
-      <c r="B104" t="s">
-        <v>213</v>
       </c>
       <c r="D104" t="s">
         <v>9</v>
@@ -7047,10 +7236,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
+        <v>213</v>
+      </c>
+      <c r="B105" t="s">
         <v>214</v>
-      </c>
-      <c r="B105" t="s">
-        <v>215</v>
       </c>
       <c r="D105" t="s">
         <v>9</v>
@@ -7058,10 +7247,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
+        <v>215</v>
+      </c>
+      <c r="B106" t="s">
         <v>216</v>
-      </c>
-      <c r="B106" t="s">
-        <v>217</v>
       </c>
       <c r="D106" t="s">
         <v>9</v>
@@ -7069,10 +7258,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
+        <v>217</v>
+      </c>
+      <c r="B107" t="s">
         <v>218</v>
-      </c>
-      <c r="B107" t="s">
-        <v>219</v>
       </c>
       <c r="D107" t="s">
         <v>9</v>
@@ -7080,10 +7269,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
+        <v>219</v>
+      </c>
+      <c r="B108" t="s">
         <v>220</v>
-      </c>
-      <c r="B108" t="s">
-        <v>221</v>
       </c>
       <c r="D108" t="s">
         <v>9</v>
@@ -7091,10 +7280,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
+        <v>221</v>
+      </c>
+      <c r="B109" t="s">
         <v>222</v>
-      </c>
-      <c r="B109" t="s">
-        <v>223</v>
       </c>
       <c r="D109" t="s">
         <v>9</v>
@@ -7102,10 +7291,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
+        <v>223</v>
+      </c>
+      <c r="B110" t="s">
         <v>224</v>
-      </c>
-      <c r="B110" t="s">
-        <v>225</v>
       </c>
       <c r="D110" t="s">
         <v>9</v>
@@ -7113,10 +7302,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
+        <v>225</v>
+      </c>
+      <c r="B111" t="s">
         <v>226</v>
-      </c>
-      <c r="B111" t="s">
-        <v>227</v>
       </c>
       <c r="D111" t="s">
         <v>9</v>
@@ -7124,10 +7313,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
+        <v>227</v>
+      </c>
+      <c r="B112" t="s">
         <v>228</v>
-      </c>
-      <c r="B112" t="s">
-        <v>229</v>
       </c>
       <c r="D112" t="s">
         <v>9</v>
@@ -7135,10 +7324,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
+        <v>229</v>
+      </c>
+      <c r="B113" t="s">
         <v>230</v>
-      </c>
-      <c r="B113" t="s">
-        <v>231</v>
       </c>
       <c r="D113" t="s">
         <v>9</v>
@@ -7146,10 +7335,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
+        <v>231</v>
+      </c>
+      <c r="B114" t="s">
         <v>232</v>
-      </c>
-      <c r="B114" t="s">
-        <v>233</v>
       </c>
       <c r="D114" t="s">
         <v>9</v>
@@ -7157,10 +7346,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
+        <v>233</v>
+      </c>
+      <c r="B115" t="s">
         <v>234</v>
-      </c>
-      <c r="B115" t="s">
-        <v>235</v>
       </c>
       <c r="D115" t="s">
         <v>9</v>
@@ -7168,10 +7357,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
+        <v>235</v>
+      </c>
+      <c r="B116" t="s">
         <v>236</v>
-      </c>
-      <c r="B116" t="s">
-        <v>237</v>
       </c>
       <c r="D116" t="s">
         <v>9</v>
@@ -7179,10 +7368,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
+        <v>237</v>
+      </c>
+      <c r="B117" t="s">
         <v>238</v>
-      </c>
-      <c r="B117" t="s">
-        <v>239</v>
       </c>
       <c r="D117" t="s">
         <v>9</v>
@@ -7190,10 +7379,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
+        <v>239</v>
+      </c>
+      <c r="B118" t="s">
         <v>240</v>
-      </c>
-      <c r="B118" t="s">
-        <v>241</v>
       </c>
       <c r="D118" t="s">
         <v>9</v>
@@ -7201,10 +7390,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
+        <v>241</v>
+      </c>
+      <c r="B119" t="s">
         <v>242</v>
-      </c>
-      <c r="B119" t="s">
-        <v>243</v>
       </c>
       <c r="D119" t="s">
         <v>9</v>
@@ -7212,10 +7401,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
+        <v>243</v>
+      </c>
+      <c r="B120" t="s">
         <v>244</v>
-      </c>
-      <c r="B120" t="s">
-        <v>245</v>
       </c>
       <c r="D120" t="s">
         <v>9</v>
@@ -7223,10 +7412,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" t="s">
+        <v>245</v>
+      </c>
+      <c r="B121" t="s">
         <v>246</v>
-      </c>
-      <c r="B121" t="s">
-        <v>247</v>
       </c>
       <c r="D121" t="s">
         <v>9</v>
@@ -7234,10 +7423,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" t="s">
+        <v>247</v>
+      </c>
+      <c r="B122" t="s">
         <v>248</v>
-      </c>
-      <c r="B122" t="s">
-        <v>249</v>
       </c>
       <c r="D122" t="s">
         <v>9</v>
@@ -7245,10 +7434,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" t="s">
+        <v>249</v>
+      </c>
+      <c r="B123" t="s">
         <v>250</v>
-      </c>
-      <c r="B123" t="s">
-        <v>251</v>
       </c>
       <c r="D123" t="s">
         <v>9</v>
@@ -7256,10 +7445,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" t="s">
+        <v>251</v>
+      </c>
+      <c r="B124" t="s">
         <v>252</v>
-      </c>
-      <c r="B124" t="s">
-        <v>253</v>
       </c>
       <c r="D124" t="s">
         <v>9</v>
@@ -7267,10 +7456,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" t="s">
+        <v>253</v>
+      </c>
+      <c r="B125" t="s">
         <v>254</v>
-      </c>
-      <c r="B125" t="s">
-        <v>255</v>
       </c>
       <c r="D125" t="s">
         <v>9</v>
@@ -7278,10 +7467,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" t="s">
+        <v>255</v>
+      </c>
+      <c r="B126" t="s">
         <v>256</v>
-      </c>
-      <c r="B126" t="s">
-        <v>255</v>
       </c>
       <c r="D126" t="s">
         <v>9</v>
@@ -7633,7 +7822,7 @@
         <v>319</v>
       </c>
       <c r="B158" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D158" t="s">
         <v>9</v>
@@ -7641,10 +7830,10 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" t="s">
+        <v>320</v>
+      </c>
+      <c r="B159" t="s">
         <v>321</v>
-      </c>
-      <c r="B159" t="s">
-        <v>322</v>
       </c>
       <c r="D159" t="s">
         <v>9</v>
@@ -7652,10 +7841,10 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" t="s">
+        <v>322</v>
+      </c>
+      <c r="B160" t="s">
         <v>323</v>
-      </c>
-      <c r="B160" t="s">
-        <v>324</v>
       </c>
       <c r="D160" t="s">
         <v>9</v>
@@ -7663,10 +7852,10 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" t="s">
+        <v>324</v>
+      </c>
+      <c r="B161" t="s">
         <v>325</v>
-      </c>
-      <c r="B161" t="s">
-        <v>326</v>
       </c>
       <c r="D161" t="s">
         <v>9</v>
@@ -7674,10 +7863,10 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" t="s">
+        <v>326</v>
+      </c>
+      <c r="B162" t="s">
         <v>327</v>
-      </c>
-      <c r="B162" t="s">
-        <v>328</v>
       </c>
       <c r="D162" t="s">
         <v>9</v>
@@ -7685,10 +7874,10 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" t="s">
+        <v>328</v>
+      </c>
+      <c r="B163" t="s">
         <v>329</v>
-      </c>
-      <c r="B163" t="s">
-        <v>330</v>
       </c>
       <c r="D163" t="s">
         <v>9</v>
@@ -7696,10 +7885,10 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" t="s">
+        <v>330</v>
+      </c>
+      <c r="B164" t="s">
         <v>331</v>
-      </c>
-      <c r="B164" t="s">
-        <v>332</v>
       </c>
       <c r="D164" t="s">
         <v>9</v>
@@ -7707,10 +7896,10 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" t="s">
+        <v>332</v>
+      </c>
+      <c r="B165" t="s">
         <v>333</v>
-      </c>
-      <c r="B165" t="s">
-        <v>334</v>
       </c>
       <c r="D165" t="s">
         <v>9</v>
@@ -7718,10 +7907,10 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" t="s">
+        <v>334</v>
+      </c>
+      <c r="B166" t="s">
         <v>335</v>
-      </c>
-      <c r="B166" t="s">
-        <v>336</v>
       </c>
       <c r="D166" t="s">
         <v>9</v>
@@ -7729,10 +7918,10 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" t="s">
+        <v>336</v>
+      </c>
+      <c r="B167" t="s">
         <v>337</v>
-      </c>
-      <c r="B167" t="s">
-        <v>338</v>
       </c>
       <c r="D167" t="s">
         <v>9</v>
@@ -7740,10 +7929,10 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" t="s">
+        <v>338</v>
+      </c>
+      <c r="B168" t="s">
         <v>339</v>
-      </c>
-      <c r="B168" t="s">
-        <v>340</v>
       </c>
       <c r="D168" t="s">
         <v>9</v>
@@ -7751,10 +7940,10 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" t="s">
+        <v>340</v>
+      </c>
+      <c r="B169" t="s">
         <v>341</v>
-      </c>
-      <c r="B169" t="s">
-        <v>342</v>
       </c>
       <c r="D169" t="s">
         <v>9</v>
@@ -7762,10 +7951,10 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" t="s">
+        <v>342</v>
+      </c>
+      <c r="B170" t="s">
         <v>343</v>
-      </c>
-      <c r="B170" t="s">
-        <v>344</v>
       </c>
       <c r="D170" t="s">
         <v>9</v>
@@ -7773,10 +7962,10 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" t="s">
+        <v>344</v>
+      </c>
+      <c r="B171" t="s">
         <v>345</v>
-      </c>
-      <c r="B171" t="s">
-        <v>346</v>
       </c>
       <c r="D171" t="s">
         <v>9</v>
@@ -7784,10 +7973,10 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" t="s">
+        <v>346</v>
+      </c>
+      <c r="B172" t="s">
         <v>347</v>
-      </c>
-      <c r="B172" t="s">
-        <v>348</v>
       </c>
       <c r="D172" t="s">
         <v>9</v>
@@ -7795,10 +7984,10 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" t="s">
+        <v>348</v>
+      </c>
+      <c r="B173" t="s">
         <v>349</v>
-      </c>
-      <c r="B173" t="s">
-        <v>350</v>
       </c>
       <c r="D173" t="s">
         <v>9</v>
@@ -7806,10 +7995,10 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" t="s">
+        <v>350</v>
+      </c>
+      <c r="B174" t="s">
         <v>351</v>
-      </c>
-      <c r="B174" t="s">
-        <v>352</v>
       </c>
       <c r="D174" t="s">
         <v>9</v>
@@ -7817,10 +8006,10 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" t="s">
+        <v>352</v>
+      </c>
+      <c r="B175" t="s">
         <v>353</v>
-      </c>
-      <c r="B175" t="s">
-        <v>352</v>
       </c>
       <c r="D175" t="s">
         <v>9</v>
@@ -8172,7 +8361,7 @@
         <v>416</v>
       </c>
       <c r="B207" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D207" t="s">
         <v>9</v>
@@ -8180,10 +8369,10 @@
     </row>
     <row r="208" spans="1:4">
       <c r="A208" t="s">
+        <v>417</v>
+      </c>
+      <c r="B208" t="s">
         <v>418</v>
-      </c>
-      <c r="B208" t="s">
-        <v>419</v>
       </c>
       <c r="D208" t="s">
         <v>9</v>
@@ -8191,10 +8380,10 @@
     </row>
     <row r="209" spans="1:4">
       <c r="A209" t="s">
+        <v>419</v>
+      </c>
+      <c r="B209" t="s">
         <v>420</v>
-      </c>
-      <c r="B209" t="s">
-        <v>421</v>
       </c>
       <c r="D209" t="s">
         <v>9</v>
@@ -8202,10 +8391,10 @@
     </row>
     <row r="210" spans="1:4">
       <c r="A210" t="s">
+        <v>421</v>
+      </c>
+      <c r="B210" t="s">
         <v>422</v>
-      </c>
-      <c r="B210" t="s">
-        <v>423</v>
       </c>
       <c r="D210" t="s">
         <v>9</v>
@@ -8213,10 +8402,10 @@
     </row>
     <row r="211" spans="1:4">
       <c r="A211" t="s">
+        <v>423</v>
+      </c>
+      <c r="B211" t="s">
         <v>424</v>
-      </c>
-      <c r="B211" t="s">
-        <v>425</v>
       </c>
       <c r="D211" t="s">
         <v>9</v>
@@ -8224,10 +8413,10 @@
     </row>
     <row r="212" spans="1:4">
       <c r="A212" t="s">
+        <v>425</v>
+      </c>
+      <c r="B212" t="s">
         <v>426</v>
-      </c>
-      <c r="B212" t="s">
-        <v>427</v>
       </c>
       <c r="D212" t="s">
         <v>9</v>
@@ -8235,10 +8424,10 @@
     </row>
     <row r="213" spans="1:4">
       <c r="A213" t="s">
+        <v>427</v>
+      </c>
+      <c r="B213" t="s">
         <v>428</v>
-      </c>
-      <c r="B213" t="s">
-        <v>429</v>
       </c>
       <c r="D213" t="s">
         <v>9</v>
@@ -8246,10 +8435,10 @@
     </row>
     <row r="214" spans="1:4">
       <c r="A214" t="s">
+        <v>429</v>
+      </c>
+      <c r="B214" t="s">
         <v>430</v>
-      </c>
-      <c r="B214" t="s">
-        <v>431</v>
       </c>
       <c r="D214" t="s">
         <v>9</v>
@@ -8257,10 +8446,10 @@
     </row>
     <row r="215" spans="1:4">
       <c r="A215" t="s">
+        <v>431</v>
+      </c>
+      <c r="B215" t="s">
         <v>432</v>
-      </c>
-      <c r="B215" t="s">
-        <v>433</v>
       </c>
       <c r="D215" t="s">
         <v>9</v>
@@ -8268,10 +8457,10 @@
     </row>
     <row r="216" spans="1:4">
       <c r="A216" t="s">
+        <v>433</v>
+      </c>
+      <c r="B216" t="s">
         <v>434</v>
-      </c>
-      <c r="B216" t="s">
-        <v>435</v>
       </c>
       <c r="D216" t="s">
         <v>9</v>
@@ -8279,10 +8468,10 @@
     </row>
     <row r="217" spans="1:4">
       <c r="A217" t="s">
+        <v>435</v>
+      </c>
+      <c r="B217" t="s">
         <v>436</v>
-      </c>
-      <c r="B217" t="s">
-        <v>437</v>
       </c>
       <c r="D217" t="s">
         <v>9</v>
@@ -8290,10 +8479,10 @@
     </row>
     <row r="218" spans="1:4">
       <c r="A218" t="s">
+        <v>437</v>
+      </c>
+      <c r="B218" t="s">
         <v>438</v>
-      </c>
-      <c r="B218" t="s">
-        <v>439</v>
       </c>
       <c r="D218" t="s">
         <v>9</v>
@@ -8301,10 +8490,10 @@
     </row>
     <row r="219" spans="1:4">
       <c r="A219" t="s">
+        <v>439</v>
+      </c>
+      <c r="B219" t="s">
         <v>440</v>
-      </c>
-      <c r="B219" t="s">
-        <v>441</v>
       </c>
       <c r="D219" t="s">
         <v>9</v>
@@ -8312,10 +8501,10 @@
     </row>
     <row r="220" spans="1:4">
       <c r="A220" t="s">
+        <v>441</v>
+      </c>
+      <c r="B220" t="s">
         <v>442</v>
-      </c>
-      <c r="B220" t="s">
-        <v>443</v>
       </c>
       <c r="D220" t="s">
         <v>9</v>
@@ -8323,10 +8512,10 @@
     </row>
     <row r="221" spans="1:4">
       <c r="A221" t="s">
+        <v>443</v>
+      </c>
+      <c r="B221" t="s">
         <v>444</v>
-      </c>
-      <c r="B221" t="s">
-        <v>445</v>
       </c>
       <c r="D221" t="s">
         <v>9</v>
@@ -8334,10 +8523,10 @@
     </row>
     <row r="222" spans="1:4">
       <c r="A222" t="s">
+        <v>445</v>
+      </c>
+      <c r="B222" t="s">
         <v>446</v>
-      </c>
-      <c r="B222" t="s">
-        <v>447</v>
       </c>
       <c r="D222" t="s">
         <v>9</v>
@@ -8345,10 +8534,10 @@
     </row>
     <row r="223" spans="1:4">
       <c r="A223" t="s">
+        <v>447</v>
+      </c>
+      <c r="B223" t="s">
         <v>448</v>
-      </c>
-      <c r="B223" t="s">
-        <v>449</v>
       </c>
       <c r="D223" t="s">
         <v>9</v>
@@ -8356,10 +8545,10 @@
     </row>
     <row r="224" spans="1:4">
       <c r="A224" t="s">
+        <v>449</v>
+      </c>
+      <c r="B224" t="s">
         <v>450</v>
-      </c>
-      <c r="B224" t="s">
-        <v>451</v>
       </c>
       <c r="D224" t="s">
         <v>9</v>
@@ -8367,10 +8556,10 @@
     </row>
     <row r="225" spans="1:4">
       <c r="A225" t="s">
+        <v>451</v>
+      </c>
+      <c r="B225" t="s">
         <v>452</v>
-      </c>
-      <c r="B225" t="s">
-        <v>453</v>
       </c>
       <c r="D225" t="s">
         <v>9</v>
@@ -8378,10 +8567,10 @@
     </row>
     <row r="226" spans="1:4">
       <c r="A226" t="s">
+        <v>453</v>
+      </c>
+      <c r="B226" t="s">
         <v>454</v>
-      </c>
-      <c r="B226" t="s">
-        <v>455</v>
       </c>
       <c r="D226" t="s">
         <v>9</v>
@@ -8389,10 +8578,10 @@
     </row>
     <row r="227" spans="1:4">
       <c r="A227" t="s">
+        <v>455</v>
+      </c>
+      <c r="B227" t="s">
         <v>456</v>
-      </c>
-      <c r="B227" t="s">
-        <v>457</v>
       </c>
       <c r="D227" t="s">
         <v>9</v>
@@ -8400,10 +8589,10 @@
     </row>
     <row r="228" spans="1:4">
       <c r="A228" t="s">
+        <v>457</v>
+      </c>
+      <c r="B228" t="s">
         <v>458</v>
-      </c>
-      <c r="B228" t="s">
-        <v>459</v>
       </c>
       <c r="D228" t="s">
         <v>9</v>
@@ -8411,10 +8600,10 @@
     </row>
     <row r="229" spans="1:4">
       <c r="A229" t="s">
+        <v>459</v>
+      </c>
+      <c r="B229" t="s">
         <v>460</v>
-      </c>
-      <c r="B229" t="s">
-        <v>461</v>
       </c>
       <c r="D229" t="s">
         <v>9</v>
@@ -8422,10 +8611,10 @@
     </row>
     <row r="230" spans="1:4">
       <c r="A230" t="s">
+        <v>461</v>
+      </c>
+      <c r="B230" t="s">
         <v>462</v>
-      </c>
-      <c r="B230" t="s">
-        <v>463</v>
       </c>
       <c r="D230" t="s">
         <v>9</v>
@@ -8433,10 +8622,10 @@
     </row>
     <row r="231" spans="1:4">
       <c r="A231" t="s">
+        <v>463</v>
+      </c>
+      <c r="B231" t="s">
         <v>464</v>
-      </c>
-      <c r="B231" t="s">
-        <v>463</v>
       </c>
       <c r="D231" t="s">
         <v>9</v>
@@ -8788,7 +8977,7 @@
         <v>527</v>
       </c>
       <c r="B263" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D263" t="s">
         <v>9</v>
@@ -8796,10 +8985,10 @@
     </row>
     <row r="264" spans="1:4">
       <c r="A264" t="s">
+        <v>528</v>
+      </c>
+      <c r="B264" t="s">
         <v>529</v>
-      </c>
-      <c r="B264" t="s">
-        <v>530</v>
       </c>
       <c r="D264" t="s">
         <v>9</v>
@@ -8807,10 +8996,10 @@
     </row>
     <row r="265" spans="1:4">
       <c r="A265" t="s">
+        <v>530</v>
+      </c>
+      <c r="B265" t="s">
         <v>531</v>
-      </c>
-      <c r="B265" t="s">
-        <v>532</v>
       </c>
       <c r="D265" t="s">
         <v>9</v>
@@ -8818,10 +9007,10 @@
     </row>
     <row r="266" spans="1:4">
       <c r="A266" t="s">
+        <v>532</v>
+      </c>
+      <c r="B266" t="s">
         <v>533</v>
-      </c>
-      <c r="B266" t="s">
-        <v>534</v>
       </c>
       <c r="D266" t="s">
         <v>9</v>
@@ -8829,10 +9018,10 @@
     </row>
     <row r="267" spans="1:4">
       <c r="A267" t="s">
+        <v>534</v>
+      </c>
+      <c r="B267" t="s">
         <v>535</v>
-      </c>
-      <c r="B267" t="s">
-        <v>536</v>
       </c>
       <c r="D267" t="s">
         <v>9</v>
@@ -8840,10 +9029,10 @@
     </row>
     <row r="268" spans="1:4">
       <c r="A268" t="s">
+        <v>536</v>
+      </c>
+      <c r="B268" t="s">
         <v>537</v>
-      </c>
-      <c r="B268" t="s">
-        <v>538</v>
       </c>
       <c r="D268" t="s">
         <v>9</v>
@@ -8851,10 +9040,10 @@
     </row>
     <row r="269" spans="1:4">
       <c r="A269" t="s">
+        <v>538</v>
+      </c>
+      <c r="B269" t="s">
         <v>539</v>
-      </c>
-      <c r="B269" t="s">
-        <v>540</v>
       </c>
       <c r="D269" t="s">
         <v>9</v>
@@ -8862,10 +9051,10 @@
     </row>
     <row r="270" spans="1:4">
       <c r="A270" t="s">
+        <v>540</v>
+      </c>
+      <c r="B270" t="s">
         <v>541</v>
-      </c>
-      <c r="B270" t="s">
-        <v>542</v>
       </c>
       <c r="D270" t="s">
         <v>9</v>
@@ -8873,10 +9062,10 @@
     </row>
     <row r="271" spans="1:4">
       <c r="A271" t="s">
+        <v>542</v>
+      </c>
+      <c r="B271" t="s">
         <v>543</v>
-      </c>
-      <c r="B271" t="s">
-        <v>544</v>
       </c>
       <c r="D271" t="s">
         <v>9</v>
@@ -8884,10 +9073,10 @@
     </row>
     <row r="272" spans="1:4">
       <c r="A272" t="s">
+        <v>544</v>
+      </c>
+      <c r="B272" t="s">
         <v>545</v>
-      </c>
-      <c r="B272" t="s">
-        <v>546</v>
       </c>
       <c r="D272" t="s">
         <v>9</v>
@@ -8895,10 +9084,10 @@
     </row>
     <row r="273" spans="1:4">
       <c r="A273" t="s">
+        <v>546</v>
+      </c>
+      <c r="B273" t="s">
         <v>547</v>
-      </c>
-      <c r="B273" t="s">
-        <v>548</v>
       </c>
       <c r="D273" t="s">
         <v>9</v>
@@ -8906,10 +9095,10 @@
     </row>
     <row r="274" spans="1:4">
       <c r="A274" t="s">
+        <v>548</v>
+      </c>
+      <c r="B274" t="s">
         <v>549</v>
-      </c>
-      <c r="B274" t="s">
-        <v>550</v>
       </c>
       <c r="D274" t="s">
         <v>9</v>
@@ -8917,10 +9106,10 @@
     </row>
     <row r="275" spans="1:4">
       <c r="A275" t="s">
+        <v>550</v>
+      </c>
+      <c r="B275" t="s">
         <v>551</v>
-      </c>
-      <c r="B275" t="s">
-        <v>552</v>
       </c>
       <c r="D275" t="s">
         <v>9</v>
@@ -8928,10 +9117,10 @@
     </row>
     <row r="276" spans="1:4">
       <c r="A276" t="s">
+        <v>552</v>
+      </c>
+      <c r="B276" t="s">
         <v>553</v>
-      </c>
-      <c r="B276" t="s">
-        <v>554</v>
       </c>
       <c r="D276" t="s">
         <v>9</v>
@@ -8939,10 +9128,10 @@
     </row>
     <row r="277" spans="1:4">
       <c r="A277" t="s">
+        <v>554</v>
+      </c>
+      <c r="B277" t="s">
         <v>555</v>
-      </c>
-      <c r="B277" t="s">
-        <v>556</v>
       </c>
       <c r="D277" t="s">
         <v>9</v>
@@ -8950,10 +9139,10 @@
     </row>
     <row r="278" spans="1:4">
       <c r="A278" t="s">
+        <v>556</v>
+      </c>
+      <c r="B278" t="s">
         <v>557</v>
-      </c>
-      <c r="B278" t="s">
-        <v>558</v>
       </c>
       <c r="D278" t="s">
         <v>9</v>
@@ -8961,10 +9150,10 @@
     </row>
     <row r="279" spans="1:4">
       <c r="A279" t="s">
+        <v>558</v>
+      </c>
+      <c r="B279" t="s">
         <v>559</v>
-      </c>
-      <c r="B279" t="s">
-        <v>560</v>
       </c>
       <c r="D279" t="s">
         <v>9</v>
@@ -8972,10 +9161,10 @@
     </row>
     <row r="280" spans="1:4">
       <c r="A280" t="s">
+        <v>560</v>
+      </c>
+      <c r="B280" t="s">
         <v>561</v>
-      </c>
-      <c r="B280" t="s">
-        <v>562</v>
       </c>
       <c r="D280" t="s">
         <v>9</v>
@@ -8983,10 +9172,10 @@
     </row>
     <row r="281" spans="1:4">
       <c r="A281" t="s">
+        <v>562</v>
+      </c>
+      <c r="B281" t="s">
         <v>563</v>
-      </c>
-      <c r="B281" t="s">
-        <v>564</v>
       </c>
       <c r="D281" t="s">
         <v>9</v>
@@ -8994,10 +9183,10 @@
     </row>
     <row r="282" spans="1:4">
       <c r="A282" t="s">
+        <v>564</v>
+      </c>
+      <c r="B282" t="s">
         <v>565</v>
-      </c>
-      <c r="B282" t="s">
-        <v>566</v>
       </c>
       <c r="D282" t="s">
         <v>9</v>
@@ -9005,10 +9194,10 @@
     </row>
     <row r="283" spans="1:4">
       <c r="A283" t="s">
+        <v>566</v>
+      </c>
+      <c r="B283" t="s">
         <v>567</v>
-      </c>
-      <c r="B283" t="s">
-        <v>568</v>
       </c>
       <c r="D283" t="s">
         <v>9</v>
@@ -9016,10 +9205,10 @@
     </row>
     <row r="284" spans="1:4">
       <c r="A284" t="s">
+        <v>568</v>
+      </c>
+      <c r="B284" t="s">
         <v>569</v>
-      </c>
-      <c r="B284" t="s">
-        <v>570</v>
       </c>
       <c r="D284" t="s">
         <v>9</v>
@@ -9027,10 +9216,10 @@
     </row>
     <row r="285" spans="1:4">
       <c r="A285" t="s">
+        <v>570</v>
+      </c>
+      <c r="B285" t="s">
         <v>571</v>
-      </c>
-      <c r="B285" t="s">
-        <v>572</v>
       </c>
       <c r="D285" t="s">
         <v>9</v>
@@ -9038,10 +9227,10 @@
     </row>
     <row r="286" spans="1:4">
       <c r="A286" t="s">
+        <v>572</v>
+      </c>
+      <c r="B286" t="s">
         <v>573</v>
-      </c>
-      <c r="B286" t="s">
-        <v>574</v>
       </c>
       <c r="D286" t="s">
         <v>9</v>
@@ -9049,10 +9238,10 @@
     </row>
     <row r="287" spans="1:4">
       <c r="A287" t="s">
+        <v>574</v>
+      </c>
+      <c r="B287" t="s">
         <v>575</v>
-      </c>
-      <c r="B287" t="s">
-        <v>576</v>
       </c>
       <c r="D287" t="s">
         <v>9</v>
@@ -9060,10 +9249,10 @@
     </row>
     <row r="288" spans="1:4">
       <c r="A288" t="s">
+        <v>576</v>
+      </c>
+      <c r="B288" t="s">
         <v>577</v>
-      </c>
-      <c r="B288" t="s">
-        <v>578</v>
       </c>
       <c r="D288" t="s">
         <v>9</v>
@@ -9071,10 +9260,10 @@
     </row>
     <row r="289" spans="1:4">
       <c r="A289" t="s">
+        <v>578</v>
+      </c>
+      <c r="B289" t="s">
         <v>579</v>
-      </c>
-      <c r="B289" t="s">
-        <v>580</v>
       </c>
       <c r="D289" t="s">
         <v>9</v>
@@ -9082,10 +9271,10 @@
     </row>
     <row r="290" spans="1:4">
       <c r="A290" t="s">
+        <v>580</v>
+      </c>
+      <c r="B290" t="s">
         <v>581</v>
-      </c>
-      <c r="B290" t="s">
-        <v>582</v>
       </c>
       <c r="D290" t="s">
         <v>9</v>
@@ -9093,10 +9282,10 @@
     </row>
     <row r="291" spans="1:4">
       <c r="A291" t="s">
+        <v>582</v>
+      </c>
+      <c r="B291" t="s">
         <v>583</v>
-      </c>
-      <c r="B291" t="s">
-        <v>584</v>
       </c>
       <c r="D291" t="s">
         <v>9</v>
@@ -9104,10 +9293,10 @@
     </row>
     <row r="292" spans="1:4">
       <c r="A292" t="s">
+        <v>584</v>
+      </c>
+      <c r="B292" t="s">
         <v>585</v>
-      </c>
-      <c r="B292" t="s">
-        <v>586</v>
       </c>
       <c r="D292" t="s">
         <v>9</v>
@@ -9115,10 +9304,10 @@
     </row>
     <row r="293" spans="1:4">
       <c r="A293" t="s">
+        <v>586</v>
+      </c>
+      <c r="B293" t="s">
         <v>587</v>
-      </c>
-      <c r="B293" t="s">
-        <v>588</v>
       </c>
       <c r="D293" t="s">
         <v>9</v>
@@ -9126,10 +9315,10 @@
     </row>
     <row r="294" spans="1:4">
       <c r="A294" t="s">
+        <v>588</v>
+      </c>
+      <c r="B294" t="s">
         <v>589</v>
-      </c>
-      <c r="B294" t="s">
-        <v>590</v>
       </c>
       <c r="D294" t="s">
         <v>9</v>
@@ -9137,10 +9326,10 @@
     </row>
     <row r="295" spans="1:4">
       <c r="A295" t="s">
+        <v>590</v>
+      </c>
+      <c r="B295" t="s">
         <v>591</v>
-      </c>
-      <c r="B295" t="s">
-        <v>592</v>
       </c>
       <c r="D295" t="s">
         <v>9</v>
@@ -9148,10 +9337,10 @@
     </row>
     <row r="296" spans="1:4">
       <c r="A296" t="s">
+        <v>592</v>
+      </c>
+      <c r="B296" t="s">
         <v>593</v>
-      </c>
-      <c r="B296" t="s">
-        <v>594</v>
       </c>
       <c r="D296" t="s">
         <v>9</v>
@@ -9159,10 +9348,10 @@
     </row>
     <row r="297" spans="1:4">
       <c r="A297" t="s">
+        <v>594</v>
+      </c>
+      <c r="B297" t="s">
         <v>595</v>
-      </c>
-      <c r="B297" t="s">
-        <v>596</v>
       </c>
       <c r="D297" t="s">
         <v>9</v>
@@ -9170,10 +9359,10 @@
     </row>
     <row r="298" spans="1:4">
       <c r="A298" t="s">
+        <v>596</v>
+      </c>
+      <c r="B298" t="s">
         <v>597</v>
-      </c>
-      <c r="B298" t="s">
-        <v>598</v>
       </c>
       <c r="D298" t="s">
         <v>9</v>
@@ -9181,10 +9370,10 @@
     </row>
     <row r="299" spans="1:4">
       <c r="A299" t="s">
+        <v>598</v>
+      </c>
+      <c r="B299" t="s">
         <v>599</v>
-      </c>
-      <c r="B299" t="s">
-        <v>600</v>
       </c>
       <c r="D299" t="s">
         <v>9</v>
@@ -9192,10 +9381,10 @@
     </row>
     <row r="300" spans="1:4">
       <c r="A300" t="s">
+        <v>600</v>
+      </c>
+      <c r="B300" t="s">
         <v>601</v>
-      </c>
-      <c r="B300" t="s">
-        <v>602</v>
       </c>
       <c r="D300" t="s">
         <v>9</v>
@@ -9203,10 +9392,10 @@
     </row>
     <row r="301" spans="1:4">
       <c r="A301" t="s">
+        <v>602</v>
+      </c>
+      <c r="B301" t="s">
         <v>603</v>
-      </c>
-      <c r="B301" t="s">
-        <v>604</v>
       </c>
       <c r="D301" t="s">
         <v>9</v>
@@ -9214,10 +9403,10 @@
     </row>
     <row r="302" spans="1:4">
       <c r="A302" t="s">
+        <v>604</v>
+      </c>
+      <c r="B302" t="s">
         <v>605</v>
-      </c>
-      <c r="B302" t="s">
-        <v>606</v>
       </c>
       <c r="D302" t="s">
         <v>9</v>
@@ -9225,10 +9414,10 @@
     </row>
     <row r="303" spans="1:4">
       <c r="A303" t="s">
+        <v>606</v>
+      </c>
+      <c r="B303" t="s">
         <v>607</v>
-      </c>
-      <c r="B303" t="s">
-        <v>608</v>
       </c>
       <c r="D303" t="s">
         <v>9</v>
@@ -9236,10 +9425,10 @@
     </row>
     <row r="304" spans="1:4">
       <c r="A304" t="s">
+        <v>608</v>
+      </c>
+      <c r="B304" t="s">
         <v>609</v>
-      </c>
-      <c r="B304" t="s">
-        <v>610</v>
       </c>
       <c r="D304" t="s">
         <v>9</v>
@@ -9247,10 +9436,10 @@
     </row>
     <row r="305" spans="1:4">
       <c r="A305" t="s">
+        <v>610</v>
+      </c>
+      <c r="B305" t="s">
         <v>611</v>
-      </c>
-      <c r="B305" t="s">
-        <v>612</v>
       </c>
       <c r="D305" t="s">
         <v>9</v>
@@ -9258,10 +9447,10 @@
     </row>
     <row r="306" spans="1:4">
       <c r="A306" t="s">
+        <v>612</v>
+      </c>
+      <c r="B306" t="s">
         <v>613</v>
-      </c>
-      <c r="B306" t="s">
-        <v>614</v>
       </c>
       <c r="D306" t="s">
         <v>9</v>
@@ -9269,10 +9458,10 @@
     </row>
     <row r="307" spans="1:4">
       <c r="A307" t="s">
+        <v>614</v>
+      </c>
+      <c r="B307" t="s">
         <v>615</v>
-      </c>
-      <c r="B307" t="s">
-        <v>616</v>
       </c>
       <c r="D307" t="s">
         <v>9</v>
@@ -9280,10 +9469,10 @@
     </row>
     <row r="308" spans="1:4">
       <c r="A308" t="s">
+        <v>616</v>
+      </c>
+      <c r="B308" t="s">
         <v>617</v>
-      </c>
-      <c r="B308" t="s">
-        <v>618</v>
       </c>
       <c r="D308" t="s">
         <v>9</v>
@@ -9291,10 +9480,10 @@
     </row>
     <row r="309" spans="1:4">
       <c r="A309" t="s">
+        <v>618</v>
+      </c>
+      <c r="B309" t="s">
         <v>619</v>
-      </c>
-      <c r="B309" t="s">
-        <v>620</v>
       </c>
       <c r="D309" t="s">
         <v>9</v>
@@ -9302,10 +9491,10 @@
     </row>
     <row r="310" spans="1:4">
       <c r="A310" t="s">
+        <v>620</v>
+      </c>
+      <c r="B310" t="s">
         <v>621</v>
-      </c>
-      <c r="B310" t="s">
-        <v>622</v>
       </c>
       <c r="D310" t="s">
         <v>9</v>
@@ -9313,10 +9502,10 @@
     </row>
     <row r="311" spans="1:4">
       <c r="A311" t="s">
+        <v>622</v>
+      </c>
+      <c r="B311" t="s">
         <v>623</v>
-      </c>
-      <c r="B311" t="s">
-        <v>624</v>
       </c>
       <c r="D311" t="s">
         <v>9</v>
@@ -9324,10 +9513,10 @@
     </row>
     <row r="312" spans="1:4">
       <c r="A312" t="s">
+        <v>624</v>
+      </c>
+      <c r="B312" t="s">
         <v>625</v>
-      </c>
-      <c r="B312" t="s">
-        <v>626</v>
       </c>
       <c r="D312" t="s">
         <v>9</v>
@@ -9335,10 +9524,10 @@
     </row>
     <row r="313" spans="1:4">
       <c r="A313" t="s">
+        <v>626</v>
+      </c>
+      <c r="B313" t="s">
         <v>627</v>
-      </c>
-      <c r="B313" t="s">
-        <v>628</v>
       </c>
       <c r="D313" t="s">
         <v>9</v>
@@ -9346,10 +9535,10 @@
     </row>
     <row r="314" spans="1:4">
       <c r="A314" t="s">
+        <v>628</v>
+      </c>
+      <c r="B314" t="s">
         <v>629</v>
-      </c>
-      <c r="B314" t="s">
-        <v>630</v>
       </c>
       <c r="D314" t="s">
         <v>9</v>
@@ -9357,10 +9546,10 @@
     </row>
     <row r="315" spans="1:4">
       <c r="A315" t="s">
+        <v>630</v>
+      </c>
+      <c r="B315" t="s">
         <v>631</v>
-      </c>
-      <c r="B315" t="s">
-        <v>632</v>
       </c>
       <c r="D315" t="s">
         <v>9</v>
@@ -9368,10 +9557,10 @@
     </row>
     <row r="316" spans="1:4">
       <c r="A316" t="s">
+        <v>632</v>
+      </c>
+      <c r="B316" t="s">
         <v>633</v>
-      </c>
-      <c r="B316" t="s">
-        <v>634</v>
       </c>
       <c r="D316" t="s">
         <v>9</v>
@@ -9379,10 +9568,10 @@
     </row>
     <row r="317" spans="1:4">
       <c r="A317" t="s">
+        <v>634</v>
+      </c>
+      <c r="B317" t="s">
         <v>635</v>
-      </c>
-      <c r="B317" t="s">
-        <v>636</v>
       </c>
       <c r="D317" t="s">
         <v>9</v>
@@ -9390,10 +9579,10 @@
     </row>
     <row r="318" spans="1:4">
       <c r="A318" t="s">
+        <v>636</v>
+      </c>
+      <c r="B318" t="s">
         <v>637</v>
-      </c>
-      <c r="B318" t="s">
-        <v>638</v>
       </c>
       <c r="D318" t="s">
         <v>9</v>
@@ -9401,10 +9590,10 @@
     </row>
     <row r="319" spans="1:4">
       <c r="A319" t="s">
+        <v>638</v>
+      </c>
+      <c r="B319" t="s">
         <v>639</v>
-      </c>
-      <c r="B319" t="s">
-        <v>640</v>
       </c>
       <c r="D319" t="s">
         <v>9</v>
@@ -9412,10 +9601,10 @@
     </row>
     <row r="320" spans="1:4">
       <c r="A320" t="s">
+        <v>640</v>
+      </c>
+      <c r="B320" t="s">
         <v>641</v>
-      </c>
-      <c r="B320" t="s">
-        <v>642</v>
       </c>
       <c r="D320" t="s">
         <v>9</v>
@@ -9423,10 +9612,10 @@
     </row>
     <row r="321" spans="1:4">
       <c r="A321" t="s">
+        <v>642</v>
+      </c>
+      <c r="B321" t="s">
         <v>643</v>
-      </c>
-      <c r="B321" t="s">
-        <v>644</v>
       </c>
       <c r="D321" t="s">
         <v>9</v>
@@ -9434,10 +9623,10 @@
     </row>
     <row r="322" spans="1:4">
       <c r="A322" t="s">
+        <v>644</v>
+      </c>
+      <c r="B322" t="s">
         <v>645</v>
-      </c>
-      <c r="B322" t="s">
-        <v>646</v>
       </c>
       <c r="D322" t="s">
         <v>9</v>
@@ -9445,10 +9634,10 @@
     </row>
     <row r="323" spans="1:4">
       <c r="A323" t="s">
+        <v>646</v>
+      </c>
+      <c r="B323" t="s">
         <v>647</v>
-      </c>
-      <c r="B323" t="s">
-        <v>648</v>
       </c>
       <c r="D323" t="s">
         <v>9</v>
@@ -9456,10 +9645,10 @@
     </row>
     <row r="324" spans="1:4">
       <c r="A324" t="s">
+        <v>648</v>
+      </c>
+      <c r="B324" t="s">
         <v>649</v>
-      </c>
-      <c r="B324" t="s">
-        <v>650</v>
       </c>
       <c r="D324" t="s">
         <v>9</v>
@@ -9467,10 +9656,10 @@
     </row>
     <row r="325" spans="1:4">
       <c r="A325" t="s">
+        <v>650</v>
+      </c>
+      <c r="B325" t="s">
         <v>651</v>
-      </c>
-      <c r="B325" t="s">
-        <v>652</v>
       </c>
       <c r="D325" t="s">
         <v>9</v>
@@ -9478,10 +9667,10 @@
     </row>
     <row r="326" spans="1:4">
       <c r="A326" t="s">
+        <v>652</v>
+      </c>
+      <c r="B326" t="s">
         <v>653</v>
-      </c>
-      <c r="B326" t="s">
-        <v>654</v>
       </c>
       <c r="D326" t="s">
         <v>9</v>
@@ -9489,10 +9678,10 @@
     </row>
     <row r="327" spans="1:4">
       <c r="A327" t="s">
+        <v>654</v>
+      </c>
+      <c r="B327" t="s">
         <v>655</v>
-      </c>
-      <c r="B327" t="s">
-        <v>656</v>
       </c>
       <c r="D327" t="s">
         <v>9</v>
@@ -9500,10 +9689,10 @@
     </row>
     <row r="328" spans="1:4">
       <c r="A328" t="s">
+        <v>656</v>
+      </c>
+      <c r="B328" t="s">
         <v>657</v>
-      </c>
-      <c r="B328" t="s">
-        <v>658</v>
       </c>
       <c r="D328" t="s">
         <v>9</v>
@@ -9511,10 +9700,10 @@
     </row>
     <row r="329" spans="1:4">
       <c r="A329" t="s">
+        <v>658</v>
+      </c>
+      <c r="B329" t="s">
         <v>659</v>
-      </c>
-      <c r="B329" t="s">
-        <v>660</v>
       </c>
       <c r="D329" t="s">
         <v>9</v>
@@ -9522,10 +9711,10 @@
     </row>
     <row r="330" spans="1:4">
       <c r="A330" t="s">
+        <v>660</v>
+      </c>
+      <c r="B330" t="s">
         <v>661</v>
-      </c>
-      <c r="B330" t="s">
-        <v>662</v>
       </c>
       <c r="D330" t="s">
         <v>9</v>
@@ -9533,10 +9722,10 @@
     </row>
     <row r="331" spans="1:4">
       <c r="A331" t="s">
+        <v>662</v>
+      </c>
+      <c r="B331" t="s">
         <v>663</v>
-      </c>
-      <c r="B331" t="s">
-        <v>664</v>
       </c>
       <c r="D331" t="s">
         <v>9</v>
@@ -9544,10 +9733,10 @@
     </row>
     <row r="332" spans="1:4">
       <c r="A332" t="s">
+        <v>664</v>
+      </c>
+      <c r="B332" t="s">
         <v>665</v>
-      </c>
-      <c r="B332" t="s">
-        <v>666</v>
       </c>
       <c r="D332" t="s">
         <v>9</v>
@@ -9555,10 +9744,10 @@
     </row>
     <row r="333" spans="1:4">
       <c r="A333" t="s">
+        <v>666</v>
+      </c>
+      <c r="B333" t="s">
         <v>667</v>
-      </c>
-      <c r="B333" t="s">
-        <v>668</v>
       </c>
       <c r="D333" t="s">
         <v>9</v>
@@ -9566,10 +9755,10 @@
     </row>
     <row r="334" spans="1:4">
       <c r="A334" t="s">
+        <v>668</v>
+      </c>
+      <c r="B334" t="s">
         <v>669</v>
-      </c>
-      <c r="B334" t="s">
-        <v>670</v>
       </c>
       <c r="D334" t="s">
         <v>9</v>
@@ -9577,10 +9766,10 @@
     </row>
     <row r="335" spans="1:4">
       <c r="A335" t="s">
+        <v>670</v>
+      </c>
+      <c r="B335" t="s">
         <v>671</v>
-      </c>
-      <c r="B335" t="s">
-        <v>672</v>
       </c>
       <c r="D335" t="s">
         <v>9</v>
@@ -9588,10 +9777,10 @@
     </row>
     <row r="336" spans="1:4">
       <c r="A336" t="s">
+        <v>672</v>
+      </c>
+      <c r="B336" t="s">
         <v>673</v>
-      </c>
-      <c r="B336" t="s">
-        <v>674</v>
       </c>
       <c r="D336" t="s">
         <v>9</v>
@@ -9599,10 +9788,10 @@
     </row>
     <row r="337" spans="1:4">
       <c r="A337" t="s">
+        <v>674</v>
+      </c>
+      <c r="B337" t="s">
         <v>675</v>
-      </c>
-      <c r="B337" t="s">
-        <v>676</v>
       </c>
       <c r="D337" t="s">
         <v>9</v>
@@ -9610,10 +9799,10 @@
     </row>
     <row r="338" spans="1:4">
       <c r="A338" t="s">
+        <v>676</v>
+      </c>
+      <c r="B338" t="s">
         <v>677</v>
-      </c>
-      <c r="B338" t="s">
-        <v>678</v>
       </c>
       <c r="D338" t="s">
         <v>9</v>
@@ -9621,10 +9810,10 @@
     </row>
     <row r="339" spans="1:4">
       <c r="A339" t="s">
+        <v>678</v>
+      </c>
+      <c r="B339" t="s">
         <v>679</v>
-      </c>
-      <c r="B339" t="s">
-        <v>680</v>
       </c>
       <c r="D339" t="s">
         <v>9</v>
@@ -9632,10 +9821,10 @@
     </row>
     <row r="340" spans="1:4">
       <c r="A340" t="s">
+        <v>680</v>
+      </c>
+      <c r="B340" t="s">
         <v>681</v>
-      </c>
-      <c r="B340" t="s">
-        <v>682</v>
       </c>
       <c r="D340" t="s">
         <v>9</v>
@@ -9643,10 +9832,10 @@
     </row>
     <row r="341" spans="1:4">
       <c r="A341" t="s">
+        <v>682</v>
+      </c>
+      <c r="B341" t="s">
         <v>683</v>
-      </c>
-      <c r="B341" t="s">
-        <v>684</v>
       </c>
       <c r="D341" t="s">
         <v>9</v>
@@ -9654,10 +9843,10 @@
     </row>
     <row r="342" spans="1:4">
       <c r="A342" t="s">
+        <v>684</v>
+      </c>
+      <c r="B342" t="s">
         <v>685</v>
-      </c>
-      <c r="B342" t="s">
-        <v>686</v>
       </c>
       <c r="D342" t="s">
         <v>9</v>
@@ -9665,10 +9854,10 @@
     </row>
     <row r="343" spans="1:4">
       <c r="A343" t="s">
+        <v>686</v>
+      </c>
+      <c r="B343" t="s">
         <v>687</v>
-      </c>
-      <c r="B343" t="s">
-        <v>688</v>
       </c>
       <c r="D343" t="s">
         <v>9</v>
@@ -9676,10 +9865,10 @@
     </row>
     <row r="344" spans="1:4">
       <c r="A344" t="s">
+        <v>688</v>
+      </c>
+      <c r="B344" t="s">
         <v>689</v>
-      </c>
-      <c r="B344" t="s">
-        <v>690</v>
       </c>
       <c r="D344" t="s">
         <v>9</v>
@@ -9687,10 +9876,10 @@
     </row>
     <row r="345" spans="1:4">
       <c r="A345" t="s">
+        <v>690</v>
+      </c>
+      <c r="B345" t="s">
         <v>691</v>
-      </c>
-      <c r="B345" t="s">
-        <v>692</v>
       </c>
       <c r="D345" t="s">
         <v>9</v>
@@ -9698,10 +9887,10 @@
     </row>
     <row r="346" spans="1:4">
       <c r="A346" t="s">
+        <v>692</v>
+      </c>
+      <c r="B346" t="s">
         <v>693</v>
-      </c>
-      <c r="B346" t="s">
-        <v>694</v>
       </c>
       <c r="D346" t="s">
         <v>9</v>
@@ -9709,10 +9898,10 @@
     </row>
     <row r="347" spans="1:4">
       <c r="A347" t="s">
+        <v>694</v>
+      </c>
+      <c r="B347" t="s">
         <v>695</v>
-      </c>
-      <c r="B347" t="s">
-        <v>696</v>
       </c>
       <c r="D347" t="s">
         <v>9</v>
@@ -9720,10 +9909,10 @@
     </row>
     <row r="348" spans="1:4">
       <c r="A348" t="s">
+        <v>696</v>
+      </c>
+      <c r="B348" t="s">
         <v>697</v>
-      </c>
-      <c r="B348" t="s">
-        <v>698</v>
       </c>
       <c r="D348" t="s">
         <v>9</v>
@@ -9731,10 +9920,10 @@
     </row>
     <row r="349" spans="1:4">
       <c r="A349" t="s">
+        <v>698</v>
+      </c>
+      <c r="B349" t="s">
         <v>699</v>
-      </c>
-      <c r="B349" t="s">
-        <v>700</v>
       </c>
       <c r="D349" t="s">
         <v>9</v>
@@ -9742,10 +9931,10 @@
     </row>
     <row r="350" spans="1:4">
       <c r="A350" t="s">
+        <v>700</v>
+      </c>
+      <c r="B350" t="s">
         <v>701</v>
-      </c>
-      <c r="B350" t="s">
-        <v>702</v>
       </c>
       <c r="D350" t="s">
         <v>9</v>
@@ -9753,10 +9942,10 @@
     </row>
     <row r="351" spans="1:4">
       <c r="A351" t="s">
+        <v>702</v>
+      </c>
+      <c r="B351" t="s">
         <v>703</v>
-      </c>
-      <c r="B351" t="s">
-        <v>704</v>
       </c>
       <c r="D351" t="s">
         <v>9</v>
@@ -9764,10 +9953,10 @@
     </row>
     <row r="352" spans="1:4">
       <c r="A352" t="s">
+        <v>704</v>
+      </c>
+      <c r="B352" t="s">
         <v>705</v>
-      </c>
-      <c r="B352" t="s">
-        <v>706</v>
       </c>
       <c r="D352" t="s">
         <v>9</v>
@@ -9775,10 +9964,10 @@
     </row>
     <row r="353" spans="1:4">
       <c r="A353" t="s">
+        <v>706</v>
+      </c>
+      <c r="B353" t="s">
         <v>707</v>
-      </c>
-      <c r="B353" t="s">
-        <v>708</v>
       </c>
       <c r="D353" t="s">
         <v>9</v>
@@ -9786,10 +9975,10 @@
     </row>
     <row r="354" spans="1:4">
       <c r="A354" t="s">
+        <v>708</v>
+      </c>
+      <c r="B354" t="s">
         <v>709</v>
-      </c>
-      <c r="B354" t="s">
-        <v>710</v>
       </c>
       <c r="D354" t="s">
         <v>9</v>
@@ -9797,10 +9986,10 @@
     </row>
     <row r="355" spans="1:4">
       <c r="A355" t="s">
+        <v>710</v>
+      </c>
+      <c r="B355" t="s">
         <v>711</v>
-      </c>
-      <c r="B355" t="s">
-        <v>712</v>
       </c>
       <c r="D355" t="s">
         <v>9</v>
@@ -9808,10 +9997,10 @@
     </row>
     <row r="356" spans="1:4">
       <c r="A356" t="s">
+        <v>712</v>
+      </c>
+      <c r="B356" t="s">
         <v>713</v>
-      </c>
-      <c r="B356" t="s">
-        <v>714</v>
       </c>
       <c r="D356" t="s">
         <v>9</v>
@@ -9819,10 +10008,10 @@
     </row>
     <row r="357" spans="1:4">
       <c r="A357" t="s">
+        <v>714</v>
+      </c>
+      <c r="B357" t="s">
         <v>715</v>
-      </c>
-      <c r="B357" t="s">
-        <v>716</v>
       </c>
       <c r="D357" t="s">
         <v>9</v>
@@ -9830,10 +10019,10 @@
     </row>
     <row r="358" spans="1:4">
       <c r="A358" t="s">
+        <v>716</v>
+      </c>
+      <c r="B358" t="s">
         <v>717</v>
-      </c>
-      <c r="B358" t="s">
-        <v>718</v>
       </c>
       <c r="D358" t="s">
         <v>9</v>
@@ -9841,10 +10030,10 @@
     </row>
     <row r="359" spans="1:4">
       <c r="A359" t="s">
+        <v>718</v>
+      </c>
+      <c r="B359" t="s">
         <v>719</v>
-      </c>
-      <c r="B359" t="s">
-        <v>720</v>
       </c>
       <c r="D359" t="s">
         <v>9</v>
@@ -9852,10 +10041,10 @@
     </row>
     <row r="360" spans="1:4">
       <c r="A360" t="s">
+        <v>720</v>
+      </c>
+      <c r="B360" t="s">
         <v>721</v>
-      </c>
-      <c r="B360" t="s">
-        <v>722</v>
       </c>
       <c r="D360" t="s">
         <v>9</v>
@@ -9863,10 +10052,10 @@
     </row>
     <row r="361" spans="1:4">
       <c r="A361" t="s">
+        <v>722</v>
+      </c>
+      <c r="B361" t="s">
         <v>723</v>
-      </c>
-      <c r="B361" t="s">
-        <v>724</v>
       </c>
       <c r="D361" t="s">
         <v>9</v>
@@ -9874,10 +10063,10 @@
     </row>
     <row r="362" spans="1:4">
       <c r="A362" t="s">
+        <v>724</v>
+      </c>
+      <c r="B362" t="s">
         <v>725</v>
-      </c>
-      <c r="B362" t="s">
-        <v>726</v>
       </c>
       <c r="D362" t="s">
         <v>9</v>
@@ -9885,10 +10074,10 @@
     </row>
     <row r="363" spans="1:4">
       <c r="A363" t="s">
+        <v>726</v>
+      </c>
+      <c r="B363" t="s">
         <v>727</v>
-      </c>
-      <c r="B363" t="s">
-        <v>728</v>
       </c>
       <c r="D363" t="s">
         <v>9</v>
@@ -9896,10 +10085,10 @@
     </row>
     <row r="364" spans="1:4">
       <c r="A364" t="s">
+        <v>728</v>
+      </c>
+      <c r="B364" t="s">
         <v>729</v>
-      </c>
-      <c r="B364" t="s">
-        <v>730</v>
       </c>
       <c r="D364" t="s">
         <v>9</v>
@@ -9907,10 +10096,10 @@
     </row>
     <row r="365" spans="1:4">
       <c r="A365" t="s">
+        <v>730</v>
+      </c>
+      <c r="B365" t="s">
         <v>731</v>
-      </c>
-      <c r="B365" t="s">
-        <v>732</v>
       </c>
       <c r="D365" t="s">
         <v>9</v>
@@ -9918,10 +10107,10 @@
     </row>
     <row r="366" spans="1:4">
       <c r="A366" t="s">
+        <v>732</v>
+      </c>
+      <c r="B366" t="s">
         <v>733</v>
-      </c>
-      <c r="B366" t="s">
-        <v>734</v>
       </c>
       <c r="D366" t="s">
         <v>9</v>
@@ -9929,10 +10118,10 @@
     </row>
     <row r="367" spans="1:4">
       <c r="A367" t="s">
+        <v>734</v>
+      </c>
+      <c r="B367" t="s">
         <v>735</v>
-      </c>
-      <c r="B367" t="s">
-        <v>736</v>
       </c>
       <c r="D367" t="s">
         <v>9</v>
@@ -9940,10 +10129,10 @@
     </row>
     <row r="368" spans="1:4">
       <c r="A368" t="s">
+        <v>736</v>
+      </c>
+      <c r="B368" t="s">
         <v>737</v>
-      </c>
-      <c r="B368" t="s">
-        <v>738</v>
       </c>
       <c r="D368" t="s">
         <v>9</v>
@@ -9951,10 +10140,10 @@
     </row>
     <row r="369" spans="1:4">
       <c r="A369" t="s">
+        <v>738</v>
+      </c>
+      <c r="B369" t="s">
         <v>739</v>
-      </c>
-      <c r="B369" t="s">
-        <v>740</v>
       </c>
       <c r="D369" t="s">
         <v>9</v>
@@ -9962,10 +10151,10 @@
     </row>
     <row r="370" spans="1:4">
       <c r="A370" t="s">
+        <v>740</v>
+      </c>
+      <c r="B370" t="s">
         <v>741</v>
-      </c>
-      <c r="B370" t="s">
-        <v>742</v>
       </c>
       <c r="D370" t="s">
         <v>9</v>
@@ -9973,10 +10162,10 @@
     </row>
     <row r="371" spans="1:4">
       <c r="A371" t="s">
+        <v>742</v>
+      </c>
+      <c r="B371" t="s">
         <v>743</v>
-      </c>
-      <c r="B371" t="s">
-        <v>744</v>
       </c>
       <c r="D371" t="s">
         <v>9</v>
@@ -9984,10 +10173,10 @@
     </row>
     <row r="372" spans="1:4">
       <c r="A372" t="s">
+        <v>744</v>
+      </c>
+      <c r="B372" t="s">
         <v>745</v>
-      </c>
-      <c r="B372" t="s">
-        <v>746</v>
       </c>
       <c r="D372" t="s">
         <v>9</v>
@@ -9995,10 +10184,10 @@
     </row>
     <row r="373" spans="1:4">
       <c r="A373" t="s">
+        <v>746</v>
+      </c>
+      <c r="B373" t="s">
         <v>747</v>
-      </c>
-      <c r="B373" t="s">
-        <v>748</v>
       </c>
       <c r="D373" t="s">
         <v>9</v>
@@ -10006,10 +10195,10 @@
     </row>
     <row r="374" spans="1:4">
       <c r="A374" t="s">
+        <v>748</v>
+      </c>
+      <c r="B374" t="s">
         <v>749</v>
-      </c>
-      <c r="B374" t="s">
-        <v>750</v>
       </c>
       <c r="D374" t="s">
         <v>9</v>
@@ -10017,10 +10206,10 @@
     </row>
     <row r="375" spans="1:4">
       <c r="A375" t="s">
+        <v>750</v>
+      </c>
+      <c r="B375" t="s">
         <v>751</v>
-      </c>
-      <c r="B375" t="s">
-        <v>752</v>
       </c>
       <c r="D375" t="s">
         <v>9</v>
@@ -10028,10 +10217,10 @@
     </row>
     <row r="376" spans="1:4">
       <c r="A376" t="s">
+        <v>752</v>
+      </c>
+      <c r="B376" t="s">
         <v>753</v>
-      </c>
-      <c r="B376" t="s">
-        <v>754</v>
       </c>
       <c r="D376" t="s">
         <v>9</v>
@@ -10039,10 +10228,10 @@
     </row>
     <row r="377" spans="1:4">
       <c r="A377" t="s">
+        <v>754</v>
+      </c>
+      <c r="B377" t="s">
         <v>755</v>
-      </c>
-      <c r="B377" t="s">
-        <v>756</v>
       </c>
       <c r="D377" t="s">
         <v>9</v>
@@ -10050,10 +10239,10 @@
     </row>
     <row r="378" spans="1:4">
       <c r="A378" t="s">
+        <v>756</v>
+      </c>
+      <c r="B378" t="s">
         <v>757</v>
-      </c>
-      <c r="B378" t="s">
-        <v>758</v>
       </c>
       <c r="D378" t="s">
         <v>9</v>
@@ -10061,10 +10250,10 @@
     </row>
     <row r="379" spans="1:4">
       <c r="A379" t="s">
+        <v>758</v>
+      </c>
+      <c r="B379" t="s">
         <v>759</v>
-      </c>
-      <c r="B379" t="s">
-        <v>760</v>
       </c>
       <c r="D379" t="s">
         <v>9</v>
@@ -10072,10 +10261,10 @@
     </row>
     <row r="380" spans="1:4">
       <c r="A380" t="s">
+        <v>760</v>
+      </c>
+      <c r="B380" t="s">
         <v>761</v>
-      </c>
-      <c r="B380" t="s">
-        <v>762</v>
       </c>
       <c r="D380" t="s">
         <v>9</v>
@@ -10083,10 +10272,10 @@
     </row>
     <row r="381" spans="1:4">
       <c r="A381" t="s">
+        <v>762</v>
+      </c>
+      <c r="B381" t="s">
         <v>763</v>
-      </c>
-      <c r="B381" t="s">
-        <v>764</v>
       </c>
       <c r="D381" t="s">
         <v>9</v>
@@ -10094,10 +10283,10 @@
     </row>
     <row r="382" spans="1:4">
       <c r="A382" t="s">
+        <v>764</v>
+      </c>
+      <c r="B382" t="s">
         <v>765</v>
-      </c>
-      <c r="B382" t="s">
-        <v>766</v>
       </c>
       <c r="D382" t="s">
         <v>9</v>
@@ -10105,10 +10294,10 @@
     </row>
     <row r="383" spans="1:4">
       <c r="A383" t="s">
+        <v>766</v>
+      </c>
+      <c r="B383" t="s">
         <v>767</v>
-      </c>
-      <c r="B383" t="s">
-        <v>768</v>
       </c>
       <c r="D383" t="s">
         <v>9</v>
@@ -10116,10 +10305,10 @@
     </row>
     <row r="384" spans="1:4">
       <c r="A384" t="s">
+        <v>768</v>
+      </c>
+      <c r="B384" t="s">
         <v>769</v>
-      </c>
-      <c r="B384" t="s">
-        <v>770</v>
       </c>
       <c r="D384" t="s">
         <v>9</v>
@@ -10127,10 +10316,10 @@
     </row>
     <row r="385" spans="1:4">
       <c r="A385" t="s">
+        <v>770</v>
+      </c>
+      <c r="B385" t="s">
         <v>771</v>
-      </c>
-      <c r="B385" t="s">
-        <v>772</v>
       </c>
       <c r="D385" t="s">
         <v>9</v>
@@ -10138,10 +10327,10 @@
     </row>
     <row r="386" spans="1:4">
       <c r="A386" t="s">
+        <v>772</v>
+      </c>
+      <c r="B386" t="s">
         <v>773</v>
-      </c>
-      <c r="B386" t="s">
-        <v>774</v>
       </c>
       <c r="D386" t="s">
         <v>9</v>
@@ -10149,10 +10338,10 @@
     </row>
     <row r="387" spans="1:4">
       <c r="A387" t="s">
+        <v>774</v>
+      </c>
+      <c r="B387" t="s">
         <v>775</v>
-      </c>
-      <c r="B387" t="s">
-        <v>776</v>
       </c>
       <c r="D387" t="s">
         <v>9</v>
@@ -10160,10 +10349,10 @@
     </row>
     <row r="388" spans="1:4">
       <c r="A388" t="s">
+        <v>776</v>
+      </c>
+      <c r="B388" t="s">
         <v>777</v>
-      </c>
-      <c r="B388" t="s">
-        <v>778</v>
       </c>
       <c r="D388" t="s">
         <v>9</v>
@@ -10171,10 +10360,10 @@
     </row>
     <row r="389" spans="1:4">
       <c r="A389" t="s">
+        <v>778</v>
+      </c>
+      <c r="B389" t="s">
         <v>779</v>
-      </c>
-      <c r="B389" t="s">
-        <v>780</v>
       </c>
       <c r="D389" t="s">
         <v>9</v>
@@ -10182,10 +10371,10 @@
     </row>
     <row r="390" spans="1:4">
       <c r="A390" t="s">
+        <v>780</v>
+      </c>
+      <c r="B390" t="s">
         <v>781</v>
-      </c>
-      <c r="B390" t="s">
-        <v>782</v>
       </c>
       <c r="D390" t="s">
         <v>9</v>
@@ -10193,10 +10382,10 @@
     </row>
     <row r="391" spans="1:4">
       <c r="A391" t="s">
+        <v>782</v>
+      </c>
+      <c r="B391" t="s">
         <v>783</v>
-      </c>
-      <c r="B391" t="s">
-        <v>784</v>
       </c>
       <c r="D391" t="s">
         <v>9</v>
@@ -10204,10 +10393,10 @@
     </row>
     <row r="392" spans="1:4">
       <c r="A392" t="s">
+        <v>784</v>
+      </c>
+      <c r="B392" t="s">
         <v>785</v>
-      </c>
-      <c r="B392" t="s">
-        <v>786</v>
       </c>
       <c r="D392" t="s">
         <v>9</v>
@@ -10215,10 +10404,10 @@
     </row>
     <row r="393" spans="1:4">
       <c r="A393" t="s">
+        <v>786</v>
+      </c>
+      <c r="B393" t="s">
         <v>787</v>
-      </c>
-      <c r="B393" t="s">
-        <v>788</v>
       </c>
       <c r="D393" t="s">
         <v>9</v>
@@ -10226,10 +10415,10 @@
     </row>
     <row r="394" spans="1:4">
       <c r="A394" t="s">
+        <v>788</v>
+      </c>
+      <c r="B394" t="s">
         <v>789</v>
-      </c>
-      <c r="B394" t="s">
-        <v>790</v>
       </c>
       <c r="D394" t="s">
         <v>9</v>
@@ -10237,10 +10426,10 @@
     </row>
     <row r="395" spans="1:4">
       <c r="A395" t="s">
+        <v>790</v>
+      </c>
+      <c r="B395" t="s">
         <v>791</v>
-      </c>
-      <c r="B395" t="s">
-        <v>792</v>
       </c>
       <c r="D395" t="s">
         <v>9</v>
@@ -10248,10 +10437,10 @@
     </row>
     <row r="396" spans="1:4">
       <c r="A396" t="s">
+        <v>792</v>
+      </c>
+      <c r="B396" t="s">
         <v>793</v>
-      </c>
-      <c r="B396" t="s">
-        <v>794</v>
       </c>
       <c r="D396" t="s">
         <v>9</v>
@@ -10259,10 +10448,10 @@
     </row>
     <row r="397" spans="1:4">
       <c r="A397" t="s">
+        <v>794</v>
+      </c>
+      <c r="B397" t="s">
         <v>795</v>
-      </c>
-      <c r="B397" t="s">
-        <v>796</v>
       </c>
       <c r="D397" t="s">
         <v>9</v>
@@ -10270,10 +10459,10 @@
     </row>
     <row r="398" spans="1:4">
       <c r="A398" t="s">
+        <v>796</v>
+      </c>
+      <c r="B398" t="s">
         <v>797</v>
-      </c>
-      <c r="B398" t="s">
-        <v>798</v>
       </c>
       <c r="D398" t="s">
         <v>9</v>
@@ -10281,10 +10470,10 @@
     </row>
     <row r="399" spans="1:4">
       <c r="A399" t="s">
+        <v>798</v>
+      </c>
+      <c r="B399" t="s">
         <v>799</v>
-      </c>
-      <c r="B399" t="s">
-        <v>800</v>
       </c>
       <c r="D399" t="s">
         <v>9</v>
@@ -10292,10 +10481,10 @@
     </row>
     <row r="400" spans="1:4">
       <c r="A400" t="s">
+        <v>800</v>
+      </c>
+      <c r="B400" t="s">
         <v>801</v>
-      </c>
-      <c r="B400" t="s">
-        <v>802</v>
       </c>
       <c r="D400" t="s">
         <v>9</v>
@@ -10303,10 +10492,10 @@
     </row>
     <row r="401" spans="1:4">
       <c r="A401" t="s">
+        <v>802</v>
+      </c>
+      <c r="B401" t="s">
         <v>803</v>
-      </c>
-      <c r="B401" t="s">
-        <v>804</v>
       </c>
       <c r="D401" t="s">
         <v>9</v>
@@ -10314,10 +10503,10 @@
     </row>
     <row r="402" spans="1:4">
       <c r="A402" t="s">
+        <v>804</v>
+      </c>
+      <c r="B402" t="s">
         <v>805</v>
-      </c>
-      <c r="B402" t="s">
-        <v>806</v>
       </c>
       <c r="D402" t="s">
         <v>9</v>
@@ -10325,10 +10514,10 @@
     </row>
     <row r="403" spans="1:4">
       <c r="A403" t="s">
+        <v>806</v>
+      </c>
+      <c r="B403" t="s">
         <v>807</v>
-      </c>
-      <c r="B403" t="s">
-        <v>808</v>
       </c>
       <c r="D403" t="s">
         <v>9</v>
@@ -10336,10 +10525,10 @@
     </row>
     <row r="404" spans="1:4">
       <c r="A404" t="s">
+        <v>808</v>
+      </c>
+      <c r="B404" t="s">
         <v>809</v>
-      </c>
-      <c r="B404" t="s">
-        <v>810</v>
       </c>
       <c r="D404" t="s">
         <v>9</v>
@@ -10347,10 +10536,10 @@
     </row>
     <row r="405" spans="1:4">
       <c r="A405" t="s">
+        <v>810</v>
+      </c>
+      <c r="B405" t="s">
         <v>811</v>
-      </c>
-      <c r="B405" t="s">
-        <v>812</v>
       </c>
       <c r="D405" t="s">
         <v>9</v>
@@ -10358,10 +10547,10 @@
     </row>
     <row r="406" spans="1:4">
       <c r="A406" t="s">
+        <v>812</v>
+      </c>
+      <c r="B406" t="s">
         <v>813</v>
-      </c>
-      <c r="B406" t="s">
-        <v>814</v>
       </c>
       <c r="D406" t="s">
         <v>9</v>
@@ -10369,10 +10558,10 @@
     </row>
     <row r="407" spans="1:4">
       <c r="A407" t="s">
+        <v>814</v>
+      </c>
+      <c r="B407" t="s">
         <v>815</v>
-      </c>
-      <c r="B407" t="s">
-        <v>816</v>
       </c>
       <c r="D407" t="s">
         <v>9</v>
@@ -10380,10 +10569,10 @@
     </row>
     <row r="408" spans="1:4">
       <c r="A408" t="s">
+        <v>816</v>
+      </c>
+      <c r="B408" t="s">
         <v>817</v>
-      </c>
-      <c r="B408" t="s">
-        <v>818</v>
       </c>
       <c r="D408" t="s">
         <v>9</v>
@@ -10391,10 +10580,10 @@
     </row>
     <row r="409" spans="1:4">
       <c r="A409" t="s">
+        <v>818</v>
+      </c>
+      <c r="B409" t="s">
         <v>819</v>
-      </c>
-      <c r="B409" t="s">
-        <v>790</v>
       </c>
       <c r="D409" t="s">
         <v>9</v>
@@ -10405,7 +10594,7 @@
         <v>820</v>
       </c>
       <c r="B410" t="s">
-        <v>764</v>
+        <v>821</v>
       </c>
       <c r="D410" t="s">
         <v>9</v>
@@ -10413,10 +10602,10 @@
     </row>
     <row r="411" spans="1:4">
       <c r="A411" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B411" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D411" t="s">
         <v>9</v>
@@ -10424,10 +10613,10 @@
     </row>
     <row r="412" spans="1:4">
       <c r="A412" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B412" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="D412" t="s">
         <v>9</v>
@@ -10435,10 +10624,10 @@
     </row>
     <row r="413" spans="1:4">
       <c r="A413" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B413" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D413" t="s">
         <v>9</v>
@@ -10446,10 +10635,10 @@
     </row>
     <row r="414" spans="1:4">
       <c r="A414" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B414" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="D414" t="s">
         <v>9</v>
@@ -10457,10 +10646,10 @@
     </row>
     <row r="415" spans="1:4">
       <c r="A415" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B415" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="D415" t="s">
         <v>9</v>
@@ -10468,10 +10657,10 @@
     </row>
     <row r="416" spans="1:4">
       <c r="A416" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B416" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D416" t="s">
         <v>9</v>
@@ -10479,10 +10668,10 @@
     </row>
     <row r="417" spans="1:4">
       <c r="A417" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B417" t="s">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="D417" t="s">
         <v>9</v>
@@ -10490,10 +10679,10 @@
     </row>
     <row r="418" spans="1:4">
       <c r="A418" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="B418" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="D418" t="s">
         <v>9</v>
@@ -10501,10 +10690,10 @@
     </row>
     <row r="419" spans="1:4">
       <c r="A419" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B419" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="D419" t="s">
         <v>9</v>
@@ -10512,10 +10701,10 @@
     </row>
     <row r="420" spans="1:4">
       <c r="A420" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="B420" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="D420" t="s">
         <v>9</v>
@@ -10523,10 +10712,10 @@
     </row>
     <row r="421" spans="1:4">
       <c r="A421" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="B421" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="D421" t="s">
         <v>9</v>
@@ -10534,10 +10723,10 @@
     </row>
     <row r="422" spans="1:4">
       <c r="A422" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B422" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="D422" t="s">
         <v>9</v>
@@ -10545,10 +10734,10 @@
     </row>
     <row r="423" spans="1:4">
       <c r="A423" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="B423" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="D423" t="s">
         <v>9</v>
@@ -10556,10 +10745,10 @@
     </row>
     <row r="424" spans="1:4">
       <c r="A424" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B424" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="D424" t="s">
         <v>9</v>
@@ -10567,10 +10756,10 @@
     </row>
     <row r="425" spans="1:4">
       <c r="A425" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="B425" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="D425" t="s">
         <v>9</v>
@@ -10578,10 +10767,10 @@
     </row>
     <row r="426" spans="1:4">
       <c r="A426" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="B426" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="D426" t="s">
         <v>9</v>
@@ -10589,10 +10778,10 @@
     </row>
     <row r="427" spans="1:4">
       <c r="A427" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B427" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="D427" t="s">
         <v>9</v>
@@ -10600,10 +10789,10 @@
     </row>
     <row r="428" spans="1:4">
       <c r="A428" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="B428" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="D428" t="s">
         <v>9</v>
@@ -10611,10 +10800,10 @@
     </row>
     <row r="429" spans="1:4">
       <c r="A429" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B429" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="D429" t="s">
         <v>9</v>
@@ -10622,10 +10811,10 @@
     </row>
     <row r="430" spans="1:4">
       <c r="A430" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="B430" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="D430" t="s">
         <v>9</v>
@@ -10633,10 +10822,10 @@
     </row>
     <row r="431" spans="1:4">
       <c r="A431" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="B431" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="D431" t="s">
         <v>9</v>
@@ -10644,10 +10833,10 @@
     </row>
     <row r="432" spans="1:4">
       <c r="A432" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="B432" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="D432" t="s">
         <v>9</v>
@@ -10655,10 +10844,10 @@
     </row>
     <row r="433" spans="1:4">
       <c r="A433" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="B433" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="D433" t="s">
         <v>9</v>
@@ -10666,10 +10855,10 @@
     </row>
     <row r="434" spans="1:4">
       <c r="A434" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="B434" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="D434" t="s">
         <v>9</v>
@@ -10677,10 +10866,10 @@
     </row>
     <row r="435" spans="1:4">
       <c r="A435" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="B435" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="D435" t="s">
         <v>9</v>
@@ -10688,10 +10877,10 @@
     </row>
     <row r="436" spans="1:4">
       <c r="A436" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="B436" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="D436" t="s">
         <v>9</v>
@@ -10699,10 +10888,10 @@
     </row>
     <row r="437" spans="1:4">
       <c r="A437" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B437" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="D437" t="s">
         <v>9</v>
@@ -10710,10 +10899,10 @@
     </row>
     <row r="438" spans="1:4">
       <c r="A438" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="B438" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="D438" t="s">
         <v>9</v>
@@ -10721,10 +10910,10 @@
     </row>
     <row r="439" spans="1:4">
       <c r="A439" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="B439" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="D439" t="s">
         <v>9</v>
@@ -10732,10 +10921,10 @@
     </row>
     <row r="440" spans="1:4">
       <c r="A440" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="B440" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="D440" t="s">
         <v>9</v>
@@ -10743,10 +10932,10 @@
     </row>
     <row r="441" spans="1:4">
       <c r="A441" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="B441" t="s">
-        <v>881</v>
+        <v>853</v>
       </c>
       <c r="D441" t="s">
         <v>9</v>
@@ -10754,10 +10943,10 @@
     </row>
     <row r="442" spans="1:4">
       <c r="A442" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B442" t="s">
-        <v>883</v>
+        <v>827</v>
       </c>
       <c r="D442" t="s">
         <v>9</v>
@@ -10823,7 +11012,7 @@
         <v>894</v>
       </c>
       <c r="B448" t="s">
-        <v>839</v>
+        <v>895</v>
       </c>
       <c r="D448" t="s">
         <v>9</v>
@@ -10831,10 +11020,10 @@
     </row>
     <row r="449" spans="1:4">
       <c r="A449" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B449" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="D449" t="s">
         <v>9</v>
@@ -10856,7 +11045,7 @@
         <v>899</v>
       </c>
       <c r="B451" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="D451" t="s">
         <v>9</v>
@@ -10864,10 +11053,10 @@
     </row>
     <row r="452" spans="1:4">
       <c r="A452" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B452" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="D452" t="s">
         <v>9</v>
@@ -10875,10 +11064,10 @@
     </row>
     <row r="453" spans="1:4">
       <c r="A453" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B453" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="D453" t="s">
         <v>9</v>
@@ -10886,10 +11075,10 @@
     </row>
     <row r="454" spans="1:4">
       <c r="A454" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B454" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="D454" t="s">
         <v>9</v>
@@ -10897,10 +11086,10 @@
     </row>
     <row r="455" spans="1:4">
       <c r="A455" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B455" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="D455" t="s">
         <v>9</v>
@@ -10908,10 +11097,10 @@
     </row>
     <row r="456" spans="1:4">
       <c r="A456" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B456" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="D456" t="s">
         <v>9</v>
@@ -10919,10 +11108,10 @@
     </row>
     <row r="457" spans="1:4">
       <c r="A457" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B457" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="D457" t="s">
         <v>9</v>
@@ -10930,10 +11119,10 @@
     </row>
     <row r="458" spans="1:4">
       <c r="A458" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B458" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D458" t="s">
         <v>9</v>
@@ -10941,10 +11130,10 @@
     </row>
     <row r="459" spans="1:4">
       <c r="A459" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B459" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D459" t="s">
         <v>9</v>
@@ -10952,10 +11141,10 @@
     </row>
     <row r="460" spans="1:4">
       <c r="A460" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B460" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="D460" t="s">
         <v>9</v>
@@ -10963,10 +11152,10 @@
     </row>
     <row r="461" spans="1:4">
       <c r="A461" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B461" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="D461" t="s">
         <v>9</v>
@@ -10974,10 +11163,10 @@
     </row>
     <row r="462" spans="1:4">
       <c r="A462" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B462" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="D462" t="s">
         <v>9</v>
@@ -10985,10 +11174,10 @@
     </row>
     <row r="463" spans="1:4">
       <c r="A463" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B463" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="D463" t="s">
         <v>9</v>
@@ -10996,10 +11185,10 @@
     </row>
     <row r="464" spans="1:4">
       <c r="A464" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B464" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="D464" t="s">
         <v>9</v>
@@ -11007,10 +11196,10 @@
     </row>
     <row r="465" spans="1:4">
       <c r="A465" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B465" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D465" t="s">
         <v>9</v>
@@ -11018,10 +11207,10 @@
     </row>
     <row r="466" spans="1:4">
       <c r="A466" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B466" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="D466" t="s">
         <v>9</v>
@@ -11029,10 +11218,10 @@
     </row>
     <row r="467" spans="1:4">
       <c r="A467" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B467" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="D467" t="s">
         <v>9</v>
@@ -11040,10 +11229,10 @@
     </row>
     <row r="468" spans="1:4">
       <c r="A468" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B468" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="D468" t="s">
         <v>9</v>
@@ -11051,10 +11240,10 @@
     </row>
     <row r="469" spans="1:4">
       <c r="A469" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B469" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="D469" t="s">
         <v>9</v>
@@ -11062,10 +11251,10 @@
     </row>
     <row r="470" spans="1:4">
       <c r="A470" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B470" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="D470" t="s">
         <v>9</v>
@@ -11073,10 +11262,10 @@
     </row>
     <row r="471" spans="1:4">
       <c r="A471" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B471" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="D471" t="s">
         <v>9</v>
@@ -11084,10 +11273,10 @@
     </row>
     <row r="472" spans="1:4">
       <c r="A472" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B472" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="D472" t="s">
         <v>9</v>
@@ -11095,10 +11284,10 @@
     </row>
     <row r="473" spans="1:4">
       <c r="A473" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B473" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="D473" t="s">
         <v>9</v>
@@ -11106,10 +11295,10 @@
     </row>
     <row r="474" spans="1:4">
       <c r="A474" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B474" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="D474" t="s">
         <v>9</v>
@@ -11117,10 +11306,10 @@
     </row>
     <row r="475" spans="1:4">
       <c r="A475" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B475" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="D475" t="s">
         <v>9</v>
@@ -11128,10 +11317,10 @@
     </row>
     <row r="476" spans="1:4">
       <c r="A476" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B476" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="D476" t="s">
         <v>9</v>
@@ -11139,10 +11328,10 @@
     </row>
     <row r="477" spans="1:4">
       <c r="A477" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B477" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="D477" t="s">
         <v>9</v>
@@ -11150,10 +11339,10 @@
     </row>
     <row r="478" spans="1:4">
       <c r="A478" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B478" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="D478" t="s">
         <v>9</v>
@@ -11161,10 +11350,10 @@
     </row>
     <row r="479" spans="1:4">
       <c r="A479" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B479" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="D479" t="s">
         <v>9</v>
@@ -11172,10 +11361,10 @@
     </row>
     <row r="480" spans="1:4">
       <c r="A480" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B480" t="s">
-        <v>957</v>
+        <v>902</v>
       </c>
       <c r="D480" t="s">
         <v>9</v>
@@ -11208,7 +11397,7 @@
         <v>962</v>
       </c>
       <c r="B483" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="D483" t="s">
         <v>9</v>
@@ -11216,10 +11405,10 @@
     </row>
     <row r="484" spans="1:4">
       <c r="A484" t="s">
+        <v>963</v>
+      </c>
+      <c r="B484" t="s">
         <v>964</v>
-      </c>
-      <c r="B484" t="s">
-        <v>961</v>
       </c>
       <c r="D484" t="s">
         <v>9</v>
@@ -11571,7 +11760,7 @@
         <v>1027</v>
       </c>
       <c r="B516" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="D516" t="s">
         <v>9</v>
@@ -11579,10 +11768,10 @@
     </row>
     <row r="517" spans="1:4">
       <c r="A517" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B517" t="s">
         <v>1029</v>
-      </c>
-      <c r="B517" t="s">
-        <v>1030</v>
       </c>
       <c r="D517" t="s">
         <v>9</v>
@@ -11590,10 +11779,10 @@
     </row>
     <row r="518" spans="1:4">
       <c r="A518" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B518" t="s">
         <v>1031</v>
-      </c>
-      <c r="B518" t="s">
-        <v>1032</v>
       </c>
       <c r="D518" t="s">
         <v>9</v>
@@ -11601,10 +11790,10 @@
     </row>
     <row r="519" spans="1:4">
       <c r="A519" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B519" t="s">
         <v>1033</v>
-      </c>
-      <c r="B519" t="s">
-        <v>1034</v>
       </c>
       <c r="D519" t="s">
         <v>9</v>
@@ -11612,10 +11801,10 @@
     </row>
     <row r="520" spans="1:4">
       <c r="A520" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B520" t="s">
         <v>1035</v>
-      </c>
-      <c r="B520" t="s">
-        <v>1036</v>
       </c>
       <c r="D520" t="s">
         <v>9</v>
@@ -11623,10 +11812,10 @@
     </row>
     <row r="521" spans="1:4">
       <c r="A521" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B521" t="s">
         <v>1037</v>
-      </c>
-      <c r="B521" t="s">
-        <v>1034</v>
       </c>
       <c r="D521" t="s">
         <v>9</v>
@@ -11978,7 +12167,7 @@
         <v>1100</v>
       </c>
       <c r="B553" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="D553" t="s">
         <v>9</v>
@@ -11986,10 +12175,10 @@
     </row>
     <row r="554" spans="1:4">
       <c r="A554" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B554" t="s">
         <v>1102</v>
-      </c>
-      <c r="B554" t="s">
-        <v>1103</v>
       </c>
       <c r="D554" t="s">
         <v>9</v>
@@ -11997,10 +12186,10 @@
     </row>
     <row r="555" spans="1:4">
       <c r="A555" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B555" t="s">
         <v>1104</v>
-      </c>
-      <c r="B555" t="s">
-        <v>1105</v>
       </c>
       <c r="D555" t="s">
         <v>9</v>
@@ -12008,10 +12197,10 @@
     </row>
     <row r="556" spans="1:4">
       <c r="A556" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B556" t="s">
         <v>1106</v>
-      </c>
-      <c r="B556" t="s">
-        <v>1107</v>
       </c>
       <c r="D556" t="s">
         <v>9</v>
@@ -12019,10 +12208,10 @@
     </row>
     <row r="557" spans="1:4">
       <c r="A557" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B557" t="s">
         <v>1108</v>
-      </c>
-      <c r="B557" t="s">
-        <v>1109</v>
       </c>
       <c r="D557" t="s">
         <v>9</v>
@@ -12030,10 +12219,10 @@
     </row>
     <row r="558" spans="1:4">
       <c r="A558" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B558" t="s">
         <v>1110</v>
-      </c>
-      <c r="B558" t="s">
-        <v>1111</v>
       </c>
       <c r="D558" t="s">
         <v>9</v>
@@ -12041,10 +12230,10 @@
     </row>
     <row r="559" spans="1:4">
       <c r="A559" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B559" t="s">
         <v>1112</v>
-      </c>
-      <c r="B559" t="s">
-        <v>1113</v>
       </c>
       <c r="D559" t="s">
         <v>9</v>
@@ -12052,10 +12241,10 @@
     </row>
     <row r="560" spans="1:4">
       <c r="A560" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B560" t="s">
         <v>1114</v>
-      </c>
-      <c r="B560" t="s">
-        <v>1115</v>
       </c>
       <c r="D560" t="s">
         <v>9</v>
@@ -12063,10 +12252,10 @@
     </row>
     <row r="561" spans="1:4">
       <c r="A561" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B561" t="s">
         <v>1116</v>
-      </c>
-      <c r="B561" t="s">
-        <v>1117</v>
       </c>
       <c r="D561" t="s">
         <v>9</v>
@@ -12074,10 +12263,10 @@
     </row>
     <row r="562" spans="1:4">
       <c r="A562" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B562" t="s">
         <v>1118</v>
-      </c>
-      <c r="B562" t="s">
-        <v>1119</v>
       </c>
       <c r="D562" t="s">
         <v>9</v>
@@ -12085,10 +12274,10 @@
     </row>
     <row r="563" spans="1:4">
       <c r="A563" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B563" t="s">
         <v>1120</v>
-      </c>
-      <c r="B563" t="s">
-        <v>1121</v>
       </c>
       <c r="D563" t="s">
         <v>9</v>
@@ -12096,10 +12285,10 @@
     </row>
     <row r="564" spans="1:4">
       <c r="A564" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B564" t="s">
         <v>1122</v>
-      </c>
-      <c r="B564" t="s">
-        <v>1123</v>
       </c>
       <c r="D564" t="s">
         <v>9</v>
@@ -12107,10 +12296,10 @@
     </row>
     <row r="565" spans="1:4">
       <c r="A565" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B565" t="s">
         <v>1124</v>
-      </c>
-      <c r="B565" t="s">
-        <v>1125</v>
       </c>
       <c r="D565" t="s">
         <v>9</v>
@@ -12118,10 +12307,10 @@
     </row>
     <row r="566" spans="1:4">
       <c r="A566" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B566" t="s">
         <v>1126</v>
-      </c>
-      <c r="B566" t="s">
-        <v>1127</v>
       </c>
       <c r="D566" t="s">
         <v>9</v>
@@ -12129,10 +12318,10 @@
     </row>
     <row r="567" spans="1:4">
       <c r="A567" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B567" t="s">
         <v>1128</v>
-      </c>
-      <c r="B567" t="s">
-        <v>1129</v>
       </c>
       <c r="D567" t="s">
         <v>9</v>
@@ -12140,10 +12329,10 @@
     </row>
     <row r="568" spans="1:4">
       <c r="A568" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B568" t="s">
         <v>1130</v>
-      </c>
-      <c r="B568" t="s">
-        <v>1131</v>
       </c>
       <c r="D568" t="s">
         <v>9</v>
@@ -12151,10 +12340,10 @@
     </row>
     <row r="569" spans="1:4">
       <c r="A569" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B569" t="s">
         <v>1132</v>
-      </c>
-      <c r="B569" t="s">
-        <v>1133</v>
       </c>
       <c r="D569" t="s">
         <v>9</v>
@@ -12162,10 +12351,10 @@
     </row>
     <row r="570" spans="1:4">
       <c r="A570" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B570" t="s">
         <v>1134</v>
-      </c>
-      <c r="B570" t="s">
-        <v>1135</v>
       </c>
       <c r="D570" t="s">
         <v>9</v>
@@ -12173,10 +12362,10 @@
     </row>
     <row r="571" spans="1:4">
       <c r="A571" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B571" t="s">
         <v>1136</v>
-      </c>
-      <c r="B571" t="s">
-        <v>1137</v>
       </c>
       <c r="D571" t="s">
         <v>9</v>
@@ -12184,10 +12373,10 @@
     </row>
     <row r="572" spans="1:4">
       <c r="A572" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B572" t="s">
         <v>1138</v>
-      </c>
-      <c r="B572" t="s">
-        <v>1139</v>
       </c>
       <c r="D572" t="s">
         <v>9</v>
@@ -12195,10 +12384,10 @@
     </row>
     <row r="573" spans="1:4">
       <c r="A573" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B573" t="s">
         <v>1140</v>
-      </c>
-      <c r="B573" t="s">
-        <v>1141</v>
       </c>
       <c r="D573" t="s">
         <v>9</v>
@@ -12206,10 +12395,10 @@
     </row>
     <row r="574" spans="1:4">
       <c r="A574" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B574" t="s">
         <v>1142</v>
-      </c>
-      <c r="B574" t="s">
-        <v>1143</v>
       </c>
       <c r="D574" t="s">
         <v>9</v>
@@ -12217,10 +12406,10 @@
     </row>
     <row r="575" spans="1:4">
       <c r="A575" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B575" t="s">
         <v>1144</v>
-      </c>
-      <c r="B575" t="s">
-        <v>1145</v>
       </c>
       <c r="D575" t="s">
         <v>9</v>
@@ -12228,10 +12417,10 @@
     </row>
     <row r="576" spans="1:4">
       <c r="A576" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B576" t="s">
         <v>1146</v>
-      </c>
-      <c r="B576" t="s">
-        <v>1147</v>
       </c>
       <c r="D576" t="s">
         <v>9</v>
@@ -12239,10 +12428,10 @@
     </row>
     <row r="577" spans="1:4">
       <c r="A577" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B577" t="s">
         <v>1148</v>
-      </c>
-      <c r="B577" t="s">
-        <v>1149</v>
       </c>
       <c r="D577" t="s">
         <v>9</v>
@@ -12250,10 +12439,10 @@
     </row>
     <row r="578" spans="1:4">
       <c r="A578" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B578" t="s">
         <v>1150</v>
-      </c>
-      <c r="B578" t="s">
-        <v>1151</v>
       </c>
       <c r="D578" t="s">
         <v>9</v>
@@ -12261,10 +12450,10 @@
     </row>
     <row r="579" spans="1:4">
       <c r="A579" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B579" t="s">
         <v>1152</v>
-      </c>
-      <c r="B579" t="s">
-        <v>1153</v>
       </c>
       <c r="D579" t="s">
         <v>9</v>
@@ -12272,10 +12461,10 @@
     </row>
     <row r="580" spans="1:4">
       <c r="A580" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B580" t="s">
         <v>1154</v>
-      </c>
-      <c r="B580" t="s">
-        <v>1155</v>
       </c>
       <c r="D580" t="s">
         <v>9</v>
@@ -12283,10 +12472,10 @@
     </row>
     <row r="581" spans="1:4">
       <c r="A581" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B581" t="s">
         <v>1156</v>
-      </c>
-      <c r="B581" t="s">
-        <v>1157</v>
       </c>
       <c r="D581" t="s">
         <v>9</v>
@@ -12294,10 +12483,10 @@
     </row>
     <row r="582" spans="1:4">
       <c r="A582" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B582" t="s">
         <v>1158</v>
-      </c>
-      <c r="B582" t="s">
-        <v>1159</v>
       </c>
       <c r="D582" t="s">
         <v>9</v>
@@ -12305,10 +12494,10 @@
     </row>
     <row r="583" spans="1:4">
       <c r="A583" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B583" t="s">
         <v>1160</v>
-      </c>
-      <c r="B583" t="s">
-        <v>1161</v>
       </c>
       <c r="D583" t="s">
         <v>9</v>
@@ -12316,10 +12505,10 @@
     </row>
     <row r="584" spans="1:4">
       <c r="A584" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B584" t="s">
         <v>1162</v>
-      </c>
-      <c r="B584" t="s">
-        <v>1163</v>
       </c>
       <c r="D584" t="s">
         <v>9</v>
@@ -12327,10 +12516,10 @@
     </row>
     <row r="585" spans="1:4">
       <c r="A585" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B585" t="s">
         <v>1164</v>
-      </c>
-      <c r="B585" t="s">
-        <v>1165</v>
       </c>
       <c r="D585" t="s">
         <v>9</v>
@@ -12338,10 +12527,10 @@
     </row>
     <row r="586" spans="1:4">
       <c r="A586" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B586" t="s">
         <v>1166</v>
-      </c>
-      <c r="B586" t="s">
-        <v>1167</v>
       </c>
       <c r="D586" t="s">
         <v>9</v>
@@ -12349,10 +12538,10 @@
     </row>
     <row r="587" spans="1:4">
       <c r="A587" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B587" t="s">
         <v>1168</v>
-      </c>
-      <c r="B587" t="s">
-        <v>1169</v>
       </c>
       <c r="D587" t="s">
         <v>9</v>
@@ -12360,10 +12549,10 @@
     </row>
     <row r="588" spans="1:4">
       <c r="A588" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B588" t="s">
         <v>1170</v>
-      </c>
-      <c r="B588" t="s">
-        <v>1171</v>
       </c>
       <c r="D588" t="s">
         <v>9</v>
@@ -12371,10 +12560,10 @@
     </row>
     <row r="589" spans="1:4">
       <c r="A589" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B589" t="s">
         <v>1172</v>
-      </c>
-      <c r="B589" t="s">
-        <v>1173</v>
       </c>
       <c r="D589" t="s">
         <v>9</v>
@@ -12382,10 +12571,10 @@
     </row>
     <row r="590" spans="1:4">
       <c r="A590" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B590" t="s">
         <v>1174</v>
-      </c>
-      <c r="B590" t="s">
-        <v>1175</v>
       </c>
       <c r="D590" t="s">
         <v>9</v>
@@ -12393,10 +12582,10 @@
     </row>
     <row r="591" spans="1:4">
       <c r="A591" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B591" t="s">
         <v>1176</v>
-      </c>
-      <c r="B591" t="s">
-        <v>1177</v>
       </c>
       <c r="D591" t="s">
         <v>9</v>
@@ -12404,10 +12593,10 @@
     </row>
     <row r="592" spans="1:4">
       <c r="A592" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B592" t="s">
         <v>1178</v>
-      </c>
-      <c r="B592" t="s">
-        <v>1179</v>
       </c>
       <c r="D592" t="s">
         <v>9</v>
@@ -12415,10 +12604,10 @@
     </row>
     <row r="593" spans="1:4">
       <c r="A593" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B593" t="s">
         <v>1180</v>
-      </c>
-      <c r="B593" t="s">
-        <v>1181</v>
       </c>
       <c r="D593" t="s">
         <v>9</v>
@@ -12426,10 +12615,10 @@
     </row>
     <row r="594" spans="1:4">
       <c r="A594" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B594" t="s">
         <v>1182</v>
-      </c>
-      <c r="B594" t="s">
-        <v>1183</v>
       </c>
       <c r="D594" t="s">
         <v>9</v>
@@ -12437,10 +12626,10 @@
     </row>
     <row r="595" spans="1:4">
       <c r="A595" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B595" t="s">
         <v>1184</v>
-      </c>
-      <c r="B595" t="s">
-        <v>1185</v>
       </c>
       <c r="D595" t="s">
         <v>9</v>
@@ -12448,10 +12637,10 @@
     </row>
     <row r="596" spans="1:4">
       <c r="A596" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B596" t="s">
         <v>1186</v>
-      </c>
-      <c r="B596" t="s">
-        <v>1187</v>
       </c>
       <c r="D596" t="s">
         <v>9</v>
@@ -12459,10 +12648,10 @@
     </row>
     <row r="597" spans="1:4">
       <c r="A597" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B597" t="s">
         <v>1188</v>
-      </c>
-      <c r="B597" t="s">
-        <v>1189</v>
       </c>
       <c r="D597" t="s">
         <v>9</v>
@@ -12470,10 +12659,10 @@
     </row>
     <row r="598" spans="1:4">
       <c r="A598" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B598" t="s">
         <v>1190</v>
-      </c>
-      <c r="B598" t="s">
-        <v>1191</v>
       </c>
       <c r="D598" t="s">
         <v>9</v>
@@ -12481,10 +12670,10 @@
     </row>
     <row r="599" spans="1:4">
       <c r="A599" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B599" t="s">
         <v>1192</v>
-      </c>
-      <c r="B599" t="s">
-        <v>1193</v>
       </c>
       <c r="D599" t="s">
         <v>9</v>
@@ -12492,10 +12681,10 @@
     </row>
     <row r="600" spans="1:4">
       <c r="A600" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B600" t="s">
         <v>1194</v>
-      </c>
-      <c r="B600" t="s">
-        <v>1195</v>
       </c>
       <c r="D600" t="s">
         <v>9</v>
@@ -12503,10 +12692,10 @@
     </row>
     <row r="601" spans="1:4">
       <c r="A601" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B601" t="s">
         <v>1196</v>
-      </c>
-      <c r="B601" t="s">
-        <v>1197</v>
       </c>
       <c r="D601" t="s">
         <v>9</v>
@@ -12514,10 +12703,10 @@
     </row>
     <row r="602" spans="1:4">
       <c r="A602" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B602" t="s">
         <v>1198</v>
-      </c>
-      <c r="B602" t="s">
-        <v>1199</v>
       </c>
       <c r="D602" t="s">
         <v>9</v>
@@ -12525,10 +12714,10 @@
     </row>
     <row r="603" spans="1:4">
       <c r="A603" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B603" t="s">
         <v>1200</v>
-      </c>
-      <c r="B603" t="s">
-        <v>1201</v>
       </c>
       <c r="D603" t="s">
         <v>9</v>
@@ -12536,10 +12725,10 @@
     </row>
     <row r="604" spans="1:4">
       <c r="A604" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B604" t="s">
         <v>1202</v>
-      </c>
-      <c r="B604" t="s">
-        <v>1203</v>
       </c>
       <c r="D604" t="s">
         <v>9</v>
@@ -12547,10 +12736,10 @@
     </row>
     <row r="605" spans="1:4">
       <c r="A605" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B605" t="s">
         <v>1204</v>
-      </c>
-      <c r="B605" t="s">
-        <v>1205</v>
       </c>
       <c r="D605" t="s">
         <v>9</v>
@@ -12558,10 +12747,10 @@
     </row>
     <row r="606" spans="1:4">
       <c r="A606" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B606" t="s">
         <v>1206</v>
-      </c>
-      <c r="B606" t="s">
-        <v>1207</v>
       </c>
       <c r="D606" t="s">
         <v>9</v>
@@ -12569,10 +12758,10 @@
     </row>
     <row r="607" spans="1:4">
       <c r="A607" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B607" t="s">
         <v>1208</v>
-      </c>
-      <c r="B607" t="s">
-        <v>1209</v>
       </c>
       <c r="D607" t="s">
         <v>9</v>
@@ -12580,10 +12769,10 @@
     </row>
     <row r="608" spans="1:4">
       <c r="A608" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B608" t="s">
         <v>1210</v>
-      </c>
-      <c r="B608" t="s">
-        <v>1211</v>
       </c>
       <c r="D608" t="s">
         <v>9</v>
@@ -12591,10 +12780,10 @@
     </row>
     <row r="609" spans="1:4">
       <c r="A609" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B609" t="s">
         <v>1212</v>
-      </c>
-      <c r="B609" t="s">
-        <v>1213</v>
       </c>
       <c r="D609" t="s">
         <v>9</v>
@@ -12602,10 +12791,10 @@
     </row>
     <row r="610" spans="1:4">
       <c r="A610" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B610" t="s">
         <v>1214</v>
-      </c>
-      <c r="B610" t="s">
-        <v>1215</v>
       </c>
       <c r="D610" t="s">
         <v>9</v>
@@ -12613,10 +12802,10 @@
     </row>
     <row r="611" spans="1:4">
       <c r="A611" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B611" t="s">
         <v>1216</v>
-      </c>
-      <c r="B611" t="s">
-        <v>1217</v>
       </c>
       <c r="D611" t="s">
         <v>9</v>
@@ -12624,10 +12813,10 @@
     </row>
     <row r="612" spans="1:4">
       <c r="A612" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B612" t="s">
         <v>1218</v>
-      </c>
-      <c r="B612" t="s">
-        <v>1219</v>
       </c>
       <c r="D612" t="s">
         <v>9</v>
@@ -12635,10 +12824,10 @@
     </row>
     <row r="613" spans="1:4">
       <c r="A613" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B613" t="s">
         <v>1220</v>
-      </c>
-      <c r="B613" t="s">
-        <v>1221</v>
       </c>
       <c r="D613" t="s">
         <v>9</v>
@@ -12646,10 +12835,10 @@
     </row>
     <row r="614" spans="1:4">
       <c r="A614" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B614" t="s">
         <v>1222</v>
-      </c>
-      <c r="B614" t="s">
-        <v>1221</v>
       </c>
       <c r="D614" t="s">
         <v>9</v>
@@ -12726,7 +12915,7 @@
         <v>1235</v>
       </c>
       <c r="B621" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="D621" t="s">
         <v>9</v>
@@ -12734,10 +12923,10 @@
     </row>
     <row r="622" spans="1:4">
       <c r="A622" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="B622" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="D622" t="s">
         <v>9</v>
@@ -12745,10 +12934,10 @@
     </row>
     <row r="623" spans="1:4">
       <c r="A623" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="B623" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="D623" t="s">
         <v>9</v>
@@ -12756,10 +12945,10 @@
     </row>
     <row r="624" spans="1:4">
       <c r="A624" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="B624" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="D624" t="s">
         <v>9</v>
@@ -12767,10 +12956,10 @@
     </row>
     <row r="625" spans="1:4">
       <c r="A625" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B625" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="D625" t="s">
         <v>9</v>
@@ -12778,10 +12967,10 @@
     </row>
     <row r="626" spans="1:4">
       <c r="A626" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B626" t="s">
-        <v>1243</v>
+        <v>1246</v>
       </c>
       <c r="D626" t="s">
         <v>9</v>
@@ -12789,10 +12978,10 @@
     </row>
     <row r="627" spans="1:4">
       <c r="A627" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="B627" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="D627" t="s">
         <v>9</v>
@@ -12800,10 +12989,10 @@
     </row>
     <row r="628" spans="1:4">
       <c r="A628" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="B628" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="D628" t="s">
         <v>9</v>
@@ -12811,10 +13000,10 @@
     </row>
     <row r="629" spans="1:4">
       <c r="A629" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="B629" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="D629" t="s">
         <v>9</v>
@@ -12822,10 +13011,10 @@
     </row>
     <row r="630" spans="1:4">
       <c r="A630" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="B630" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="D630" t="s">
         <v>9</v>
@@ -12833,10 +13022,10 @@
     </row>
     <row r="631" spans="1:4">
       <c r="A631" t="s">
-        <v>1252</v>
+        <v>1255</v>
       </c>
       <c r="B631" t="s">
-        <v>1253</v>
+        <v>1256</v>
       </c>
       <c r="D631" t="s">
         <v>9</v>
@@ -12844,10 +13033,10 @@
     </row>
     <row r="632" spans="1:4">
       <c r="A632" t="s">
-        <v>1254</v>
+        <v>1257</v>
       </c>
       <c r="B632" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
       <c r="D632" t="s">
         <v>9</v>
@@ -12855,10 +13044,10 @@
     </row>
     <row r="633" spans="1:4">
       <c r="A633" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="B633" t="s">
-        <v>1257</v>
+        <v>1260</v>
       </c>
       <c r="D633" t="s">
         <v>9</v>
@@ -12866,10 +13055,10 @@
     </row>
     <row r="634" spans="1:4">
       <c r="A634" t="s">
-        <v>1258</v>
+        <v>1261</v>
       </c>
       <c r="B634" t="s">
-        <v>1259</v>
+        <v>1262</v>
       </c>
       <c r="D634" t="s">
         <v>9</v>
@@ -12877,10 +13066,10 @@
     </row>
     <row r="635" spans="1:4">
       <c r="A635" t="s">
-        <v>1260</v>
+        <v>1263</v>
       </c>
       <c r="B635" t="s">
-        <v>1261</v>
+        <v>1264</v>
       </c>
       <c r="D635" t="s">
         <v>9</v>
@@ -12888,10 +13077,10 @@
     </row>
     <row r="636" spans="1:4">
       <c r="A636" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="B636" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
       <c r="D636" t="s">
         <v>9</v>
@@ -12899,10 +13088,10 @@
     </row>
     <row r="637" spans="1:4">
       <c r="A637" t="s">
-        <v>1264</v>
+        <v>1267</v>
       </c>
       <c r="B637" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="D637" t="s">
         <v>9</v>
@@ -12910,10 +13099,10 @@
     </row>
     <row r="638" spans="1:4">
       <c r="A638" t="s">
-        <v>1266</v>
+        <v>1269</v>
       </c>
       <c r="B638" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="D638" t="s">
         <v>9</v>
@@ -12921,10 +13110,10 @@
     </row>
     <row r="639" spans="1:4">
       <c r="A639" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="B639" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="D639" t="s">
         <v>9</v>
@@ -12932,10 +13121,10 @@
     </row>
     <row r="640" spans="1:4">
       <c r="A640" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="B640" t="s">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="D640" t="s">
         <v>9</v>
@@ -12943,10 +13132,10 @@
     </row>
     <row r="641" spans="1:4">
       <c r="A641" t="s">
-        <v>1272</v>
+        <v>1275</v>
       </c>
       <c r="B641" t="s">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="D641" t="s">
         <v>9</v>
@@ -12954,10 +13143,10 @@
     </row>
     <row r="642" spans="1:4">
       <c r="A642" t="s">
-        <v>1274</v>
+        <v>1277</v>
       </c>
       <c r="B642" t="s">
-        <v>1273</v>
+        <v>1278</v>
       </c>
       <c r="D642" t="s">
         <v>9</v>
@@ -12965,10 +13154,10 @@
     </row>
     <row r="643" spans="1:4">
       <c r="A643" t="s">
-        <v>1275</v>
+        <v>1279</v>
       </c>
       <c r="B643" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="D643" t="s">
         <v>9</v>
@@ -12976,10 +13165,10 @@
     </row>
     <row r="644" spans="1:4">
       <c r="A644" t="s">
-        <v>1277</v>
+        <v>1281</v>
       </c>
       <c r="B644" t="s">
-        <v>1278</v>
+        <v>1282</v>
       </c>
       <c r="D644" t="s">
         <v>9</v>
@@ -12987,10 +13176,10 @@
     </row>
     <row r="645" spans="1:4">
       <c r="A645" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
       <c r="B645" t="s">
-        <v>1280</v>
+        <v>1284</v>
       </c>
       <c r="D645" t="s">
         <v>9</v>
@@ -12998,10 +13187,10 @@
     </row>
     <row r="646" spans="1:4">
       <c r="A646" t="s">
-        <v>1281</v>
+        <v>1285</v>
       </c>
       <c r="B646" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="D646" t="s">
         <v>9</v>
@@ -13009,10 +13198,10 @@
     </row>
     <row r="647" spans="1:4">
       <c r="A647" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="B647" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="D647" t="s">
         <v>9</v>
@@ -13020,10 +13209,10 @@
     </row>
     <row r="648" spans="1:4">
       <c r="A648" t="s">
-        <v>1285</v>
+        <v>1288</v>
       </c>
       <c r="B648" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="D648" t="s">
         <v>9</v>
@@ -13031,10 +13220,10 @@
     </row>
     <row r="649" spans="1:4">
       <c r="A649" t="s">
-        <v>1287</v>
+        <v>1290</v>
       </c>
       <c r="B649" t="s">
-        <v>1288</v>
+        <v>1291</v>
       </c>
       <c r="D649" t="s">
         <v>9</v>
@@ -13042,10 +13231,10 @@
     </row>
     <row r="650" spans="1:4">
       <c r="A650" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="B650" t="s">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="D650" t="s">
         <v>9</v>
@@ -13053,10 +13242,10 @@
     </row>
     <row r="651" spans="1:4">
       <c r="A651" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="B651" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="D651" t="s">
         <v>9</v>
@@ -13064,10 +13253,10 @@
     </row>
     <row r="652" spans="1:4">
       <c r="A652" t="s">
-        <v>1293</v>
+        <v>1296</v>
       </c>
       <c r="B652" t="s">
-        <v>1294</v>
+        <v>1297</v>
       </c>
       <c r="D652" t="s">
         <v>9</v>
@@ -13075,10 +13264,10 @@
     </row>
     <row r="653" spans="1:4">
       <c r="A653" t="s">
-        <v>1295</v>
+        <v>1298</v>
       </c>
       <c r="B653" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="D653" t="s">
         <v>9</v>
@@ -13086,10 +13275,10 @@
     </row>
     <row r="654" spans="1:4">
       <c r="A654" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="B654" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="D654" t="s">
         <v>9</v>
@@ -13097,10 +13286,10 @@
     </row>
     <row r="655" spans="1:4">
       <c r="A655" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="B655" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="D655" t="s">
         <v>9</v>
@@ -13108,10 +13297,10 @@
     </row>
     <row r="656" spans="1:4">
       <c r="A656" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="B656" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="D656" t="s">
         <v>9</v>
@@ -13119,10 +13308,10 @@
     </row>
     <row r="657" spans="1:4">
       <c r="A657" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="B657" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="D657" t="s">
         <v>9</v>
@@ -13130,10 +13319,10 @@
     </row>
     <row r="658" spans="1:4">
       <c r="A658" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="B658" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="D658" t="s">
         <v>9</v>
@@ -13141,10 +13330,10 @@
     </row>
     <row r="659" spans="1:4">
       <c r="A659" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="B659" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="D659" t="s">
         <v>9</v>
@@ -13152,10 +13341,10 @@
     </row>
     <row r="660" spans="1:4">
       <c r="A660" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="B660" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="D660" t="s">
         <v>9</v>
@@ -13163,10 +13352,10 @@
     </row>
     <row r="661" spans="1:4">
       <c r="A661" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="B661" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="D661" t="s">
         <v>9</v>
@@ -13174,7 +13363,7 @@
     </row>
     <row r="662" spans="1:4">
       <c r="A662" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="B662" t="s">
         <v>1313</v>
@@ -13185,10 +13374,10 @@
     </row>
     <row r="663" spans="1:4">
       <c r="A663" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="B663" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="D663" t="s">
         <v>9</v>
@@ -13196,10 +13385,10 @@
     </row>
     <row r="664" spans="1:4">
       <c r="A664" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="B664" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="D664" t="s">
         <v>9</v>
@@ -13207,10 +13396,10 @@
     </row>
     <row r="665" spans="1:4">
       <c r="A665" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B665" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="D665" t="s">
         <v>9</v>
@@ -13218,10 +13407,10 @@
     </row>
     <row r="666" spans="1:4">
       <c r="A666" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="B666" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="D666" t="s">
         <v>9</v>
@@ -13229,10 +13418,10 @@
     </row>
     <row r="667" spans="1:4">
       <c r="A667" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B667" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="D667" t="s">
         <v>9</v>
@@ -13240,10 +13429,10 @@
     </row>
     <row r="668" spans="1:4">
       <c r="A668" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B668" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="D668" t="s">
         <v>9</v>
@@ -13251,10 +13440,10 @@
     </row>
     <row r="669" spans="1:4">
       <c r="A669" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="B669" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="D669" t="s">
         <v>9</v>
@@ -13262,10 +13451,10 @@
     </row>
     <row r="670" spans="1:4">
       <c r="A670" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B670" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="D670" t="s">
         <v>9</v>
@@ -13273,10 +13462,10 @@
     </row>
     <row r="671" spans="1:4">
       <c r="A671" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="B671" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="D671" t="s">
         <v>9</v>
@@ -13284,10 +13473,10 @@
     </row>
     <row r="672" spans="1:4">
       <c r="A672" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="B672" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="D672" t="s">
         <v>9</v>
@@ -13295,10 +13484,10 @@
     </row>
     <row r="673" spans="1:4">
       <c r="A673" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="B673" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="D673" t="s">
         <v>9</v>
@@ -13306,10 +13495,10 @@
     </row>
     <row r="674" spans="1:4">
       <c r="A674" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B674" t="s">
         <v>1336</v>
-      </c>
-      <c r="B674" t="s">
-        <v>1337</v>
       </c>
       <c r="D674" t="s">
         <v>9</v>
@@ -13364,7 +13553,7 @@
         <v>1346</v>
       </c>
       <c r="B679" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="D679" t="s">
         <v>9</v>
@@ -13372,10 +13561,10 @@
     </row>
     <row r="680" spans="1:4">
       <c r="A680" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="B680" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="D680" t="s">
         <v>9</v>
@@ -13383,10 +13572,10 @@
     </row>
     <row r="681" spans="1:4">
       <c r="A681" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B681" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="D681" t="s">
         <v>9</v>
@@ -13394,10 +13583,10 @@
     </row>
     <row r="682" spans="1:4">
       <c r="A682" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="B682" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="D682" t="s">
         <v>9</v>
@@ -13405,10 +13594,10 @@
     </row>
     <row r="683" spans="1:4">
       <c r="A683" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B683" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="D683" t="s">
         <v>9</v>
@@ -13416,10 +13605,10 @@
     </row>
     <row r="684" spans="1:4">
       <c r="A684" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="B684" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="D684" t="s">
         <v>9</v>
@@ -13427,10 +13616,10 @@
     </row>
     <row r="685" spans="1:4">
       <c r="A685" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="B685" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="D685" t="s">
         <v>9</v>
@@ -13438,10 +13627,10 @@
     </row>
     <row r="686" spans="1:4">
       <c r="A686" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="B686" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="D686" t="s">
         <v>9</v>
@@ -13449,10 +13638,10 @@
     </row>
     <row r="687" spans="1:4">
       <c r="A687" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B687" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="D687" t="s">
         <v>9</v>
@@ -13460,10 +13649,10 @@
     </row>
     <row r="688" spans="1:4">
       <c r="A688" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B688" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="D688" t="s">
         <v>9</v>
@@ -13471,10 +13660,10 @@
     </row>
     <row r="689" spans="1:4">
       <c r="A689" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B689" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="D689" t="s">
         <v>9</v>
@@ -13482,10 +13671,10 @@
     </row>
     <row r="690" spans="1:4">
       <c r="A690" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B690" t="s">
         <v>1367</v>
-      </c>
-      <c r="B690" t="s">
-        <v>1368</v>
       </c>
       <c r="D690" t="s">
         <v>9</v>
@@ -13518,7 +13707,7 @@
         <v>1373</v>
       </c>
       <c r="B693" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="D693" t="s">
         <v>9</v>
@@ -13526,10 +13715,10 @@
     </row>
     <row r="694" spans="1:4">
       <c r="A694" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="B694" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="D694" t="s">
         <v>9</v>
@@ -13537,10 +13726,10 @@
     </row>
     <row r="695" spans="1:4">
       <c r="A695" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="B695" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="D695" t="s">
         <v>9</v>
@@ -13548,10 +13737,10 @@
     </row>
     <row r="696" spans="1:4">
       <c r="A696" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="B696" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="D696" t="s">
         <v>9</v>
@@ -13559,10 +13748,10 @@
     </row>
     <row r="697" spans="1:4">
       <c r="A697" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="B697" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="D697" t="s">
         <v>9</v>
@@ -13570,10 +13759,10 @@
     </row>
     <row r="698" spans="1:4">
       <c r="A698" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="B698" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="D698" t="s">
         <v>9</v>
@@ -13581,10 +13770,10 @@
     </row>
     <row r="699" spans="1:4">
       <c r="A699" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="B699" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="D699" t="s">
         <v>9</v>
@@ -13592,10 +13781,10 @@
     </row>
     <row r="700" spans="1:4">
       <c r="A700" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="B700" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="D700" t="s">
         <v>9</v>
@@ -13603,10 +13792,10 @@
     </row>
     <row r="701" spans="1:4">
       <c r="A701" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="B701" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="D701" t="s">
         <v>9</v>
@@ -13614,10 +13803,10 @@
     </row>
     <row r="702" spans="1:4">
       <c r="A702" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="B702" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="D702" t="s">
         <v>9</v>
@@ -13625,10 +13814,10 @@
     </row>
     <row r="703" spans="1:4">
       <c r="A703" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="B703" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="D703" t="s">
         <v>9</v>
@@ -13636,10 +13825,10 @@
     </row>
     <row r="704" spans="1:4">
       <c r="A704" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="B704" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="D704" t="s">
         <v>9</v>
@@ -13647,10 +13836,10 @@
     </row>
     <row r="705" spans="1:4">
       <c r="A705" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="B705" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="D705" t="s">
         <v>9</v>
@@ -13658,10 +13847,10 @@
     </row>
     <row r="706" spans="1:4">
       <c r="A706" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="B706" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="D706" t="s">
         <v>9</v>
@@ -13669,10 +13858,10 @@
     </row>
     <row r="707" spans="1:4">
       <c r="A707" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="B707" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="D707" t="s">
         <v>9</v>
@@ -13680,10 +13869,10 @@
     </row>
     <row r="708" spans="1:4">
       <c r="A708" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="B708" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="D708" t="s">
         <v>9</v>
@@ -13691,10 +13880,10 @@
     </row>
     <row r="709" spans="1:4">
       <c r="A709" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="B709" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="D709" t="s">
         <v>9</v>
@@ -13702,10 +13891,10 @@
     </row>
     <row r="710" spans="1:4">
       <c r="A710" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="B710" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="D710" t="s">
         <v>9</v>
@@ -13713,10 +13902,10 @@
     </row>
     <row r="711" spans="1:4">
       <c r="A711" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B711" t="s">
         <v>1408</v>
-      </c>
-      <c r="B711" t="s">
-        <v>1409</v>
       </c>
       <c r="D711" t="s">
         <v>9</v>
@@ -13848,7 +14037,7 @@
         <v>1432</v>
       </c>
       <c r="B723" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="D723" t="s">
         <v>9</v>
@@ -13856,10 +14045,10 @@
     </row>
     <row r="724" spans="1:4">
       <c r="A724" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="B724" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="D724" t="s">
         <v>9</v>
@@ -13867,10 +14056,10 @@
     </row>
     <row r="725" spans="1:4">
       <c r="A725" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B725" t="s">
         <v>1435</v>
-      </c>
-      <c r="B725" t="s">
-        <v>1436</v>
       </c>
       <c r="D725" t="s">
         <v>9</v>
@@ -13936,7 +14125,7 @@
         <v>1447</v>
       </c>
       <c r="B731" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="D731" t="s">
         <v>9</v>
@@ -13944,10 +14133,10 @@
     </row>
     <row r="732" spans="1:4">
       <c r="A732" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="B732" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="D732" t="s">
         <v>9</v>
@@ -13955,10 +14144,10 @@
     </row>
     <row r="733" spans="1:4">
       <c r="A733" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="B733" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="D733" t="s">
         <v>9</v>
@@ -13966,10 +14155,10 @@
     </row>
     <row r="734" spans="1:4">
       <c r="A734" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="B734" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="D734" t="s">
         <v>9</v>
@@ -13977,10 +14166,10 @@
     </row>
     <row r="735" spans="1:4">
       <c r="A735" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="B735" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="D735" t="s">
         <v>9</v>
@@ -13988,10 +14177,10 @@
     </row>
     <row r="736" spans="1:4">
       <c r="A736" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="B736" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="D736" t="s">
         <v>9</v>
@@ -13999,10 +14188,10 @@
     </row>
     <row r="737" spans="1:4">
       <c r="A737" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="B737" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="D737" t="s">
         <v>9</v>
@@ -14010,10 +14199,10 @@
     </row>
     <row r="738" spans="1:4">
       <c r="A738" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="B738" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="D738" t="s">
         <v>9</v>
@@ -14021,10 +14210,10 @@
     </row>
     <row r="739" spans="1:4">
       <c r="A739" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="B739" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="D739" t="s">
         <v>9</v>
@@ -14032,10 +14221,10 @@
     </row>
     <row r="740" spans="1:4">
       <c r="A740" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="B740" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="D740" t="s">
         <v>9</v>
@@ -14043,10 +14232,10 @@
     </row>
     <row r="741" spans="1:4">
       <c r="A741" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="B741" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="D741" t="s">
         <v>9</v>
@@ -14054,10 +14243,10 @@
     </row>
     <row r="742" spans="1:4">
       <c r="A742" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="B742" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="D742" t="s">
         <v>9</v>
@@ -14065,10 +14254,10 @@
     </row>
     <row r="743" spans="1:4">
       <c r="A743" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="B743" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="D743" t="s">
         <v>9</v>
@@ -14076,10 +14265,10 @@
     </row>
     <row r="744" spans="1:4">
       <c r="A744" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="B744" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="D744" t="s">
         <v>9</v>
@@ -14087,10 +14276,10 @@
     </row>
     <row r="745" spans="1:4">
       <c r="A745" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="B745" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="D745" t="s">
         <v>9</v>
@@ -14098,10 +14287,10 @@
     </row>
     <row r="746" spans="1:4">
       <c r="A746" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="B746" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="D746" t="s">
         <v>9</v>
@@ -14109,10 +14298,10 @@
     </row>
     <row r="747" spans="1:4">
       <c r="A747" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="B747" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="D747" t="s">
         <v>9</v>
@@ -14120,10 +14309,10 @@
     </row>
     <row r="748" spans="1:4">
       <c r="A748" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="B748" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="D748" t="s">
         <v>9</v>
@@ -14131,10 +14320,10 @@
     </row>
     <row r="749" spans="1:4">
       <c r="A749" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="B749" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="D749" t="s">
         <v>9</v>
@@ -14142,10 +14331,10 @@
     </row>
     <row r="750" spans="1:4">
       <c r="A750" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="B750" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="D750" t="s">
         <v>9</v>
@@ -14153,10 +14342,10 @@
     </row>
     <row r="751" spans="1:4">
       <c r="A751" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="B751" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="D751" t="s">
         <v>9</v>
@@ -14164,10 +14353,10 @@
     </row>
     <row r="752" spans="1:4">
       <c r="A752" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="B752" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="D752" t="s">
         <v>9</v>
@@ -14175,10 +14364,10 @@
     </row>
     <row r="753" spans="1:4">
       <c r="A753" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="B753" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="D753" t="s">
         <v>9</v>
@@ -14186,10 +14375,10 @@
     </row>
     <row r="754" spans="1:4">
       <c r="A754" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="B754" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="D754" t="s">
         <v>9</v>
@@ -14197,10 +14386,10 @@
     </row>
     <row r="755" spans="1:4">
       <c r="A755" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B755" t="s">
         <v>1494</v>
-      </c>
-      <c r="B755" t="s">
-        <v>1495</v>
       </c>
       <c r="D755" t="s">
         <v>9</v>
@@ -14288,7 +14477,7 @@
         <v>1510</v>
       </c>
       <c r="B763" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="D763" t="s">
         <v>9</v>
@@ -14296,10 +14485,10 @@
     </row>
     <row r="764" spans="1:4">
       <c r="A764" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B764" t="s">
         <v>1512</v>
-      </c>
-      <c r="B764" t="s">
-        <v>1513</v>
       </c>
       <c r="D764" t="s">
         <v>9</v>
@@ -14307,10 +14496,10 @@
     </row>
     <row r="765" spans="1:4">
       <c r="A765" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B765" t="s">
         <v>1514</v>
-      </c>
-      <c r="B765" t="s">
-        <v>1513</v>
       </c>
       <c r="D765" t="s">
         <v>9</v>
@@ -14519,7 +14708,7 @@
         <v>1551</v>
       </c>
       <c r="B784" t="s">
-        <v>1542</v>
+        <v>1552</v>
       </c>
       <c r="D784" t="s">
         <v>9</v>
@@ -14527,10 +14716,10 @@
     </row>
     <row r="785" spans="1:4">
       <c r="A785" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="B785" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="D785" t="s">
         <v>9</v>
@@ -14538,10 +14727,10 @@
     </row>
     <row r="786" spans="1:4">
       <c r="A786" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="B786" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="D786" t="s">
         <v>9</v>
@@ -14549,10 +14738,10 @@
     </row>
     <row r="787" spans="1:4">
       <c r="A787" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="B787" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="D787" t="s">
         <v>9</v>
@@ -14560,10 +14749,10 @@
     </row>
     <row r="788" spans="1:4">
       <c r="A788" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="B788" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="D788" t="s">
         <v>9</v>
@@ -14571,10 +14760,10 @@
     </row>
     <row r="789" spans="1:4">
       <c r="A789" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="B789" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="D789" t="s">
         <v>9</v>
@@ -14582,10 +14771,10 @@
     </row>
     <row r="790" spans="1:4">
       <c r="A790" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B790" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="D790" t="s">
         <v>9</v>
@@ -14593,10 +14782,10 @@
     </row>
     <row r="791" spans="1:4">
       <c r="A791" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="B791" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="D791" t="s">
         <v>9</v>
@@ -14604,10 +14793,10 @@
     </row>
     <row r="792" spans="1:4">
       <c r="A792" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B792" t="s">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="D792" t="s">
         <v>9</v>
@@ -14615,10 +14804,10 @@
     </row>
     <row r="793" spans="1:4">
       <c r="A793" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="B793" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="D793" t="s">
         <v>9</v>
@@ -14626,10 +14815,10 @@
     </row>
     <row r="794" spans="1:4">
       <c r="A794" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="B794" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="D794" t="s">
         <v>9</v>
@@ -14637,10 +14826,10 @@
     </row>
     <row r="795" spans="1:4">
       <c r="A795" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="B795" t="s">
-        <v>1561</v>
+        <v>1574</v>
       </c>
       <c r="D795" t="s">
         <v>9</v>
@@ -14648,10 +14837,10 @@
     </row>
     <row r="796" spans="1:4">
       <c r="A796" t="s">
-        <v>1572</v>
+        <v>1575</v>
       </c>
       <c r="B796" t="s">
-        <v>1573</v>
+        <v>1576</v>
       </c>
       <c r="D796" t="s">
         <v>9</v>
@@ -14659,10 +14848,10 @@
     </row>
     <row r="797" spans="1:4">
       <c r="A797" t="s">
-        <v>1574</v>
+        <v>1577</v>
       </c>
       <c r="B797" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="D797" t="s">
         <v>9</v>
@@ -14670,10 +14859,10 @@
     </row>
     <row r="798" spans="1:4">
       <c r="A798" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="B798" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="D798" t="s">
         <v>9</v>
@@ -14681,10 +14870,10 @@
     </row>
     <row r="799" spans="1:4">
       <c r="A799" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="B799" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="D799" t="s">
         <v>9</v>
@@ -14692,10 +14881,10 @@
     </row>
     <row r="800" spans="1:4">
       <c r="A800" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="B800" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="D800" t="s">
         <v>9</v>
@@ -14703,10 +14892,10 @@
     </row>
     <row r="801" spans="1:4">
       <c r="A801" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="B801" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="D801" t="s">
         <v>9</v>
@@ -14714,10 +14903,10 @@
     </row>
     <row r="802" spans="1:4">
       <c r="A802" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="B802" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
       <c r="D802" t="s">
         <v>9</v>
@@ -14725,10 +14914,10 @@
     </row>
     <row r="803" spans="1:4">
       <c r="A803" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="B803" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
       <c r="D803" t="s">
         <v>9</v>
@@ -14736,10 +14925,10 @@
     </row>
     <row r="804" spans="1:4">
       <c r="A804" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
       <c r="B804" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="D804" t="s">
         <v>9</v>
@@ -14747,10 +14936,10 @@
     </row>
     <row r="805" spans="1:4">
       <c r="A805" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
       <c r="B805" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="D805" t="s">
         <v>9</v>
@@ -14758,10 +14947,10 @@
     </row>
     <row r="806" spans="1:4">
       <c r="A806" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="B806" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="D806" t="s">
         <v>9</v>
@@ -14769,10 +14958,10 @@
     </row>
     <row r="807" spans="1:4">
       <c r="A807" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="B807" t="s">
-        <v>1595</v>
+        <v>1597</v>
       </c>
       <c r="D807" t="s">
         <v>9</v>
@@ -14780,10 +14969,10 @@
     </row>
     <row r="808" spans="1:4">
       <c r="A808" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="B808" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="D808" t="s">
         <v>9</v>
@@ -14791,10 +14980,10 @@
     </row>
     <row r="809" spans="1:4">
       <c r="A809" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="B809" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="D809" t="s">
         <v>9</v>
@@ -14802,10 +14991,10 @@
     </row>
     <row r="810" spans="1:4">
       <c r="A810" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="B810" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="D810" t="s">
         <v>9</v>
@@ -14813,10 +15002,10 @@
     </row>
     <row r="811" spans="1:4">
       <c r="A811" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="B811" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="D811" t="s">
         <v>9</v>
@@ -14824,10 +15013,10 @@
     </row>
     <row r="812" spans="1:4">
       <c r="A812" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="B812" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="D812" t="s">
         <v>9</v>
@@ -14835,10 +15024,10 @@
     </row>
     <row r="813" spans="1:4">
       <c r="A813" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="B813" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="D813" t="s">
         <v>9</v>
@@ -14846,10 +15035,10 @@
     </row>
     <row r="814" spans="1:4">
       <c r="A814" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="B814" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="D814" t="s">
         <v>9</v>
@@ -14857,10 +15046,10 @@
     </row>
     <row r="815" spans="1:4">
       <c r="A815" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="B815" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="D815" t="s">
         <v>9</v>
@@ -14868,10 +15057,10 @@
     </row>
     <row r="816" spans="1:4">
       <c r="A816" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="B816" t="s">
-        <v>1613</v>
+        <v>1605</v>
       </c>
       <c r="D816" t="s">
         <v>9</v>
@@ -14879,10 +15068,10 @@
     </row>
     <row r="817" spans="1:4">
       <c r="A817" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="B817" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="D817" t="s">
         <v>9</v>
@@ -14890,10 +15079,10 @@
     </row>
     <row r="818" spans="1:4">
       <c r="A818" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="B818" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="D818" t="s">
         <v>9</v>
@@ -14901,10 +15090,10 @@
     </row>
     <row r="819" spans="1:4">
       <c r="A819" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="B819" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="D819" t="s">
         <v>9</v>
@@ -14912,10 +15101,10 @@
     </row>
     <row r="820" spans="1:4">
       <c r="A820" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="B820" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="D820" t="s">
         <v>9</v>
@@ -14923,10 +15112,10 @@
     </row>
     <row r="821" spans="1:4">
       <c r="A821" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="B821" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="D821" t="s">
         <v>9</v>
@@ -14934,10 +15123,10 @@
     </row>
     <row r="822" spans="1:4">
       <c r="A822" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="B822" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="D822" t="s">
         <v>9</v>
@@ -14945,10 +15134,10 @@
     </row>
     <row r="823" spans="1:4">
       <c r="A823" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="B823" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="D823" t="s">
         <v>9</v>
@@ -14956,10 +15145,10 @@
     </row>
     <row r="824" spans="1:4">
       <c r="A824" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="B824" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="D824" t="s">
         <v>9</v>
@@ -14992,7 +15181,7 @@
         <v>1634</v>
       </c>
       <c r="B827" t="s">
-        <v>1591</v>
+        <v>1624</v>
       </c>
       <c r="D827" t="s">
         <v>9</v>
@@ -15113,7 +15302,7 @@
         <v>1655</v>
       </c>
       <c r="B838" t="s">
-        <v>1652</v>
+        <v>1656</v>
       </c>
       <c r="D838" t="s">
         <v>9</v>
@@ -15121,10 +15310,10 @@
     </row>
     <row r="839" spans="1:4">
       <c r="A839" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="B839" t="s">
-        <v>1654</v>
+        <v>1658</v>
       </c>
       <c r="D839" t="s">
         <v>9</v>
@@ -15132,10 +15321,10 @@
     </row>
     <row r="840" spans="1:4">
       <c r="A840" t="s">
-        <v>1657</v>
+        <v>1659</v>
       </c>
       <c r="B840" t="s">
-        <v>1658</v>
+        <v>1660</v>
       </c>
       <c r="D840" t="s">
         <v>9</v>
@@ -15143,10 +15332,10 @@
     </row>
     <row r="841" spans="1:4">
       <c r="A841" t="s">
-        <v>1659</v>
+        <v>1661</v>
       </c>
       <c r="B841" t="s">
-        <v>1660</v>
+        <v>1662</v>
       </c>
       <c r="D841" t="s">
         <v>9</v>
@@ -15154,10 +15343,10 @@
     </row>
     <row r="842" spans="1:4">
       <c r="A842" t="s">
-        <v>1661</v>
+        <v>1663</v>
       </c>
       <c r="B842" t="s">
-        <v>1662</v>
+        <v>1664</v>
       </c>
       <c r="D842" t="s">
         <v>9</v>
@@ -15165,10 +15354,10 @@
     </row>
     <row r="843" spans="1:4">
       <c r="A843" t="s">
-        <v>1663</v>
+        <v>1665</v>
       </c>
       <c r="B843" t="s">
-        <v>1664</v>
+        <v>1666</v>
       </c>
       <c r="D843" t="s">
         <v>9</v>
@@ -15176,10 +15365,10 @@
     </row>
     <row r="844" spans="1:4">
       <c r="A844" t="s">
-        <v>1665</v>
+        <v>1667</v>
       </c>
       <c r="B844" t="s">
-        <v>1664</v>
+        <v>1668</v>
       </c>
       <c r="D844" t="s">
         <v>9</v>
@@ -15187,10 +15376,10 @@
     </row>
     <row r="845" spans="1:4">
       <c r="A845" t="s">
-        <v>1666</v>
+        <v>1669</v>
       </c>
       <c r="B845" t="s">
-        <v>1667</v>
+        <v>1670</v>
       </c>
       <c r="D845" t="s">
         <v>9</v>
@@ -15198,10 +15387,10 @@
     </row>
     <row r="846" spans="1:4">
       <c r="A846" t="s">
-        <v>1668</v>
+        <v>1671</v>
       </c>
       <c r="B846" t="s">
-        <v>1669</v>
+        <v>1672</v>
       </c>
       <c r="D846" t="s">
         <v>9</v>
@@ -15209,10 +15398,10 @@
     </row>
     <row r="847" spans="1:4">
       <c r="A847" t="s">
-        <v>1670</v>
+        <v>1673</v>
       </c>
       <c r="B847" t="s">
-        <v>1671</v>
+        <v>1674</v>
       </c>
       <c r="D847" t="s">
         <v>9</v>
@@ -15220,10 +15409,10 @@
     </row>
     <row r="848" spans="1:4">
       <c r="A848" t="s">
-        <v>1672</v>
+        <v>1675</v>
       </c>
       <c r="B848" t="s">
-        <v>1673</v>
+        <v>1676</v>
       </c>
       <c r="D848" t="s">
         <v>9</v>
@@ -15231,10 +15420,10 @@
     </row>
     <row r="849" spans="1:4">
       <c r="A849" t="s">
-        <v>1674</v>
+        <v>1677</v>
       </c>
       <c r="B849" t="s">
-        <v>1675</v>
+        <v>1678</v>
       </c>
       <c r="D849" t="s">
         <v>9</v>
@@ -15242,10 +15431,10 @@
     </row>
     <row r="850" spans="1:4">
       <c r="A850" t="s">
-        <v>1676</v>
+        <v>1679</v>
       </c>
       <c r="B850" t="s">
-        <v>1677</v>
+        <v>1680</v>
       </c>
       <c r="D850" t="s">
         <v>9</v>
@@ -15253,10 +15442,10 @@
     </row>
     <row r="851" spans="1:4">
       <c r="A851" t="s">
-        <v>1678</v>
+        <v>1681</v>
       </c>
       <c r="B851" t="s">
-        <v>1677</v>
+        <v>1682</v>
       </c>
       <c r="D851" t="s">
         <v>9</v>
@@ -15264,10 +15453,10 @@
     </row>
     <row r="852" spans="1:4">
       <c r="A852" t="s">
-        <v>1679</v>
+        <v>1683</v>
       </c>
       <c r="B852" t="s">
-        <v>1680</v>
+        <v>1684</v>
       </c>
       <c r="D852" t="s">
         <v>9</v>
@@ -15275,10 +15464,10 @@
     </row>
     <row r="853" spans="1:4">
       <c r="A853" t="s">
-        <v>1681</v>
+        <v>1685</v>
       </c>
       <c r="B853" t="s">
-        <v>1682</v>
+        <v>1686</v>
       </c>
       <c r="D853" t="s">
         <v>9</v>
@@ -15286,10 +15475,10 @@
     </row>
     <row r="854" spans="1:4">
       <c r="A854" t="s">
-        <v>1683</v>
+        <v>1687</v>
       </c>
       <c r="B854" t="s">
-        <v>1684</v>
+        <v>1688</v>
       </c>
       <c r="D854" t="s">
         <v>9</v>
@@ -15297,10 +15486,10 @@
     </row>
     <row r="855" spans="1:4">
       <c r="A855" t="s">
-        <v>1685</v>
+        <v>1689</v>
       </c>
       <c r="B855" t="s">
-        <v>1686</v>
+        <v>1690</v>
       </c>
       <c r="D855" t="s">
         <v>9</v>
@@ -15308,10 +15497,10 @@
     </row>
     <row r="856" spans="1:4">
       <c r="A856" t="s">
-        <v>1687</v>
+        <v>1691</v>
       </c>
       <c r="B856" t="s">
-        <v>1688</v>
+        <v>1692</v>
       </c>
       <c r="D856" t="s">
         <v>9</v>
@@ -15319,10 +15508,10 @@
     </row>
     <row r="857" spans="1:4">
       <c r="A857" t="s">
-        <v>1689</v>
+        <v>1693</v>
       </c>
       <c r="B857" t="s">
-        <v>1688</v>
+        <v>1694</v>
       </c>
       <c r="D857" t="s">
         <v>9</v>
@@ -15330,10 +15519,10 @@
     </row>
     <row r="858" spans="1:4">
       <c r="A858" t="s">
-        <v>1690</v>
+        <v>1695</v>
       </c>
       <c r="B858" t="s">
-        <v>1691</v>
+        <v>1696</v>
       </c>
       <c r="D858" t="s">
         <v>9</v>
@@ -15341,10 +15530,10 @@
     </row>
     <row r="859" spans="1:4">
       <c r="A859" t="s">
-        <v>1692</v>
+        <v>1697</v>
       </c>
       <c r="B859" t="s">
-        <v>1693</v>
+        <v>1654</v>
       </c>
       <c r="D859" t="s">
         <v>9</v>
@@ -15352,10 +15541,10 @@
     </row>
     <row r="860" spans="1:4">
       <c r="A860" t="s">
-        <v>1694</v>
+        <v>1698</v>
       </c>
       <c r="B860" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="D860" t="s">
         <v>9</v>
@@ -15363,10 +15552,10 @@
     </row>
     <row r="861" spans="1:4">
       <c r="A861" t="s">
-        <v>1696</v>
+        <v>1700</v>
       </c>
       <c r="B861" t="s">
-        <v>1697</v>
+        <v>1701</v>
       </c>
       <c r="D861" t="s">
         <v>9</v>
@@ -15374,10 +15563,10 @@
     </row>
     <row r="862" spans="1:4">
       <c r="A862" t="s">
-        <v>1698</v>
+        <v>1702</v>
       </c>
       <c r="B862" t="s">
-        <v>1699</v>
+        <v>1703</v>
       </c>
       <c r="D862" t="s">
         <v>9</v>
@@ -15385,10 +15574,10 @@
     </row>
     <row r="863" spans="1:4">
       <c r="A863" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="B863" t="s">
-        <v>1701</v>
+        <v>1705</v>
       </c>
       <c r="D863" t="s">
         <v>9</v>
@@ -15396,10 +15585,10 @@
     </row>
     <row r="864" spans="1:4">
       <c r="A864" t="s">
-        <v>1702</v>
+        <v>1706</v>
       </c>
       <c r="B864" t="s">
-        <v>1703</v>
+        <v>1707</v>
       </c>
       <c r="D864" t="s">
         <v>9</v>
@@ -15407,10 +15596,10 @@
     </row>
     <row r="865" spans="1:4">
       <c r="A865" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="B865" t="s">
-        <v>1705</v>
+        <v>1709</v>
       </c>
       <c r="D865" t="s">
         <v>9</v>
@@ -15418,10 +15607,10 @@
     </row>
     <row r="866" spans="1:4">
       <c r="A866" t="s">
-        <v>1706</v>
+        <v>1710</v>
       </c>
       <c r="B866" t="s">
-        <v>1707</v>
+        <v>1711</v>
       </c>
       <c r="D866" t="s">
         <v>9</v>
@@ -15429,10 +15618,10 @@
     </row>
     <row r="867" spans="1:4">
       <c r="A867" t="s">
-        <v>1708</v>
+        <v>1712</v>
       </c>
       <c r="B867" t="s">
-        <v>1709</v>
+        <v>1713</v>
       </c>
       <c r="D867" t="s">
         <v>9</v>
@@ -15440,10 +15629,10 @@
     </row>
     <row r="868" spans="1:4">
       <c r="A868" t="s">
-        <v>1710</v>
+        <v>1714</v>
       </c>
       <c r="B868" t="s">
-        <v>1711</v>
+        <v>1715</v>
       </c>
       <c r="D868" t="s">
         <v>9</v>
@@ -15451,10 +15640,10 @@
     </row>
     <row r="869" spans="1:4">
       <c r="A869" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="B869" t="s">
-        <v>1713</v>
+        <v>1717</v>
       </c>
       <c r="D869" t="s">
         <v>9</v>
@@ -15462,7 +15651,7 @@
     </row>
     <row r="870" spans="1:4">
       <c r="A870" t="s">
-        <v>1714</v>
+        <v>1718</v>
       </c>
       <c r="B870" t="s">
         <v>1715</v>
@@ -15473,7 +15662,7 @@
     </row>
     <row r="871" spans="1:4">
       <c r="A871" t="s">
-        <v>1716</v>
+        <v>1719</v>
       </c>
       <c r="B871" t="s">
         <v>1717</v>
@@ -15484,10 +15673,10 @@
     </row>
     <row r="872" spans="1:4">
       <c r="A872" t="s">
-        <v>1718</v>
+        <v>1720</v>
       </c>
       <c r="B872" t="s">
-        <v>1719</v>
+        <v>1721</v>
       </c>
       <c r="D872" t="s">
         <v>9</v>
@@ -15495,10 +15684,10 @@
     </row>
     <row r="873" spans="1:4">
       <c r="A873" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
       <c r="B873" t="s">
-        <v>1721</v>
+        <v>1723</v>
       </c>
       <c r="D873" t="s">
         <v>9</v>
@@ -15506,10 +15695,10 @@
     </row>
     <row r="874" spans="1:4">
       <c r="A874" t="s">
-        <v>1722</v>
+        <v>1724</v>
       </c>
       <c r="B874" t="s">
-        <v>1723</v>
+        <v>1725</v>
       </c>
       <c r="D874" t="s">
         <v>9</v>
@@ -15517,10 +15706,10 @@
     </row>
     <row r="875" spans="1:4">
       <c r="A875" t="s">
-        <v>1724</v>
+        <v>1726</v>
       </c>
       <c r="B875" t="s">
-        <v>1725</v>
+        <v>1727</v>
       </c>
       <c r="D875" t="s">
         <v>9</v>
@@ -15528,7 +15717,7 @@
     </row>
     <row r="876" spans="1:4">
       <c r="A876" t="s">
-        <v>1726</v>
+        <v>1728</v>
       </c>
       <c r="B876" t="s">
         <v>1727</v>
@@ -15539,10 +15728,10 @@
     </row>
     <row r="877" spans="1:4">
       <c r="A877" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="B877" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="D877" t="s">
         <v>9</v>
@@ -15550,10 +15739,10 @@
     </row>
     <row r="878" spans="1:4">
       <c r="A878" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="B878" t="s">
-        <v>1729</v>
+        <v>1732</v>
       </c>
       <c r="D878" t="s">
         <v>9</v>
@@ -15561,10 +15750,10 @@
     </row>
     <row r="879" spans="1:4">
       <c r="A879" t="s">
-        <v>1731</v>
+        <v>1733</v>
       </c>
       <c r="B879" t="s">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="D879" t="s">
         <v>9</v>
@@ -15572,10 +15761,10 @@
     </row>
     <row r="880" spans="1:4">
       <c r="A880" t="s">
-        <v>1733</v>
+        <v>1735</v>
       </c>
       <c r="B880" t="s">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="D880" t="s">
         <v>9</v>
@@ -15583,10 +15772,10 @@
     </row>
     <row r="881" spans="1:4">
       <c r="A881" t="s">
-        <v>1735</v>
+        <v>1737</v>
       </c>
       <c r="B881" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
       <c r="D881" t="s">
         <v>9</v>
@@ -15594,10 +15783,10 @@
     </row>
     <row r="882" spans="1:4">
       <c r="A882" t="s">
-        <v>1737</v>
+        <v>1739</v>
       </c>
       <c r="B882" t="s">
-        <v>1738</v>
+        <v>1740</v>
       </c>
       <c r="D882" t="s">
         <v>9</v>
@@ -15605,7 +15794,7 @@
     </row>
     <row r="883" spans="1:4">
       <c r="A883" t="s">
-        <v>1739</v>
+        <v>1741</v>
       </c>
       <c r="B883" t="s">
         <v>1740</v>
@@ -15616,10 +15805,10 @@
     </row>
     <row r="884" spans="1:4">
       <c r="A884" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="B884" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="D884" t="s">
         <v>9</v>
@@ -15627,10 +15816,10 @@
     </row>
     <row r="885" spans="1:4">
       <c r="A885" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="B885" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="D885" t="s">
         <v>9</v>
@@ -15638,10 +15827,10 @@
     </row>
     <row r="886" spans="1:4">
       <c r="A886" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="B886" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="D886" t="s">
         <v>9</v>
@@ -15649,10 +15838,10 @@
     </row>
     <row r="887" spans="1:4">
       <c r="A887" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="B887" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="D887" t="s">
         <v>9</v>
@@ -15660,10 +15849,10 @@
     </row>
     <row r="888" spans="1:4">
       <c r="A888" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="B888" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="D888" t="s">
         <v>9</v>
@@ -15671,10 +15860,10 @@
     </row>
     <row r="889" spans="1:4">
       <c r="A889" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B889" t="s">
         <v>1751</v>
-      </c>
-      <c r="B889" t="s">
-        <v>1752</v>
       </c>
       <c r="D889" t="s">
         <v>9</v>
@@ -15740,7 +15929,7 @@
         <v>1763</v>
       </c>
       <c r="B895" t="s">
-        <v>1719</v>
+        <v>1764</v>
       </c>
       <c r="D895" t="s">
         <v>9</v>
@@ -15748,10 +15937,10 @@
     </row>
     <row r="896" spans="1:4">
       <c r="A896" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="B896" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="D896" t="s">
         <v>9</v>
@@ -15759,10 +15948,10 @@
     </row>
     <row r="897" spans="1:4">
       <c r="A897" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="B897" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="D897" t="s">
         <v>9</v>
@@ -15770,10 +15959,10 @@
     </row>
     <row r="898" spans="1:4">
       <c r="A898" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="B898" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="D898" t="s">
         <v>9</v>
@@ -15781,10 +15970,10 @@
     </row>
     <row r="899" spans="1:4">
       <c r="A899" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="B899" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="D899" t="s">
         <v>9</v>
@@ -15792,10 +15981,10 @@
     </row>
     <row r="900" spans="1:4">
       <c r="A900" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="B900" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="D900" t="s">
         <v>9</v>
@@ -15803,10 +15992,10 @@
     </row>
     <row r="901" spans="1:4">
       <c r="A901" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="B901" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="D901" t="s">
         <v>9</v>
@@ -15814,10 +16003,10 @@
     </row>
     <row r="902" spans="1:4">
       <c r="A902" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="B902" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="D902" t="s">
         <v>9</v>
@@ -15825,10 +16014,10 @@
     </row>
     <row r="903" spans="1:4">
       <c r="A903" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="B903" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="D903" t="s">
         <v>9</v>
@@ -15836,10 +16025,10 @@
     </row>
     <row r="904" spans="1:4">
       <c r="A904" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="B904" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="D904" t="s">
         <v>9</v>
@@ -15847,10 +16036,10 @@
     </row>
     <row r="905" spans="1:4">
       <c r="A905" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="B905" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="D905" t="s">
         <v>9</v>
@@ -15858,10 +16047,10 @@
     </row>
     <row r="906" spans="1:4">
       <c r="A906" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="B906" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="D906" t="s">
         <v>9</v>
@@ -15869,10 +16058,10 @@
     </row>
     <row r="907" spans="1:4">
       <c r="A907" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="B907" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="D907" t="s">
         <v>9</v>
@@ -15880,10 +16069,10 @@
     </row>
     <row r="908" spans="1:4">
       <c r="A908" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="B908" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="D908" t="s">
         <v>9</v>
@@ -15891,10 +16080,10 @@
     </row>
     <row r="909" spans="1:4">
       <c r="A909" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="B909" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="D909" t="s">
         <v>9</v>
@@ -15902,10 +16091,10 @@
     </row>
     <row r="910" spans="1:4">
       <c r="A910" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B910" t="s">
         <v>1792</v>
-      </c>
-      <c r="B910" t="s">
-        <v>1793</v>
       </c>
       <c r="D910" t="s">
         <v>9</v>
@@ -16004,7 +16193,7 @@
         <v>1810</v>
       </c>
       <c r="B919" t="s">
-        <v>1777</v>
+        <v>1811</v>
       </c>
       <c r="D919" t="s">
         <v>9</v>
@@ -16012,10 +16201,10 @@
     </row>
     <row r="920" spans="1:4">
       <c r="A920" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B920" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="D920" t="s">
         <v>9</v>
@@ -16023,10 +16212,10 @@
     </row>
     <row r="921" spans="1:4">
       <c r="A921" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="B921" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="D921" t="s">
         <v>9</v>
@@ -16034,10 +16223,10 @@
     </row>
     <row r="922" spans="1:4">
       <c r="A922" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="B922" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="D922" t="s">
         <v>9</v>
@@ -16045,10 +16234,10 @@
     </row>
     <row r="923" spans="1:4">
       <c r="A923" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="B923" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="D923" t="s">
         <v>9</v>
@@ -16056,10 +16245,10 @@
     </row>
     <row r="924" spans="1:4">
       <c r="A924" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="B924" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="D924" t="s">
         <v>9</v>
@@ -16067,10 +16256,10 @@
     </row>
     <row r="925" spans="1:4">
       <c r="A925" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="B925" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="D925" t="s">
         <v>9</v>
@@ -16078,10 +16267,10 @@
     </row>
     <row r="926" spans="1:4">
       <c r="A926" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="B926" t="s">
-        <v>1822</v>
+        <v>1825</v>
       </c>
       <c r="D926" t="s">
         <v>9</v>
@@ -16089,10 +16278,10 @@
     </row>
     <row r="927" spans="1:4">
       <c r="A927" t="s">
-        <v>1824</v>
+        <v>1826</v>
       </c>
       <c r="B927" t="s">
-        <v>1825</v>
+        <v>1782</v>
       </c>
       <c r="D927" t="s">
         <v>9</v>
@@ -16100,10 +16289,10 @@
     </row>
     <row r="928" spans="1:4">
       <c r="A928" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="B928" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="D928" t="s">
         <v>9</v>
@@ -16111,10 +16300,10 @@
     </row>
     <row r="929" spans="1:4">
       <c r="A929" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="B929" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="D929" t="s">
         <v>9</v>
@@ -16122,10 +16311,10 @@
     </row>
     <row r="930" spans="1:4">
       <c r="A930" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="B930" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="D930" t="s">
         <v>9</v>
@@ -16133,10 +16322,10 @@
     </row>
     <row r="931" spans="1:4">
       <c r="A931" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="B931" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="D931" t="s">
         <v>9</v>
@@ -16144,10 +16333,10 @@
     </row>
     <row r="932" spans="1:4">
       <c r="A932" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="B932" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="D932" t="s">
         <v>9</v>
@@ -16155,10 +16344,10 @@
     </row>
     <row r="933" spans="1:4">
       <c r="A933" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="B933" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="D933" t="s">
         <v>9</v>
@@ -16166,10 +16355,10 @@
     </row>
     <row r="934" spans="1:4">
       <c r="A934" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="B934" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="D934" t="s">
         <v>9</v>
@@ -16177,10 +16366,10 @@
     </row>
     <row r="935" spans="1:4">
       <c r="A935" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="B935" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="D935" t="s">
         <v>9</v>
@@ -16188,10 +16377,10 @@
     </row>
     <row r="936" spans="1:4">
       <c r="A936" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="B936" t="s">
-        <v>1831</v>
+        <v>1844</v>
       </c>
       <c r="D936" t="s">
         <v>9</v>
@@ -16199,10 +16388,10 @@
     </row>
     <row r="937" spans="1:4">
       <c r="A937" t="s">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="B937" t="s">
-        <v>1844</v>
+        <v>1846</v>
       </c>
       <c r="D937" t="s">
         <v>9</v>
@@ -16210,12 +16399,364 @@
     </row>
     <row r="938" spans="1:4">
       <c r="A938" t="s">
-        <v>1845</v>
+        <v>1847</v>
       </c>
       <c r="B938" t="s">
-        <v>1846</v>
+        <v>1848</v>
       </c>
       <c r="D938" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="939" spans="1:4">
+      <c r="A939" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B939" t="s">
+        <v>1850</v>
+      </c>
+      <c r="D939" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="940" spans="1:4">
+      <c r="A940" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B940" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D940" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="941" spans="1:4">
+      <c r="A941" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B941" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D941" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="942" spans="1:4">
+      <c r="A942" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B942" t="s">
+        <v>1856</v>
+      </c>
+      <c r="D942" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="943" spans="1:4">
+      <c r="A943" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B943" t="s">
+        <v>1858</v>
+      </c>
+      <c r="D943" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="944" spans="1:4">
+      <c r="A944" t="s">
+        <v>1859</v>
+      </c>
+      <c r="B944" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D944" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="945" spans="1:4">
+      <c r="A945" t="s">
+        <v>1861</v>
+      </c>
+      <c r="B945" t="s">
+        <v>1862</v>
+      </c>
+      <c r="D945" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="946" spans="1:4">
+      <c r="A946" t="s">
+        <v>1863</v>
+      </c>
+      <c r="B946" t="s">
+        <v>1864</v>
+      </c>
+      <c r="D946" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="947" spans="1:4">
+      <c r="A947" t="s">
+        <v>1865</v>
+      </c>
+      <c r="B947" t="s">
+        <v>1866</v>
+      </c>
+      <c r="D947" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="948" spans="1:4">
+      <c r="A948" t="s">
+        <v>1867</v>
+      </c>
+      <c r="B948" t="s">
+        <v>1868</v>
+      </c>
+      <c r="D948" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="949" spans="1:4">
+      <c r="A949" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B949" t="s">
+        <v>1870</v>
+      </c>
+      <c r="D949" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="950" spans="1:4">
+      <c r="A950" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B950" t="s">
+        <v>1872</v>
+      </c>
+      <c r="D950" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="951" spans="1:4">
+      <c r="A951" t="s">
+        <v>1873</v>
+      </c>
+      <c r="B951" t="s">
+        <v>1840</v>
+      </c>
+      <c r="D951" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="952" spans="1:4">
+      <c r="A952" t="s">
+        <v>1874</v>
+      </c>
+      <c r="B952" t="s">
+        <v>1875</v>
+      </c>
+      <c r="D952" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="953" spans="1:4">
+      <c r="A953" t="s">
+        <v>1876</v>
+      </c>
+      <c r="B953" t="s">
+        <v>1877</v>
+      </c>
+      <c r="D953" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="954" spans="1:4">
+      <c r="A954" t="s">
+        <v>1878</v>
+      </c>
+      <c r="B954" t="s">
+        <v>1879</v>
+      </c>
+      <c r="D954" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="955" spans="1:4">
+      <c r="A955" t="s">
+        <v>1880</v>
+      </c>
+      <c r="B955" t="s">
+        <v>1881</v>
+      </c>
+      <c r="D955" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="956" spans="1:4">
+      <c r="A956" t="s">
+        <v>1882</v>
+      </c>
+      <c r="B956" t="s">
+        <v>1883</v>
+      </c>
+      <c r="D956" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="957" spans="1:4">
+      <c r="A957" t="s">
+        <v>1884</v>
+      </c>
+      <c r="B957" t="s">
+        <v>1885</v>
+      </c>
+      <c r="D957" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="958" spans="1:4">
+      <c r="A958" t="s">
+        <v>1886</v>
+      </c>
+      <c r="B958" t="s">
+        <v>1885</v>
+      </c>
+      <c r="D958" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="959" spans="1:4">
+      <c r="A959" t="s">
+        <v>1887</v>
+      </c>
+      <c r="B959" t="s">
+        <v>1888</v>
+      </c>
+      <c r="D959" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="960" spans="1:4">
+      <c r="A960" t="s">
+        <v>1889</v>
+      </c>
+      <c r="B960" t="s">
+        <v>1890</v>
+      </c>
+      <c r="D960" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="961" spans="1:4">
+      <c r="A961" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B961" t="s">
+        <v>1892</v>
+      </c>
+      <c r="D961" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="962" spans="1:4">
+      <c r="A962" t="s">
+        <v>1893</v>
+      </c>
+      <c r="B962" t="s">
+        <v>1894</v>
+      </c>
+      <c r="D962" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="963" spans="1:4">
+      <c r="A963" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B963" t="s">
+        <v>1896</v>
+      </c>
+      <c r="D963" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="964" spans="1:4">
+      <c r="A964" t="s">
+        <v>1897</v>
+      </c>
+      <c r="B964" t="s">
+        <v>1898</v>
+      </c>
+      <c r="D964" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="965" spans="1:4">
+      <c r="A965" t="s">
+        <v>1899</v>
+      </c>
+      <c r="B965" t="s">
+        <v>1900</v>
+      </c>
+      <c r="D965" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="966" spans="1:4">
+      <c r="A966" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B966" t="s">
+        <v>1902</v>
+      </c>
+      <c r="D966" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="967" spans="1:4">
+      <c r="A967" t="s">
+        <v>1903</v>
+      </c>
+      <c r="B967" t="s">
+        <v>1904</v>
+      </c>
+      <c r="D967" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="968" spans="1:4">
+      <c r="A968" t="s">
+        <v>1905</v>
+      </c>
+      <c r="B968" t="s">
+        <v>1894</v>
+      </c>
+      <c r="D968" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="969" spans="1:4">
+      <c r="A969" t="s">
+        <v>1906</v>
+      </c>
+      <c r="B969" t="s">
+        <v>1907</v>
+      </c>
+      <c r="D969" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="970" spans="1:4">
+      <c r="A970" t="s">
+        <v>1908</v>
+      </c>
+      <c r="B970" t="s">
+        <v>1909</v>
+      </c>
+      <c r="D970" t="s">
         <v>9</v>
       </c>
     </row>

--- a/api/1/clv1/codelist/HumanitarianPlan.xlsx
+++ b/api/1/clv1/codelist/HumanitarianPlan.xlsx
@@ -202,7 +202,7 @@
     <t>HSYR26</t>
   </si>
   <si>
-    <t>Syrian Arab Republic Humanitarian Response Priorities 2026</t>
+    <t>Syrian Arab Republic Humanitarian Needs and Response Plan 2026</t>
   </si>
   <si>
     <t>RJORLBNTUR26</t>

--- a/api/1/clv1/codelist/HumanitarianPlan.xlsx
+++ b/api/1/clv1/codelist/HumanitarianPlan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2935" uniqueCount="1923">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2938" uniqueCount="1925">
   <si>
     <t>code</t>
   </si>
@@ -122,6 +122,12 @@
   </si>
   <si>
     <t>Myanmar Humanitarian Needs and Response Plan 2026</t>
+  </si>
+  <si>
+    <t>FNPL26</t>
+  </si>
+  <si>
+    <t>Nepal Rasuwa Flood Flash Appeal</t>
   </si>
   <si>
     <t>HNER26</t>
@@ -6114,7 +6120,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G977"/>
+  <dimension ref="A1:G978"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -6343,7 +6349,7 @@
         <v>44</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D20" t="s">
         <v>9</v>
@@ -6351,10 +6357,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" t="s">
         <v>45</v>
-      </c>
-      <c r="B21" t="s">
-        <v>46</v>
       </c>
       <c r="D21" t="s">
         <v>9</v>
@@ -7014,7 +7020,7 @@
         <v>165</v>
       </c>
       <c r="B81" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D81" t="s">
         <v>9</v>
@@ -7022,10 +7028,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
+        <v>167</v>
+      </c>
+      <c r="B82" t="s">
         <v>166</v>
-      </c>
-      <c r="B82" t="s">
-        <v>167</v>
       </c>
       <c r="D82" t="s">
         <v>9</v>
@@ -7938,7 +7944,7 @@
         <v>332</v>
       </c>
       <c r="B165" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D165" t="s">
         <v>9</v>
@@ -7946,10 +7952,10 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" t="s">
+        <v>334</v>
+      </c>
+      <c r="B166" t="s">
         <v>333</v>
-      </c>
-      <c r="B166" t="s">
-        <v>334</v>
       </c>
       <c r="D166" t="s">
         <v>9</v>
@@ -8477,7 +8483,7 @@
         <v>429</v>
       </c>
       <c r="B214" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D214" t="s">
         <v>9</v>
@@ -8485,10 +8491,10 @@
     </row>
     <row r="215" spans="1:4">
       <c r="A215" t="s">
+        <v>431</v>
+      </c>
+      <c r="B215" t="s">
         <v>430</v>
-      </c>
-      <c r="B215" t="s">
-        <v>431</v>
       </c>
       <c r="D215" t="s">
         <v>9</v>
@@ -9093,7 +9099,7 @@
         <v>540</v>
       </c>
       <c r="B270" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="D270" t="s">
         <v>9</v>
@@ -9101,10 +9107,10 @@
     </row>
     <row r="271" spans="1:4">
       <c r="A271" t="s">
+        <v>542</v>
+      </c>
+      <c r="B271" t="s">
         <v>541</v>
-      </c>
-      <c r="B271" t="s">
-        <v>542</v>
       </c>
       <c r="D271" t="s">
         <v>9</v>
@@ -11051,7 +11057,7 @@
         <v>895</v>
       </c>
       <c r="B448" t="s">
-        <v>866</v>
+        <v>896</v>
       </c>
       <c r="D448" t="s">
         <v>9</v>
@@ -11059,10 +11065,10 @@
     </row>
     <row r="449" spans="1:4">
       <c r="A449" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B449" t="s">
-        <v>840</v>
+        <v>868</v>
       </c>
       <c r="D449" t="s">
         <v>9</v>
@@ -11070,10 +11076,10 @@
     </row>
     <row r="450" spans="1:4">
       <c r="A450" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B450" t="s">
-        <v>898</v>
+        <v>842</v>
       </c>
       <c r="D450" t="s">
         <v>9</v>
@@ -11139,7 +11145,7 @@
         <v>909</v>
       </c>
       <c r="B456" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="D456" t="s">
         <v>9</v>
@@ -11147,10 +11153,10 @@
     </row>
     <row r="457" spans="1:4">
       <c r="A457" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B457" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="D457" t="s">
         <v>9</v>
@@ -11480,7 +11486,7 @@
         <v>970</v>
       </c>
       <c r="B487" t="s">
-        <v>915</v>
+        <v>971</v>
       </c>
       <c r="D487" t="s">
         <v>9</v>
@@ -11488,10 +11494,10 @@
     </row>
     <row r="488" spans="1:4">
       <c r="A488" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B488" t="s">
-        <v>972</v>
+        <v>917</v>
       </c>
       <c r="D488" t="s">
         <v>9</v>
@@ -11513,7 +11519,7 @@
         <v>975</v>
       </c>
       <c r="B490" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="D490" t="s">
         <v>9</v>
@@ -11521,10 +11527,10 @@
     </row>
     <row r="491" spans="1:4">
       <c r="A491" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B491" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="D491" t="s">
         <v>9</v>
@@ -11876,7 +11882,7 @@
         <v>1040</v>
       </c>
       <c r="B523" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="D523" t="s">
         <v>9</v>
@@ -11884,10 +11890,10 @@
     </row>
     <row r="524" spans="1:4">
       <c r="A524" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B524" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="D524" t="s">
         <v>9</v>
@@ -12283,7 +12289,7 @@
         <v>1113</v>
       </c>
       <c r="B560" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="D560" t="s">
         <v>9</v>
@@ -12291,10 +12297,10 @@
     </row>
     <row r="561" spans="1:4">
       <c r="A561" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B561" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="D561" t="s">
         <v>9</v>
@@ -13306,7 +13312,7 @@
         <v>1298</v>
       </c>
       <c r="B653" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="D653" t="s">
         <v>9</v>
@@ -13314,10 +13320,10 @@
     </row>
     <row r="654" spans="1:4">
       <c r="A654" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B654" t="s">
         <v>1299</v>
-      </c>
-      <c r="B654" t="s">
-        <v>1300</v>
       </c>
       <c r="D654" t="s">
         <v>9</v>
@@ -13383,7 +13389,7 @@
         <v>1311</v>
       </c>
       <c r="B660" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="D660" t="s">
         <v>9</v>
@@ -13391,10 +13397,10 @@
     </row>
     <row r="661" spans="1:4">
       <c r="A661" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B661" t="s">
         <v>1312</v>
-      </c>
-      <c r="B661" t="s">
-        <v>1313</v>
       </c>
       <c r="D661" t="s">
         <v>9</v>
@@ -13438,7 +13444,7 @@
         <v>1320</v>
       </c>
       <c r="B665" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="D665" t="s">
         <v>9</v>
@@ -13446,10 +13452,10 @@
     </row>
     <row r="666" spans="1:4">
       <c r="A666" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B666" t="s">
         <v>1321</v>
-      </c>
-      <c r="B666" t="s">
-        <v>1322</v>
       </c>
       <c r="D666" t="s">
         <v>9</v>
@@ -13482,7 +13488,7 @@
         <v>1327</v>
       </c>
       <c r="B669" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="D669" t="s">
         <v>9</v>
@@ -13490,10 +13496,10 @@
     </row>
     <row r="670" spans="1:4">
       <c r="A670" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B670" t="s">
         <v>1328</v>
-      </c>
-      <c r="B670" t="s">
-        <v>1329</v>
       </c>
       <c r="D670" t="s">
         <v>9</v>
@@ -13614,7 +13620,7 @@
         <v>1350</v>
       </c>
       <c r="B681" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="D681" t="s">
         <v>9</v>
@@ -13622,10 +13628,10 @@
     </row>
     <row r="682" spans="1:4">
       <c r="A682" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B682" t="s">
         <v>1351</v>
-      </c>
-      <c r="B682" t="s">
-        <v>1352</v>
       </c>
       <c r="D682" t="s">
         <v>9</v>
@@ -13790,7 +13796,7 @@
         <v>1381</v>
       </c>
       <c r="B697" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="D697" t="s">
         <v>9</v>
@@ -13798,10 +13804,10 @@
     </row>
     <row r="698" spans="1:4">
       <c r="A698" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B698" t="s">
         <v>1382</v>
-      </c>
-      <c r="B698" t="s">
-        <v>1383</v>
       </c>
       <c r="D698" t="s">
         <v>9</v>
@@ -14021,7 +14027,7 @@
         <v>1422</v>
       </c>
       <c r="B718" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="D718" t="s">
         <v>9</v>
@@ -14029,10 +14035,10 @@
     </row>
     <row r="719" spans="1:4">
       <c r="A719" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B719" t="s">
         <v>1423</v>
-      </c>
-      <c r="B719" t="s">
-        <v>1424</v>
       </c>
       <c r="D719" t="s">
         <v>9</v>
@@ -14175,7 +14181,7 @@
         <v>1449</v>
       </c>
       <c r="B732" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="D732" t="s">
         <v>9</v>
@@ -14183,10 +14189,10 @@
     </row>
     <row r="733" spans="1:4">
       <c r="A733" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B733" t="s">
         <v>1450</v>
-      </c>
-      <c r="B733" t="s">
-        <v>1451</v>
       </c>
       <c r="D733" t="s">
         <v>9</v>
@@ -14505,7 +14511,7 @@
         <v>1508</v>
       </c>
       <c r="B762" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="D762" t="s">
         <v>9</v>
@@ -14513,10 +14519,10 @@
     </row>
     <row r="763" spans="1:4">
       <c r="A763" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B763" t="s">
         <v>1509</v>
-      </c>
-      <c r="B763" t="s">
-        <v>1510</v>
       </c>
       <c r="D763" t="s">
         <v>9</v>
@@ -14593,7 +14599,7 @@
         <v>1523</v>
       </c>
       <c r="B770" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="D770" t="s">
         <v>9</v>
@@ -14601,10 +14607,10 @@
     </row>
     <row r="771" spans="1:4">
       <c r="A771" t="s">
+        <v>1525</v>
+      </c>
+      <c r="B771" t="s">
         <v>1524</v>
-      </c>
-      <c r="B771" t="s">
-        <v>1525</v>
       </c>
       <c r="D771" t="s">
         <v>9</v>
@@ -14967,7 +14973,7 @@
         <v>1590</v>
       </c>
       <c r="B804" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="D804" t="s">
         <v>9</v>
@@ -14975,10 +14981,10 @@
     </row>
     <row r="805" spans="1:4">
       <c r="A805" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B805" t="s">
         <v>1591</v>
-      </c>
-      <c r="B805" t="s">
-        <v>1592</v>
       </c>
       <c r="D805" t="s">
         <v>9</v>
@@ -15176,7 +15182,7 @@
         <v>1627</v>
       </c>
       <c r="B823" t="s">
-        <v>1618</v>
+        <v>1628</v>
       </c>
       <c r="D823" t="s">
         <v>9</v>
@@ -15184,10 +15190,10 @@
     </row>
     <row r="824" spans="1:4">
       <c r="A824" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="B824" t="s">
-        <v>1629</v>
+        <v>1620</v>
       </c>
       <c r="D824" t="s">
         <v>9</v>
@@ -15264,7 +15270,7 @@
         <v>1642</v>
       </c>
       <c r="B831" t="s">
-        <v>1639</v>
+        <v>1643</v>
       </c>
       <c r="D831" t="s">
         <v>9</v>
@@ -15272,10 +15278,10 @@
     </row>
     <row r="832" spans="1:4">
       <c r="A832" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B832" t="s">
-        <v>1644</v>
+        <v>1641</v>
       </c>
       <c r="D832" t="s">
         <v>9</v>
@@ -15297,7 +15303,7 @@
         <v>1647</v>
       </c>
       <c r="B834" t="s">
-        <v>1637</v>
+        <v>1648</v>
       </c>
       <c r="D834" t="s">
         <v>9</v>
@@ -15305,10 +15311,10 @@
     </row>
     <row r="835" spans="1:4">
       <c r="A835" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="B835" t="s">
-        <v>1649</v>
+        <v>1639</v>
       </c>
       <c r="D835" t="s">
         <v>9</v>
@@ -15649,7 +15655,7 @@
         <v>1710</v>
       </c>
       <c r="B866" t="s">
-        <v>1667</v>
+        <v>1711</v>
       </c>
       <c r="D866" t="s">
         <v>9</v>
@@ -15657,10 +15663,10 @@
     </row>
     <row r="867" spans="1:4">
       <c r="A867" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="B867" t="s">
-        <v>1712</v>
+        <v>1669</v>
       </c>
       <c r="D867" t="s">
         <v>9</v>
@@ -15770,7 +15776,7 @@
         <v>1731</v>
       </c>
       <c r="B877" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="D877" t="s">
         <v>9</v>
@@ -15778,7 +15784,7 @@
     </row>
     <row r="878" spans="1:4">
       <c r="A878" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="B878" t="s">
         <v>1730</v>
@@ -15789,10 +15795,10 @@
     </row>
     <row r="879" spans="1:4">
       <c r="A879" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="B879" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
       <c r="D879" t="s">
         <v>9</v>
@@ -15836,7 +15842,7 @@
         <v>1741</v>
       </c>
       <c r="B883" t="s">
-        <v>1740</v>
+        <v>1742</v>
       </c>
       <c r="D883" t="s">
         <v>9</v>
@@ -15844,10 +15850,10 @@
     </row>
     <row r="884" spans="1:4">
       <c r="A884" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B884" t="s">
         <v>1742</v>
-      </c>
-      <c r="B884" t="s">
-        <v>1743</v>
       </c>
       <c r="D884" t="s">
         <v>9</v>
@@ -15913,7 +15919,7 @@
         <v>1754</v>
       </c>
       <c r="B890" t="s">
-        <v>1753</v>
+        <v>1755</v>
       </c>
       <c r="D890" t="s">
         <v>9</v>
@@ -15921,10 +15927,10 @@
     </row>
     <row r="891" spans="1:4">
       <c r="A891" t="s">
+        <v>1756</v>
+      </c>
+      <c r="B891" t="s">
         <v>1755</v>
-      </c>
-      <c r="B891" t="s">
-        <v>1756</v>
       </c>
       <c r="D891" t="s">
         <v>9</v>
@@ -15979,7 +15985,7 @@
         <v>1765</v>
       </c>
       <c r="B896" t="s">
-        <v>1764</v>
+        <v>1766</v>
       </c>
       <c r="D896" t="s">
         <v>9</v>
@@ -15987,10 +15993,10 @@
     </row>
     <row r="897" spans="1:4">
       <c r="A897" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B897" t="s">
         <v>1766</v>
-      </c>
-      <c r="B897" t="s">
-        <v>1767</v>
       </c>
       <c r="D897" t="s">
         <v>9</v>
@@ -16210,7 +16216,7 @@
         <v>1806</v>
       </c>
       <c r="B917" t="s">
-        <v>1805</v>
+        <v>1807</v>
       </c>
       <c r="D917" t="s">
         <v>9</v>
@@ -16218,10 +16224,10 @@
     </row>
     <row r="918" spans="1:4">
       <c r="A918" t="s">
+        <v>1808</v>
+      </c>
+      <c r="B918" t="s">
         <v>1807</v>
-      </c>
-      <c r="B918" t="s">
-        <v>1808</v>
       </c>
       <c r="D918" t="s">
         <v>9</v>
@@ -16397,7 +16403,7 @@
         <v>1839</v>
       </c>
       <c r="B934" t="s">
-        <v>1795</v>
+        <v>1840</v>
       </c>
       <c r="D934" t="s">
         <v>9</v>
@@ -16405,10 +16411,10 @@
     </row>
     <row r="935" spans="1:4">
       <c r="A935" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="B935" t="s">
-        <v>1841</v>
+        <v>1797</v>
       </c>
       <c r="D935" t="s">
         <v>9</v>
@@ -16661,7 +16667,7 @@
         <v>1886</v>
       </c>
       <c r="B958" t="s">
-        <v>1853</v>
+        <v>1887</v>
       </c>
       <c r="D958" t="s">
         <v>9</v>
@@ -16669,10 +16675,10 @@
     </row>
     <row r="959" spans="1:4">
       <c r="A959" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="B959" t="s">
-        <v>1888</v>
+        <v>1855</v>
       </c>
       <c r="D959" t="s">
         <v>9</v>
@@ -16738,7 +16744,7 @@
         <v>1899</v>
       </c>
       <c r="B965" t="s">
-        <v>1898</v>
+        <v>1900</v>
       </c>
       <c r="D965" t="s">
         <v>9</v>
@@ -16746,10 +16752,10 @@
     </row>
     <row r="966" spans="1:4">
       <c r="A966" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B966" t="s">
         <v>1900</v>
-      </c>
-      <c r="B966" t="s">
-        <v>1901</v>
       </c>
       <c r="D966" t="s">
         <v>9</v>
@@ -16848,7 +16854,7 @@
         <v>1918</v>
       </c>
       <c r="B975" t="s">
-        <v>1907</v>
+        <v>1919</v>
       </c>
       <c r="D975" t="s">
         <v>9</v>
@@ -16856,10 +16862,10 @@
     </row>
     <row r="976" spans="1:4">
       <c r="A976" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="B976" t="s">
-        <v>1920</v>
+        <v>1909</v>
       </c>
       <c r="D976" t="s">
         <v>9</v>
@@ -16873,6 +16879,17 @@
         <v>1922</v>
       </c>
       <c r="D977" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="978" spans="1:4">
+      <c r="A978" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B978" t="s">
+        <v>1924</v>
+      </c>
+      <c r="D978" t="s">
         <v>9</v>
       </c>
     </row>
